--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="183">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,12 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
+    <t>Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Czech 1 Liga</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
@@ -358,10 +364,16 @@
     <t>Gwangju FC</t>
   </si>
   <si>
+    <t>Modern Sport FC</t>
+  </si>
+  <si>
+    <t>Kairat Almaty</t>
+  </si>
+  <si>
     <t>Pyramids</t>
   </si>
   <si>
-    <t>Modern Sport FC</t>
+    <t>FK Jablonec</t>
   </si>
   <si>
     <t>HJK Helsinki</t>
@@ -373,24 +385,27 @@
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>Parnu JK Vaprus</t>
+  </si>
+  <si>
     <t>Tammeka Tartu</t>
   </si>
   <si>
     <t>FCI Tallinn</t>
   </si>
   <si>
-    <t>Parnu JK Vaprus</t>
+    <t>Stuttgart</t>
   </si>
   <si>
     <t>Barcelona</t>
   </si>
   <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
     <t>FC Twente</t>
   </si>
   <si>
+    <t>Hradec Kralove</t>
+  </si>
+  <si>
     <t>ENPPI</t>
   </si>
   <si>
@@ -421,21 +436,21 @@
     <t>Norwich</t>
   </si>
   <si>
+    <t>Charlton</t>
+  </si>
+  <si>
+    <t>Paris St-G</t>
+  </si>
+  <si>
+    <t>Napoli</t>
+  </si>
+  <si>
     <t>Liverpool</t>
   </si>
   <si>
-    <t>Napoli</t>
-  </si>
-  <si>
     <t>Sporting Lisbon</t>
   </si>
   <si>
-    <t>Charlton</t>
-  </si>
-  <si>
-    <t>Paris St-G</t>
-  </si>
-  <si>
     <t>Moreirense</t>
   </si>
   <si>
@@ -457,10 +472,16 @@
     <t>Jeju Utd</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
+    <t>Banik Ostrava</t>
   </si>
   <si>
     <t>FC Inter Turku</t>
@@ -472,24 +493,27 @@
     <t>Al-Shabab (KSA)</t>
   </si>
   <si>
+    <t>Harju JK Laagri</t>
+  </si>
+  <si>
     <t>Paide Linnameeskond</t>
   </si>
   <si>
     <t>Kuressaare</t>
   </si>
   <si>
-    <t>Harju JK Laagri</t>
+    <t>Viking</t>
   </si>
   <si>
     <t>Feyenoord</t>
   </si>
   <si>
-    <t>Viking</t>
-  </si>
-  <si>
     <t>SC Telstar</t>
   </si>
   <si>
+    <t>Plzen</t>
+  </si>
+  <si>
     <t>ZED FC</t>
   </si>
   <si>
@@ -520,25 +544,25 @@
     <t>Birmingham</t>
   </si>
   <si>
+    <t>QPR</t>
+  </si>
+  <si>
+    <t>Slovan Bratislava</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
     <t>Atletico Madrid</t>
   </si>
   <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
     <t>Galatasaray</t>
   </si>
   <si>
-    <t>QPR</t>
-  </si>
-  <si>
-    <t>Slovan Bratislava</t>
-  </si>
-  <si>
     <t>Benfica</t>
   </si>
   <si>
-    <t>2026-09-07 10:32:34</t>
+    <t>2026-09-07 12:46:00</t>
   </si>
 </sst>
 </file>
@@ -870,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB34"/>
+  <dimension ref="A1:CB37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1120,22 +1144,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
         <v>4.4</v>
@@ -1144,7 +1168,7 @@
         <v>4.8</v>
       </c>
       <c r="J2">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K2">
         <v>3.15</v>
@@ -1174,7 +1198,7 @@
         <v>6</v>
       </c>
       <c r="T2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U2">
         <v>1.69</v>
@@ -1183,16 +1207,16 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y2">
         <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA2">
         <v>150</v>
@@ -1231,13 +1255,13 @@
         <v>85</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP2">
         <v>7</v>
@@ -1285,13 +1309,13 @@
         <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
         <v>7.4</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH2">
         <v>2.62</v>
@@ -1354,7 +1378,7 @@
         <v>11</v>
       </c>
       <c r="CB2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1362,28 +1386,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>4.8</v>
@@ -1422,10 +1446,10 @@
         <v>1.74</v>
       </c>
       <c r="V3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W3">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="X3">
         <v>26</v>
@@ -1539,19 +1563,19 @@
         <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3">
         <v>13</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BN3">
         <v>3.85</v>
@@ -1563,40 +1587,40 @@
         <v>7.8</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
         <v>15</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BZ3">
         <v>13</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1604,34 +1628,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F4">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
         <v>4.2</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
         <v>1.33</v>
@@ -1640,16 +1664,16 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4">
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
         <v>1.42</v>
@@ -1658,16 +1682,16 @@
         <v>3.05</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X4">
         <v>18</v>
@@ -1676,10 +1700,10 @@
         <v>22</v>
       </c>
       <c r="Z4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA4">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB4">
         <v>9.199999999999999</v>
@@ -1691,7 +1715,7 @@
         <v>24</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF4">
         <v>10.5</v>
@@ -1700,10 +1724,10 @@
         <v>10</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
         <v>16.5</v>
@@ -1715,13 +1739,13 @@
         <v>36</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4">
         <v>9</v>
       </c>
       <c r="AO4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP4">
         <v>15</v>
@@ -1730,22 +1754,22 @@
         <v>18</v>
       </c>
       <c r="AR4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
         <v>8</v>
       </c>
       <c r="AU4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX4">
         <v>9</v>
@@ -1754,10 +1778,10 @@
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB4">
         <v>13.5</v>
@@ -1766,16 +1790,16 @@
         <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
         <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1838,7 +1862,7 @@
         <v>2.52</v>
       </c>
       <c r="CB4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1846,16 +1870,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F5">
         <v>2.7</v>
@@ -1867,7 +1891,7 @@
         <v>2.86</v>
       </c>
       <c r="I5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J5">
         <v>3.2</v>
@@ -1882,7 +1906,7 @@
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
         <v>1.42</v>
@@ -1969,7 +1993,7 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
         <v>17</v>
@@ -2080,7 +2104,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2088,16 +2112,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>2.4</v>
@@ -2106,16 +2130,16 @@
         <v>2.68</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I6">
         <v>3.55</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2142,16 +2166,16 @@
         <v>4</v>
       </c>
       <c r="T6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V6">
         <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X6">
         <v>13</v>
@@ -2271,58 +2295,58 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="CB6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2330,28 +2354,28 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F7">
         <v>4.2</v>
       </c>
       <c r="G7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H7">
         <v>1.95</v>
       </c>
       <c r="I7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="J7">
         <v>3.45</v>
@@ -2360,7 +2384,7 @@
         <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2384,13 +2408,13 @@
         <v>3.8</v>
       </c>
       <c r="T7">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W7">
         <v>1.27</v>
@@ -2480,7 +2504,7 @@
         <v>15.5</v>
       </c>
       <c r="AZ7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA7">
         <v>8.4</v>
@@ -2504,16 +2528,16 @@
         <v>14</v>
       </c>
       <c r="BH7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI7">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2522,13 +2546,13 @@
         <v>14</v>
       </c>
       <c r="BN7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO7">
         <v>6.8</v>
       </c>
       <c r="BP7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ7">
         <v>11</v>
@@ -2555,16 +2579,16 @@
         <v>32</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA7">
         <v>10</v>
       </c>
       <c r="CB7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2572,179 +2596,179 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F8">
-        <v>1.47</v>
+        <v>3.15</v>
       </c>
       <c r="G8">
-        <v>1.53</v>
+        <v>3.7</v>
       </c>
       <c r="H8">
+        <v>2.66</v>
+      </c>
+      <c r="I8">
+        <v>2.98</v>
+      </c>
+      <c r="J8">
+        <v>2.8</v>
+      </c>
+      <c r="K8">
+        <v>2.98</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.13</v>
+      </c>
+      <c r="N8">
+        <v>2.18</v>
+      </c>
+      <c r="O8">
+        <v>1.67</v>
+      </c>
+      <c r="P8">
+        <v>1.42</v>
+      </c>
+      <c r="Q8">
+        <v>2.76</v>
+      </c>
+      <c r="R8">
+        <v>1.13</v>
+      </c>
+      <c r="S8">
+        <v>5.5</v>
+      </c>
+      <c r="T8">
+        <v>2.3</v>
+      </c>
+      <c r="U8">
+        <v>1.69</v>
+      </c>
+      <c r="V8">
+        <v>1.51</v>
+      </c>
+      <c r="W8">
+        <v>1.37</v>
+      </c>
+      <c r="X8">
+        <v>7.2</v>
+      </c>
+      <c r="Y8">
+        <v>7.4</v>
+      </c>
+      <c r="Z8">
+        <v>16.5</v>
+      </c>
+      <c r="AA8">
+        <v>60</v>
+      </c>
+      <c r="AB8">
+        <v>8.4</v>
+      </c>
+      <c r="AC8">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>15</v>
+      </c>
+      <c r="AE8">
+        <v>55</v>
+      </c>
+      <c r="AF8">
+        <v>21</v>
+      </c>
+      <c r="AG8">
+        <v>17</v>
+      </c>
+      <c r="AH8">
+        <v>28</v>
+      </c>
+      <c r="AI8">
+        <v>100</v>
+      </c>
+      <c r="AJ8">
+        <v>85</v>
+      </c>
+      <c r="AK8">
+        <v>70</v>
+      </c>
+      <c r="AL8">
+        <v>110</v>
+      </c>
+      <c r="AM8">
+        <v>290</v>
+      </c>
+      <c r="AN8">
+        <v>100</v>
+      </c>
+      <c r="AO8">
+        <v>75</v>
+      </c>
+      <c r="AP8">
+        <v>6.4</v>
+      </c>
+      <c r="AQ8">
+        <v>6.6</v>
+      </c>
+      <c r="AR8">
+        <v>14</v>
+      </c>
+      <c r="AS8">
+        <v>9.4</v>
+      </c>
+      <c r="AT8">
+        <v>7.4</v>
+      </c>
+      <c r="AU8">
+        <v>6.2</v>
+      </c>
+      <c r="AV8">
+        <v>12.5</v>
+      </c>
+      <c r="AW8">
+        <v>9.4</v>
+      </c>
+      <c r="AX8">
+        <v>17.5</v>
+      </c>
+      <c r="AY8">
+        <v>14</v>
+      </c>
+      <c r="AZ8">
+        <v>20</v>
+      </c>
+      <c r="BA8">
         <v>10</v>
       </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>3.95</v>
-      </c>
-      <c r="K8">
-        <v>4.3</v>
-      </c>
-      <c r="L8">
-        <v>1.44</v>
-      </c>
-      <c r="M8">
-        <v>1.11</v>
-      </c>
-      <c r="N8">
-        <v>2.72</v>
-      </c>
-      <c r="O8">
-        <v>1.52</v>
-      </c>
-      <c r="P8">
-        <v>1.54</v>
-      </c>
-      <c r="Q8">
-        <v>2.56</v>
-      </c>
-      <c r="R8">
-        <v>1.2</v>
-      </c>
-      <c r="S8">
-        <v>5.4</v>
-      </c>
-      <c r="T8">
-        <v>2.74</v>
-      </c>
-      <c r="U8">
-        <v>1.51</v>
-      </c>
-      <c r="V8">
-        <v>1.09</v>
-      </c>
-      <c r="W8">
-        <v>2.88</v>
-      </c>
-      <c r="X8">
-        <v>11.5</v>
-      </c>
-      <c r="Y8">
-        <v>28</v>
-      </c>
-      <c r="Z8">
-        <v>130</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>5.3</v>
-      </c>
-      <c r="AC8">
-        <v>12.5</v>
-      </c>
-      <c r="AD8">
-        <v>60</v>
-      </c>
-      <c r="AE8">
-        <v>400</v>
-      </c>
-      <c r="AF8">
-        <v>7</v>
-      </c>
-      <c r="AG8">
-        <v>13.5</v>
-      </c>
-      <c r="AH8">
-        <v>55</v>
-      </c>
-      <c r="AI8">
-        <v>370</v>
-      </c>
-      <c r="AJ8">
-        <v>15.5</v>
-      </c>
-      <c r="AK8">
-        <v>29</v>
-      </c>
-      <c r="AL8">
-        <v>95</v>
-      </c>
-      <c r="AM8">
-        <v>540</v>
-      </c>
-      <c r="AN8">
-        <v>16.5</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>8.4</v>
-      </c>
-      <c r="AQ8">
-        <v>16</v>
-      </c>
-      <c r="AR8">
-        <v>5.9</v>
-      </c>
-      <c r="AS8">
-        <v>5.8</v>
-      </c>
-      <c r="AT8">
-        <v>4.7</v>
-      </c>
-      <c r="AU8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV8">
-        <v>5.6</v>
-      </c>
-      <c r="AW8">
-        <v>6</v>
-      </c>
-      <c r="AX8">
-        <v>6.2</v>
-      </c>
-      <c r="AY8">
+      <c r="BB8">
+        <v>10</v>
+      </c>
+      <c r="BC8">
+        <v>9.6</v>
+      </c>
+      <c r="BD8">
+        <v>10</v>
+      </c>
+      <c r="BE8">
+        <v>10.5</v>
+      </c>
+      <c r="BF8">
+        <v>10</v>
+      </c>
+      <c r="BG8">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ8">
-        <v>5.5</v>
-      </c>
-      <c r="BA8">
-        <v>6</v>
-      </c>
-      <c r="BB8">
-        <v>11</v>
-      </c>
-      <c r="BC8">
-        <v>17</v>
-      </c>
-      <c r="BD8">
-        <v>5.8</v>
-      </c>
-      <c r="BE8">
-        <v>5.7</v>
-      </c>
-      <c r="BF8">
-        <v>11.5</v>
-      </c>
-      <c r="BG8">
-        <v>5.8</v>
-      </c>
       <c r="BH8">
         <v>1000</v>
       </c>
@@ -2806,491 +2830,491 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F9">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="K9">
-        <v>2.98</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>2.96</v>
+        <v>1.21</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F10">
-        <v>2.64</v>
+        <v>1.47</v>
       </c>
       <c r="G10">
+        <v>1.54</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>3.95</v>
+      </c>
+      <c r="K10">
+        <v>4.4</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.11</v>
+      </c>
+      <c r="N10">
+        <v>2.68</v>
+      </c>
+      <c r="O10">
+        <v>1.52</v>
+      </c>
+      <c r="P10">
+        <v>1.54</v>
+      </c>
+      <c r="Q10">
+        <v>2.56</v>
+      </c>
+      <c r="R10">
+        <v>1.19</v>
+      </c>
+      <c r="S10">
+        <v>5.4</v>
+      </c>
+      <c r="T10">
         <v>2.74</v>
       </c>
-      <c r="H10">
-        <v>2.84</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>3.45</v>
-      </c>
-      <c r="K10">
-        <v>3.65</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>1.89</v>
-      </c>
-      <c r="Q10">
-        <v>1.96</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>1.76</v>
-      </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X10">
+        <v>11.5</v>
+      </c>
+      <c r="Y10">
+        <v>27</v>
+      </c>
+      <c r="Z10">
+        <v>130</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>5.3</v>
+      </c>
+      <c r="AC10">
+        <v>12.5</v>
+      </c>
+      <c r="AD10">
+        <v>60</v>
+      </c>
+      <c r="AE10">
+        <v>400</v>
+      </c>
+      <c r="AF10">
+        <v>7</v>
+      </c>
+      <c r="AG10">
+        <v>13.5</v>
+      </c>
+      <c r="AH10">
+        <v>55</v>
+      </c>
+      <c r="AI10">
+        <v>370</v>
+      </c>
+      <c r="AJ10">
+        <v>15.5</v>
+      </c>
+      <c r="AK10">
+        <v>29</v>
+      </c>
+      <c r="AL10">
+        <v>95</v>
+      </c>
+      <c r="AM10">
+        <v>540</v>
+      </c>
+      <c r="AN10">
+        <v>16.5</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>8.4</v>
+      </c>
+      <c r="AQ10">
         <v>16</v>
       </c>
-      <c r="Y10">
-        <v>12</v>
-      </c>
-      <c r="Z10">
-        <v>20</v>
-      </c>
-      <c r="AA10">
-        <v>55</v>
-      </c>
-      <c r="AB10">
+      <c r="AR10">
+        <v>5.7</v>
+      </c>
+      <c r="AS10">
+        <v>5.8</v>
+      </c>
+      <c r="AT10">
+        <v>4.7</v>
+      </c>
+      <c r="AU10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV10">
+        <v>5.4</v>
+      </c>
+      <c r="AW10">
+        <v>5.7</v>
+      </c>
+      <c r="AX10">
+        <v>6.2</v>
+      </c>
+      <c r="AY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>5.3</v>
+      </c>
+      <c r="BA10">
+        <v>5.7</v>
+      </c>
+      <c r="BB10">
+        <v>11</v>
+      </c>
+      <c r="BC10">
+        <v>17</v>
+      </c>
+      <c r="BD10">
+        <v>5.6</v>
+      </c>
+      <c r="BE10">
+        <v>5.7</v>
+      </c>
+      <c r="BF10">
         <v>11.5</v>
       </c>
-      <c r="AC10">
-        <v>8</v>
-      </c>
-      <c r="AD10">
-        <v>13.5</v>
-      </c>
-      <c r="AE10">
-        <v>34</v>
-      </c>
-      <c r="AF10">
-        <v>18</v>
-      </c>
-      <c r="AG10">
-        <v>13</v>
-      </c>
-      <c r="AH10">
-        <v>18</v>
-      </c>
-      <c r="AI10">
-        <v>50</v>
-      </c>
-      <c r="AJ10">
-        <v>42</v>
-      </c>
-      <c r="AK10">
-        <v>32</v>
-      </c>
-      <c r="AL10">
-        <v>50</v>
-      </c>
-      <c r="AM10">
-        <v>110</v>
-      </c>
-      <c r="AN10">
-        <v>26</v>
-      </c>
-      <c r="AO10">
-        <v>34</v>
-      </c>
-      <c r="AP10">
-        <v>12</v>
-      </c>
-      <c r="AQ10">
-        <v>10</v>
-      </c>
-      <c r="AR10">
-        <v>16</v>
-      </c>
-      <c r="AS10">
-        <v>7.6</v>
-      </c>
-      <c r="AT10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU10">
-        <v>7</v>
-      </c>
-      <c r="AV10">
-        <v>11</v>
-      </c>
-      <c r="AW10">
-        <v>7</v>
-      </c>
-      <c r="AX10">
-        <v>15.5</v>
-      </c>
-      <c r="AY10">
-        <v>11</v>
-      </c>
-      <c r="AZ10">
-        <v>15</v>
-      </c>
-      <c r="BA10">
-        <v>7.6</v>
-      </c>
-      <c r="BB10">
-        <v>7.4</v>
-      </c>
-      <c r="BC10">
-        <v>7</v>
-      </c>
-      <c r="BD10">
-        <v>7.6</v>
-      </c>
-      <c r="BE10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF10">
-        <v>20</v>
-      </c>
       <c r="BG10">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3298,241 +3322,241 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J11">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
+        <v>1.88</v>
+      </c>
+      <c r="Q11">
+        <v>1.85</v>
+      </c>
+      <c r="R11">
+        <v>1.33</v>
+      </c>
+      <c r="S11">
+        <v>2.06</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
         <v>1.24</v>
       </c>
-      <c r="Q11">
-        <v>1.01</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3540,241 +3564,241 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F12">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="H12">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="I12">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P12">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3782,16 +3806,16 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
         <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>1.04</v>
@@ -4016,42 +4040,42 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J14">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4066,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4258,24 +4282,24 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F15">
         <v>1.04</v>
@@ -4500,314 +4524,314 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F16">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G16">
-        <v>1.11</v>
+        <v>1000</v>
       </c>
       <c r="H16">
-        <v>30</v>
+        <v>1.04</v>
       </c>
       <c r="I16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="J16">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="K16">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>5.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="R16">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BG16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BH16">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BI16">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BJ16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BK16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL16">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM16">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BN16">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO16">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP16">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BQ16">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BR16">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BS16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BU16">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BV16">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX16">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BY16">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BZ16">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F17">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="G17">
-        <v>1.28</v>
+        <v>1000</v>
       </c>
       <c r="H17">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="I17">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="J17">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="K17">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q17">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4816,694 +4840,694 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BG17">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI17">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK17">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO17">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ17">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS17">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU17">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F18">
         <v>1.27</v>
       </c>
       <c r="G18">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I18">
+        <v>12.5</v>
+      </c>
+      <c r="J18">
+        <v>7.6</v>
+      </c>
+      <c r="K18">
+        <v>7.8</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>10.5</v>
+      </c>
+      <c r="O18">
+        <v>1.09</v>
+      </c>
+      <c r="P18">
+        <v>4.2</v>
+      </c>
+      <c r="Q18">
+        <v>1.28</v>
+      </c>
+      <c r="R18">
+        <v>2.34</v>
+      </c>
+      <c r="S18">
+        <v>1.69</v>
+      </c>
+      <c r="T18">
+        <v>1.66</v>
+      </c>
+      <c r="U18">
+        <v>2.44</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>60</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>410</v>
+      </c>
+      <c r="AB18">
+        <v>20</v>
+      </c>
+      <c r="AC18">
+        <v>19.5</v>
+      </c>
+      <c r="AD18">
+        <v>55</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>14</v>
+      </c>
+      <c r="AG18">
+        <v>13</v>
+      </c>
+      <c r="AH18">
+        <v>25</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>13</v>
+      </c>
+      <c r="AK18">
         <v>13.5</v>
       </c>
-      <c r="J18">
-        <v>7</v>
-      </c>
-      <c r="K18">
-        <v>8</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>3.5</v>
-      </c>
-      <c r="Q18">
-        <v>1.34</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18">
-        <v>0</v>
-      </c>
-      <c r="AI18">
-        <v>0</v>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
       <c r="AL18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F19">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="G19">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="H19">
+        <v>30</v>
+      </c>
+      <c r="I19">
+        <v>32</v>
+      </c>
+      <c r="J19">
+        <v>15</v>
+      </c>
+      <c r="K19">
+        <v>16</v>
+      </c>
+      <c r="L19">
+        <v>1.12</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>15</v>
+      </c>
+      <c r="O19">
+        <v>1.06</v>
+      </c>
+      <c r="P19">
+        <v>5.6</v>
+      </c>
+      <c r="Q19">
+        <v>1.19</v>
+      </c>
+      <c r="R19">
         <v>2.82</v>
       </c>
-      <c r="I19">
-        <v>3.2</v>
-      </c>
-      <c r="J19">
-        <v>2.7</v>
-      </c>
-      <c r="K19">
-        <v>3.15</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>1.41</v>
-      </c>
-      <c r="Q19">
-        <v>2.92</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T19">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="U19">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>7.6</v>
+        <v>120</v>
       </c>
       <c r="Y19">
-        <v>8.800000000000001</v>
+        <v>180</v>
       </c>
       <c r="Z19">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="AA19">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AD19">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="AE19">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="AF19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AG19">
         <v>18</v>
       </c>
       <c r="AH19">
+        <v>55</v>
+      </c>
+      <c r="AI19">
+        <v>230</v>
+      </c>
+      <c r="AJ19">
+        <v>10.5</v>
+      </c>
+      <c r="AK19">
+        <v>15</v>
+      </c>
+      <c r="AL19">
+        <v>38</v>
+      </c>
+      <c r="AM19">
+        <v>190</v>
+      </c>
+      <c r="AN19">
+        <v>1.98</v>
+      </c>
+      <c r="AO19">
+        <v>380</v>
+      </c>
+      <c r="AP19">
+        <v>34</v>
+      </c>
+      <c r="AQ19">
+        <v>42</v>
+      </c>
+      <c r="AR19">
+        <v>20</v>
+      </c>
+      <c r="AS19">
+        <v>17</v>
+      </c>
+      <c r="AT19">
+        <v>20</v>
+      </c>
+      <c r="AU19">
         <v>32</v>
       </c>
-      <c r="AI19">
-        <v>100</v>
-      </c>
-      <c r="AJ19">
-        <v>75</v>
-      </c>
-      <c r="AK19">
-        <v>65</v>
-      </c>
-      <c r="AL19">
-        <v>110</v>
-      </c>
-      <c r="AM19">
-        <v>280</v>
-      </c>
-      <c r="AN19">
+      <c r="AV19">
+        <v>38</v>
+      </c>
+      <c r="AW19">
+        <v>20</v>
+      </c>
+      <c r="AX19">
+        <v>12.5</v>
+      </c>
+      <c r="AY19">
+        <v>15.5</v>
+      </c>
+      <c r="AZ19">
+        <v>29</v>
+      </c>
+      <c r="BA19">
+        <v>48</v>
+      </c>
+      <c r="BB19">
+        <v>9.4</v>
+      </c>
+      <c r="BC19">
+        <v>12.5</v>
+      </c>
+      <c r="BD19">
+        <v>24</v>
+      </c>
+      <c r="BE19">
+        <v>46</v>
+      </c>
+      <c r="BF19">
+        <v>1.91</v>
+      </c>
+      <c r="BG19">
+        <v>55</v>
+      </c>
+      <c r="BH19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI19">
+        <v>7</v>
+      </c>
+      <c r="BJ19">
+        <v>16</v>
+      </c>
+      <c r="BK19">
+        <v>10</v>
+      </c>
+      <c r="BL19">
+        <v>120</v>
+      </c>
+      <c r="BM19">
+        <v>70</v>
+      </c>
+      <c r="BN19">
+        <v>5.5</v>
+      </c>
+      <c r="BO19">
+        <v>4.1</v>
+      </c>
+      <c r="BP19">
+        <v>6.8</v>
+      </c>
+      <c r="BQ19">
+        <v>5.2</v>
+      </c>
+      <c r="BR19">
+        <v>19.5</v>
+      </c>
+      <c r="BS19">
+        <v>12</v>
+      </c>
+      <c r="BT19">
+        <v>27</v>
+      </c>
+      <c r="BU19">
+        <v>16.5</v>
+      </c>
+      <c r="BV19">
+        <v>150</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
         <v>90</v>
       </c>
-      <c r="AO19">
-        <v>80</v>
-      </c>
-      <c r="AP19">
-        <v>5.6</v>
-      </c>
-      <c r="AQ19">
-        <v>6</v>
-      </c>
-      <c r="AR19">
-        <v>13.5</v>
-      </c>
-      <c r="AS19">
-        <v>1.01</v>
-      </c>
-      <c r="AT19">
-        <v>6.2</v>
-      </c>
-      <c r="AU19">
-        <v>6</v>
-      </c>
-      <c r="AV19">
-        <v>11</v>
-      </c>
-      <c r="AW19">
-        <v>1.03</v>
-      </c>
-      <c r="AX19">
-        <v>14.5</v>
-      </c>
-      <c r="AY19">
-        <v>11.5</v>
-      </c>
-      <c r="AZ19">
-        <v>21</v>
-      </c>
-      <c r="BA19">
-        <v>1.01</v>
-      </c>
-      <c r="BB19">
-        <v>1.01</v>
-      </c>
-      <c r="BC19">
-        <v>1.01</v>
-      </c>
-      <c r="BD19">
-        <v>1.01</v>
-      </c>
-      <c r="BE19">
-        <v>1.01</v>
-      </c>
-      <c r="BF19">
-        <v>1.01</v>
-      </c>
-      <c r="BG19">
-        <v>1.01</v>
-      </c>
-      <c r="BH19">
-        <v>0</v>
-      </c>
-      <c r="BI19">
-        <v>0</v>
-      </c>
-      <c r="BJ19">
-        <v>0</v>
-      </c>
-      <c r="BK19">
-        <v>0</v>
-      </c>
-      <c r="BL19">
-        <v>0</v>
-      </c>
-      <c r="BM19">
-        <v>0</v>
-      </c>
-      <c r="BN19">
-        <v>0</v>
-      </c>
-      <c r="BO19">
-        <v>0</v>
-      </c>
-      <c r="BP19">
-        <v>0</v>
-      </c>
-      <c r="BQ19">
-        <v>0</v>
-      </c>
-      <c r="BR19">
-        <v>0</v>
-      </c>
-      <c r="BS19">
-        <v>0</v>
-      </c>
-      <c r="BT19">
-        <v>0</v>
-      </c>
-      <c r="BU19">
-        <v>0</v>
-      </c>
-      <c r="BV19">
-        <v>0</v>
-      </c>
-      <c r="BW19">
-        <v>0</v>
-      </c>
-      <c r="BX19">
-        <v>0</v>
-      </c>
       <c r="BY19">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="CB19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F20">
-        <v>9.800000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="G20">
-        <v>11.5</v>
+        <v>1.3</v>
       </c>
       <c r="H20">
-        <v>1.44</v>
+        <v>10.5</v>
       </c>
       <c r="I20">
-        <v>1.49</v>
+        <v>13.5</v>
       </c>
       <c r="J20">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5518,10 +5542,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
-        <v>2.16</v>
+        <v>1.34</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5530,10 +5554,10 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -5542,112 +5566,112 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="AL20">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ20">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AR20">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AU20">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV20">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AW20">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AX20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AZ20">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BA20">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BB20">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BC20">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BD20">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BE20">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BF20">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BG20">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BH20">
         <v>0</v>
@@ -5710,43 +5734,43 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F21">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="G21">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="H21">
+        <v>2.06</v>
+      </c>
+      <c r="I21">
+        <v>2.3</v>
+      </c>
+      <c r="J21">
         <v>3.45</v>
       </c>
-      <c r="I21">
-        <v>3.75</v>
-      </c>
-      <c r="J21">
+      <c r="K21">
         <v>3.85</v>
       </c>
-      <c r="K21">
-        <v>4.2</v>
-      </c>
       <c r="L21">
         <v>0</v>
       </c>
@@ -5760,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q21">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5952,186 +5976,186 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>3.4</v>
+      </c>
+      <c r="H22">
+        <v>2.82</v>
+      </c>
+      <c r="I22">
+        <v>3.2</v>
+      </c>
+      <c r="J22">
+        <v>2.7</v>
+      </c>
+      <c r="K22">
+        <v>3.15</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.41</v>
+      </c>
+      <c r="Q22">
+        <v>2.92</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>2.26</v>
+      </c>
+      <c r="U22">
+        <v>1.67</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>7.6</v>
+      </c>
+      <c r="Y22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z22">
+        <v>21</v>
+      </c>
+      <c r="AA22">
+        <v>65</v>
+      </c>
+      <c r="AB22">
+        <v>9.4</v>
+      </c>
+      <c r="AC22">
+        <v>8</v>
+      </c>
+      <c r="AD22">
+        <v>17</v>
+      </c>
+      <c r="AE22">
+        <v>60</v>
+      </c>
+      <c r="AF22">
+        <v>23</v>
+      </c>
+      <c r="AG22">
+        <v>18</v>
+      </c>
+      <c r="AH22">
+        <v>32</v>
+      </c>
+      <c r="AI22">
+        <v>100</v>
+      </c>
+      <c r="AJ22">
+        <v>75</v>
+      </c>
+      <c r="AK22">
+        <v>65</v>
+      </c>
+      <c r="AL22">
+        <v>110</v>
+      </c>
+      <c r="AM22">
+        <v>280</v>
+      </c>
+      <c r="AN22">
         <v>90</v>
       </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" t="s">
-        <v>161</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22">
-        <v>2.18</v>
-      </c>
-      <c r="H22">
-        <v>3.65</v>
-      </c>
-      <c r="I22">
-        <v>4.2</v>
-      </c>
-      <c r="J22">
-        <v>3.8</v>
-      </c>
-      <c r="K22">
-        <v>4.5</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>2</v>
-      </c>
-      <c r="Q22">
-        <v>1.57</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
       <c r="AO22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
         <v>0</v>
@@ -6194,42 +6218,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F23">
-        <v>2.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G23">
-        <v>2.68</v>
+        <v>13</v>
       </c>
       <c r="H23">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="I23">
-        <v>3.1</v>
+        <v>1.49</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K23">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6244,10 +6268,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="Q23">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6256,10 +6280,10 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6268,112 +6292,112 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH23">
         <v>0</v>
@@ -6436,42 +6460,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F24">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="H24">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="I24">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="J24">
         <v>3.85</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6486,10 +6510,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q24">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6678,42 +6702,42 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F25">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="G25">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="H25">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="I25">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="J25">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6728,10 +6752,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6920,42 +6944,42 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F26">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="G26">
-        <v>1.31</v>
+        <v>2.54</v>
       </c>
       <c r="H26">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="J26">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="K26">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6970,10 +6994,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7162,42 +7186,42 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E27" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="G27">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="I27">
-        <v>2.56</v>
+        <v>5.1</v>
       </c>
       <c r="J27">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7212,10 +7236,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="Q27">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7404,42 +7428,42 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F28">
-        <v>2.06</v>
+        <v>3.65</v>
       </c>
       <c r="G28">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="H28">
+        <v>1.9</v>
+      </c>
+      <c r="I28">
+        <v>2.14</v>
+      </c>
+      <c r="J28">
         <v>3.85</v>
       </c>
-      <c r="I28">
-        <v>3.9</v>
-      </c>
-      <c r="J28">
-        <v>3.75</v>
-      </c>
       <c r="K28">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7454,10 +7478,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q28">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7646,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7654,64 +7678,64 @@
         <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
         <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F29">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="G29">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="H29">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="J29">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="R29">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -7720,240 +7744,240 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AR29">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU29">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AW29">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AX29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ29">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA29">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB29">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BC29">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BE29">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF29">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BG29">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BH29">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BI29">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BJ29">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK29">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL29">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BM29">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BN29">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO29">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP29">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR29">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS29">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BT29">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU29">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BV29">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BW29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BX29">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BY29">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BZ29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA29">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F30">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="G30">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="H30">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="I30">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K30">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <v>1.9</v>
       </c>
       <c r="Q30">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="R30">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -7962,240 +7986,240 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL30">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AR30">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AS30">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AT30">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AU30">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV30">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW30">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AX30">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AY30">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AZ30">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA30">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB30">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BD30">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF30">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BG30">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BH30">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BI30">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK30">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO30">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU30">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW30">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F31">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="G31">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="H31">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I31">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K31">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="Q31">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="R31">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -8204,210 +8228,210 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AO31">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BG31">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BH31">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BI31">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BJ31">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL31">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BM31">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BN31">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO31">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP31">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BQ31">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR31">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BS31">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BT31">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BU31">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BV31">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BW31">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BX31">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY31">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BZ31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CA31">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F32">
         <v>3.3</v>
       </c>
       <c r="G32">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H32">
+        <v>2.34</v>
+      </c>
+      <c r="I32">
         <v>2.42</v>
       </c>
-      <c r="I32">
-        <v>2.44</v>
-      </c>
       <c r="J32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K32">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8422,10 +8446,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q32">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8614,24 +8638,24 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F33">
         <v>1.06</v>
@@ -8643,13 +8667,13 @@
         <v>50</v>
       </c>
       <c r="I33">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J33">
         <v>24</v>
       </c>
       <c r="K33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -8670,16 +8694,16 @@
         <v>1.22</v>
       </c>
       <c r="R33">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="S33">
         <v>1.54</v>
       </c>
       <c r="T33">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -8724,7 +8748,7 @@
         <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK33">
         <v>20</v>
@@ -8736,7 +8760,7 @@
         <v>1000</v>
       </c>
       <c r="AN33">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AO33">
         <v>1000</v>
@@ -8754,28 +8778,28 @@
         <v>60</v>
       </c>
       <c r="AT33">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AW33">
         <v>60</v>
       </c>
       <c r="AX33">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY33">
         <v>21</v>
       </c>
       <c r="AZ33">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BA33">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB33">
         <v>7.2</v>
@@ -8784,13 +8808,13 @@
         <v>16.5</v>
       </c>
       <c r="BD33">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE33">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="BF33">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BG33">
         <v>60</v>
@@ -8856,249 +8880,975 @@
         <v>3.3</v>
       </c>
       <c r="CB33" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F34">
+        <v>5.2</v>
+      </c>
+      <c r="G34">
+        <v>5.4</v>
+      </c>
+      <c r="H34">
+        <v>1.81</v>
+      </c>
+      <c r="I34">
+        <v>1.82</v>
+      </c>
+      <c r="J34">
+        <v>3.8</v>
+      </c>
+      <c r="K34">
+        <v>3.9</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1.07</v>
+      </c>
+      <c r="N34">
+        <v>3.75</v>
+      </c>
+      <c r="O34">
+        <v>1.34</v>
+      </c>
+      <c r="P34">
+        <v>1.9</v>
+      </c>
+      <c r="Q34">
+        <v>2.02</v>
+      </c>
+      <c r="R34">
+        <v>1.35</v>
+      </c>
+      <c r="S34">
+        <v>3.7</v>
+      </c>
+      <c r="T34">
+        <v>1.92</v>
+      </c>
+      <c r="U34">
+        <v>2.02</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>14.5</v>
+      </c>
+      <c r="Y34">
+        <v>8</v>
+      </c>
+      <c r="Z34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA34">
         <v>19</v>
       </c>
-      <c r="G34">
-        <v>24</v>
-      </c>
-      <c r="H34">
-        <v>1.17</v>
-      </c>
-      <c r="I34">
+      <c r="AB34">
+        <v>17.5</v>
+      </c>
+      <c r="AC34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD34">
+        <v>10.5</v>
+      </c>
+      <c r="AE34">
+        <v>21</v>
+      </c>
+      <c r="AF34">
+        <v>44</v>
+      </c>
+      <c r="AG34">
+        <v>21</v>
+      </c>
+      <c r="AH34">
+        <v>21</v>
+      </c>
+      <c r="AI34">
+        <v>40</v>
+      </c>
+      <c r="AJ34">
+        <v>150</v>
+      </c>
+      <c r="AK34">
+        <v>80</v>
+      </c>
+      <c r="AL34">
+        <v>80</v>
+      </c>
+      <c r="AM34">
+        <v>130</v>
+      </c>
+      <c r="AN34">
+        <v>100</v>
+      </c>
+      <c r="AO34">
+        <v>12.5</v>
+      </c>
+      <c r="AP34">
+        <v>13</v>
+      </c>
+      <c r="AQ34">
+        <v>7.6</v>
+      </c>
+      <c r="AR34">
+        <v>9.4</v>
+      </c>
+      <c r="AS34">
+        <v>17.5</v>
+      </c>
+      <c r="AT34">
+        <v>15</v>
+      </c>
+      <c r="AU34">
+        <v>7.6</v>
+      </c>
+      <c r="AV34">
+        <v>9.4</v>
+      </c>
+      <c r="AW34">
+        <v>17.5</v>
+      </c>
+      <c r="AX34">
+        <v>34</v>
+      </c>
+      <c r="AY34">
+        <v>18</v>
+      </c>
+      <c r="AZ34">
+        <v>18.5</v>
+      </c>
+      <c r="BA34">
+        <v>23</v>
+      </c>
+      <c r="BB34">
+        <v>40</v>
+      </c>
+      <c r="BC34">
+        <v>55</v>
+      </c>
+      <c r="BD34">
+        <v>34</v>
+      </c>
+      <c r="BE34">
+        <v>100</v>
+      </c>
+      <c r="BF34">
+        <v>60</v>
+      </c>
+      <c r="BG34">
+        <v>11</v>
+      </c>
+      <c r="BH34">
+        <v>3.65</v>
+      </c>
+      <c r="BI34">
+        <v>2.78</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>7.2</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>6.2</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>3.6</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>8.4</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" t="s">
+        <v>179</v>
+      </c>
+      <c r="F35">
+        <v>1.76</v>
+      </c>
+      <c r="G35">
+        <v>1.77</v>
+      </c>
+      <c r="H35">
+        <v>5</v>
+      </c>
+      <c r="I35">
+        <v>5.1</v>
+      </c>
+      <c r="J35">
+        <v>4.2</v>
+      </c>
+      <c r="K35">
+        <v>4.3</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>1.04</v>
+      </c>
+      <c r="N35">
+        <v>5.4</v>
+      </c>
+      <c r="O35">
         <v>1.2</v>
       </c>
-      <c r="J34">
+      <c r="P35">
+        <v>2.52</v>
+      </c>
+      <c r="Q35">
+        <v>1.62</v>
+      </c>
+      <c r="R35">
+        <v>1.59</v>
+      </c>
+      <c r="S35">
+        <v>2.58</v>
+      </c>
+      <c r="T35">
+        <v>1.65</v>
+      </c>
+      <c r="U35">
+        <v>2.44</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>23</v>
+      </c>
+      <c r="Y35">
+        <v>23</v>
+      </c>
+      <c r="Z35">
+        <v>42</v>
+      </c>
+      <c r="AA35">
+        <v>120</v>
+      </c>
+      <c r="AB35">
+        <v>12</v>
+      </c>
+      <c r="AC35">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD35">
+        <v>19</v>
+      </c>
+      <c r="AE35">
+        <v>55</v>
+      </c>
+      <c r="AF35">
+        <v>12.5</v>
+      </c>
+      <c r="AG35">
+        <v>10</v>
+      </c>
+      <c r="AH35">
+        <v>17</v>
+      </c>
+      <c r="AI35">
+        <v>55</v>
+      </c>
+      <c r="AJ35">
+        <v>19</v>
+      </c>
+      <c r="AK35">
+        <v>17</v>
+      </c>
+      <c r="AL35">
+        <v>29</v>
+      </c>
+      <c r="AM35">
+        <v>85</v>
+      </c>
+      <c r="AN35">
+        <v>8</v>
+      </c>
+      <c r="AO35">
+        <v>48</v>
+      </c>
+      <c r="AP35">
+        <v>20</v>
+      </c>
+      <c r="AQ35">
+        <v>19.5</v>
+      </c>
+      <c r="AR35">
+        <v>34</v>
+      </c>
+      <c r="AS35">
+        <v>40</v>
+      </c>
+      <c r="AT35">
+        <v>11</v>
+      </c>
+      <c r="AU35">
+        <v>9</v>
+      </c>
+      <c r="AV35">
+        <v>17</v>
+      </c>
+      <c r="AW35">
+        <v>28</v>
+      </c>
+      <c r="AX35">
+        <v>12</v>
+      </c>
+      <c r="AY35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ35">
+        <v>15</v>
+      </c>
+      <c r="BA35">
+        <v>28</v>
+      </c>
+      <c r="BB35">
+        <v>17.5</v>
+      </c>
+      <c r="BC35">
+        <v>14.5</v>
+      </c>
+      <c r="BD35">
+        <v>19</v>
+      </c>
+      <c r="BE35">
+        <v>32</v>
+      </c>
+      <c r="BF35">
+        <v>7.4</v>
+      </c>
+      <c r="BG35">
+        <v>27</v>
+      </c>
+      <c r="BH35">
+        <v>4.1</v>
+      </c>
+      <c r="BI35">
+        <v>3.8</v>
+      </c>
+      <c r="BJ35">
+        <v>11</v>
+      </c>
+      <c r="BK35">
+        <v>8</v>
+      </c>
+      <c r="BL35">
+        <v>110</v>
+      </c>
+      <c r="BM35">
+        <v>60</v>
+      </c>
+      <c r="BN35">
+        <v>4.7</v>
+      </c>
+      <c r="BO35">
+        <v>4.3</v>
+      </c>
+      <c r="BP35">
+        <v>13.5</v>
+      </c>
+      <c r="BQ35">
+        <v>10</v>
+      </c>
+      <c r="BR35">
+        <v>27</v>
+      </c>
+      <c r="BS35">
+        <v>16</v>
+      </c>
+      <c r="BT35">
+        <v>10.5</v>
+      </c>
+      <c r="BU35">
+        <v>7.4</v>
+      </c>
+      <c r="BV35">
+        <v>42</v>
+      </c>
+      <c r="BW35">
+        <v>25</v>
+      </c>
+      <c r="BX35">
+        <v>46</v>
+      </c>
+      <c r="BY35">
+        <v>27</v>
+      </c>
+      <c r="BZ35">
+        <v>18.5</v>
+      </c>
+      <c r="CA35">
+        <v>11.5</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36">
+        <v>1.89</v>
+      </c>
+      <c r="G36">
+        <v>1.91</v>
+      </c>
+      <c r="H36">
+        <v>4.3</v>
+      </c>
+      <c r="I36">
+        <v>4.5</v>
+      </c>
+      <c r="J36">
+        <v>4</v>
+      </c>
+      <c r="K36">
+        <v>4.2</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>1.05</v>
+      </c>
+      <c r="N36">
+        <v>5.1</v>
+      </c>
+      <c r="O36">
+        <v>1.22</v>
+      </c>
+      <c r="P36">
+        <v>2.4</v>
+      </c>
+      <c r="Q36">
+        <v>1.66</v>
+      </c>
+      <c r="R36">
+        <v>1.56</v>
+      </c>
+      <c r="S36">
+        <v>2.64</v>
+      </c>
+      <c r="T36">
+        <v>1.65</v>
+      </c>
+      <c r="U36">
+        <v>2.44</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>21</v>
+      </c>
+      <c r="Y36">
+        <v>21</v>
+      </c>
+      <c r="Z36">
+        <v>36</v>
+      </c>
+      <c r="AA36">
+        <v>1000</v>
+      </c>
+      <c r="AB36">
+        <v>12</v>
+      </c>
+      <c r="AC36">
+        <v>9.6</v>
+      </c>
+      <c r="AD36">
+        <v>17.5</v>
+      </c>
+      <c r="AE36">
+        <v>48</v>
+      </c>
+      <c r="AF36">
+        <v>13.5</v>
+      </c>
+      <c r="AG36">
+        <v>10.5</v>
+      </c>
+      <c r="AH36">
+        <v>16.5</v>
+      </c>
+      <c r="AI36">
+        <v>60</v>
+      </c>
+      <c r="AJ36">
+        <v>21</v>
+      </c>
+      <c r="AK36">
+        <v>17.5</v>
+      </c>
+      <c r="AL36">
+        <v>32</v>
+      </c>
+      <c r="AM36">
+        <v>80</v>
+      </c>
+      <c r="AN36">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO36">
+        <v>46</v>
+      </c>
+      <c r="AP36">
+        <v>18.5</v>
+      </c>
+      <c r="AQ36">
+        <v>17.5</v>
+      </c>
+      <c r="AR36">
+        <v>29</v>
+      </c>
+      <c r="AS36">
+        <v>36</v>
+      </c>
+      <c r="AT36">
+        <v>10.5</v>
+      </c>
+      <c r="AU36">
+        <v>8.6</v>
+      </c>
+      <c r="AV36">
+        <v>15.5</v>
+      </c>
+      <c r="AW36">
+        <v>38</v>
+      </c>
+      <c r="AX36">
+        <v>12</v>
+      </c>
+      <c r="AY36">
+        <v>9.6</v>
+      </c>
+      <c r="AZ36">
+        <v>14.5</v>
+      </c>
+      <c r="BA36">
+        <v>26</v>
+      </c>
+      <c r="BB36">
+        <v>19</v>
+      </c>
+      <c r="BC36">
+        <v>15.5</v>
+      </c>
+      <c r="BD36">
+        <v>19</v>
+      </c>
+      <c r="BE36">
+        <v>32</v>
+      </c>
+      <c r="BF36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG36">
+        <v>32</v>
+      </c>
+      <c r="BH36">
+        <v>4.8</v>
+      </c>
+      <c r="BI36">
+        <v>3.7</v>
+      </c>
+      <c r="BJ36">
+        <v>11</v>
+      </c>
+      <c r="BK36">
+        <v>8</v>
+      </c>
+      <c r="BL36">
+        <v>110</v>
+      </c>
+      <c r="BM36">
+        <v>60</v>
+      </c>
+      <c r="BN36">
+        <v>5.7</v>
+      </c>
+      <c r="BO36">
+        <v>4.4</v>
+      </c>
+      <c r="BP36">
+        <v>14.5</v>
+      </c>
+      <c r="BQ36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR36">
+        <v>28</v>
+      </c>
+      <c r="BS36">
+        <v>16</v>
+      </c>
+      <c r="BT36">
+        <v>9.6</v>
+      </c>
+      <c r="BU36">
+        <v>7</v>
+      </c>
+      <c r="BV36">
+        <v>40</v>
+      </c>
+      <c r="BW36">
+        <v>23</v>
+      </c>
+      <c r="BX36">
+        <v>44</v>
+      </c>
+      <c r="BY36">
+        <v>26</v>
+      </c>
+      <c r="BZ36">
+        <v>20</v>
+      </c>
+      <c r="CA36">
+        <v>12</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37">
+        <v>19</v>
+      </c>
+      <c r="G37">
+        <v>25</v>
+      </c>
+      <c r="H37">
+        <v>1.18</v>
+      </c>
+      <c r="I37">
+        <v>1.2</v>
+      </c>
+      <c r="J37">
         <v>8.4</v>
       </c>
-      <c r="K34">
-        <v>10.5</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>2.74</v>
-      </c>
-      <c r="Q34">
+      <c r="K37">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>2.78</v>
+      </c>
+      <c r="Q37">
         <v>1.45</v>
       </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AI34">
-        <v>0</v>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>0</v>
-      </c>
-      <c r="BC34">
-        <v>0</v>
-      </c>
-      <c r="BD34">
-        <v>0</v>
-      </c>
-      <c r="BE34">
-        <v>0</v>
-      </c>
-      <c r="BF34">
-        <v>0</v>
-      </c>
-      <c r="BG34">
-        <v>0</v>
-      </c>
-      <c r="BH34">
-        <v>0</v>
-      </c>
-      <c r="BI34">
-        <v>0</v>
-      </c>
-      <c r="BJ34">
-        <v>0</v>
-      </c>
-      <c r="BK34">
-        <v>0</v>
-      </c>
-      <c r="BL34">
-        <v>0</v>
-      </c>
-      <c r="BM34">
-        <v>0</v>
-      </c>
-      <c r="BN34">
-        <v>0</v>
-      </c>
-      <c r="BO34">
-        <v>0</v>
-      </c>
-      <c r="BP34">
-        <v>0</v>
-      </c>
-      <c r="BQ34">
-        <v>0</v>
-      </c>
-      <c r="BR34">
-        <v>0</v>
-      </c>
-      <c r="BS34">
-        <v>0</v>
-      </c>
-      <c r="BT34">
-        <v>0</v>
-      </c>
-      <c r="BU34">
-        <v>0</v>
-      </c>
-      <c r="BV34">
-        <v>0</v>
-      </c>
-      <c r="BW34">
-        <v>0</v>
-      </c>
-      <c r="BX34">
-        <v>0</v>
-      </c>
-      <c r="BY34">
-        <v>0</v>
-      </c>
-      <c r="BZ34">
-        <v>0</v>
-      </c>
-      <c r="CA34">
-        <v>0</v>
-      </c>
-      <c r="CB34" t="s">
-        <v>174</v>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>0</v>
+      </c>
+      <c r="AV37">
+        <v>0</v>
+      </c>
+      <c r="AW37">
+        <v>0</v>
+      </c>
+      <c r="AX37">
+        <v>0</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37">
+        <v>0</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
+      </c>
+      <c r="BQ37">
+        <v>0</v>
+      </c>
+      <c r="BR37">
+        <v>0</v>
+      </c>
+      <c r="BS37">
+        <v>0</v>
+      </c>
+      <c r="BT37">
+        <v>0</v>
+      </c>
+      <c r="BU37">
+        <v>0</v>
+      </c>
+      <c r="BV37">
+        <v>0</v>
+      </c>
+      <c r="BW37">
+        <v>0</v>
+      </c>
+      <c r="BX37">
+        <v>0</v>
+      </c>
+      <c r="BY37">
+        <v>0</v>
+      </c>
+      <c r="BZ37">
+        <v>0</v>
+      </c>
+      <c r="CA37">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -562,7 +562,7 @@
     <t>Benfica</t>
   </si>
   <si>
-    <t>2026-09-07 12:46:00</t>
+    <t>2026-09-07 14:58:24</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1183,7 @@
         <v>2.5</v>
       </c>
       <c r="O2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P2">
         <v>1.48</v>
@@ -1207,7 +1207,7 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
         <v>8</v>
@@ -1240,7 +1240,7 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1270,10 +1270,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1285,7 +1285,7 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1297,25 +1297,25 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC2">
+        <v>7.8</v>
+      </c>
+      <c r="BD2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE2">
+        <v>9.6</v>
+      </c>
+      <c r="BF2">
         <v>7.6</v>
       </c>
-      <c r="BD2">
-        <v>8.6</v>
-      </c>
-      <c r="BE2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF2">
-        <v>7.4</v>
-      </c>
       <c r="BG2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>2.62</v>
@@ -1398,82 +1398,82 @@
         <v>147</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G3">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <v>4.8</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V3">
         <v>1.08</v>
       </c>
       <c r="W3">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="X3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA3">
-        <v>610</v>
+        <v>520</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE3">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AF3">
         <v>9.6</v>
@@ -1482,10 +1482,10 @@
         <v>13</v>
       </c>
       <c r="AH3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ3">
         <v>12.5</v>
@@ -1494,79 +1494,79 @@
         <v>18</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM3">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN3">
         <v>6.4</v>
       </c>
       <c r="AO3">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="AP3">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
+        <v>4.3</v>
+      </c>
+      <c r="AR3">
+        <v>4.6</v>
+      </c>
+      <c r="AS3">
+        <v>4.8</v>
+      </c>
+      <c r="AT3">
+        <v>6.4</v>
+      </c>
+      <c r="AU3">
+        <v>3.65</v>
+      </c>
+      <c r="AV3">
+        <v>4.4</v>
+      </c>
+      <c r="AW3">
+        <v>4.7</v>
+      </c>
+      <c r="AX3">
+        <v>3.2</v>
+      </c>
+      <c r="AY3">
+        <v>3.5</v>
+      </c>
+      <c r="AZ3">
+        <v>4.2</v>
+      </c>
+      <c r="BA3">
+        <v>4.7</v>
+      </c>
+      <c r="BB3">
+        <v>8</v>
+      </c>
+      <c r="BC3">
+        <v>11</v>
+      </c>
+      <c r="BD3">
+        <v>4.4</v>
+      </c>
+      <c r="BE3">
+        <v>4.7</v>
+      </c>
+      <c r="BF3">
+        <v>2.76</v>
+      </c>
+      <c r="BG3">
+        <v>4.7</v>
+      </c>
+      <c r="BH3">
         <v>4.1</v>
       </c>
-      <c r="AR3">
-        <v>4.4</v>
-      </c>
-      <c r="AS3">
-        <v>4.5</v>
-      </c>
-      <c r="AT3">
+      <c r="BI3">
         <v>3.15</v>
       </c>
-      <c r="AU3">
-        <v>3.55</v>
-      </c>
-      <c r="AV3">
-        <v>4.2</v>
-      </c>
-      <c r="AW3">
-        <v>4.4</v>
-      </c>
-      <c r="AX3">
-        <v>3.05</v>
-      </c>
-      <c r="AY3">
-        <v>3.35</v>
-      </c>
-      <c r="AZ3">
-        <v>4</v>
-      </c>
-      <c r="BA3">
-        <v>4.4</v>
-      </c>
-      <c r="BB3">
-        <v>3.3</v>
-      </c>
-      <c r="BC3">
-        <v>3.6</v>
-      </c>
-      <c r="BD3">
-        <v>4.1</v>
-      </c>
-      <c r="BE3">
-        <v>4.4</v>
-      </c>
-      <c r="BF3">
-        <v>2.66</v>
-      </c>
-      <c r="BG3">
-        <v>4.5</v>
-      </c>
-      <c r="BH3">
-        <v>4.2</v>
-      </c>
-      <c r="BI3">
-        <v>3.05</v>
-      </c>
       <c r="BJ3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
         <v>6</v>
@@ -1575,28 +1575,28 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.69</v>
+        <v>11</v>
       </c>
       <c r="BN3">
         <v>3.85</v>
       </c>
       <c r="BO3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BP3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BU3">
         <v>6.4</v>
@@ -1605,19 +1605,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.78</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CA3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="s">
         <v>182</v>
@@ -1649,7 +1649,7 @@
         <v>5.6</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
         <v>4.2</v>
@@ -1670,7 +1670,7 @@
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q4">
         <v>1.78</v>
@@ -1685,10 +1685,10 @@
         <v>1.84</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>2.44</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
@@ -1906,7 +1906,7 @@
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
         <v>1.42</v>
@@ -1993,7 +1993,7 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR5">
         <v>17</v>
@@ -2151,7 +2151,7 @@
         <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P6">
         <v>1.68</v>
@@ -2163,7 +2163,7 @@
         <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
         <v>1.86</v>
@@ -2202,7 +2202,7 @@
         <v>50</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG6">
         <v>14</v>
@@ -2217,7 +2217,7 @@
         <v>44</v>
       </c>
       <c r="AK6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL6">
         <v>55</v>
@@ -2229,7 +2229,7 @@
         <v>32</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP6">
         <v>8.6</v>
@@ -2241,7 +2241,7 @@
         <v>18</v>
       </c>
       <c r="AS6">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT6">
         <v>7.2</v>
@@ -2253,7 +2253,7 @@
         <v>11</v>
       </c>
       <c r="AW6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX6">
         <v>12</v>
@@ -2265,25 +2265,25 @@
         <v>16</v>
       </c>
       <c r="BA6">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB6">
+        <v>5</v>
+      </c>
+      <c r="BC6">
         <v>4.8</v>
       </c>
-      <c r="BC6">
-        <v>4.7</v>
-      </c>
       <c r="BD6">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE6">
+        <v>5.4</v>
+      </c>
+      <c r="BF6">
+        <v>4.8</v>
+      </c>
+      <c r="BG6">
         <v>5.1</v>
-      </c>
-      <c r="BF6">
-        <v>4.6</v>
-      </c>
-      <c r="BG6">
-        <v>36</v>
       </c>
       <c r="BH6">
         <v>3.65</v>
@@ -2611,19 +2611,19 @@
         <v>3.15</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H8">
         <v>2.66</v>
       </c>
       <c r="I8">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J8">
         <v>2.8</v>
       </c>
       <c r="K8">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2638,10 +2638,10 @@
         <v>1.67</v>
       </c>
       <c r="P8">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Q8">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="R8">
         <v>1.13</v>
@@ -2653,13 +2653,13 @@
         <v>2.3</v>
       </c>
       <c r="U8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X8">
         <v>7.2</v>
@@ -2853,16 +2853,16 @@
         <v>1.04</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9">
         <v>1.04</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2880,16 +2880,16 @@
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2898,10 +2898,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3095,7 +3095,7 @@
         <v>1.47</v>
       </c>
       <c r="G10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H10">
         <v>10</v>
@@ -3143,7 +3143,7 @@
         <v>1.09</v>
       </c>
       <c r="W10">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="X10">
         <v>11.5</v>
@@ -3343,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J11">
         <v>3.15</v>
@@ -3352,7 +3352,7 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
         <v>1.01</v>
@@ -3364,7 +3364,7 @@
         <v>1.25</v>
       </c>
       <c r="P11">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="Q11">
         <v>1.85</v>
@@ -3376,13 +3376,13 @@
         <v>2.06</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U11">
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W11">
         <v>1.92</v>
@@ -3442,28 +3442,28 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AQ11">
         <v>11</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>1.31</v>
       </c>
       <c r="AX11">
         <v>9</v>
@@ -3472,28 +3472,28 @@
         <v>7.4</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BA11">
-        <v>38</v>
+        <v>1.31</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BG11">
-        <v>34</v>
+        <v>1.31</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3505,13 +3505,13 @@
         <v>13.5</v>
       </c>
       <c r="BK11">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>6.6</v>
@@ -3523,13 +3523,13 @@
         <v>20</v>
       </c>
       <c r="BQ11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
         <v>10.5</v>
@@ -3541,19 +3541,19 @@
         <v>50</v>
       </c>
       <c r="BW11">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>182</v>
@@ -3582,7 +3582,7 @@
         <v>2.8</v>
       </c>
       <c r="H12">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I12">
         <v>2.96</v>
@@ -3597,25 +3597,25 @@
         <v>1.37</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O12">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P12">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
         <v>1.76</v>
@@ -3741,61 +3741,61 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.8</v>
+        <v>2.24</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>10</v>
+        <v>2.54</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="CB12" t="s">
         <v>182</v>
@@ -3830,214 +3830,214 @@
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K13">
         <v>950</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
         <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>182</v>
@@ -4060,16 +4060,16 @@
         <v>158</v>
       </c>
       <c r="F14">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G14">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H14">
         <v>2.24</v>
       </c>
       <c r="I14">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J14">
         <v>3.5</v>
@@ -4078,16 +4078,16 @@
         <v>4.1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
         <v>2.06</v>
@@ -4096,190 +4096,190 @@
         <v>1.76</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>182</v>
@@ -4302,226 +4302,226 @@
         <v>159</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>182</v>
@@ -4544,226 +4544,226 @@
         <v>160</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G16">
         <v>1000</v>
       </c>
       <c r="H16">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J16">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <v>950</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P16">
         <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
         <v>182</v>
@@ -4786,226 +4786,226 @@
         <v>161</v>
       </c>
       <c r="F17">
+        <v>1.17</v>
+      </c>
+      <c r="G17">
+        <v>1.23</v>
+      </c>
+      <c r="H17">
+        <v>15.5</v>
+      </c>
+      <c r="I17">
+        <v>22</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <v>10.5</v>
+      </c>
+      <c r="L17">
+        <v>1.17</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>1.01</v>
+      </c>
+      <c r="O17">
+        <v>1.11</v>
+      </c>
+      <c r="P17">
+        <v>2.48</v>
+      </c>
+      <c r="Q17">
+        <v>1.3</v>
+      </c>
+      <c r="R17">
+        <v>1.89</v>
+      </c>
+      <c r="S17">
+        <v>1.7</v>
+      </c>
+      <c r="T17">
+        <v>1.73</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
         <v>1.04</v>
       </c>
-      <c r="G17">
-        <v>1000</v>
-      </c>
-      <c r="H17">
-        <v>1.04</v>
-      </c>
-      <c r="I17">
-        <v>1000</v>
-      </c>
-      <c r="J17">
-        <v>1.01</v>
-      </c>
-      <c r="K17">
-        <v>950</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>1.24</v>
-      </c>
-      <c r="Q17">
-        <v>1.01</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
       <c r="W17">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
         <v>182</v>
@@ -5028,46 +5028,46 @@
         <v>162</v>
       </c>
       <c r="F18">
+        <v>1.26</v>
+      </c>
+      <c r="G18">
         <v>1.27</v>
-      </c>
-      <c r="G18">
-        <v>1.28</v>
       </c>
       <c r="H18">
         <v>12</v>
       </c>
       <c r="I18">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K18">
         <v>7.8</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O18">
         <v>1.09</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q18">
         <v>1.28</v>
       </c>
       <c r="R18">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S18">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T18">
         <v>1.66</v>
@@ -5076,10 +5076,10 @@
         <v>2.44</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X18">
         <v>60</v>
@@ -5097,22 +5097,22 @@
         <v>20</v>
       </c>
       <c r="AC18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AD18">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI18">
         <v>1000</v>
@@ -5121,40 +5121,40 @@
         <v>13</v>
       </c>
       <c r="AK18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM18">
         <v>1000</v>
       </c>
       <c r="AN18">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP18">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AQ18">
         <v>32</v>
       </c>
       <c r="AR18">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS18">
         <v>55</v>
       </c>
       <c r="AT18">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU18">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AV18">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AW18">
         <v>42</v>
@@ -5166,7 +5166,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA18">
         <v>36</v>
@@ -5178,13 +5178,13 @@
         <v>11.5</v>
       </c>
       <c r="BD18">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BE18">
         <v>34</v>
       </c>
       <c r="BF18">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BG18">
         <v>38</v>
@@ -5205,7 +5205,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BN18">
         <v>1000</v>
@@ -5235,19 +5235,19 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB18" t="s">
         <v>182</v>
@@ -5282,40 +5282,40 @@
         <v>32</v>
       </c>
       <c r="J19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="K19">
         <v>16</v>
       </c>
       <c r="L19">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O19">
         <v>1.06</v>
       </c>
       <c r="P19">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q19">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="R19">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="S19">
         <v>1.51</v>
       </c>
       <c r="T19">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V19">
         <v>1.03</v>
@@ -5324,22 +5324,22 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="Y19">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="Z19">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="AA19">
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AD19">
         <v>120</v>
@@ -5351,7 +5351,7 @@
         <v>14</v>
       </c>
       <c r="AG19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH19">
         <v>55</v>
@@ -5372,10 +5372,10 @@
         <v>190</v>
       </c>
       <c r="AN19">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AO19">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AP19">
         <v>34</v>
@@ -5387,10 +5387,10 @@
         <v>20</v>
       </c>
       <c r="AS19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AT19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU19">
         <v>32</v>
@@ -5399,10 +5399,10 @@
         <v>38</v>
       </c>
       <c r="AW19">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="AX19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY19">
         <v>15.5</v>
@@ -5417,7 +5417,7 @@
         <v>9.4</v>
       </c>
       <c r="BC19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD19">
         <v>24</v>
@@ -5426,7 +5426,7 @@
         <v>46</v>
       </c>
       <c r="BF19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BG19">
         <v>55</v>
@@ -5435,61 +5435,61 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BI19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BJ19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BK19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BL19">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="BM19">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="BN19">
         <v>5.5</v>
       </c>
       <c r="BO19">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP19">
         <v>6.8</v>
       </c>
       <c r="BQ19">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR19">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BS19">
         <v>12</v>
       </c>
       <c r="BT19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BU19">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BV19">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BX19">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BY19">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="BZ19">
         <v>5.1</v>
       </c>
       <c r="CA19">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="CB19" t="s">
         <v>182</v>
@@ -5521,7 +5521,7 @@
         <v>10.5</v>
       </c>
       <c r="I20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -5530,208 +5530,208 @@
         <v>7.8</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P20">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q20">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="CB20" t="s">
         <v>182</v>
@@ -5754,226 +5754,226 @@
         <v>165</v>
       </c>
       <c r="F21">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G21">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H21">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I21">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J21">
         <v>3.45</v>
       </c>
       <c r="K21">
+        <v>3.95</v>
+      </c>
+      <c r="L21">
+        <v>1.29</v>
+      </c>
+      <c r="M21">
+        <v>1.06</v>
+      </c>
+      <c r="N21">
         <v>3.85</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P21">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>182</v>
@@ -5996,76 +5996,76 @@
         <v>166</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G22">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H22">
+        <v>2.84</v>
+      </c>
+      <c r="I22">
+        <v>3.05</v>
+      </c>
+      <c r="J22">
         <v>2.82</v>
       </c>
-      <c r="I22">
-        <v>3.2</v>
-      </c>
-      <c r="J22">
-        <v>2.7</v>
-      </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q22">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="T22">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U22">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X22">
         <v>7.6</v>
       </c>
       <c r="Y22">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Z22">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA22">
         <v>65</v>
       </c>
       <c r="AB22">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD22">
         <v>17</v>
@@ -6074,10 +6074,10 @@
         <v>60</v>
       </c>
       <c r="AF22">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AG22">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH22">
         <v>32</v>
@@ -6104,118 +6104,118 @@
         <v>80</v>
       </c>
       <c r="AP22">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR22">
+        <v>15</v>
+      </c>
+      <c r="AS22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT22">
+        <v>7.2</v>
+      </c>
+      <c r="AU22">
+        <v>6.2</v>
+      </c>
+      <c r="AV22">
+        <v>13</v>
+      </c>
+      <c r="AW22">
+        <v>8</v>
+      </c>
+      <c r="AX22">
+        <v>16</v>
+      </c>
+      <c r="AY22">
         <v>13.5</v>
-      </c>
-      <c r="AS22">
-        <v>1.01</v>
-      </c>
-      <c r="AT22">
-        <v>6.2</v>
-      </c>
-      <c r="AU22">
-        <v>6</v>
-      </c>
-      <c r="AV22">
-        <v>11</v>
-      </c>
-      <c r="AW22">
-        <v>1.03</v>
-      </c>
-      <c r="AX22">
-        <v>14.5</v>
-      </c>
-      <c r="AY22">
-        <v>11.5</v>
       </c>
       <c r="AZ22">
         <v>21</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>182</v>
@@ -6241,70 +6241,70 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="H23">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I23">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q23">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y23">
         <v>6.4</v>
       </c>
       <c r="Z23">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AA23">
         <v>15</v>
       </c>
       <c r="AB23">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AC23">
         <v>12.5</v>
@@ -6313,13 +6313,13 @@
         <v>13</v>
       </c>
       <c r="AE23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AG23">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AH23">
         <v>42</v>
@@ -6328,136 +6328,136 @@
         <v>65</v>
       </c>
       <c r="AJ23">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="AK23">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL23">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AM23">
         <v>320</v>
       </c>
       <c r="AN23">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="AO23">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AP23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ23">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR23">
         <v>6.6</v>
       </c>
       <c r="AS23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT23">
         <v>21</v>
       </c>
       <c r="AU23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV23">
         <v>9.6</v>
       </c>
       <c r="AW23">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY23">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ23">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG23">
         <v>8.4</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CB23" t="s">
         <v>182</v>
@@ -6498,208 +6498,208 @@
         <v>4.2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
         <v>2.32</v>
       </c>
       <c r="Q24">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
         <v>182</v>
@@ -6722,10 +6722,10 @@
         <v>169</v>
       </c>
       <c r="F25">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G25">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H25">
         <v>3.65</v>
@@ -6734,22 +6734,22 @@
         <v>4.2</v>
       </c>
       <c r="J25">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K25">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P25">
         <v>2</v>
@@ -6758,190 +6758,190 @@
         <v>1.57</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
         <v>182</v>
@@ -6964,226 +6964,226 @@
         <v>170</v>
       </c>
       <c r="F26">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G26">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.02</v>
+      </c>
+      <c r="N26">
         <v>3.9</v>
       </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P26">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q26">
         <v>1.79</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CB26" t="s">
         <v>182</v>
@@ -7215,7 +7215,7 @@
         <v>3.95</v>
       </c>
       <c r="I27">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>3.85</v>
@@ -7224,208 +7224,208 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P27">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q27">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
         <v>182</v>
@@ -7478,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q28">
         <v>1.69</v>
@@ -7693,16 +7693,16 @@
         <v>1.22</v>
       </c>
       <c r="G29">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="H29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I29">
         <v>15.5</v>
       </c>
       <c r="J29">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K29">
         <v>8.6</v>
@@ -7720,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q29">
         <v>1.28</v>
@@ -7935,13 +7935,13 @@
         <v>3.1</v>
       </c>
       <c r="G30">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H30">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I30">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J30">
         <v>3.5</v>
@@ -7962,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q30">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8177,19 +8177,19 @@
         <v>2.06</v>
       </c>
       <c r="G31">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H31">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I31">
         <v>3.9</v>
       </c>
       <c r="J31">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K31">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8207,7 +8207,7 @@
         <v>2.08</v>
       </c>
       <c r="Q31">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8419,10 +8419,10 @@
         <v>3.3</v>
       </c>
       <c r="G32">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H32">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I32">
         <v>2.42</v>
@@ -8449,7 +8449,7 @@
         <v>1.92</v>
       </c>
       <c r="Q32">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8685,19 +8685,19 @@
         <v>13.5</v>
       </c>
       <c r="O33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P33">
         <v>5.2</v>
       </c>
       <c r="Q33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R33">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="S33">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T33">
         <v>2.8</v>
@@ -8739,7 +8739,7 @@
         <v>11.5</v>
       </c>
       <c r="AG33">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH33">
         <v>1000</v>
@@ -8790,7 +8790,7 @@
         <v>60</v>
       </c>
       <c r="AX33">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY33">
         <v>21</v>
@@ -8799,7 +8799,7 @@
         <v>38</v>
       </c>
       <c r="BA33">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB33">
         <v>7.2</v>
@@ -8844,10 +8844,10 @@
         <v>3.75</v>
       </c>
       <c r="BP33">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BQ33">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR33">
         <v>24</v>
@@ -8906,7 +8906,7 @@
         <v>5.4</v>
       </c>
       <c r="H34">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I34">
         <v>1.82</v>
@@ -8930,7 +8930,7 @@
         <v>1.34</v>
       </c>
       <c r="P34">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q34">
         <v>2.02</v>
@@ -8939,7 +8939,7 @@
         <v>1.35</v>
       </c>
       <c r="S34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T34">
         <v>1.92</v>
@@ -8969,19 +8969,19 @@
         <v>17.5</v>
       </c>
       <c r="AC34">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE34">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF34">
         <v>44</v>
       </c>
       <c r="AG34">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH34">
         <v>21</v>
@@ -8993,7 +8993,7 @@
         <v>150</v>
       </c>
       <c r="AK34">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL34">
         <v>80</v>
@@ -9017,7 +9017,7 @@
         <v>9.4</v>
       </c>
       <c r="AS34">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT34">
         <v>15</v>
@@ -9026,13 +9026,13 @@
         <v>7.6</v>
       </c>
       <c r="AV34">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW34">
         <v>17.5</v>
       </c>
       <c r="AX34">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AY34">
         <v>18</v>
@@ -9041,7 +9041,7 @@
         <v>18.5</v>
       </c>
       <c r="BA34">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BB34">
         <v>40</v>
@@ -9142,10 +9142,10 @@
         <v>179</v>
       </c>
       <c r="F35">
+        <v>1.75</v>
+      </c>
+      <c r="G35">
         <v>1.76</v>
-      </c>
-      <c r="G35">
-        <v>1.77</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -9154,10 +9154,10 @@
         <v>5.1</v>
       </c>
       <c r="J35">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K35">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9175,7 +9175,7 @@
         <v>2.52</v>
       </c>
       <c r="Q35">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R35">
         <v>1.59</v>
@@ -9214,7 +9214,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD35">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE35">
         <v>55</v>
@@ -9241,13 +9241,13 @@
         <v>29</v>
       </c>
       <c r="AM35">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN35">
         <v>8</v>
       </c>
       <c r="AO35">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP35">
         <v>20</v>
@@ -9283,7 +9283,7 @@
         <v>15</v>
       </c>
       <c r="BA35">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BB35">
         <v>17.5</v>
@@ -9334,7 +9334,7 @@
         <v>10</v>
       </c>
       <c r="BR35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS35">
         <v>16</v>
@@ -9387,7 +9387,7 @@
         <v>1.89</v>
       </c>
       <c r="G36">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H36">
         <v>4.3</v>
@@ -9408,13 +9408,13 @@
         <v>1.05</v>
       </c>
       <c r="N36">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O36">
         <v>1.22</v>
       </c>
       <c r="P36">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q36">
         <v>1.66</v>
@@ -9423,13 +9423,13 @@
         <v>1.56</v>
       </c>
       <c r="S36">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T36">
         <v>1.65</v>
       </c>
       <c r="U36">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -9438,7 +9438,7 @@
         <v>0</v>
       </c>
       <c r="X36">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y36">
         <v>21</v>
@@ -9453,7 +9453,7 @@
         <v>12</v>
       </c>
       <c r="AC36">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD36">
         <v>17.5</v>
@@ -9468,7 +9468,7 @@
         <v>10.5</v>
       </c>
       <c r="AH36">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI36">
         <v>60</v>
@@ -9477,16 +9477,16 @@
         <v>21</v>
       </c>
       <c r="AK36">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL36">
         <v>32</v>
       </c>
       <c r="AM36">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN36">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO36">
         <v>46</v>
@@ -9504,7 +9504,7 @@
         <v>36</v>
       </c>
       <c r="AT36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU36">
         <v>8.6</v>
@@ -9528,13 +9528,13 @@
         <v>26</v>
       </c>
       <c r="BB36">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BC36">
         <v>15.5</v>
       </c>
       <c r="BD36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BE36">
         <v>32</v>
@@ -9570,13 +9570,13 @@
         <v>4.4</v>
       </c>
       <c r="BP36">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ36">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS36">
         <v>16</v>
@@ -9591,7 +9591,7 @@
         <v>40</v>
       </c>
       <c r="BW36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BX36">
         <v>44</v>
@@ -9629,7 +9629,7 @@
         <v>19</v>
       </c>
       <c r="G37">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H37">
         <v>1.18</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="188">
   <si>
     <t>League</t>
   </si>
@@ -298,6 +298,9 @@
     <t>English Sky Bet Championship</t>
   </si>
   <si>
+    <t>Scottish Premiership</t>
+  </si>
+  <si>
     <t>Portuguese Primeira Liga</t>
   </si>
   <si>
@@ -394,12 +397,12 @@
     <t>FCI Tallinn</t>
   </si>
   <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
     <t>FC Twente</t>
   </si>
   <si>
@@ -436,21 +439,27 @@
     <t>Norwich</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Napoli</t>
+  </si>
+  <si>
+    <t>Sporting Lisbon</t>
+  </si>
+  <si>
+    <t>St Johnstone</t>
+  </si>
+  <si>
     <t>Charlton</t>
   </si>
   <si>
     <t>Paris St-G</t>
   </si>
   <si>
-    <t>Napoli</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Sporting Lisbon</t>
-  </si>
-  <si>
     <t>Moreirense</t>
   </si>
   <si>
@@ -502,12 +511,12 @@
     <t>Kuressaare</t>
   </si>
   <si>
+    <t>Feyenoord</t>
+  </si>
+  <si>
     <t>Viking</t>
   </si>
   <si>
-    <t>Feyenoord</t>
-  </si>
-  <si>
     <t>SC Telstar</t>
   </si>
   <si>
@@ -544,25 +553,31 @@
     <t>Birmingham</t>
   </si>
   <si>
+    <t>St Mirren</t>
+  </si>
+  <si>
+    <t>Atletico Madrid</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
     <t>QPR</t>
   </si>
   <si>
     <t>Slovan Bratislava</t>
   </si>
   <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
-    <t>Atletico Madrid</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
     <t>Benfica</t>
   </si>
   <si>
-    <t>2026-09-07 14:58:24</t>
+    <t>2026-09-07 17:10:43</t>
   </si>
 </sst>
 </file>
@@ -894,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB37"/>
+  <dimension ref="A1:CB39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1144,16 +1159,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F2">
         <v>2.14</v>
@@ -1240,7 +1255,7 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1252,7 +1267,7 @@
         <v>36</v>
       </c>
       <c r="AL2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>280</v>
@@ -1273,7 +1288,7 @@
         <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1285,7 +1300,7 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1297,25 +1312,25 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB2">
         <v>7.6</v>
       </c>
       <c r="BC2">
+        <v>8</v>
+      </c>
+      <c r="BD2">
+        <v>9</v>
+      </c>
+      <c r="BE2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF2">
         <v>7.8</v>
       </c>
-      <c r="BD2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE2">
+      <c r="BG2">
         <v>9.6</v>
-      </c>
-      <c r="BF2">
-        <v>7.6</v>
-      </c>
-      <c r="BG2">
-        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>2.62</v>
@@ -1378,7 +1393,7 @@
         <v>11</v>
       </c>
       <c r="CB2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1386,16 +1401,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>1.33</v>
@@ -1410,13 +1425,13 @@
         <v>13</v>
       </c>
       <c r="J3">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K3">
         <v>6</v>
       </c>
       <c r="L3">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.04</v>
@@ -1425,13 +1440,13 @@
         <v>4.4</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
         <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="R3">
         <v>1.46</v>
@@ -1485,7 +1500,7 @@
         <v>36</v>
       </c>
       <c r="AI3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ3">
         <v>12.5</v>
@@ -1620,7 +1635,7 @@
         <v>6.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1628,16 +1643,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F4">
         <v>1.63</v>
@@ -1670,7 +1685,7 @@
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
         <v>1.78</v>
@@ -1862,7 +1877,7 @@
         <v>2.52</v>
       </c>
       <c r="CB4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1870,16 +1885,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F5">
         <v>2.7</v>
@@ -1891,7 +1906,7 @@
         <v>2.86</v>
       </c>
       <c r="I5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J5">
         <v>3.2</v>
@@ -1906,22 +1921,22 @@
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q5">
         <v>2.28</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
         <v>1.9</v>
@@ -1993,13 +2008,13 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
         <v>17</v>
       </c>
       <c r="AS5">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
@@ -2104,7 +2119,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2112,109 +2127,109 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I6">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M6">
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P6">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T6">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
         <v>1.6</v>
       </c>
       <c r="X6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA6">
         <v>70</v>
       </c>
       <c r="AB6">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
+        <v>15</v>
+      </c>
+      <c r="AE6">
+        <v>46</v>
+      </c>
+      <c r="AF6">
         <v>16.5</v>
-      </c>
-      <c r="AE6">
-        <v>50</v>
-      </c>
-      <c r="AF6">
-        <v>17</v>
       </c>
       <c r="AG6">
         <v>14</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI6">
         <v>85</v>
       </c>
       <c r="AJ6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK6">
         <v>34</v>
@@ -2226,76 +2241,76 @@
         <v>140</v>
       </c>
       <c r="AN6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO6">
         <v>50</v>
       </c>
       <c r="AP6">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR6">
         <v>18</v>
       </c>
       <c r="AS6">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AU6">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW6">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY6">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6">
+        <v>16.5</v>
+      </c>
+      <c r="BA6">
+        <v>8.6</v>
+      </c>
+      <c r="BB6">
+        <v>8</v>
+      </c>
+      <c r="BC6">
+        <v>7.6</v>
+      </c>
+      <c r="BD6">
+        <v>8.4</v>
+      </c>
+      <c r="BE6">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ6">
-        <v>16</v>
-      </c>
-      <c r="BA6">
-        <v>5.2</v>
-      </c>
-      <c r="BB6">
-        <v>5</v>
-      </c>
-      <c r="BC6">
-        <v>4.8</v>
-      </c>
-      <c r="BD6">
-        <v>5.1</v>
-      </c>
-      <c r="BE6">
-        <v>5.4</v>
-      </c>
       <c r="BF6">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG6">
-        <v>5.1</v>
+        <v>38</v>
       </c>
       <c r="BH6">
         <v>3.65</v>
       </c>
       <c r="BI6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2307,13 +2322,13 @@
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2325,7 +2340,7 @@
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2346,7 +2361,7 @@
         <v>1.39</v>
       </c>
       <c r="CB6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2354,16 +2369,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F7">
         <v>4.2</v>
@@ -2384,7 +2399,7 @@
         <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2537,7 +2552,7 @@
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2573,7 +2588,7 @@
         <v>14.5</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
         <v>32</v>
@@ -2588,7 +2603,7 @@
         <v>10</v>
       </c>
       <c r="CB7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2596,19 +2611,19 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
         <v>3.65</v>
@@ -2617,31 +2632,31 @@
         <v>2.66</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="J8">
         <v>2.8</v>
       </c>
       <c r="K8">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N8">
         <v>2.18</v>
       </c>
       <c r="O8">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="P8">
         <v>1.38</v>
       </c>
       <c r="Q8">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R8">
         <v>1.13</v>
@@ -2653,13 +2668,13 @@
         <v>2.3</v>
       </c>
       <c r="U8">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X8">
         <v>7.2</v>
@@ -2830,7 +2845,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2838,31 +2853,31 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>1.04</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>2.56</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>110</v>
       </c>
       <c r="J9">
-        <v>1.06</v>
+        <v>3.65</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2874,13 +2889,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O9">
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q9">
         <v>1.22</v>
@@ -2889,7 +2904,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2898,10 +2913,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2952,7 +2967,7 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -3072,7 +3087,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3080,16 +3095,16 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F10">
         <v>1.47</v>
@@ -3113,7 +3128,7 @@
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
         <v>2.68</v>
@@ -3122,16 +3137,16 @@
         <v>1.52</v>
       </c>
       <c r="P10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q10">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
         <v>1.19</v>
       </c>
       <c r="S10">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="T10">
         <v>2.74</v>
@@ -3200,7 +3215,7 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10">
         <v>16</v>
@@ -3314,7 +3329,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3322,34 +3337,34 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F11">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="G11">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I11">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L11">
         <v>1.28</v>
@@ -3358,43 +3373,43 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O11">
         <v>1.25</v>
       </c>
       <c r="P11">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R11">
         <v>1.33</v>
       </c>
       <c r="S11">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="T11">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3406,7 +3421,7 @@
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE11">
         <v>1000</v>
@@ -3442,28 +3457,28 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11">
         <v>11</v>
       </c>
       <c r="AR11">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AS11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AT11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AU11">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AV11">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AW11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AX11">
         <v>9</v>
@@ -3472,64 +3487,64 @@
         <v>7.4</v>
       </c>
       <c r="AZ11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BA11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BB11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BC11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BD11">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BE11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BF11">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="BG11">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BJ11">
         <v>13.5</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BN11">
         <v>6.6</v>
       </c>
       <c r="BO11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP11">
         <v>20</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BT11">
         <v>10.5</v>
@@ -3541,22 +3556,22 @@
         <v>50</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="CB11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3564,31 +3579,31 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F12">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G12">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H12">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I12">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
         <v>3.7</v>
@@ -3600,7 +3615,7 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
         <v>1.32</v>
@@ -3609,10 +3624,10 @@
         <v>1.88</v>
       </c>
       <c r="Q12">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R12">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S12">
         <v>3.3</v>
@@ -3627,7 +3642,7 @@
         <v>1.52</v>
       </c>
       <c r="W12">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X12">
         <v>16</v>
@@ -3636,10 +3651,10 @@
         <v>12</v>
       </c>
       <c r="Z12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB12">
         <v>11.5</v>
@@ -3648,13 +3663,13 @@
         <v>8</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE12">
         <v>34</v>
       </c>
       <c r="AF12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG12">
         <v>13</v>
@@ -3678,10 +3693,10 @@
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP12">
         <v>12</v>
@@ -3693,7 +3708,7 @@
         <v>16</v>
       </c>
       <c r="AS12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT12">
         <v>9.800000000000001</v>
@@ -3705,7 +3720,7 @@
         <v>11</v>
       </c>
       <c r="AW12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX12">
         <v>15.5</v>
@@ -3717,19 +3732,19 @@
         <v>15</v>
       </c>
       <c r="BA12">
+        <v>8</v>
+      </c>
+      <c r="BB12">
         <v>7.6</v>
       </c>
-      <c r="BB12">
-        <v>7.4</v>
-      </c>
       <c r="BC12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF12">
         <v>20</v>
@@ -3759,7 +3774,7 @@
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="BP12">
         <v>1000</v>
@@ -3798,7 +3813,7 @@
         <v>2.54</v>
       </c>
       <c r="CB12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3806,31 +3821,31 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H13">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3842,22 +3857,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="R13">
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3866,10 +3881,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4040,7 +4055,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4048,16 +4063,16 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F14">
         <v>3.05</v>
@@ -4066,7 +4081,7 @@
         <v>3.4</v>
       </c>
       <c r="H14">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I14">
         <v>2.46</v>
@@ -4225,19 +4240,19 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BJ14">
         <v>12.5</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BN14">
         <v>8.800000000000001</v>
@@ -4249,13 +4264,13 @@
         <v>32</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BR14">
         <v>46</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BT14">
         <v>7.4</v>
@@ -4267,22 +4282,22 @@
         <v>23</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BX14">
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BZ14">
         <v>30</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="CB14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4290,19 +4305,19 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F15">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G15">
         <v>3.5</v>
@@ -4317,7 +4332,7 @@
         <v>3.2</v>
       </c>
       <c r="K15">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4524,7 +4539,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4532,22 +4547,22 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F16">
         <v>2.3</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H16">
         <v>1.33</v>
@@ -4568,13 +4583,13 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>5.1</v>
+        <v>1.26</v>
       </c>
       <c r="O16">
         <v>1.16</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q16">
         <v>1.16</v>
@@ -4592,10 +4607,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4766,7 +4781,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4774,16 +4789,16 @@
         <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F17">
         <v>1.17</v>
@@ -4795,10 +4810,10 @@
         <v>15.5</v>
       </c>
       <c r="I17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="K17">
         <v>10.5</v>
@@ -4834,7 +4849,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W17">
         <v>5.1</v>
@@ -4921,7 +4936,7 @@
         <v>1.48</v>
       </c>
       <c r="AY17">
-        <v>1.51</v>
+        <v>2.6</v>
       </c>
       <c r="AZ17">
         <v>1.6</v>
@@ -4951,64 +4966,64 @@
         <v>6.2</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ17">
         <v>14</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN17">
         <v>4.2</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP17">
         <v>6.4</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BR17">
         <v>20</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT17">
         <v>19.5</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17">
         <v>6.8</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB17" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5016,241 +5031,241 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F18">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="G18">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="H18">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I18">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="J18">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="K18">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="L18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="O18">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="P18">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="Q18">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="R18">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="S18">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="T18">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="U18">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="V18">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W18">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X18">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AA18">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
+        <v>23</v>
+      </c>
+      <c r="AC18">
+        <v>40</v>
+      </c>
+      <c r="AD18">
+        <v>120</v>
+      </c>
+      <c r="AE18">
+        <v>520</v>
+      </c>
+      <c r="AF18">
+        <v>14</v>
+      </c>
+      <c r="AG18">
+        <v>17.5</v>
+      </c>
+      <c r="AH18">
+        <v>55</v>
+      </c>
+      <c r="AI18">
+        <v>300</v>
+      </c>
+      <c r="AJ18">
+        <v>10.5</v>
+      </c>
+      <c r="AK18">
+        <v>15</v>
+      </c>
+      <c r="AL18">
+        <v>38</v>
+      </c>
+      <c r="AM18">
+        <v>190</v>
+      </c>
+      <c r="AN18">
+        <v>1.97</v>
+      </c>
+      <c r="AO18">
+        <v>430</v>
+      </c>
+      <c r="AP18">
+        <v>34</v>
+      </c>
+      <c r="AQ18">
+        <v>42</v>
+      </c>
+      <c r="AR18">
         <v>20</v>
       </c>
-      <c r="AC18">
-        <v>20</v>
-      </c>
-      <c r="AD18">
-        <v>46</v>
-      </c>
-      <c r="AE18">
-        <v>140</v>
-      </c>
-      <c r="AF18">
-        <v>13.5</v>
-      </c>
-      <c r="AG18">
-        <v>12.5</v>
-      </c>
-      <c r="AH18">
-        <v>26</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>13</v>
-      </c>
-      <c r="AK18">
-        <v>13</v>
-      </c>
-      <c r="AL18">
-        <v>25</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>2.76</v>
-      </c>
-      <c r="AO18">
-        <v>90</v>
-      </c>
-      <c r="AP18">
-        <v>48</v>
-      </c>
-      <c r="AQ18">
+      <c r="AS18">
+        <v>21</v>
+      </c>
+      <c r="AT18">
+        <v>19</v>
+      </c>
+      <c r="AU18">
         <v>32</v>
-      </c>
-      <c r="AR18">
-        <v>44</v>
-      </c>
-      <c r="AS18">
-        <v>55</v>
-      </c>
-      <c r="AT18">
-        <v>17.5</v>
-      </c>
-      <c r="AU18">
-        <v>17.5</v>
       </c>
       <c r="AV18">
         <v>40</v>
       </c>
       <c r="AW18">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AX18">
         <v>12</v>
       </c>
       <c r="AY18">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ18">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="BA18">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB18">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BC18">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD18">
+        <v>24</v>
+      </c>
+      <c r="BE18">
+        <v>46</v>
+      </c>
+      <c r="BF18">
+        <v>1.9</v>
+      </c>
+      <c r="BG18">
+        <v>20</v>
+      </c>
+      <c r="BH18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI18">
+        <v>7.2</v>
+      </c>
+      <c r="BJ18">
+        <v>17</v>
+      </c>
+      <c r="BK18">
+        <v>12</v>
+      </c>
+      <c r="BL18">
+        <v>140</v>
+      </c>
+      <c r="BM18">
         <v>21</v>
       </c>
-      <c r="BE18">
-        <v>34</v>
-      </c>
-      <c r="BF18">
-        <v>2.68</v>
-      </c>
-      <c r="BG18">
-        <v>38</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>4.7</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>7.4</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>19</v>
-      </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO18">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BQ18">
         <v>5.1</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS18">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BU18">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BW18">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="CA18">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="CB18" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5258,241 +5273,241 @@
         <v>90</v>
       </c>
       <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19">
+        <v>1.26</v>
+      </c>
+      <c r="G19">
+        <v>1.28</v>
+      </c>
+      <c r="H19">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>13</v>
+      </c>
+      <c r="J19">
+        <v>7.6</v>
+      </c>
+      <c r="K19">
+        <v>7.8</v>
+      </c>
+      <c r="L19">
+        <v>1.17</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>11.5</v>
+      </c>
+      <c r="O19">
+        <v>1.09</v>
+      </c>
+      <c r="P19">
+        <v>4.3</v>
+      </c>
+      <c r="Q19">
+        <v>1.28</v>
+      </c>
+      <c r="R19">
+        <v>2.36</v>
+      </c>
+      <c r="S19">
+        <v>1.69</v>
+      </c>
+      <c r="T19">
+        <v>1.66</v>
+      </c>
+      <c r="U19">
+        <v>2.42</v>
+      </c>
+      <c r="V19">
+        <v>1.08</v>
+      </c>
+      <c r="W19">
+        <v>4.6</v>
+      </c>
+      <c r="X19">
+        <v>60</v>
+      </c>
+      <c r="Y19">
+        <v>75</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>410</v>
+      </c>
+      <c r="AB19">
+        <v>20</v>
+      </c>
+      <c r="AC19">
+        <v>20</v>
+      </c>
+      <c r="AD19">
+        <v>46</v>
+      </c>
+      <c r="AE19">
+        <v>140</v>
+      </c>
+      <c r="AF19">
+        <v>13.5</v>
+      </c>
+      <c r="AG19">
+        <v>12.5</v>
+      </c>
+      <c r="AH19">
+        <v>26</v>
+      </c>
+      <c r="AI19">
         <v>95</v>
       </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" t="s">
-        <v>163</v>
-      </c>
-      <c r="F19">
-        <v>1.1</v>
-      </c>
-      <c r="G19">
-        <v>1.11</v>
-      </c>
-      <c r="H19">
-        <v>30</v>
-      </c>
-      <c r="I19">
+      <c r="AJ19">
+        <v>13</v>
+      </c>
+      <c r="AK19">
+        <v>13</v>
+      </c>
+      <c r="AL19">
+        <v>25</v>
+      </c>
+      <c r="AM19">
+        <v>80</v>
+      </c>
+      <c r="AN19">
+        <v>2.76</v>
+      </c>
+      <c r="AO19">
+        <v>90</v>
+      </c>
+      <c r="AP19">
+        <v>50</v>
+      </c>
+      <c r="AQ19">
         <v>32</v>
       </c>
-      <c r="J19">
-        <v>15.5</v>
-      </c>
-      <c r="K19">
-        <v>16</v>
-      </c>
-      <c r="L19">
-        <v>1.14</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>14</v>
-      </c>
-      <c r="O19">
-        <v>1.06</v>
-      </c>
-      <c r="P19">
-        <v>5.5</v>
-      </c>
-      <c r="Q19">
-        <v>1.21</v>
-      </c>
-      <c r="R19">
-        <v>2.8</v>
-      </c>
-      <c r="S19">
-        <v>1.51</v>
-      </c>
-      <c r="T19">
-        <v>1.97</v>
-      </c>
-      <c r="U19">
-        <v>1.99</v>
-      </c>
-      <c r="V19">
-        <v>1.03</v>
-      </c>
-      <c r="W19">
-        <v>10</v>
-      </c>
-      <c r="X19">
-        <v>95</v>
-      </c>
-      <c r="Y19">
-        <v>170</v>
-      </c>
-      <c r="Z19">
-        <v>460</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>23</v>
-      </c>
-      <c r="AC19">
-        <v>42</v>
-      </c>
-      <c r="AD19">
-        <v>120</v>
-      </c>
-      <c r="AE19">
-        <v>400</v>
-      </c>
-      <c r="AF19">
-        <v>14</v>
-      </c>
-      <c r="AG19">
+      <c r="AR19">
+        <v>44</v>
+      </c>
+      <c r="AS19">
+        <v>55</v>
+      </c>
+      <c r="AT19">
         <v>17.5</v>
       </c>
-      <c r="AH19">
-        <v>55</v>
-      </c>
-      <c r="AI19">
-        <v>230</v>
-      </c>
-      <c r="AJ19">
-        <v>10.5</v>
-      </c>
-      <c r="AK19">
-        <v>15</v>
-      </c>
-      <c r="AL19">
-        <v>38</v>
-      </c>
-      <c r="AM19">
-        <v>190</v>
-      </c>
-      <c r="AN19">
-        <v>1.97</v>
-      </c>
-      <c r="AO19">
-        <v>350</v>
-      </c>
-      <c r="AP19">
-        <v>34</v>
-      </c>
-      <c r="AQ19">
-        <v>42</v>
-      </c>
-      <c r="AR19">
-        <v>20</v>
-      </c>
-      <c r="AS19">
-        <v>21</v>
-      </c>
-      <c r="AT19">
-        <v>18</v>
-      </c>
       <c r="AU19">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AV19">
         <v>38</v>
       </c>
       <c r="AW19">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AX19">
         <v>12</v>
       </c>
       <c r="AY19">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BA19">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BB19">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC19">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BD19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE19">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BF19">
-        <v>1.9</v>
+        <v>2.68</v>
       </c>
       <c r="BG19">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BH19">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BI19">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BL19">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP19">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
         <v>5.1</v>
       </c>
       <c r="BR19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BT19">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="BV19">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5500,28 +5515,28 @@
         <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F20">
         <v>1.27</v>
       </c>
       <c r="G20">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H20">
         <v>10.5</v>
       </c>
       <c r="I20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -5536,7 +5551,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O20">
         <v>1.11</v>
@@ -5545,133 +5560,133 @@
         <v>3.55</v>
       </c>
       <c r="Q20">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R20">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="T20">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB20">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD20">
         <v>44</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF20">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AG20">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ20">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AK20">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN20">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP20">
-        <v>2.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ20">
-        <v>2.14</v>
+        <v>9</v>
       </c>
       <c r="AR20">
-        <v>2.28</v>
+        <v>9.4</v>
       </c>
       <c r="AS20">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="AT20">
+        <v>14</v>
+      </c>
+      <c r="AU20">
+        <v>15.5</v>
+      </c>
+      <c r="AV20">
+        <v>8.4</v>
+      </c>
+      <c r="AW20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX20">
+        <v>10</v>
+      </c>
+      <c r="AY20">
         <v>10.5</v>
       </c>
-      <c r="AU20">
-        <v>2.28</v>
-      </c>
-      <c r="AV20">
-        <v>2.04</v>
-      </c>
-      <c r="AW20">
-        <v>2.14</v>
-      </c>
-      <c r="AX20">
+      <c r="AZ20">
+        <v>7.6</v>
+      </c>
+      <c r="BA20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB20">
+        <v>10.5</v>
+      </c>
+      <c r="BC20">
+        <v>11.5</v>
+      </c>
+      <c r="BD20">
         <v>8</v>
       </c>
-      <c r="AY20">
-        <v>10</v>
-      </c>
-      <c r="AZ20">
-        <v>2.14</v>
-      </c>
-      <c r="BA20">
-        <v>2.14</v>
-      </c>
-      <c r="BB20">
-        <v>10</v>
-      </c>
-      <c r="BC20">
-        <v>11</v>
-      </c>
-      <c r="BD20">
-        <v>2.14</v>
-      </c>
       <c r="BE20">
-        <v>2.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="BG20">
-        <v>2.14</v>
+        <v>9.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5734,7 +5749,7 @@
         <v>1.37</v>
       </c>
       <c r="CB20" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5742,16 +5757,16 @@
         <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F21">
         <v>3.5</v>
@@ -5769,7 +5784,7 @@
         <v>3.45</v>
       </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L21">
         <v>1.29</v>
@@ -5784,7 +5799,7 @@
         <v>1.31</v>
       </c>
       <c r="P21">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q21">
         <v>1.89</v>
@@ -5895,22 +5910,22 @@
         <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="BB21">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="BC21">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="BD21">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="BE21">
-        <v>60</v>
+        <v>7.2</v>
       </c>
       <c r="BF21">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="BG21">
         <v>13.5</v>
@@ -5976,7 +5991,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5984,16 +5999,16 @@
         <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F22">
         <v>3.05</v>
@@ -6002,7 +6017,7 @@
         <v>3.25</v>
       </c>
       <c r="H22">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I22">
         <v>3.05</v>
@@ -6017,13 +6032,13 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="N22">
         <v>2.28</v>
       </c>
       <c r="O22">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P22">
         <v>1.42</v>
@@ -6167,58 +6182,58 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="CB22" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6226,22 +6241,22 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F23">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="H23">
         <v>1.43</v>
@@ -6250,7 +6265,7 @@
         <v>1.48</v>
       </c>
       <c r="J23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K23">
         <v>4.9</v>
@@ -6259,7 +6274,7 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
         <v>3.3</v>
@@ -6268,7 +6283,7 @@
         <v>1.39</v>
       </c>
       <c r="P23">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q23">
         <v>2.14</v>
@@ -6283,13 +6298,13 @@
         <v>2.4</v>
       </c>
       <c r="U23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V23">
         <v>3.05</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>16</v>
@@ -6301,7 +6316,7 @@
         <v>7.2</v>
       </c>
       <c r="AA23">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AB23">
         <v>25</v>
@@ -6310,7 +6325,7 @@
         <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE23">
         <v>22</v>
@@ -6328,7 +6343,7 @@
         <v>65</v>
       </c>
       <c r="AJ23">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AK23">
         <v>270</v>
@@ -6340,7 +6355,7 @@
         <v>320</v>
       </c>
       <c r="AN23">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AO23">
         <v>10.5</v>
@@ -6370,31 +6385,31 @@
         <v>15.5</v>
       </c>
       <c r="AX23">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY23">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AZ23">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA23">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB23">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC23">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD23">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE23">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF23">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG23">
         <v>8.4</v>
@@ -6403,64 +6418,64 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BJ23">
         <v>19</v>
       </c>
       <c r="BK23">
-        <v>8</v>
+        <v>1.65</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BN23">
         <v>18.5</v>
       </c>
       <c r="BO23">
-        <v>8</v>
+        <v>1.64</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BT23">
         <v>4.9</v>
       </c>
       <c r="BU23">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="BV23">
         <v>13</v>
       </c>
       <c r="BW23">
-        <v>5.6</v>
+        <v>1.58</v>
       </c>
       <c r="BX23">
         <v>46</v>
       </c>
       <c r="BY23">
-        <v>18.5</v>
+        <v>1.73</v>
       </c>
       <c r="BZ23">
         <v>30</v>
       </c>
       <c r="CA23">
-        <v>12.5</v>
+        <v>1.7</v>
       </c>
       <c r="CB23" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6468,16 +6483,16 @@
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F24">
         <v>2.04</v>
@@ -6489,7 +6504,7 @@
         <v>3.45</v>
       </c>
       <c r="I24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J24">
         <v>3.85</v>
@@ -6513,22 +6528,22 @@
         <v>2.32</v>
       </c>
       <c r="Q24">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="R24">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S24">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
         <v>1.84</v>
@@ -6573,7 +6588,7 @@
         <v>38</v>
       </c>
       <c r="AK24">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL24">
         <v>44</v>
@@ -6588,7 +6603,7 @@
         <v>44</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
         <v>10.5</v>
@@ -6597,7 +6612,7 @@
         <v>16.5</v>
       </c>
       <c r="AS24">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
         <v>7.8</v>
@@ -6609,7 +6624,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW24">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
         <v>9.199999999999999</v>
@@ -6621,7 +6636,7 @@
         <v>9.6</v>
       </c>
       <c r="BA24">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
         <v>15.5</v>
@@ -6633,7 +6648,7 @@
         <v>17.5</v>
       </c>
       <c r="BE24">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
         <v>7.2</v>
@@ -6702,7 +6717,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6710,16 +6725,16 @@
         <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F25">
         <v>1.97</v>
@@ -6758,7 +6773,7 @@
         <v>1.57</v>
       </c>
       <c r="R25">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S25">
         <v>2.38</v>
@@ -6830,52 +6845,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -6944,7 +6959,7 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6952,22 +6967,22 @@
         <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F26">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H26">
         <v>3.25</v>
@@ -6988,40 +7003,40 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P26">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
         <v>1.79</v>
       </c>
       <c r="R26">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S26">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="T26">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U26">
         <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X26">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Y26">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
         <v>1000</v>
@@ -7033,16 +7048,16 @@
         <v>1000</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD26">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
         <v>44</v>
       </c>
       <c r="AF26">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
         <v>1000</v>
@@ -7066,61 +7081,61 @@
         <v>90</v>
       </c>
       <c r="AN26">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
         <v>36</v>
       </c>
       <c r="AP26">
-        <v>11</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>9.6</v>
+        <v>1.42</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="AS26">
-        <v>32</v>
+        <v>1.42</v>
       </c>
       <c r="AT26">
-        <v>8</v>
+        <v>1.42</v>
       </c>
       <c r="AU26">
-        <v>7.4</v>
+        <v>1.28</v>
       </c>
       <c r="AV26">
-        <v>9.4</v>
+        <v>1.42</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AX26">
-        <v>9.800000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="AY26">
-        <v>7.8</v>
+        <v>1.42</v>
       </c>
       <c r="AZ26">
-        <v>10.5</v>
+        <v>1.31</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BC26">
         <v>17.5</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BF26">
-        <v>9.4</v>
+        <v>1.42</v>
       </c>
       <c r="BG26">
         <v>17.5</v>
@@ -7129,64 +7144,64 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="BJ26">
         <v>12.5</v>
       </c>
       <c r="BK26">
-        <v>5.9</v>
+        <v>1.69</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>21</v>
+        <v>1.96</v>
       </c>
       <c r="BN26">
         <v>7</v>
       </c>
       <c r="BO26">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP26">
         <v>22</v>
       </c>
       <c r="BQ26">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="BR26">
         <v>38</v>
       </c>
       <c r="BS26">
-        <v>16.5</v>
+        <v>1.86</v>
       </c>
       <c r="BT26">
         <v>9</v>
       </c>
       <c r="BU26">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV26">
         <v>34</v>
       </c>
       <c r="BW26">
-        <v>15.5</v>
+        <v>1.85</v>
       </c>
       <c r="BX26">
         <v>48</v>
       </c>
       <c r="BY26">
-        <v>21</v>
+        <v>1.88</v>
       </c>
       <c r="BZ26">
         <v>30</v>
       </c>
       <c r="CA26">
-        <v>14</v>
+        <v>1.84</v>
       </c>
       <c r="CB26" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7194,16 +7209,16 @@
         <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F27">
         <v>1.83</v>
@@ -7314,52 +7329,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
         <v>1.01</v>
@@ -7428,7 +7443,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7436,28 +7451,28 @@
         <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F28">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G28">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H28">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="I28">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="J28">
         <v>3.85</v>
@@ -7466,211 +7481,211 @@
         <v>4.2</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P28">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q28">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="CB28" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7678,28 +7693,28 @@
         <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F29">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G29">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="H29">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="I29">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J29">
         <v>7.4</v>
@@ -7708,211 +7723,211 @@
         <v>8.6</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P29">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="CB29" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7920,16 +7935,16 @@
         <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F30">
         <v>3.1</v>
@@ -7938,7 +7953,7 @@
         <v>3.2</v>
       </c>
       <c r="H30">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I30">
         <v>2.54</v>
@@ -7950,211 +7965,211 @@
         <v>3.6</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P30">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q30">
         <v>2</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="CB30" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8162,25 +8177,25 @@
         <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F31">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G31">
         <v>2.08</v>
       </c>
       <c r="H31">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I31">
         <v>3.9</v>
@@ -8189,456 +8204,456 @@
         <v>3.8</v>
       </c>
       <c r="K31">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P31">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q31">
         <v>1.86</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="CB31" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
         <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F32">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="G32">
+        <v>1.36</v>
+      </c>
+      <c r="H32">
+        <v>9.6</v>
+      </c>
+      <c r="I32">
+        <v>10.5</v>
+      </c>
+      <c r="J32">
+        <v>5.8</v>
+      </c>
+      <c r="K32">
+        <v>6.4</v>
+      </c>
+      <c r="L32">
+        <v>1.23</v>
+      </c>
+      <c r="M32">
+        <v>1.03</v>
+      </c>
+      <c r="N32">
+        <v>6.2</v>
+      </c>
+      <c r="O32">
+        <v>1.16</v>
+      </c>
+      <c r="P32">
+        <v>2.88</v>
+      </c>
+      <c r="Q32">
+        <v>1.49</v>
+      </c>
+      <c r="R32">
+        <v>1.76</v>
+      </c>
+      <c r="S32">
+        <v>2.2</v>
+      </c>
+      <c r="T32">
+        <v>1.81</v>
+      </c>
+      <c r="U32">
+        <v>2.1</v>
+      </c>
+      <c r="V32">
+        <v>1.1</v>
+      </c>
+      <c r="W32">
+        <v>3.7</v>
+      </c>
+      <c r="X32">
+        <v>34</v>
+      </c>
+      <c r="Y32">
+        <v>50</v>
+      </c>
+      <c r="Z32">
+        <v>120</v>
+      </c>
+      <c r="AA32">
+        <v>370</v>
+      </c>
+      <c r="AB32">
+        <v>12.5</v>
+      </c>
+      <c r="AC32">
+        <v>14</v>
+      </c>
+      <c r="AD32">
+        <v>44</v>
+      </c>
+      <c r="AE32">
+        <v>150</v>
+      </c>
+      <c r="AF32">
+        <v>10.5</v>
+      </c>
+      <c r="AG32">
+        <v>11.5</v>
+      </c>
+      <c r="AH32">
+        <v>27</v>
+      </c>
+      <c r="AI32">
+        <v>120</v>
+      </c>
+      <c r="AJ32">
+        <v>12</v>
+      </c>
+      <c r="AK32">
+        <v>14</v>
+      </c>
+      <c r="AL32">
+        <v>36</v>
+      </c>
+      <c r="AM32">
+        <v>130</v>
+      </c>
+      <c r="AN32">
+        <v>4.3</v>
+      </c>
+      <c r="AO32">
+        <v>150</v>
+      </c>
+      <c r="AP32">
+        <v>7.8</v>
+      </c>
+      <c r="AQ32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR32">
+        <v>9.4</v>
+      </c>
+      <c r="AS32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT32">
+        <v>10.5</v>
+      </c>
+      <c r="AU32">
+        <v>12.5</v>
+      </c>
+      <c r="AV32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW32">
+        <v>9.4</v>
+      </c>
+      <c r="AX32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ32">
+        <v>21</v>
+      </c>
+      <c r="BA32">
+        <v>9.4</v>
+      </c>
+      <c r="BB32">
+        <v>10.5</v>
+      </c>
+      <c r="BC32">
+        <v>11.5</v>
+      </c>
+      <c r="BD32">
+        <v>7.8</v>
+      </c>
+      <c r="BE32">
+        <v>9.4</v>
+      </c>
+      <c r="BF32">
+        <v>4</v>
+      </c>
+      <c r="BG32">
+        <v>9.4</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>2.26</v>
+      </c>
+      <c r="BJ32">
+        <v>15.5</v>
+      </c>
+      <c r="BK32">
+        <v>6.8</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>2.26</v>
+      </c>
+      <c r="BN32">
+        <v>4.6</v>
+      </c>
+      <c r="BO32">
         <v>3.4</v>
       </c>
-      <c r="H32">
-        <v>2.36</v>
-      </c>
-      <c r="I32">
-        <v>2.42</v>
-      </c>
-      <c r="J32">
+      <c r="BP32">
+        <v>10.5</v>
+      </c>
+      <c r="BQ32">
+        <v>5.6</v>
+      </c>
+      <c r="BR32">
+        <v>29</v>
+      </c>
+      <c r="BS32">
+        <v>3.55</v>
+      </c>
+      <c r="BT32">
+        <v>19</v>
+      </c>
+      <c r="BU32">
         <v>3.45</v>
       </c>
-      <c r="K32">
-        <v>3.55</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>1.92</v>
-      </c>
-      <c r="Q32">
-        <v>2</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
-      <c r="BC32">
-        <v>0</v>
-      </c>
-      <c r="BD32">
-        <v>0</v>
-      </c>
-      <c r="BE32">
-        <v>0</v>
-      </c>
-      <c r="BF32">
-        <v>0</v>
-      </c>
-      <c r="BG32">
-        <v>0</v>
-      </c>
-      <c r="BH32">
-        <v>0</v>
-      </c>
-      <c r="BI32">
-        <v>0</v>
-      </c>
-      <c r="BJ32">
-        <v>0</v>
-      </c>
-      <c r="BK32">
-        <v>0</v>
-      </c>
-      <c r="BL32">
-        <v>0</v>
-      </c>
-      <c r="BM32">
-        <v>0</v>
-      </c>
-      <c r="BN32">
-        <v>0</v>
-      </c>
-      <c r="BO32">
-        <v>0</v>
-      </c>
-      <c r="BP32">
-        <v>0</v>
-      </c>
-      <c r="BQ32">
-        <v>0</v>
-      </c>
-      <c r="BR32">
-        <v>0</v>
-      </c>
-      <c r="BS32">
-        <v>0</v>
-      </c>
-      <c r="BT32">
-        <v>0</v>
-      </c>
-      <c r="BU32">
-        <v>0</v>
-      </c>
       <c r="BV32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CA32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="CB32" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8646,241 +8661,241 @@
         <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F33">
-        <v>1.06</v>
+        <v>1.75</v>
       </c>
       <c r="G33">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="H33">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I33">
-        <v>65</v>
+        <v>5.2</v>
       </c>
       <c r="J33">
+        <v>4.2</v>
+      </c>
+      <c r="K33">
+        <v>4.3</v>
+      </c>
+      <c r="L33">
+        <v>1.29</v>
+      </c>
+      <c r="M33">
+        <v>1.04</v>
+      </c>
+      <c r="N33">
+        <v>5.4</v>
+      </c>
+      <c r="O33">
+        <v>1.2</v>
+      </c>
+      <c r="P33">
+        <v>2.52</v>
+      </c>
+      <c r="Q33">
+        <v>1.63</v>
+      </c>
+      <c r="R33">
+        <v>1.59</v>
+      </c>
+      <c r="S33">
+        <v>2.56</v>
+      </c>
+      <c r="T33">
+        <v>1.65</v>
+      </c>
+      <c r="U33">
+        <v>2.46</v>
+      </c>
+      <c r="V33">
+        <v>1.23</v>
+      </c>
+      <c r="W33">
+        <v>2.3</v>
+      </c>
+      <c r="X33">
+        <v>23</v>
+      </c>
+      <c r="Y33">
         <v>24</v>
       </c>
-      <c r="K33">
+      <c r="Z33">
+        <v>42</v>
+      </c>
+      <c r="AA33">
+        <v>130</v>
+      </c>
+      <c r="AB33">
+        <v>12</v>
+      </c>
+      <c r="AC33">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD33">
+        <v>19</v>
+      </c>
+      <c r="AE33">
+        <v>55</v>
+      </c>
+      <c r="AF33">
+        <v>12.5</v>
+      </c>
+      <c r="AG33">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH33">
+        <v>17</v>
+      </c>
+      <c r="AI33">
+        <v>55</v>
+      </c>
+      <c r="AJ33">
+        <v>19</v>
+      </c>
+      <c r="AK33">
+        <v>16</v>
+      </c>
+      <c r="AL33">
+        <v>27</v>
+      </c>
+      <c r="AM33">
+        <v>75</v>
+      </c>
+      <c r="AN33">
+        <v>7.8</v>
+      </c>
+      <c r="AO33">
+        <v>46</v>
+      </c>
+      <c r="AP33">
+        <v>20</v>
+      </c>
+      <c r="AQ33">
+        <v>22</v>
+      </c>
+      <c r="AR33">
+        <v>38</v>
+      </c>
+      <c r="AS33">
+        <v>80</v>
+      </c>
+      <c r="AT33">
+        <v>11</v>
+      </c>
+      <c r="AU33">
+        <v>9</v>
+      </c>
+      <c r="AV33">
+        <v>17.5</v>
+      </c>
+      <c r="AW33">
+        <v>48</v>
+      </c>
+      <c r="AX33">
+        <v>11.5</v>
+      </c>
+      <c r="AY33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ33">
+        <v>15</v>
+      </c>
+      <c r="BA33">
+        <v>46</v>
+      </c>
+      <c r="BB33">
+        <v>17</v>
+      </c>
+      <c r="BC33">
+        <v>14.5</v>
+      </c>
+      <c r="BD33">
+        <v>24</v>
+      </c>
+      <c r="BE33">
+        <v>60</v>
+      </c>
+      <c r="BF33">
+        <v>7.2</v>
+      </c>
+      <c r="BG33">
+        <v>27</v>
+      </c>
+      <c r="BH33">
+        <v>4.1</v>
+      </c>
+      <c r="BI33">
+        <v>3.85</v>
+      </c>
+      <c r="BJ33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK33">
+        <v>8</v>
+      </c>
+      <c r="BL33">
+        <v>110</v>
+      </c>
+      <c r="BM33">
+        <v>21</v>
+      </c>
+      <c r="BN33">
+        <v>4.7</v>
+      </c>
+      <c r="BO33">
+        <v>4.3</v>
+      </c>
+      <c r="BP33">
+        <v>13.5</v>
+      </c>
+      <c r="BQ33">
+        <v>10</v>
+      </c>
+      <c r="BR33">
+        <v>26</v>
+      </c>
+      <c r="BS33">
+        <v>16</v>
+      </c>
+      <c r="BT33">
+        <v>8.4</v>
+      </c>
+      <c r="BU33">
+        <v>7.4</v>
+      </c>
+      <c r="BV33">
+        <v>44</v>
+      </c>
+      <c r="BW33">
         <v>25</v>
       </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>1.01</v>
-      </c>
-      <c r="N33">
-        <v>13.5</v>
-      </c>
-      <c r="O33">
-        <v>1.06</v>
-      </c>
-      <c r="P33">
-        <v>5.2</v>
-      </c>
-      <c r="Q33">
-        <v>1.21</v>
-      </c>
-      <c r="R33">
-        <v>2.74</v>
-      </c>
-      <c r="S33">
-        <v>1.53</v>
-      </c>
-      <c r="T33">
-        <v>2.8</v>
-      </c>
-      <c r="U33">
-        <v>1.53</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>1000</v>
-      </c>
-      <c r="Y33">
-        <v>1000</v>
-      </c>
-      <c r="Z33">
-        <v>1000</v>
-      </c>
-      <c r="AA33">
-        <v>1000</v>
-      </c>
-      <c r="AB33">
-        <v>22</v>
-      </c>
-      <c r="AC33">
-        <v>80</v>
-      </c>
-      <c r="AD33">
-        <v>1000</v>
-      </c>
-      <c r="AE33">
-        <v>1000</v>
-      </c>
-      <c r="AF33">
-        <v>11.5</v>
-      </c>
-      <c r="AG33">
+      <c r="BX33">
+        <v>48</v>
+      </c>
+      <c r="BY33">
         <v>27</v>
       </c>
-      <c r="AH33">
-        <v>1000</v>
-      </c>
-      <c r="AI33">
-        <v>1000</v>
-      </c>
-      <c r="AJ33">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AK33">
-        <v>20</v>
-      </c>
-      <c r="AL33">
-        <v>85</v>
-      </c>
-      <c r="AM33">
-        <v>1000</v>
-      </c>
-      <c r="AN33">
-        <v>1.84</v>
-      </c>
-      <c r="AO33">
-        <v>1000</v>
-      </c>
-      <c r="AP33">
-        <v>38</v>
-      </c>
-      <c r="AQ33">
-        <v>44</v>
-      </c>
-      <c r="AR33">
-        <v>60</v>
-      </c>
-      <c r="AS33">
-        <v>60</v>
-      </c>
-      <c r="AT33">
-        <v>18</v>
-      </c>
-      <c r="AU33">
-        <v>28</v>
-      </c>
-      <c r="AV33">
-        <v>44</v>
-      </c>
-      <c r="AW33">
-        <v>60</v>
-      </c>
-      <c r="AX33">
-        <v>9.6</v>
-      </c>
-      <c r="AY33">
-        <v>21</v>
-      </c>
-      <c r="AZ33">
-        <v>38</v>
-      </c>
-      <c r="BA33">
-        <v>15</v>
-      </c>
-      <c r="BB33">
-        <v>7.2</v>
-      </c>
-      <c r="BC33">
-        <v>16.5</v>
-      </c>
-      <c r="BD33">
-        <v>36</v>
-      </c>
-      <c r="BE33">
-        <v>55</v>
-      </c>
-      <c r="BF33">
-        <v>1.78</v>
-      </c>
-      <c r="BG33">
-        <v>60</v>
-      </c>
-      <c r="BH33">
-        <v>8</v>
-      </c>
-      <c r="BI33">
-        <v>6.6</v>
-      </c>
-      <c r="BJ33">
-        <v>21</v>
-      </c>
-      <c r="BK33">
-        <v>15</v>
-      </c>
-      <c r="BL33">
-        <v>1000</v>
-      </c>
-      <c r="BM33">
-        <v>1.01</v>
-      </c>
-      <c r="BN33">
-        <v>4.4</v>
-      </c>
-      <c r="BO33">
-        <v>3.75</v>
-      </c>
-      <c r="BP33">
-        <v>5.1</v>
-      </c>
-      <c r="BQ33">
-        <v>4.3</v>
-      </c>
-      <c r="BR33">
-        <v>24</v>
-      </c>
-      <c r="BS33">
-        <v>17.5</v>
-      </c>
-      <c r="BT33">
-        <v>36</v>
-      </c>
-      <c r="BU33">
-        <v>26</v>
-      </c>
-      <c r="BV33">
-        <v>1000</v>
-      </c>
-      <c r="BW33">
-        <v>1.01</v>
-      </c>
-      <c r="BX33">
-        <v>1000</v>
-      </c>
-      <c r="BY33">
-        <v>1.01</v>
-      </c>
       <c r="BZ33">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="CA33">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="CB33" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8888,16 +8903,16 @@
         <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F34">
         <v>5.2</v>
@@ -8909,16 +8924,16 @@
         <v>1.8</v>
       </c>
       <c r="I34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J34">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K34">
         <v>3.9</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M34">
         <v>1.07</v>
@@ -8930,7 +8945,7 @@
         <v>1.34</v>
       </c>
       <c r="P34">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q34">
         <v>2.02</v>
@@ -8948,13 +8963,13 @@
         <v>2.02</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -8972,13 +8987,13 @@
         <v>8.4</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE34">
         <v>19.5</v>
       </c>
       <c r="AF34">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG34">
         <v>20</v>
@@ -8987,13 +9002,13 @@
         <v>21</v>
       </c>
       <c r="AI34">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ34">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK34">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL34">
         <v>80</v>
@@ -9002,7 +9017,7 @@
         <v>130</v>
       </c>
       <c r="AN34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO34">
         <v>12.5</v>
@@ -9011,7 +9026,7 @@
         <v>13</v>
       </c>
       <c r="AQ34">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR34">
         <v>9.4</v>
@@ -9020,37 +9035,37 @@
         <v>17</v>
       </c>
       <c r="AT34">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU34">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV34">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW34">
         <v>17.5</v>
       </c>
       <c r="AX34">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AY34">
         <v>18</v>
       </c>
       <c r="AZ34">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA34">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB34">
         <v>40</v>
       </c>
       <c r="BC34">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BD34">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BE34">
         <v>100</v>
@@ -9065,7 +9080,7 @@
         <v>3.65</v>
       </c>
       <c r="BI34">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
@@ -9122,7 +9137,7 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9130,154 +9145,154 @@
         <v>90</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F35">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="G35">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I35">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J35">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K35">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N35">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O35">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P35">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q35">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="R35">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S35">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T35">
         <v>1.65</v>
       </c>
       <c r="U35">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X35">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y35">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z35">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA35">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB35">
         <v>12</v>
       </c>
       <c r="AC35">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD35">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE35">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF35">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH35">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI35">
         <v>55</v>
       </c>
       <c r="AJ35">
+        <v>21</v>
+      </c>
+      <c r="AK35">
+        <v>17.5</v>
+      </c>
+      <c r="AL35">
+        <v>28</v>
+      </c>
+      <c r="AM35">
+        <v>70</v>
+      </c>
+      <c r="AN35">
+        <v>9</v>
+      </c>
+      <c r="AO35">
+        <v>38</v>
+      </c>
+      <c r="AP35">
+        <v>18.5</v>
+      </c>
+      <c r="AQ35">
         <v>19</v>
       </c>
-      <c r="AK35">
-        <v>17</v>
-      </c>
-      <c r="AL35">
-        <v>29</v>
-      </c>
-      <c r="AM35">
-        <v>75</v>
-      </c>
-      <c r="AN35">
-        <v>8</v>
-      </c>
-      <c r="AO35">
-        <v>46</v>
-      </c>
-      <c r="AP35">
-        <v>20</v>
-      </c>
-      <c r="AQ35">
-        <v>19.5</v>
-      </c>
       <c r="AR35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS35">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT35">
         <v>11</v>
       </c>
       <c r="AU35">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV35">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AW35">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AX35">
         <v>12</v>
       </c>
       <c r="AY35">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ35">
         <v>15</v>
@@ -9286,569 +9301,1053 @@
         <v>40</v>
       </c>
       <c r="BB35">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC35">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD35">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BE35">
         <v>32</v>
       </c>
       <c r="BF35">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG35">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BH35">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI35">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="BJ35">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK35">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BL35">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM35">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BN35">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO35">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP35">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BR35">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS35">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BT35">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU35">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV35">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW35">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BX35">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY35">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA35">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F36">
-        <v>1.89</v>
+        <v>6</v>
       </c>
       <c r="G36">
-        <v>1.92</v>
+        <v>6.6</v>
       </c>
       <c r="H36">
-        <v>4.3</v>
+        <v>1.51</v>
       </c>
       <c r="I36">
-        <v>4.5</v>
+        <v>1.54</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K36">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N36">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="P36">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="Q36">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="R36">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="S36">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="T36">
         <v>1.65</v>
       </c>
       <c r="U36">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="Y36">
+        <v>13.5</v>
+      </c>
+      <c r="Z36">
+        <v>12.5</v>
+      </c>
+      <c r="AA36">
+        <v>15</v>
+      </c>
+      <c r="AB36">
+        <v>34</v>
+      </c>
+      <c r="AC36">
+        <v>12.5</v>
+      </c>
+      <c r="AD36">
+        <v>11</v>
+      </c>
+      <c r="AE36">
+        <v>15</v>
+      </c>
+      <c r="AF36">
+        <v>60</v>
+      </c>
+      <c r="AG36">
+        <v>25</v>
+      </c>
+      <c r="AH36">
+        <v>20</v>
+      </c>
+      <c r="AI36">
+        <v>30</v>
+      </c>
+      <c r="AJ36">
+        <v>180</v>
+      </c>
+      <c r="AK36">
+        <v>75</v>
+      </c>
+      <c r="AL36">
+        <v>65</v>
+      </c>
+      <c r="AM36">
+        <v>90</v>
+      </c>
+      <c r="AN36">
+        <v>60</v>
+      </c>
+      <c r="AO36">
+        <v>5.7</v>
+      </c>
+      <c r="AP36">
         <v>21</v>
       </c>
-      <c r="Z36">
-        <v>36</v>
-      </c>
-      <c r="AA36">
-        <v>1000</v>
-      </c>
-      <c r="AB36">
-        <v>12</v>
-      </c>
-      <c r="AC36">
+      <c r="AQ36">
+        <v>11</v>
+      </c>
+      <c r="AR36">
+        <v>10</v>
+      </c>
+      <c r="AS36">
+        <v>13</v>
+      </c>
+      <c r="AT36">
+        <v>21</v>
+      </c>
+      <c r="AU36">
+        <v>10.5</v>
+      </c>
+      <c r="AV36">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW36">
+        <v>12.5</v>
+      </c>
+      <c r="AX36">
         <v>9.4</v>
       </c>
-      <c r="AD36">
-        <v>17.5</v>
-      </c>
-      <c r="AE36">
-        <v>48</v>
-      </c>
-      <c r="AF36">
-        <v>13.5</v>
-      </c>
-      <c r="AG36">
-        <v>10.5</v>
-      </c>
-      <c r="AH36">
-        <v>16</v>
-      </c>
-      <c r="AI36">
-        <v>60</v>
-      </c>
-      <c r="AJ36">
-        <v>21</v>
-      </c>
-      <c r="AK36">
-        <v>18.5</v>
-      </c>
-      <c r="AL36">
-        <v>32</v>
-      </c>
-      <c r="AM36">
-        <v>1000</v>
-      </c>
-      <c r="AN36">
-        <v>9</v>
-      </c>
-      <c r="AO36">
-        <v>46</v>
-      </c>
-      <c r="AP36">
-        <v>18.5</v>
-      </c>
-      <c r="AQ36">
-        <v>17.5</v>
-      </c>
-      <c r="AR36">
-        <v>29</v>
-      </c>
-      <c r="AS36">
-        <v>36</v>
-      </c>
-      <c r="AT36">
-        <v>11</v>
-      </c>
-      <c r="AU36">
-        <v>8.6</v>
-      </c>
-      <c r="AV36">
-        <v>15.5</v>
-      </c>
-      <c r="AW36">
-        <v>38</v>
-      </c>
-      <c r="AX36">
-        <v>12</v>
-      </c>
       <c r="AY36">
+        <v>20</v>
+      </c>
+      <c r="AZ36">
+        <v>16.5</v>
+      </c>
+      <c r="BA36">
+        <v>19</v>
+      </c>
+      <c r="BB36">
         <v>9.6</v>
       </c>
-      <c r="AZ36">
-        <v>14.5</v>
-      </c>
-      <c r="BA36">
-        <v>26</v>
-      </c>
-      <c r="BB36">
-        <v>17.5</v>
-      </c>
       <c r="BC36">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD36">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="BE36">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BF36">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG36">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="BH36">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ36">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK36">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BL36">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM36">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BN36">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO36">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BP36">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BR36">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS36">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BT36">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU36">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="BV36">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW36">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="BX36">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY36">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BZ36">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA36">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
         <v>109</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>3.3</v>
       </c>
       <c r="G37">
+        <v>3.4</v>
+      </c>
+      <c r="H37">
+        <v>2.36</v>
+      </c>
+      <c r="I37">
+        <v>2.42</v>
+      </c>
+      <c r="J37">
+        <v>3.45</v>
+      </c>
+      <c r="K37">
+        <v>3.55</v>
+      </c>
+      <c r="L37">
+        <v>1.39</v>
+      </c>
+      <c r="M37">
+        <v>1.07</v>
+      </c>
+      <c r="N37">
+        <v>3.65</v>
+      </c>
+      <c r="O37">
+        <v>1.33</v>
+      </c>
+      <c r="P37">
+        <v>1.9</v>
+      </c>
+      <c r="Q37">
+        <v>2</v>
+      </c>
+      <c r="R37">
+        <v>1.34</v>
+      </c>
+      <c r="S37">
+        <v>3.65</v>
+      </c>
+      <c r="T37">
+        <v>1.76</v>
+      </c>
+      <c r="U37">
+        <v>2.14</v>
+      </c>
+      <c r="V37">
+        <v>1.7</v>
+      </c>
+      <c r="W37">
+        <v>1.41</v>
+      </c>
+      <c r="X37">
+        <v>13.5</v>
+      </c>
+      <c r="Y37">
+        <v>10.5</v>
+      </c>
+      <c r="Z37">
+        <v>15.5</v>
+      </c>
+      <c r="AA37">
+        <v>34</v>
+      </c>
+      <c r="AB37">
+        <v>13</v>
+      </c>
+      <c r="AC37">
+        <v>7.6</v>
+      </c>
+      <c r="AD37">
+        <v>11.5</v>
+      </c>
+      <c r="AE37">
+        <v>27</v>
+      </c>
+      <c r="AF37">
+        <v>23</v>
+      </c>
+      <c r="AG37">
+        <v>14</v>
+      </c>
+      <c r="AH37">
+        <v>18</v>
+      </c>
+      <c r="AI37">
+        <v>42</v>
+      </c>
+      <c r="AJ37">
+        <v>60</v>
+      </c>
+      <c r="AK37">
+        <v>40</v>
+      </c>
+      <c r="AL37">
+        <v>60</v>
+      </c>
+      <c r="AM37">
+        <v>100</v>
+      </c>
+      <c r="AN37">
+        <v>40</v>
+      </c>
+      <c r="AO37">
+        <v>21</v>
+      </c>
+      <c r="AP37">
+        <v>12.5</v>
+      </c>
+      <c r="AQ37">
+        <v>9.4</v>
+      </c>
+      <c r="AR37">
+        <v>13.5</v>
+      </c>
+      <c r="AS37">
+        <v>28</v>
+      </c>
+      <c r="AT37">
+        <v>11.5</v>
+      </c>
+      <c r="AU37">
+        <v>7.2</v>
+      </c>
+      <c r="AV37">
+        <v>10.5</v>
+      </c>
+      <c r="AW37">
+        <v>23</v>
+      </c>
+      <c r="AX37">
+        <v>20</v>
+      </c>
+      <c r="AY37">
+        <v>12.5</v>
+      </c>
+      <c r="AZ37">
+        <v>16</v>
+      </c>
+      <c r="BA37">
+        <v>34</v>
+      </c>
+      <c r="BB37">
+        <v>50</v>
+      </c>
+      <c r="BC37">
+        <v>34</v>
+      </c>
+      <c r="BD37">
+        <v>42</v>
+      </c>
+      <c r="BE37">
+        <v>36</v>
+      </c>
+      <c r="BF37">
+        <v>30</v>
+      </c>
+      <c r="BG37">
+        <v>17.5</v>
+      </c>
+      <c r="BH37">
+        <v>3.7</v>
+      </c>
+      <c r="BI37">
+        <v>2.82</v>
+      </c>
+      <c r="BJ37">
+        <v>1000</v>
+      </c>
+      <c r="BK37">
+        <v>6.8</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>1.01</v>
+      </c>
+      <c r="BN37">
+        <v>1000</v>
+      </c>
+      <c r="BO37">
+        <v>5</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>1.01</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>1.01</v>
+      </c>
+      <c r="BT37">
+        <v>1000</v>
+      </c>
+      <c r="BU37">
+        <v>4.1</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>10.5</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" t="s">
+        <v>185</v>
+      </c>
+      <c r="F38">
+        <v>1.05</v>
+      </c>
+      <c r="G38">
+        <v>1.06</v>
+      </c>
+      <c r="H38">
+        <v>55</v>
+      </c>
+      <c r="I38">
+        <v>65</v>
+      </c>
+      <c r="J38">
+        <v>25</v>
+      </c>
+      <c r="K38">
+        <v>26</v>
+      </c>
+      <c r="L38">
+        <v>1.14</v>
+      </c>
+      <c r="M38">
+        <v>1.01</v>
+      </c>
+      <c r="N38">
+        <v>14</v>
+      </c>
+      <c r="O38">
+        <v>1.06</v>
+      </c>
+      <c r="P38">
+        <v>5.2</v>
+      </c>
+      <c r="Q38">
+        <v>1.21</v>
+      </c>
+      <c r="R38">
+        <v>2.7</v>
+      </c>
+      <c r="S38">
+        <v>1.54</v>
+      </c>
+      <c r="T38">
+        <v>2.88</v>
+      </c>
+      <c r="U38">
+        <v>1.49</v>
+      </c>
+      <c r="V38">
+        <v>1.01</v>
+      </c>
+      <c r="W38">
+        <v>17.5</v>
+      </c>
+      <c r="X38">
+        <v>1000</v>
+      </c>
+      <c r="Y38">
+        <v>1000</v>
+      </c>
+      <c r="Z38">
+        <v>1000</v>
+      </c>
+      <c r="AA38">
+        <v>1000</v>
+      </c>
+      <c r="AB38">
         <v>22</v>
       </c>
-      <c r="H37">
+      <c r="AC38">
+        <v>610</v>
+      </c>
+      <c r="AD38">
+        <v>1000</v>
+      </c>
+      <c r="AE38">
+        <v>1000</v>
+      </c>
+      <c r="AF38">
+        <v>11.5</v>
+      </c>
+      <c r="AG38">
+        <v>27</v>
+      </c>
+      <c r="AH38">
+        <v>1000</v>
+      </c>
+      <c r="AI38">
+        <v>1000</v>
+      </c>
+      <c r="AJ38">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AK38">
+        <v>20</v>
+      </c>
+      <c r="AL38">
+        <v>90</v>
+      </c>
+      <c r="AM38">
+        <v>1000</v>
+      </c>
+      <c r="AN38">
+        <v>1.82</v>
+      </c>
+      <c r="AO38">
+        <v>1000</v>
+      </c>
+      <c r="AP38">
+        <v>40</v>
+      </c>
+      <c r="AQ38">
+        <v>55</v>
+      </c>
+      <c r="AR38">
+        <v>60</v>
+      </c>
+      <c r="AS38">
+        <v>60</v>
+      </c>
+      <c r="AT38">
+        <v>18</v>
+      </c>
+      <c r="AU38">
+        <v>30</v>
+      </c>
+      <c r="AV38">
+        <v>46</v>
+      </c>
+      <c r="AW38">
+        <v>60</v>
+      </c>
+      <c r="AX38">
+        <v>9.6</v>
+      </c>
+      <c r="AY38">
+        <v>21</v>
+      </c>
+      <c r="AZ38">
+        <v>40</v>
+      </c>
+      <c r="BA38">
+        <v>16.5</v>
+      </c>
+      <c r="BB38">
+        <v>7</v>
+      </c>
+      <c r="BC38">
+        <v>17</v>
+      </c>
+      <c r="BD38">
+        <v>36</v>
+      </c>
+      <c r="BE38">
+        <v>55</v>
+      </c>
+      <c r="BF38">
+        <v>1.77</v>
+      </c>
+      <c r="BG38">
+        <v>60</v>
+      </c>
+      <c r="BH38">
+        <v>8</v>
+      </c>
+      <c r="BI38">
+        <v>6.6</v>
+      </c>
+      <c r="BJ38">
+        <v>21</v>
+      </c>
+      <c r="BK38">
+        <v>16.5</v>
+      </c>
+      <c r="BL38">
+        <v>1000</v>
+      </c>
+      <c r="BM38">
+        <v>21</v>
+      </c>
+      <c r="BN38">
+        <v>4.4</v>
+      </c>
+      <c r="BO38">
+        <v>3.75</v>
+      </c>
+      <c r="BP38">
+        <v>5.1</v>
+      </c>
+      <c r="BQ38">
+        <v>4.3</v>
+      </c>
+      <c r="BR38">
+        <v>24</v>
+      </c>
+      <c r="BS38">
+        <v>19.5</v>
+      </c>
+      <c r="BT38">
+        <v>38</v>
+      </c>
+      <c r="BU38">
+        <v>30</v>
+      </c>
+      <c r="BV38">
+        <v>1000</v>
+      </c>
+      <c r="BW38">
+        <v>21</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>21</v>
+      </c>
+      <c r="BZ38">
+        <v>4.2</v>
+      </c>
+      <c r="CA38">
+        <v>3.6</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" t="s">
+        <v>148</v>
+      </c>
+      <c r="E39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39">
+        <v>17</v>
+      </c>
+      <c r="G39">
+        <v>24</v>
+      </c>
+      <c r="H39">
         <v>1.18</v>
       </c>
-      <c r="I37">
+      <c r="I39">
         <v>1.2</v>
       </c>
-      <c r="J37">
+      <c r="J39">
         <v>8.4</v>
       </c>
-      <c r="K37">
+      <c r="K39">
         <v>9.800000000000001</v>
       </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>2.78</v>
-      </c>
-      <c r="Q37">
-        <v>1.45</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>0</v>
-      </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
-      </c>
-      <c r="AB37">
-        <v>0</v>
-      </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
-      <c r="AD37">
-        <v>0</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>0</v>
-      </c>
-      <c r="AG37">
-        <v>0</v>
-      </c>
-      <c r="AH37">
-        <v>0</v>
-      </c>
-      <c r="AI37">
-        <v>0</v>
-      </c>
-      <c r="AJ37">
-        <v>0</v>
-      </c>
-      <c r="AK37">
-        <v>0</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>0</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>0</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37">
-        <v>0</v>
-      </c>
-      <c r="AV37">
-        <v>0</v>
-      </c>
-      <c r="AW37">
-        <v>0</v>
-      </c>
-      <c r="AX37">
-        <v>0</v>
-      </c>
-      <c r="AY37">
-        <v>0</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>0</v>
-      </c>
-      <c r="BC37">
-        <v>0</v>
-      </c>
-      <c r="BD37">
-        <v>0</v>
-      </c>
-      <c r="BE37">
-        <v>0</v>
-      </c>
-      <c r="BF37">
-        <v>0</v>
-      </c>
-      <c r="BG37">
-        <v>0</v>
-      </c>
-      <c r="BH37">
-        <v>0</v>
-      </c>
-      <c r="BI37">
-        <v>0</v>
-      </c>
-      <c r="BJ37">
-        <v>0</v>
-      </c>
-      <c r="BK37">
-        <v>0</v>
-      </c>
-      <c r="BL37">
-        <v>0</v>
-      </c>
-      <c r="BM37">
-        <v>0</v>
-      </c>
-      <c r="BN37">
-        <v>0</v>
-      </c>
-      <c r="BO37">
-        <v>0</v>
-      </c>
-      <c r="BP37">
-        <v>0</v>
-      </c>
-      <c r="BQ37">
-        <v>0</v>
-      </c>
-      <c r="BR37">
-        <v>0</v>
-      </c>
-      <c r="BS37">
-        <v>0</v>
-      </c>
-      <c r="BT37">
-        <v>0</v>
-      </c>
-      <c r="BU37">
-        <v>0</v>
-      </c>
-      <c r="BV37">
-        <v>0</v>
-      </c>
-      <c r="BW37">
-        <v>0</v>
-      </c>
-      <c r="BX37">
-        <v>0</v>
-      </c>
-      <c r="BY37">
-        <v>0</v>
-      </c>
-      <c r="BZ37">
-        <v>0</v>
-      </c>
-      <c r="CA37">
-        <v>0</v>
-      </c>
-      <c r="CB37" t="s">
-        <v>182</v>
+      <c r="L39">
+        <v>1.26</v>
+      </c>
+      <c r="M39">
+        <v>1.02</v>
+      </c>
+      <c r="N39">
+        <v>5.6</v>
+      </c>
+      <c r="O39">
+        <v>1.14</v>
+      </c>
+      <c r="P39">
+        <v>2.8</v>
+      </c>
+      <c r="Q39">
+        <v>1.46</v>
+      </c>
+      <c r="R39">
+        <v>1.66</v>
+      </c>
+      <c r="S39">
+        <v>2.1</v>
+      </c>
+      <c r="T39">
+        <v>2.22</v>
+      </c>
+      <c r="U39">
+        <v>1.59</v>
+      </c>
+      <c r="V39">
+        <v>6</v>
+      </c>
+      <c r="W39">
+        <v>1.04</v>
+      </c>
+      <c r="X39">
+        <v>1000</v>
+      </c>
+      <c r="Y39">
+        <v>12.5</v>
+      </c>
+      <c r="Z39">
+        <v>9.4</v>
+      </c>
+      <c r="AA39">
+        <v>9.4</v>
+      </c>
+      <c r="AB39">
+        <v>75</v>
+      </c>
+      <c r="AC39">
+        <v>25</v>
+      </c>
+      <c r="AD39">
+        <v>16</v>
+      </c>
+      <c r="AE39">
+        <v>18.5</v>
+      </c>
+      <c r="AF39">
+        <v>1000</v>
+      </c>
+      <c r="AG39">
+        <v>80</v>
+      </c>
+      <c r="AH39">
+        <v>65</v>
+      </c>
+      <c r="AI39">
+        <v>65</v>
+      </c>
+      <c r="AJ39">
+        <v>1000</v>
+      </c>
+      <c r="AK39">
+        <v>1000</v>
+      </c>
+      <c r="AL39">
+        <v>1000</v>
+      </c>
+      <c r="AM39">
+        <v>1000</v>
+      </c>
+      <c r="AN39">
+        <v>1000</v>
+      </c>
+      <c r="AO39">
+        <v>3.6</v>
+      </c>
+      <c r="AP39">
+        <v>4.7</v>
+      </c>
+      <c r="AQ39">
+        <v>9.4</v>
+      </c>
+      <c r="AR39">
+        <v>5.9</v>
+      </c>
+      <c r="AS39">
+        <v>6</v>
+      </c>
+      <c r="AT39">
+        <v>4.4</v>
+      </c>
+      <c r="AU39">
+        <v>16</v>
+      </c>
+      <c r="AV39">
+        <v>10.5</v>
+      </c>
+      <c r="AW39">
+        <v>12</v>
+      </c>
+      <c r="AX39">
+        <v>4.7</v>
+      </c>
+      <c r="AY39">
+        <v>4.4</v>
+      </c>
+      <c r="AZ39">
+        <v>30</v>
+      </c>
+      <c r="BA39">
+        <v>4.3</v>
+      </c>
+      <c r="BB39">
+        <v>4.7</v>
+      </c>
+      <c r="BC39">
+        <v>4.7</v>
+      </c>
+      <c r="BD39">
+        <v>4.7</v>
+      </c>
+      <c r="BE39">
+        <v>4.7</v>
+      </c>
+      <c r="BF39">
+        <v>4.7</v>
+      </c>
+      <c r="BG39">
+        <v>2.88</v>
+      </c>
+      <c r="BH39">
+        <v>1000</v>
+      </c>
+      <c r="BI39">
+        <v>3.9</v>
+      </c>
+      <c r="BJ39">
+        <v>23</v>
+      </c>
+      <c r="BK39">
+        <v>11</v>
+      </c>
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
+        <v>21</v>
+      </c>
+      <c r="BN39">
+        <v>32</v>
+      </c>
+      <c r="BO39">
+        <v>13</v>
+      </c>
+      <c r="BP39">
+        <v>1000</v>
+      </c>
+      <c r="BQ39">
+        <v>21</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>21</v>
+      </c>
+      <c r="BT39">
+        <v>4.1</v>
+      </c>
+      <c r="BU39">
+        <v>3.1</v>
+      </c>
+      <c r="BV39">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BW39">
+        <v>4.5</v>
+      </c>
+      <c r="BX39">
+        <v>36</v>
+      </c>
+      <c r="BY39">
+        <v>14.5</v>
+      </c>
+      <c r="BZ39">
+        <v>11</v>
+      </c>
+      <c r="CA39">
+        <v>4.9</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -577,7 +577,7 @@
     <t>Benfica</t>
   </si>
   <si>
-    <t>2026-09-07 17:10:43</t>
+    <t>2026-09-07 19:22:10</t>
   </si>
 </sst>
 </file>
@@ -1174,37 +1174,37 @@
         <v>2.14</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
         <v>4.8</v>
       </c>
       <c r="J2">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K2">
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
         <v>1.61</v>
       </c>
       <c r="P2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
         <v>1.17</v>
@@ -1213,7 +1213,7 @@
         <v>6</v>
       </c>
       <c r="T2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U2">
         <v>1.69</v>
@@ -1222,175 +1222,175 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y2">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2">
         <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>7.6</v>
+        <v>2.02</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>2.02</v>
       </c>
       <c r="AT2">
+        <v>5.2</v>
+      </c>
+      <c r="AU2">
+        <v>5.4</v>
+      </c>
+      <c r="AV2">
+        <v>2.02</v>
+      </c>
+      <c r="AW2">
+        <v>2.02</v>
+      </c>
+      <c r="AX2">
+        <v>7.8</v>
+      </c>
+      <c r="AY2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>2.02</v>
+      </c>
+      <c r="BA2">
+        <v>2.02</v>
+      </c>
+      <c r="BB2">
+        <v>2.02</v>
+      </c>
+      <c r="BC2">
+        <v>2.02</v>
+      </c>
+      <c r="BD2">
+        <v>2.02</v>
+      </c>
+      <c r="BE2">
+        <v>2.02</v>
+      </c>
+      <c r="BF2">
+        <v>2.02</v>
+      </c>
+      <c r="BG2">
+        <v>2.02</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.78</v>
+      </c>
+      <c r="BJ2">
+        <v>17.5</v>
+      </c>
+      <c r="BK2">
+        <v>8.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.77</v>
+      </c>
+      <c r="BN2">
+        <v>5.5</v>
+      </c>
+      <c r="BO2">
+        <v>2.6</v>
+      </c>
+      <c r="BP2">
+        <v>28</v>
+      </c>
+      <c r="BQ2">
+        <v>1.67</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.73</v>
+      </c>
+      <c r="BT2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU2">
         <v>5.9</v>
       </c>
-      <c r="AU2">
-        <v>6.4</v>
-      </c>
-      <c r="AV2">
-        <v>17</v>
-      </c>
-      <c r="AW2">
-        <v>9.4</v>
-      </c>
-      <c r="AX2">
-        <v>10</v>
-      </c>
-      <c r="AY2">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2">
-        <v>19</v>
-      </c>
-      <c r="BA2">
-        <v>9.4</v>
-      </c>
-      <c r="BB2">
-        <v>7.6</v>
-      </c>
-      <c r="BC2">
-        <v>8</v>
-      </c>
-      <c r="BD2">
-        <v>9</v>
-      </c>
-      <c r="BE2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF2">
-        <v>7.8</v>
-      </c>
-      <c r="BG2">
-        <v>9.6</v>
-      </c>
-      <c r="BH2">
-        <v>2.62</v>
-      </c>
-      <c r="BI2">
-        <v>2.4</v>
-      </c>
-      <c r="BJ2">
-        <v>12.5</v>
-      </c>
-      <c r="BK2">
-        <v>7.8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>13</v>
-      </c>
-      <c r="BN2">
-        <v>4.7</v>
-      </c>
-      <c r="BO2">
-        <v>4.1</v>
-      </c>
-      <c r="BP2">
-        <v>20</v>
-      </c>
-      <c r="BQ2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR2">
-        <v>48</v>
-      </c>
-      <c r="BS2">
-        <v>10.5</v>
-      </c>
-      <c r="BT2">
-        <v>7.8</v>
-      </c>
-      <c r="BU2">
-        <v>6.6</v>
-      </c>
       <c r="BV2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>1.73</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>1.74</v>
       </c>
       <c r="BZ2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>1.73</v>
       </c>
       <c r="CB2" t="s">
         <v>187</v>
@@ -1413,226 +1413,226 @@
         <v>150</v>
       </c>
       <c r="F3">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="G3">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="J3">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="O3">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="P3">
         <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="R3">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W3">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="AS3">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>1.02</v>
       </c>
       <c r="AU3">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="AV3">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW3">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="AX3">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="AY3">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="AZ3">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA3">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="BB3">
-        <v>8</v>
+        <v>1.02</v>
       </c>
       <c r="BC3">
-        <v>11</v>
+        <v>1.02</v>
       </c>
       <c r="BD3">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="BF3">
-        <v>2.76</v>
+        <v>1.02</v>
       </c>
       <c r="BG3">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>187</v>
@@ -1655,16 +1655,16 @@
         <v>151</v>
       </c>
       <c r="F4">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="G4">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
         <v>4.2</v>
@@ -1673,19 +1673,19 @@
         <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
         <v>1.78</v>
@@ -1694,127 +1694,127 @@
         <v>1.42</v>
       </c>
       <c r="S4">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V4">
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="X4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AD4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
         <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AL4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>9</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR4">
-        <v>9.6</v>
+        <v>3.55</v>
       </c>
       <c r="AS4">
+        <v>3.55</v>
+      </c>
+      <c r="AT4">
+        <v>7.8</v>
+      </c>
+      <c r="AU4">
+        <v>8.4</v>
+      </c>
+      <c r="AV4">
+        <v>19</v>
+      </c>
+      <c r="AW4">
+        <v>3.55</v>
+      </c>
+      <c r="AX4">
+        <v>8.6</v>
+      </c>
+      <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
+        <v>17</v>
+      </c>
+      <c r="BA4">
+        <v>3.4</v>
+      </c>
+      <c r="BB4">
+        <v>10</v>
+      </c>
+      <c r="BC4">
         <v>10.5</v>
       </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV4">
-        <v>19.5</v>
-      </c>
-      <c r="AW4">
-        <v>10</v>
-      </c>
-      <c r="AX4">
-        <v>9</v>
-      </c>
-      <c r="AY4">
-        <v>9</v>
-      </c>
-      <c r="AZ4">
-        <v>18</v>
-      </c>
-      <c r="BA4">
-        <v>10</v>
-      </c>
-      <c r="BB4">
-        <v>13.5</v>
-      </c>
-      <c r="BC4">
-        <v>14.5</v>
-      </c>
       <c r="BD4">
-        <v>8.6</v>
+        <v>3.25</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1823,58 +1823,58 @@
         <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK4">
-        <v>2.26</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.52</v>
+        <v>4.1</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO4">
-        <v>1.67</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ4">
-        <v>2.26</v>
+        <v>8</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU4">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA4">
-        <v>2.52</v>
+        <v>3.55</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1897,40 +1897,40 @@
         <v>152</v>
       </c>
       <c r="F5">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="G5">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H5">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="I5">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
         <v>1.26</v>
@@ -1939,184 +1939,184 @@
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="X5">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y5">
         <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE5">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>1.96</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AW5">
-        <v>6.4</v>
+        <v>1.96</v>
       </c>
       <c r="AX5">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>6.8</v>
+        <v>1.96</v>
       </c>
       <c r="BB5">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="BC5">
-        <v>6.4</v>
+        <v>1.96</v>
       </c>
       <c r="BD5">
-        <v>6.8</v>
+        <v>1.96</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>1.96</v>
       </c>
       <c r="BF5">
-        <v>6.4</v>
+        <v>1.96</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2139,34 +2139,34 @@
         <v>153</v>
       </c>
       <c r="F6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G6">
         <v>2.66</v>
       </c>
       <c r="H6">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
         <v>1.71</v>
@@ -2175,190 +2175,190 @@
         <v>2.22</v>
       </c>
       <c r="R6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
         <v>4.3</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U6">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.6</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA6">
         <v>70</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC6">
+        <v>8.6</v>
+      </c>
+      <c r="AD6">
+        <v>17</v>
+      </c>
+      <c r="AE6">
+        <v>55</v>
+      </c>
+      <c r="AF6">
+        <v>19</v>
+      </c>
+      <c r="AG6">
+        <v>14.5</v>
+      </c>
+      <c r="AH6">
+        <v>23</v>
+      </c>
+      <c r="AI6">
+        <v>70</v>
+      </c>
+      <c r="AJ6">
+        <v>46</v>
+      </c>
+      <c r="AK6">
+        <v>38</v>
+      </c>
+      <c r="AL6">
+        <v>60</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>36</v>
+      </c>
+      <c r="AO6">
+        <v>55</v>
+      </c>
+      <c r="AP6">
         <v>7.6</v>
       </c>
-      <c r="AD6">
-        <v>15</v>
-      </c>
-      <c r="AE6">
-        <v>46</v>
-      </c>
-      <c r="AF6">
-        <v>16.5</v>
-      </c>
-      <c r="AG6">
+      <c r="AQ6">
+        <v>8.4</v>
+      </c>
+      <c r="AR6">
+        <v>15.5</v>
+      </c>
+      <c r="AS6">
+        <v>4.2</v>
+      </c>
+      <c r="AT6">
+        <v>7</v>
+      </c>
+      <c r="AU6">
+        <v>5.6</v>
+      </c>
+      <c r="AV6">
+        <v>11</v>
+      </c>
+      <c r="AW6">
+        <v>4.1</v>
+      </c>
+      <c r="AX6">
+        <v>12</v>
+      </c>
+      <c r="AY6">
+        <v>9</v>
+      </c>
+      <c r="AZ6">
         <v>14</v>
       </c>
-      <c r="AH6">
-        <v>20</v>
-      </c>
-      <c r="AI6">
-        <v>85</v>
-      </c>
-      <c r="AJ6">
-        <v>40</v>
-      </c>
-      <c r="AK6">
-        <v>34</v>
-      </c>
-      <c r="AL6">
-        <v>55</v>
-      </c>
-      <c r="AM6">
-        <v>140</v>
-      </c>
-      <c r="AN6">
-        <v>30</v>
-      </c>
-      <c r="AO6">
-        <v>50</v>
-      </c>
-      <c r="AP6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ6">
-        <v>9.6</v>
-      </c>
-      <c r="AR6">
-        <v>18</v>
-      </c>
-      <c r="AS6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT6">
-        <v>8</v>
-      </c>
-      <c r="AU6">
-        <v>6.6</v>
-      </c>
-      <c r="AV6">
-        <v>12.5</v>
-      </c>
-      <c r="AW6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX6">
-        <v>13.5</v>
-      </c>
-      <c r="AY6">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6">
-        <v>16.5</v>
-      </c>
       <c r="BA6">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB6">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BC6">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BD6">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE6">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BF6">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="BG6">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="BH6">
-        <v>3.65</v>
+        <v>9.4</v>
       </c>
       <c r="BI6">
         <v>2.52</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>2.42</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO6">
-        <v>1.76</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ6">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS6">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU6">
+        <v>5</v>
+      </c>
+      <c r="BV6">
+        <v>38</v>
+      </c>
+      <c r="BW6">
+        <v>1.85</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.88</v>
+      </c>
+      <c r="BZ6">
+        <v>50</v>
+      </c>
+      <c r="CA6">
         <v>1.87</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.39</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.39</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>1.39</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2381,19 +2381,19 @@
         <v>154</v>
       </c>
       <c r="F7">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="G7">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="H7">
         <v>1.95</v>
       </c>
       <c r="I7">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
         <v>3.75</v>
@@ -2405,202 +2405,202 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
         <v>2.06</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
+        <v>3.55</v>
+      </c>
+      <c r="T7">
+        <v>1.86</v>
+      </c>
+      <c r="U7">
+        <v>1.9</v>
+      </c>
+      <c r="V7">
+        <v>1.88</v>
+      </c>
+      <c r="W7">
+        <v>1.26</v>
+      </c>
+      <c r="X7">
+        <v>970</v>
+      </c>
+      <c r="Y7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z7">
+        <v>14</v>
+      </c>
+      <c r="AA7">
+        <v>30</v>
+      </c>
+      <c r="AB7">
+        <v>18</v>
+      </c>
+      <c r="AC7">
+        <v>9.6</v>
+      </c>
+      <c r="AD7">
+        <v>12.5</v>
+      </c>
+      <c r="AE7">
+        <v>29</v>
+      </c>
+      <c r="AF7">
+        <v>40</v>
+      </c>
+      <c r="AG7">
+        <v>23</v>
+      </c>
+      <c r="AH7">
+        <v>25</v>
+      </c>
+      <c r="AI7">
+        <v>50</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>85</v>
+      </c>
+      <c r="AL7">
+        <v>100</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>100</v>
+      </c>
+      <c r="AO7">
+        <v>20</v>
+      </c>
+      <c r="AP7">
+        <v>8.6</v>
+      </c>
+      <c r="AQ7">
+        <v>6.2</v>
+      </c>
+      <c r="AR7">
+        <v>8.6</v>
+      </c>
+      <c r="AS7">
+        <v>16.5</v>
+      </c>
+      <c r="AT7">
+        <v>11</v>
+      </c>
+      <c r="AU7">
+        <v>6.4</v>
+      </c>
+      <c r="AV7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW7">
+        <v>14</v>
+      </c>
+      <c r="AX7">
+        <v>3.45</v>
+      </c>
+      <c r="AY7">
+        <v>13</v>
+      </c>
+      <c r="AZ7">
+        <v>15</v>
+      </c>
+      <c r="BA7">
+        <v>3.5</v>
+      </c>
+      <c r="BB7">
         <v>3.8</v>
       </c>
-      <c r="T7">
-        <v>1.89</v>
-      </c>
-      <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7">
-        <v>1.92</v>
-      </c>
-      <c r="W7">
-        <v>1.27</v>
-      </c>
-      <c r="X7">
-        <v>13</v>
-      </c>
-      <c r="Y7">
-        <v>8.4</v>
-      </c>
-      <c r="Z7">
-        <v>12</v>
-      </c>
-      <c r="AA7">
-        <v>25</v>
-      </c>
-      <c r="AB7">
-        <v>15</v>
-      </c>
-      <c r="AC7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7">
-        <v>11</v>
-      </c>
-      <c r="AE7">
-        <v>23</v>
-      </c>
-      <c r="AF7">
-        <v>34</v>
-      </c>
-      <c r="AG7">
-        <v>19</v>
-      </c>
-      <c r="AH7">
-        <v>21</v>
-      </c>
-      <c r="AI7">
-        <v>42</v>
-      </c>
-      <c r="AJ7">
-        <v>130</v>
-      </c>
-      <c r="AK7">
-        <v>75</v>
-      </c>
-      <c r="AL7">
-        <v>85</v>
-      </c>
-      <c r="AM7">
-        <v>150</v>
-      </c>
-      <c r="AN7">
-        <v>90</v>
-      </c>
-      <c r="AO7">
-        <v>16.5</v>
-      </c>
-      <c r="AP7">
-        <v>11</v>
-      </c>
-      <c r="AQ7">
-        <v>7.4</v>
-      </c>
-      <c r="AR7">
-        <v>10</v>
-      </c>
-      <c r="AS7">
-        <v>20</v>
-      </c>
-      <c r="AT7">
+      <c r="BC7">
+        <v>3.65</v>
+      </c>
+      <c r="BD7">
+        <v>3.65</v>
+      </c>
+      <c r="BE7">
+        <v>3.8</v>
+      </c>
+      <c r="BF7">
+        <v>3.65</v>
+      </c>
+      <c r="BG7">
         <v>12.5</v>
       </c>
-      <c r="AU7">
-        <v>7.2</v>
-      </c>
-      <c r="AV7">
-        <v>9.4</v>
-      </c>
-      <c r="AW7">
-        <v>16.5</v>
-      </c>
-      <c r="AX7">
-        <v>20</v>
-      </c>
-      <c r="AY7">
-        <v>15.5</v>
-      </c>
-      <c r="AZ7">
-        <v>17</v>
-      </c>
-      <c r="BA7">
-        <v>8.4</v>
-      </c>
-      <c r="BB7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC7">
-        <v>9.4</v>
-      </c>
-      <c r="BD7">
-        <v>9.4</v>
-      </c>
-      <c r="BE7">
-        <v>10</v>
-      </c>
-      <c r="BF7">
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>2.78</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>2.34</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>2.66</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>5.8</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>2.66</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>2.66</v>
+      </c>
+      <c r="BT7">
+        <v>5.4</v>
+      </c>
+      <c r="BU7">
+        <v>1.78</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
         <v>9.6</v>
       </c>
-      <c r="BG7">
-        <v>14</v>
-      </c>
-      <c r="BH7">
-        <v>3.2</v>
-      </c>
-      <c r="BI7">
-        <v>2.98</v>
-      </c>
-      <c r="BJ7">
-        <v>10.5</v>
-      </c>
-      <c r="BK7">
-        <v>7.4</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>14</v>
-      </c>
-      <c r="BN7">
-        <v>7.6</v>
-      </c>
-      <c r="BO7">
-        <v>6.8</v>
-      </c>
-      <c r="BP7">
-        <v>40</v>
-      </c>
-      <c r="BQ7">
-        <v>11</v>
-      </c>
-      <c r="BR7">
-        <v>55</v>
-      </c>
-      <c r="BS7">
-        <v>12</v>
-      </c>
-      <c r="BT7">
-        <v>4.6</v>
-      </c>
-      <c r="BU7">
-        <v>4.1</v>
-      </c>
-      <c r="BV7">
-        <v>14.5</v>
-      </c>
-      <c r="BW7">
-        <v>9.4</v>
-      </c>
       <c r="BX7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>2.66</v>
       </c>
       <c r="BZ7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>2.66</v>
       </c>
       <c r="CB7" t="s">
         <v>187</v>
@@ -2626,19 +2626,19 @@
         <v>3.1</v>
       </c>
       <c r="G8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H8">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I8">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J8">
         <v>2.8</v>
       </c>
       <c r="K8">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2650,13 +2650,13 @@
         <v>2.18</v>
       </c>
       <c r="O8">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="P8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q8">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R8">
         <v>1.13</v>
@@ -2665,124 +2665,124 @@
         <v>5.5</v>
       </c>
       <c r="T8">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U8">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="V8">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X8">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Y8">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="Z8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AD8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG8">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AR8">
-        <v>14</v>
+        <v>1.79</v>
       </c>
       <c r="AS8">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="AT8">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>1.79</v>
       </c>
       <c r="AW8">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>1.66</v>
       </c>
       <c r="AY8">
-        <v>14</v>
+        <v>1.79</v>
       </c>
       <c r="AZ8">
-        <v>20</v>
+        <v>1.8</v>
       </c>
       <c r="BA8">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="BB8">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="BC8">
-        <v>9.6</v>
+        <v>1.8</v>
       </c>
       <c r="BD8">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="BE8">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="BG8">
-        <v>9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2865,7 +2865,7 @@
         <v>156</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G9">
         <v>2.56</v>
@@ -2889,13 +2889,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O9">
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q9">
         <v>1.22</v>
@@ -2913,10 +2913,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3110,19 +3110,19 @@
         <v>1.47</v>
       </c>
       <c r="G10">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J10">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3146,187 +3146,187 @@
         <v>1.19</v>
       </c>
       <c r="S10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="U10">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V10">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W10">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="X10">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y10">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>5.3</v>
+        <v>970</v>
       </c>
       <c r="AC10">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AG10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>8.6</v>
+        <v>1.46</v>
       </c>
       <c r="AQ10">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AR10">
-        <v>5.7</v>
+        <v>1.63</v>
       </c>
       <c r="AS10">
-        <v>5.8</v>
+        <v>1.63</v>
       </c>
       <c r="AT10">
-        <v>4.7</v>
+        <v>1.31</v>
       </c>
       <c r="AU10">
-        <v>8.800000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="AV10">
-        <v>5.4</v>
+        <v>1.63</v>
       </c>
       <c r="AW10">
-        <v>5.7</v>
+        <v>1.63</v>
       </c>
       <c r="AX10">
-        <v>6.2</v>
+        <v>1.38</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="AZ10">
-        <v>5.3</v>
+        <v>1.63</v>
       </c>
       <c r="BA10">
-        <v>5.7</v>
+        <v>1.63</v>
       </c>
       <c r="BB10">
+        <v>10.5</v>
+      </c>
+      <c r="BC10">
+        <v>1.63</v>
+      </c>
+      <c r="BD10">
+        <v>1.63</v>
+      </c>
+      <c r="BE10">
+        <v>1.63</v>
+      </c>
+      <c r="BF10">
         <v>11</v>
       </c>
-      <c r="BC10">
-        <v>17</v>
-      </c>
-      <c r="BD10">
-        <v>5.6</v>
-      </c>
-      <c r="BE10">
-        <v>5.7</v>
-      </c>
-      <c r="BF10">
-        <v>11.5</v>
-      </c>
       <c r="BG10">
-        <v>5.8</v>
+        <v>1.63</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="CB10" t="s">
         <v>187</v>
@@ -3349,46 +3349,46 @@
         <v>158</v>
       </c>
       <c r="F11">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G11">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H11">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I11">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
+        <v>1.29</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>3.45</v>
+      </c>
+      <c r="O11">
         <v>1.28</v>
       </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>3.5</v>
-      </c>
-      <c r="O11">
-        <v>1.25</v>
-      </c>
       <c r="P11">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="Q11">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>1.88</v>
+        <v>2.54</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3397,19 +3397,19 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3418,10 +3418,10 @@
         <v>1000</v>
       </c>
       <c r="AC11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE11">
         <v>1000</v>
@@ -3451,64 +3451,64 @@
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11">
-        <v>11</v>
+        <v>1.24</v>
       </c>
       <c r="AR11">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AT11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AU11">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AV11">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AW11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AX11">
-        <v>9</v>
+        <v>1.24</v>
       </c>
       <c r="AY11">
-        <v>7.4</v>
+        <v>1.24</v>
       </c>
       <c r="AZ11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="BA11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="BB11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="BC11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="BD11">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="BE11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>1.24</v>
       </c>
       <c r="BG11">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3532,10 +3532,10 @@
         <v>6.6</v>
       </c>
       <c r="BO11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ11">
         <v>1.7</v>
@@ -3550,10 +3550,10 @@
         <v>10.5</v>
       </c>
       <c r="BU11">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW11">
         <v>1.79</v>
@@ -3594,7 +3594,7 @@
         <v>2.66</v>
       </c>
       <c r="G12">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H12">
         <v>2.74</v>
@@ -3606,7 +3606,7 @@
         <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L12">
         <v>1.37</v>
@@ -3615,7 +3615,7 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
         <v>1.32</v>
@@ -3624,19 +3624,19 @@
         <v>1.88</v>
       </c>
       <c r="Q12">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S12">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U12">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
         <v>1.52</v>
@@ -3645,118 +3645,118 @@
         <v>1.54</v>
       </c>
       <c r="X12">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>970</v>
+      </c>
+      <c r="AC12">
+        <v>11.5</v>
+      </c>
+      <c r="AD12">
+        <v>970</v>
+      </c>
+      <c r="AE12">
+        <v>36</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>970</v>
+      </c>
+      <c r="AH12">
         <v>19</v>
       </c>
-      <c r="AA12">
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
         <v>50</v>
       </c>
-      <c r="AB12">
-        <v>11.5</v>
-      </c>
-      <c r="AC12">
-        <v>8</v>
-      </c>
-      <c r="AD12">
-        <v>13</v>
-      </c>
-      <c r="AE12">
+      <c r="AK12">
         <v>34</v>
       </c>
-      <c r="AF12">
-        <v>19</v>
-      </c>
-      <c r="AG12">
-        <v>13</v>
-      </c>
-      <c r="AH12">
-        <v>18</v>
-      </c>
-      <c r="AI12">
-        <v>50</v>
-      </c>
-      <c r="AJ12">
-        <v>42</v>
-      </c>
-      <c r="AK12">
-        <v>32</v>
-      </c>
       <c r="AL12">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ12">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AR12">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AS12">
-        <v>8</v>
+        <v>1.68</v>
       </c>
       <c r="AT12">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AU12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12">
+        <v>8.6</v>
+      </c>
+      <c r="AW12">
+        <v>1.61</v>
+      </c>
+      <c r="AX12">
         <v>11</v>
       </c>
-      <c r="AW12">
-        <v>7.4</v>
-      </c>
-      <c r="AX12">
-        <v>15.5</v>
-      </c>
       <c r="AY12">
+        <v>8.4</v>
+      </c>
+      <c r="AZ12">
         <v>11</v>
       </c>
-      <c r="AZ12">
-        <v>15</v>
-      </c>
       <c r="BA12">
-        <v>8</v>
+        <v>1.68</v>
       </c>
       <c r="BB12">
-        <v>7.6</v>
+        <v>1.62</v>
       </c>
       <c r="BC12">
-        <v>7.2</v>
+        <v>1.6</v>
       </c>
       <c r="BD12">
-        <v>8</v>
+        <v>1.68</v>
       </c>
       <c r="BE12">
-        <v>8.6</v>
+        <v>1.68</v>
       </c>
       <c r="BF12">
-        <v>20</v>
+        <v>1.68</v>
       </c>
       <c r="BG12">
-        <v>21</v>
+        <v>1.68</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3836,7 +3836,7 @@
         <v>1.35</v>
       </c>
       <c r="G13">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="H13">
         <v>2.3</v>
@@ -3845,7 +3845,7 @@
         <v>110</v>
       </c>
       <c r="J13">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3857,22 +3857,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q13">
-        <v>1.29</v>
+        <v>1.78</v>
       </c>
       <c r="R13">
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>1.31</v>
+        <v>2.68</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3881,10 +3881,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4078,223 +4078,223 @@
         <v>3.05</v>
       </c>
       <c r="G14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H14">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="O14">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P14">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="R14">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U14">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W14">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y14">
+        <v>14.5</v>
+      </c>
+      <c r="Z14">
+        <v>20</v>
+      </c>
+      <c r="AA14">
+        <v>38</v>
+      </c>
+      <c r="AB14">
         <v>17</v>
       </c>
-      <c r="Z14">
-        <v>23</v>
-      </c>
-      <c r="AA14">
-        <v>46</v>
-      </c>
-      <c r="AB14">
-        <v>20</v>
-      </c>
       <c r="AC14">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH14">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI14">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK14">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AL14">
         <v>55</v>
       </c>
       <c r="AM14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO14">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AP14">
-        <v>2.74</v>
+        <v>13</v>
       </c>
       <c r="AQ14">
-        <v>2.36</v>
+        <v>9.6</v>
       </c>
       <c r="AR14">
+        <v>12.5</v>
+      </c>
+      <c r="AS14">
+        <v>21</v>
+      </c>
+      <c r="AT14">
         <v>10.5</v>
       </c>
-      <c r="AS14">
-        <v>2.58</v>
-      </c>
-      <c r="AT14">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AU14">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV14">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="AW14">
-        <v>2.54</v>
+        <v>17.5</v>
       </c>
       <c r="AX14">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY14">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="BA14">
-        <v>2.58</v>
+        <v>24</v>
       </c>
       <c r="BB14">
-        <v>2.64</v>
+        <v>4.8</v>
       </c>
       <c r="BC14">
-        <v>2.58</v>
+        <v>24</v>
       </c>
       <c r="BD14">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE14">
-        <v>2.66</v>
+        <v>4.9</v>
       </c>
       <c r="BF14">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BG14">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="BJ14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>1.68</v>
+        <v>5.9</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="BN14">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BO14">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP14">
         <v>32</v>
       </c>
       <c r="BQ14">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BR14">
         <v>46</v>
       </c>
       <c r="BS14">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="BT14">
         <v>7.4</v>
       </c>
       <c r="BU14">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BV14">
         <v>23</v>
       </c>
       <c r="BW14">
-        <v>1.79</v>
+        <v>3.5</v>
       </c>
       <c r="BX14">
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BZ14">
         <v>30</v>
       </c>
       <c r="CA14">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="CB14" t="s">
         <v>187</v>
@@ -4317,22 +4317,22 @@
         <v>162</v>
       </c>
       <c r="F15">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="G15">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="H15">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I15">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K15">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4341,22 +4341,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O15">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P15">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R15">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S15">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4365,10 +4365,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4589,7 +4589,7 @@
         <v>1.16</v>
       </c>
       <c r="P16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
         <v>1.16</v>
@@ -4607,10 +4607,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4801,49 +4801,49 @@
         <v>164</v>
       </c>
       <c r="F17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G17">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="H17">
         <v>15.5</v>
       </c>
       <c r="I17">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="J17">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="K17">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="L17">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="P17">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="Q17">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="R17">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="S17">
         <v>1.7</v>
       </c>
       <c r="T17">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
         <v>1.01</v>
@@ -4852,13 +4852,13 @@
         <v>1.05</v>
       </c>
       <c r="W17">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="X17">
         <v>1000</v>
       </c>
       <c r="Y17">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Z17">
         <v>1000</v>
@@ -4867,160 +4867,160 @@
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC17">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AD17">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AE17">
         <v>1000</v>
       </c>
       <c r="AF17">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG17">
+        <v>16.5</v>
+      </c>
+      <c r="AH17">
+        <v>44</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>12</v>
+      </c>
+      <c r="AK17">
+        <v>17</v>
+      </c>
+      <c r="AL17">
+        <v>44</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>3.45</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>3.85</v>
+      </c>
+      <c r="AQ17">
+        <v>3.65</v>
+      </c>
+      <c r="AR17">
+        <v>3.85</v>
+      </c>
+      <c r="AS17">
+        <v>3.85</v>
+      </c>
+      <c r="AT17">
+        <v>3.1</v>
+      </c>
+      <c r="AU17">
+        <v>3.35</v>
+      </c>
+      <c r="AV17">
+        <v>3.65</v>
+      </c>
+      <c r="AW17">
+        <v>3.85</v>
+      </c>
+      <c r="AX17">
+        <v>2.94</v>
+      </c>
+      <c r="AY17">
+        <v>3.1</v>
+      </c>
+      <c r="AZ17">
+        <v>3.5</v>
+      </c>
+      <c r="BA17">
+        <v>3.85</v>
+      </c>
+      <c r="BB17">
+        <v>2.9</v>
+      </c>
+      <c r="BC17">
+        <v>3.1</v>
+      </c>
+      <c r="BD17">
+        <v>3.5</v>
+      </c>
+      <c r="BE17">
+        <v>3.85</v>
+      </c>
+      <c r="BF17">
+        <v>2.38</v>
+      </c>
+      <c r="BG17">
+        <v>3.85</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>2.2</v>
+      </c>
+      <c r="BJ17">
         <v>18.5</v>
       </c>
-      <c r="AH17">
-        <v>50</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>13</v>
-      </c>
-      <c r="AK17">
-        <v>20</v>
-      </c>
-      <c r="AL17">
-        <v>50</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>970</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.65</v>
-      </c>
-      <c r="AQ17">
-        <v>1.62</v>
-      </c>
-      <c r="AR17">
-        <v>1.65</v>
-      </c>
-      <c r="AS17">
-        <v>1.65</v>
-      </c>
-      <c r="AT17">
-        <v>1.52</v>
-      </c>
-      <c r="AU17">
-        <v>1.56</v>
-      </c>
-      <c r="AV17">
-        <v>1.62</v>
-      </c>
-      <c r="AW17">
-        <v>1.65</v>
-      </c>
-      <c r="AX17">
-        <v>1.48</v>
-      </c>
-      <c r="AY17">
-        <v>2.6</v>
-      </c>
-      <c r="AZ17">
-        <v>1.6</v>
-      </c>
-      <c r="BA17">
-        <v>1.65</v>
-      </c>
-      <c r="BB17">
-        <v>1.46</v>
-      </c>
-      <c r="BC17">
-        <v>1.52</v>
-      </c>
-      <c r="BD17">
-        <v>1.6</v>
-      </c>
-      <c r="BE17">
-        <v>1.65</v>
-      </c>
-      <c r="BF17">
-        <v>1.65</v>
-      </c>
-      <c r="BG17">
-        <v>1.65</v>
-      </c>
-      <c r="BH17">
-        <v>6.2</v>
-      </c>
-      <c r="BI17">
-        <v>3.8</v>
-      </c>
-      <c r="BJ17">
-        <v>14</v>
-      </c>
       <c r="BK17">
-        <v>5.8</v>
+        <v>1.97</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="BN17">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO17">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BP17">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ17">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="BR17">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BS17">
-        <v>6.6</v>
+        <v>2.04</v>
       </c>
       <c r="BT17">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BU17">
-        <v>6.6</v>
+        <v>2.02</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="BZ17">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA17">
-        <v>4</v>
+        <v>1.78</v>
       </c>
       <c r="CB17" t="s">
         <v>187</v>
@@ -5049,7 +5049,7 @@
         <v>1.12</v>
       </c>
       <c r="H18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I18">
         <v>34</v>
@@ -5058,7 +5058,7 @@
         <v>14.5</v>
       </c>
       <c r="K18">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="L18">
         <v>1.14</v>
@@ -5073,7 +5073,7 @@
         <v>1.06</v>
       </c>
       <c r="P18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q18">
         <v>1.2</v>
@@ -5082,7 +5082,7 @@
         <v>2.88</v>
       </c>
       <c r="S18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T18">
         <v>1.97</v>
@@ -5094,43 +5094,43 @@
         <v>1.03</v>
       </c>
       <c r="W18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y18">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="Z18">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AA18">
         <v>1000</v>
       </c>
       <c r="AB18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC18">
         <v>40</v>
       </c>
       <c r="AD18">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AE18">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="AF18">
         <v>14</v>
       </c>
       <c r="AG18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH18">
         <v>55</v>
       </c>
       <c r="AI18">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AJ18">
         <v>10.5</v>
@@ -5139,16 +5139,16 @@
         <v>15</v>
       </c>
       <c r="AL18">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM18">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN18">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AO18">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AP18">
         <v>34</v>
@@ -5157,31 +5157,31 @@
         <v>42</v>
       </c>
       <c r="AR18">
+        <v>22</v>
+      </c>
+      <c r="AS18">
         <v>20</v>
       </c>
-      <c r="AS18">
-        <v>21</v>
-      </c>
       <c r="AT18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU18">
         <v>32</v>
       </c>
       <c r="AV18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AW18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY18">
         <v>15.5</v>
       </c>
       <c r="AZ18">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BA18">
         <v>48</v>
@@ -5199,70 +5199,70 @@
         <v>46</v>
       </c>
       <c r="BF18">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BG18">
+        <v>55</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.93</v>
+      </c>
+      <c r="BJ18">
         <v>20</v>
       </c>
-      <c r="BH18">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BI18">
-        <v>7.2</v>
-      </c>
-      <c r="BJ18">
-        <v>17</v>
-      </c>
       <c r="BK18">
-        <v>12</v>
+        <v>2.42</v>
       </c>
       <c r="BL18">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>21</v>
+        <v>1.93</v>
       </c>
       <c r="BN18">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP18">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BR18">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BS18">
-        <v>14</v>
+        <v>2.48</v>
       </c>
       <c r="BT18">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BU18">
-        <v>20</v>
+        <v>1.83</v>
       </c>
       <c r="BV18">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>21</v>
+        <v>1.93</v>
       </c>
       <c r="BX18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>22</v>
+        <v>1.93</v>
       </c>
       <c r="BZ18">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="CA18">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5288,19 +5288,19 @@
         <v>1.26</v>
       </c>
       <c r="G19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I19">
         <v>13</v>
       </c>
       <c r="J19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="K19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>1.17</v>
@@ -5309,7 +5309,7 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="O19">
         <v>1.09</v>
@@ -5324,10 +5324,10 @@
         <v>2.36</v>
       </c>
       <c r="S19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U19">
         <v>2.42</v>
@@ -5336,7 +5336,7 @@
         <v>1.08</v>
       </c>
       <c r="W19">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="X19">
         <v>60</v>
@@ -5348,13 +5348,13 @@
         <v>1000</v>
       </c>
       <c r="AA19">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="AB19">
         <v>20</v>
       </c>
       <c r="AC19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD19">
         <v>46</v>
@@ -5390,7 +5390,7 @@
         <v>2.76</v>
       </c>
       <c r="AO19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP19">
         <v>50</v>
@@ -5408,10 +5408,10 @@
         <v>17.5</v>
       </c>
       <c r="AU19">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AV19">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AW19">
         <v>42</v>
@@ -5420,7 +5420,7 @@
         <v>12</v>
       </c>
       <c r="AY19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ19">
         <v>22</v>
@@ -5429,7 +5429,7 @@
         <v>36</v>
       </c>
       <c r="BB19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC19">
         <v>11.5</v>
@@ -5444,67 +5444,67 @@
         <v>2.68</v>
       </c>
       <c r="BG19">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BH19">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
         <v>4.7</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK19">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO19">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ19">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU19">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="CB19" t="s">
         <v>187</v>
@@ -5530,7 +5530,7 @@
         <v>1.27</v>
       </c>
       <c r="G20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H20">
         <v>10.5</v>
@@ -5539,22 +5539,22 @@
         <v>12.5</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K20">
         <v>7.8</v>
       </c>
       <c r="L20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M20">
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="O20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P20">
         <v>3.55</v>
@@ -5563,190 +5563,190 @@
         <v>1.34</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="T20">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V20">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W20">
         <v>4.3</v>
       </c>
       <c r="X20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
         <v>44</v>
       </c>
       <c r="AE20">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AK20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AO20">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>8.800000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="AQ20">
-        <v>9</v>
+        <v>1.49</v>
       </c>
       <c r="AR20">
-        <v>9.4</v>
+        <v>1.49</v>
       </c>
       <c r="AS20">
+        <v>1.49</v>
+      </c>
+      <c r="AT20">
+        <v>1.95</v>
+      </c>
+      <c r="AU20">
+        <v>1.95</v>
+      </c>
+      <c r="AV20">
+        <v>1.44</v>
+      </c>
+      <c r="AW20">
+        <v>1.49</v>
+      </c>
+      <c r="AX20">
+        <v>1.95</v>
+      </c>
+      <c r="AY20">
         <v>10</v>
       </c>
-      <c r="AT20">
-        <v>14</v>
-      </c>
-      <c r="AU20">
-        <v>15.5</v>
-      </c>
-      <c r="AV20">
-        <v>8.4</v>
-      </c>
-      <c r="AW20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX20">
+      <c r="AZ20">
+        <v>21</v>
+      </c>
+      <c r="BA20">
+        <v>1.49</v>
+      </c>
+      <c r="BB20">
         <v>10</v>
       </c>
-      <c r="AY20">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20">
-        <v>7.6</v>
-      </c>
-      <c r="BA20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB20">
-        <v>10.5</v>
-      </c>
       <c r="BC20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD20">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="BE20">
-        <v>9.199999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="BF20">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BG20">
-        <v>9.4</v>
+        <v>1.49</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
         <v>187</v>
@@ -5772,163 +5772,163 @@
         <v>3.5</v>
       </c>
       <c r="G21">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H21">
         <v>2.08</v>
       </c>
       <c r="I21">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="J21">
         <v>3.45</v>
       </c>
       <c r="K21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M21">
         <v>1.06</v>
       </c>
       <c r="N21">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O21">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q21">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R21">
         <v>1.36</v>
       </c>
       <c r="S21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T21">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U21">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W21">
         <v>1.33</v>
       </c>
       <c r="X21">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z21">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
         <v>34</v>
       </c>
       <c r="AB21">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD21">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE21">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
         <v>34</v>
       </c>
       <c r="AG21">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
         <v>44</v>
       </c>
       <c r="AJ21">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>13</v>
+        <v>1.45</v>
       </c>
       <c r="AQ21">
-        <v>8.6</v>
+        <v>1.27</v>
       </c>
       <c r="AR21">
-        <v>12</v>
+        <v>1.45</v>
       </c>
       <c r="AS21">
-        <v>19.5</v>
+        <v>1.39</v>
       </c>
       <c r="AT21">
-        <v>12</v>
+        <v>1.45</v>
       </c>
       <c r="AU21">
-        <v>7.2</v>
+        <v>1.29</v>
       </c>
       <c r="AV21">
-        <v>9.4</v>
+        <v>1.36</v>
       </c>
       <c r="AW21">
-        <v>16.5</v>
+        <v>1.45</v>
       </c>
       <c r="AX21">
-        <v>19.5</v>
+        <v>1.39</v>
       </c>
       <c r="AY21">
-        <v>13</v>
+        <v>1.45</v>
       </c>
       <c r="AZ21">
-        <v>14.5</v>
+        <v>1.45</v>
       </c>
       <c r="BA21">
-        <v>6.6</v>
+        <v>1.41</v>
       </c>
       <c r="BB21">
-        <v>7</v>
+        <v>1.45</v>
       </c>
       <c r="BC21">
-        <v>6.8</v>
+        <v>1.45</v>
       </c>
       <c r="BD21">
-        <v>6.8</v>
+        <v>1.45</v>
       </c>
       <c r="BE21">
-        <v>7.2</v>
+        <v>1.45</v>
       </c>
       <c r="BF21">
-        <v>6.8</v>
+        <v>1.45</v>
       </c>
       <c r="BG21">
-        <v>13.5</v>
+        <v>1.45</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6011,37 +6011,37 @@
         <v>169</v>
       </c>
       <c r="F22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G22">
+        <v>3.5</v>
+      </c>
+      <c r="H22">
+        <v>2.84</v>
+      </c>
+      <c r="I22">
         <v>3.25</v>
       </c>
-      <c r="H22">
-        <v>2.86</v>
-      </c>
-      <c r="I22">
-        <v>3.05</v>
-      </c>
       <c r="J22">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="K22">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N22">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="O22">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P22">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Q22">
         <v>2.96</v>
@@ -6050,187 +6050,187 @@
         <v>1.13</v>
       </c>
       <c r="S22">
+        <v>6.2</v>
+      </c>
+      <c r="T22">
+        <v>2.18</v>
+      </c>
+      <c r="U22">
+        <v>1.64</v>
+      </c>
+      <c r="V22">
+        <v>1.45</v>
+      </c>
+      <c r="W22">
+        <v>1.4</v>
+      </c>
+      <c r="X22">
+        <v>970</v>
+      </c>
+      <c r="Y22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z22">
+        <v>19</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>8.6</v>
+      </c>
+      <c r="AC22">
+        <v>970</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>17</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>5.3</v>
+      </c>
+      <c r="AQ22">
         <v>5.9</v>
       </c>
-      <c r="T22">
-        <v>2.28</v>
-      </c>
-      <c r="U22">
-        <v>1.7</v>
-      </c>
-      <c r="V22">
-        <v>1.48</v>
-      </c>
-      <c r="W22">
-        <v>1.44</v>
-      </c>
-      <c r="X22">
+      <c r="AR22">
+        <v>2.08</v>
+      </c>
+      <c r="AS22">
+        <v>2.34</v>
+      </c>
+      <c r="AT22">
+        <v>6</v>
+      </c>
+      <c r="AU22">
+        <v>6</v>
+      </c>
+      <c r="AV22">
+        <v>2.32</v>
+      </c>
+      <c r="AW22">
+        <v>2.34</v>
+      </c>
+      <c r="AX22">
+        <v>2.32</v>
+      </c>
+      <c r="AY22">
+        <v>2.04</v>
+      </c>
+      <c r="AZ22">
+        <v>2.34</v>
+      </c>
+      <c r="BA22">
+        <v>2.34</v>
+      </c>
+      <c r="BB22">
+        <v>2.34</v>
+      </c>
+      <c r="BC22">
+        <v>2.34</v>
+      </c>
+      <c r="BD22">
+        <v>2.34</v>
+      </c>
+      <c r="BE22">
+        <v>2.34</v>
+      </c>
+      <c r="BF22">
+        <v>2.34</v>
+      </c>
+      <c r="BG22">
+        <v>2.34</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.66</v>
+      </c>
+      <c r="BJ22">
+        <v>17</v>
+      </c>
+      <c r="BK22">
+        <v>1.51</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.66</v>
+      </c>
+      <c r="BN22">
+        <v>8</v>
+      </c>
+      <c r="BO22">
+        <v>4.1</v>
+      </c>
+      <c r="BP22">
+        <v>46</v>
+      </c>
+      <c r="BQ22">
+        <v>1.6</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.63</v>
+      </c>
+      <c r="BT22">
         <v>7.6</v>
       </c>
-      <c r="Y22">
-        <v>7.8</v>
-      </c>
-      <c r="Z22">
-        <v>970</v>
-      </c>
-      <c r="AA22">
-        <v>65</v>
-      </c>
-      <c r="AB22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC22">
-        <v>7</v>
-      </c>
-      <c r="AD22">
-        <v>17</v>
-      </c>
-      <c r="AE22">
-        <v>60</v>
-      </c>
-      <c r="AF22">
-        <v>970</v>
-      </c>
-      <c r="AG22">
-        <v>16</v>
-      </c>
-      <c r="AH22">
-        <v>32</v>
-      </c>
-      <c r="AI22">
-        <v>100</v>
-      </c>
-      <c r="AJ22">
-        <v>75</v>
-      </c>
-      <c r="AK22">
-        <v>65</v>
-      </c>
-      <c r="AL22">
-        <v>110</v>
-      </c>
-      <c r="AM22">
-        <v>280</v>
-      </c>
-      <c r="AN22">
-        <v>90</v>
-      </c>
-      <c r="AO22">
-        <v>80</v>
-      </c>
-      <c r="AP22">
-        <v>6.4</v>
-      </c>
-      <c r="AQ22">
-        <v>7</v>
-      </c>
-      <c r="AR22">
-        <v>15</v>
-      </c>
-      <c r="AS22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT22">
-        <v>7.2</v>
-      </c>
-      <c r="AU22">
-        <v>6.2</v>
-      </c>
-      <c r="AV22">
-        <v>13</v>
-      </c>
-      <c r="AW22">
-        <v>8</v>
-      </c>
-      <c r="AX22">
-        <v>16</v>
-      </c>
-      <c r="AY22">
-        <v>13.5</v>
-      </c>
-      <c r="AZ22">
-        <v>21</v>
-      </c>
-      <c r="BA22">
-        <v>8.6</v>
-      </c>
-      <c r="BB22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD22">
-        <v>8.6</v>
-      </c>
-      <c r="BE22">
-        <v>9</v>
-      </c>
-      <c r="BF22">
-        <v>8.4</v>
-      </c>
-      <c r="BG22">
-        <v>8.4</v>
-      </c>
-      <c r="BH22">
-        <v>2.84</v>
-      </c>
-      <c r="BI22">
-        <v>2.04</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.56</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.56</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.56</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>1.56</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>1.56</v>
-      </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
       <c r="BU22">
-        <v>1.56</v>
+        <v>3.85</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW22">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="CB22" t="s">
         <v>187</v>
@@ -6256,16 +6256,16 @@
         <v>9.4</v>
       </c>
       <c r="G23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23">
         <v>1.43</v>
       </c>
       <c r="I23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="J23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
         <v>4.9</v>
@@ -6295,7 +6295,7 @@
         <v>4</v>
       </c>
       <c r="T23">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
         <v>1.65</v>
@@ -6313,31 +6313,31 @@
         <v>6.4</v>
       </c>
       <c r="Z23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AA23">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AB23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC23">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD23">
         <v>11</v>
       </c>
       <c r="AE23">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AF23">
         <v>110</v>
       </c>
       <c r="AG23">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AH23">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AI23">
         <v>65</v>
@@ -6358,10 +6358,10 @@
         <v>490</v>
       </c>
       <c r="AO23">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AP23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23">
         <v>5.6</v>
@@ -6370,46 +6370,46 @@
         <v>6.6</v>
       </c>
       <c r="AS23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT23">
         <v>21</v>
       </c>
       <c r="AU23">
+        <v>9.6</v>
+      </c>
+      <c r="AV23">
         <v>9.4</v>
       </c>
-      <c r="AV23">
+      <c r="AW23">
+        <v>16</v>
+      </c>
+      <c r="AX23">
         <v>9.6</v>
       </c>
-      <c r="AW23">
-        <v>15.5</v>
-      </c>
-      <c r="AX23">
-        <v>7.4</v>
-      </c>
       <c r="AY23">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="AZ23">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BA23">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BB23">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BC23">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BD23">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BE23">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BF23">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BG23">
         <v>8.4</v>
@@ -6418,37 +6418,37 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BJ23">
         <v>19</v>
       </c>
       <c r="BK23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BN23">
         <v>18.5</v>
       </c>
       <c r="BO23">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BT23">
         <v>4.9</v>
@@ -6457,7 +6457,7 @@
         <v>2.88</v>
       </c>
       <c r="BV23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BW23">
         <v>1.58</v>
@@ -6472,7 +6472,7 @@
         <v>30</v>
       </c>
       <c r="CA23">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CB23" t="s">
         <v>187</v>
@@ -6495,166 +6495,166 @@
         <v>171</v>
       </c>
       <c r="F24">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G24">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H24">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I24">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J24">
         <v>3.85</v>
       </c>
       <c r="K24">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P24">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q24">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R24">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S24">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="T24">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y24">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="Z24">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA24">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB24">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC24">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AE24">
         <v>55</v>
       </c>
       <c r="AF24">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AG24">
+        <v>11</v>
+      </c>
+      <c r="AH24">
         <v>16</v>
       </c>
-      <c r="AH24">
-        <v>23</v>
-      </c>
       <c r="AI24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ24">
         <v>38</v>
       </c>
       <c r="AK24">
+        <v>20</v>
+      </c>
+      <c r="AL24">
+        <v>42</v>
+      </c>
+      <c r="AM24">
+        <v>95</v>
+      </c>
+      <c r="AN24">
+        <v>11.5</v>
+      </c>
+      <c r="AO24">
+        <v>29</v>
+      </c>
+      <c r="AP24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ24">
+        <v>15</v>
+      </c>
+      <c r="AR24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS24">
+        <v>11</v>
+      </c>
+      <c r="AT24">
+        <v>11</v>
+      </c>
+      <c r="AU24">
+        <v>8.4</v>
+      </c>
+      <c r="AV24">
+        <v>13</v>
+      </c>
+      <c r="AW24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX24">
+        <v>13.5</v>
+      </c>
+      <c r="AY24">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24">
+        <v>13.5</v>
+      </c>
+      <c r="BA24">
         <v>25</v>
       </c>
-      <c r="AL24">
-        <v>44</v>
-      </c>
-      <c r="AM24">
-        <v>100</v>
-      </c>
-      <c r="AN24">
-        <v>17</v>
-      </c>
-      <c r="AO24">
-        <v>44</v>
-      </c>
-      <c r="AP24">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24">
-        <v>10.5</v>
-      </c>
-      <c r="AR24">
-        <v>16.5</v>
-      </c>
-      <c r="AS24">
-        <v>1.01</v>
-      </c>
-      <c r="AT24">
-        <v>7.8</v>
-      </c>
-      <c r="AU24">
-        <v>5.9</v>
-      </c>
-      <c r="AV24">
+      <c r="BB24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC24">
+        <v>12.5</v>
+      </c>
+      <c r="BD24">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW24">
-        <v>1.03</v>
-      </c>
-      <c r="AX24">
+      <c r="BE24">
+        <v>11</v>
+      </c>
+      <c r="BF24">
+        <v>10</v>
+      </c>
+      <c r="BG24">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AY24">
-        <v>7</v>
-      </c>
-      <c r="AZ24">
-        <v>9.6</v>
-      </c>
-      <c r="BA24">
-        <v>1.03</v>
-      </c>
-      <c r="BB24">
-        <v>15.5</v>
-      </c>
-      <c r="BC24">
-        <v>12</v>
-      </c>
-      <c r="BD24">
-        <v>17.5</v>
-      </c>
-      <c r="BE24">
-        <v>1.01</v>
-      </c>
-      <c r="BF24">
-        <v>7.2</v>
-      </c>
-      <c r="BG24">
-        <v>17.5</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6737,55 +6737,55 @@
         <v>172</v>
       </c>
       <c r="F25">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="G25">
         <v>2.18</v>
       </c>
       <c r="H25">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="I25">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J25">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K25">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q25">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R25">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S25">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V25">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
         <v>1.86</v>
@@ -6803,10 +6803,10 @@
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD25">
         <v>1000</v>
@@ -6818,7 +6818,7 @@
         <v>1000</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH25">
         <v>1000</v>
@@ -6839,64 +6839,64 @@
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO25">
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6982,16 +6982,16 @@
         <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H26">
         <v>3.25</v>
       </c>
       <c r="I26">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J26">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K26">
         <v>4</v>
@@ -7000,145 +7000,145 @@
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N26">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P26">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R26">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S26">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="T26">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U26">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V26">
         <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X26">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC26">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE26">
+        <v>42</v>
+      </c>
+      <c r="AF26">
+        <v>16.5</v>
+      </c>
+      <c r="AG26">
+        <v>12</v>
+      </c>
+      <c r="AH26">
+        <v>16.5</v>
+      </c>
+      <c r="AI26">
         <v>44</v>
-      </c>
-      <c r="AF26">
-        <v>1000</v>
-      </c>
-      <c r="AG26">
-        <v>1000</v>
-      </c>
-      <c r="AH26">
-        <v>17.5</v>
-      </c>
-      <c r="AI26">
-        <v>1000</v>
       </c>
       <c r="AJ26">
         <v>36</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL26">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM26">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>16</v>
       </c>
       <c r="AQ26">
-        <v>1.42</v>
+        <v>13.5</v>
       </c>
       <c r="AR26">
-        <v>1.42</v>
+        <v>5.7</v>
       </c>
       <c r="AS26">
-        <v>1.42</v>
+        <v>6.2</v>
       </c>
       <c r="AT26">
-        <v>1.42</v>
+        <v>10.5</v>
       </c>
       <c r="AU26">
-        <v>1.28</v>
+        <v>8</v>
       </c>
       <c r="AV26">
-        <v>1.42</v>
+        <v>13</v>
       </c>
       <c r="AW26">
-        <v>1.38</v>
+        <v>5.9</v>
       </c>
       <c r="AX26">
-        <v>1.42</v>
+        <v>14</v>
       </c>
       <c r="AY26">
-        <v>1.42</v>
+        <v>10</v>
       </c>
       <c r="AZ26">
-        <v>1.31</v>
+        <v>14</v>
       </c>
       <c r="BA26">
-        <v>1.42</v>
+        <v>6</v>
       </c>
       <c r="BB26">
-        <v>1.37</v>
+        <v>5.9</v>
       </c>
       <c r="BC26">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD26">
-        <v>1.37</v>
+        <v>5.8</v>
       </c>
       <c r="BE26">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF26">
-        <v>1.42</v>
+        <v>11.5</v>
       </c>
       <c r="BG26">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7162,7 +7162,7 @@
         <v>7</v>
       </c>
       <c r="BO26">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP26">
         <v>22</v>
@@ -7221,22 +7221,22 @@
         <v>174</v>
       </c>
       <c r="F27">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H27">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I27">
         <v>5</v>
       </c>
       <c r="J27">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7245,22 +7245,22 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="O27">
         <v>1.19</v>
       </c>
       <c r="P27">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q27">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R27">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S27">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="T27">
         <v>1.01</v>
@@ -7272,7 +7272,7 @@
         <v>1.25</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7466,55 +7466,55 @@
         <v>3.8</v>
       </c>
       <c r="G28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H28">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I28">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J28">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K28">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L28">
         <v>1.3</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O28">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P28">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q28">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="R28">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S28">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="T28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U28">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V28">
         <v>1.94</v>
       </c>
       <c r="W28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7535,13 +7535,13 @@
         <v>970</v>
       </c>
       <c r="AD28">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE28">
         <v>21</v>
       </c>
       <c r="AF28">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG28">
         <v>18</v>
@@ -7550,10 +7550,10 @@
         <v>18</v>
       </c>
       <c r="AI28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ28">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
         <v>1000</v>
@@ -7565,13 +7565,13 @@
         <v>85</v>
       </c>
       <c r="AN28">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO28">
         <v>11.5</v>
       </c>
       <c r="AP28">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="AQ28">
         <v>8</v>
@@ -7580,7 +7580,7 @@
         <v>9</v>
       </c>
       <c r="AS28">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT28">
         <v>11</v>
@@ -7595,7 +7595,7 @@
         <v>11.5</v>
       </c>
       <c r="AX28">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AY28">
         <v>10</v>
@@ -7604,25 +7604,25 @@
         <v>10.5</v>
       </c>
       <c r="BA28">
-        <v>21</v>
+        <v>2.32</v>
       </c>
       <c r="BB28">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="BC28">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BD28">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BE28">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="BF28">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="BG28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7640,31 +7640,31 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="BT28">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>3.55</v>
+        <v>1.46</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7676,13 +7676,13 @@
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="CB28" t="s">
         <v>187</v>
@@ -7705,226 +7705,226 @@
         <v>176</v>
       </c>
       <c r="F29">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="G29">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="H29">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="I29">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="J29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K29">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M29">
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P29">
         <v>3.75</v>
       </c>
       <c r="Q29">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="R29">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="S29">
         <v>1.74</v>
       </c>
       <c r="T29">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V29">
         <v>1.06</v>
       </c>
       <c r="W29">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA29">
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF29">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AG29">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ29">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AK29">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN29">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP29">
-        <v>1.84</v>
+        <v>8</v>
       </c>
       <c r="AQ29">
-        <v>1.84</v>
+        <v>8.4</v>
       </c>
       <c r="AR29">
-        <v>1.84</v>
+        <v>9</v>
       </c>
       <c r="AS29">
-        <v>1.84</v>
+        <v>9.4</v>
       </c>
       <c r="AT29">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AU29">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AV29">
-        <v>1.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW29">
-        <v>1.84</v>
+        <v>9</v>
       </c>
       <c r="AX29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY29">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ29">
-        <v>1.92</v>
+        <v>7.4</v>
       </c>
       <c r="BA29">
-        <v>1.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BC29">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BD29">
-        <v>1.84</v>
+        <v>7.6</v>
       </c>
       <c r="BE29">
-        <v>1.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BG29">
-        <v>1.84</v>
+        <v>9</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="CB29" t="s">
         <v>187</v>
@@ -7971,31 +7971,31 @@
         <v>1.07</v>
       </c>
       <c r="N30">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O30">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P30">
         <v>1.92</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R30">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S30">
         <v>3.55</v>
       </c>
       <c r="T30">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W30">
         <v>1.46</v>
@@ -8007,7 +8007,7 @@
         <v>11</v>
       </c>
       <c r="Z30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA30">
         <v>36</v>
@@ -8016,13 +8016,13 @@
         <v>12.5</v>
       </c>
       <c r="AC30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE30">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF30">
         <v>22</v>
@@ -8034,25 +8034,25 @@
         <v>18</v>
       </c>
       <c r="AI30">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ30">
         <v>55</v>
       </c>
       <c r="AK30">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL30">
         <v>48</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN30">
         <v>34</v>
       </c>
       <c r="AO30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP30">
         <v>12.5</v>
@@ -8064,19 +8064,19 @@
         <v>14.5</v>
       </c>
       <c r="AS30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT30">
         <v>11.5</v>
       </c>
       <c r="AU30">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV30">
         <v>10.5</v>
       </c>
       <c r="AW30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX30">
         <v>18.5</v>
@@ -8088,31 +8088,31 @@
         <v>15</v>
       </c>
       <c r="BA30">
+        <v>36</v>
+      </c>
+      <c r="BB30">
+        <v>46</v>
+      </c>
+      <c r="BC30">
         <v>32</v>
-      </c>
-      <c r="BB30">
-        <v>27</v>
-      </c>
-      <c r="BC30">
-        <v>30</v>
       </c>
       <c r="BD30">
         <v>40</v>
       </c>
       <c r="BE30">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BF30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG30">
         <v>19.5</v>
       </c>
       <c r="BH30">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>2.86</v>
+        <v>1.5</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
@@ -8130,7 +8130,7 @@
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>4.1</v>
+        <v>1.92</v>
       </c>
       <c r="BP30">
         <v>1000</v>
@@ -8148,7 +8148,7 @@
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>3.7</v>
+        <v>1.83</v>
       </c>
       <c r="BV30">
         <v>1000</v>
@@ -8192,13 +8192,13 @@
         <v>2.04</v>
       </c>
       <c r="G31">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H31">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I31">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J31">
         <v>3.8</v>
@@ -8213,55 +8213,55 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O31">
         <v>1.27</v>
       </c>
       <c r="P31">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="R31">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S31">
         <v>3.1</v>
       </c>
       <c r="T31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U31">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y31">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z31">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA31">
         <v>1000</v>
       </c>
       <c r="AB31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC31">
         <v>8.6</v>
       </c>
       <c r="AD31">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE31">
         <v>110</v>
@@ -8270,70 +8270,70 @@
         <v>14</v>
       </c>
       <c r="AG31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH31">
         <v>18</v>
       </c>
       <c r="AI31">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ31">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AK31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL31">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM31">
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO31">
         <v>100</v>
       </c>
       <c r="AP31">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR31">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS31">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT31">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV31">
         <v>13</v>
       </c>
       <c r="AW31">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AX31">
         <v>11.5</v>
       </c>
       <c r="AY31">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA31">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB31">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BC31">
         <v>17</v>
@@ -8345,22 +8345,22 @@
         <v>50</v>
       </c>
       <c r="BF31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG31">
         <v>24</v>
       </c>
       <c r="BH31">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>2.72</v>
+        <v>1.5</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8372,7 +8372,7 @@
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="BP31">
         <v>1000</v>
@@ -8390,7 +8390,7 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>4.8</v>
+        <v>1.92</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8431,13 +8431,13 @@
         <v>179</v>
       </c>
       <c r="F32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="G32">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H32">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I32">
         <v>10.5</v>
@@ -8449,13 +8449,13 @@
         <v>6.4</v>
       </c>
       <c r="L32">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M32">
         <v>1.03</v>
       </c>
       <c r="N32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O32">
         <v>1.16</v>
@@ -8473,130 +8473,130 @@
         <v>2.2</v>
       </c>
       <c r="T32">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U32">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V32">
         <v>1.1</v>
       </c>
       <c r="W32">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="X32">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
         <v>12.5</v>
       </c>
       <c r="AC32">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD32">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AG32">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH32">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AK32">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AL32">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AO32">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>7.8</v>
+        <v>1.99</v>
       </c>
       <c r="AQ32">
-        <v>8.199999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="AR32">
-        <v>9.4</v>
+        <v>1.99</v>
       </c>
       <c r="AS32">
-        <v>9.800000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="AT32">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AU32">
-        <v>12.5</v>
+        <v>1.87</v>
       </c>
       <c r="AV32">
-        <v>8.199999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="AW32">
-        <v>9.4</v>
+        <v>1.99</v>
       </c>
       <c r="AX32">
         <v>8.800000000000001</v>
       </c>
       <c r="AY32">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AZ32">
-        <v>21</v>
+        <v>1.99</v>
       </c>
       <c r="BA32">
-        <v>9.4</v>
+        <v>1.99</v>
       </c>
       <c r="BB32">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC32">
-        <v>11.5</v>
+        <v>1.87</v>
       </c>
       <c r="BD32">
-        <v>7.8</v>
+        <v>1.99</v>
       </c>
       <c r="BE32">
-        <v>9.4</v>
+        <v>1.99</v>
       </c>
       <c r="BF32">
         <v>4</v>
       </c>
       <c r="BG32">
-        <v>9.4</v>
+        <v>1.99</v>
       </c>
       <c r="BH32">
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BJ32">
         <v>15.5</v>
@@ -8608,13 +8608,13 @@
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BN32">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO32">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP32">
         <v>10.5</v>
@@ -8626,31 +8626,31 @@
         <v>29</v>
       </c>
       <c r="BS32">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="BT32">
         <v>19</v>
       </c>
       <c r="BU32">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BZ32">
         <v>13.5</v>
       </c>
       <c r="CA32">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="CB32" t="s">
         <v>187</v>
@@ -8673,16 +8673,16 @@
         <v>180</v>
       </c>
       <c r="F33">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G33">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H33">
         <v>5</v>
       </c>
       <c r="I33">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33">
         <v>4.2</v>
@@ -8691,13 +8691,13 @@
         <v>4.3</v>
       </c>
       <c r="L33">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M33">
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O33">
         <v>1.2</v>
@@ -8709,28 +8709,28 @@
         <v>1.63</v>
       </c>
       <c r="R33">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S33">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U33">
         <v>2.46</v>
       </c>
       <c r="V33">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W33">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X33">
+        <v>22</v>
+      </c>
+      <c r="Y33">
         <v>23</v>
-      </c>
-      <c r="Y33">
-        <v>24</v>
       </c>
       <c r="Z33">
         <v>42</v>
@@ -8745,7 +8745,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE33">
         <v>55</v>
@@ -8757,28 +8757,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH33">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI33">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK33">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM33">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN33">
         <v>7.8</v>
       </c>
       <c r="AO33">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP33">
         <v>20</v>
@@ -8790,19 +8790,19 @@
         <v>38</v>
       </c>
       <c r="AS33">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AT33">
         <v>11</v>
       </c>
       <c r="AU33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV33">
         <v>17.5</v>
       </c>
       <c r="AW33">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX33">
         <v>11.5</v>
@@ -8814,10 +8814,10 @@
         <v>15</v>
       </c>
       <c r="BA33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB33">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC33">
         <v>14.5</v>
@@ -8829,70 +8829,70 @@
         <v>60</v>
       </c>
       <c r="BF33">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG33">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BH33">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BI33">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="BJ33">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BK33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BL33">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
         <v>21</v>
       </c>
       <c r="BN33">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BO33">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP33">
+        <v>15.5</v>
+      </c>
+      <c r="BQ33">
+        <v>8.4</v>
+      </c>
+      <c r="BR33">
+        <v>30</v>
+      </c>
+      <c r="BS33">
         <v>13.5</v>
       </c>
-      <c r="BQ33">
+      <c r="BT33">
         <v>10</v>
       </c>
-      <c r="BR33">
-        <v>26</v>
-      </c>
-      <c r="BS33">
-        <v>16</v>
-      </c>
-      <c r="BT33">
-        <v>8.4</v>
-      </c>
       <c r="BU33">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BV33">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BW33">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BX33">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BZ33">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="CA33">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="CB33" t="s">
         <v>187</v>
@@ -8924,7 +8924,7 @@
         <v>1.8</v>
       </c>
       <c r="I34">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J34">
         <v>3.85</v>
@@ -8933,19 +8933,19 @@
         <v>3.9</v>
       </c>
       <c r="L34">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M34">
         <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O34">
         <v>1.34</v>
       </c>
       <c r="P34">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q34">
         <v>2.02</v>
@@ -8954,16 +8954,16 @@
         <v>1.35</v>
       </c>
       <c r="S34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T34">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U34">
         <v>2.02</v>
       </c>
       <c r="V34">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W34">
         <v>1.22</v>
@@ -8981,7 +8981,7 @@
         <v>19</v>
       </c>
       <c r="AB34">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC34">
         <v>8.4</v>
@@ -8999,10 +8999,10 @@
         <v>20</v>
       </c>
       <c r="AH34">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI34">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ34">
         <v>140</v>
@@ -9011,7 +9011,7 @@
         <v>75</v>
       </c>
       <c r="AL34">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM34">
         <v>130</v>
@@ -9023,7 +9023,7 @@
         <v>12.5</v>
       </c>
       <c r="AP34">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ34">
         <v>7.8</v>
@@ -9035,7 +9035,7 @@
         <v>17</v>
       </c>
       <c r="AT34">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AU34">
         <v>8</v>
@@ -9053,25 +9053,25 @@
         <v>18</v>
       </c>
       <c r="AZ34">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA34">
         <v>34</v>
       </c>
       <c r="BB34">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC34">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BD34">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BE34">
         <v>100</v>
       </c>
       <c r="BF34">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BG34">
         <v>11</v>
@@ -9083,58 +9083,58 @@
         <v>2.82</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK34">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO34">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU34">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW34">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA34">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="CB34" t="s">
         <v>187</v>
@@ -9157,19 +9157,19 @@
         <v>182</v>
       </c>
       <c r="F35">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G35">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H35">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I35">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J35">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K35">
         <v>4.2</v>
@@ -9178,10 +9178,10 @@
         <v>1.32</v>
       </c>
       <c r="M35">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N35">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O35">
         <v>1.22</v>
@@ -9190,25 +9190,25 @@
         <v>2.44</v>
       </c>
       <c r="Q35">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R35">
         <v>1.57</v>
       </c>
       <c r="S35">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T35">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U35">
         <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W35">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X35">
         <v>21</v>
@@ -9217,10 +9217,10 @@
         <v>21</v>
       </c>
       <c r="Z35">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA35">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB35">
         <v>12</v>
@@ -9229,10 +9229,10 @@
         <v>9.6</v>
       </c>
       <c r="AD35">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE35">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF35">
         <v>13.5</v>
@@ -9244,13 +9244,13 @@
         <v>16</v>
       </c>
       <c r="AI35">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ35">
         <v>21</v>
       </c>
       <c r="AK35">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL35">
         <v>28</v>
@@ -9259,13 +9259,13 @@
         <v>70</v>
       </c>
       <c r="AN35">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO35">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP35">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ35">
         <v>19</v>
@@ -9283,10 +9283,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV35">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW35">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AX35">
         <v>12</v>
@@ -9298,25 +9298,25 @@
         <v>15</v>
       </c>
       <c r="BA35">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB35">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC35">
         <v>15.5</v>
       </c>
       <c r="BD35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE35">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF35">
         <v>8.199999999999999</v>
       </c>
       <c r="BG35">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9325,58 +9325,58 @@
         <v>3.25</v>
       </c>
       <c r="BJ35">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK35">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO35">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ35">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT35">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU35">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ35">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA35">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB35" t="s">
         <v>187</v>
@@ -9402,7 +9402,7 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H36">
         <v>1.51</v>
@@ -9411,10 +9411,10 @@
         <v>1.54</v>
       </c>
       <c r="J36">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K36">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L36">
         <v>1.27</v>
@@ -9435,16 +9435,16 @@
         <v>1.51</v>
       </c>
       <c r="R36">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S36">
         <v>2.24</v>
       </c>
       <c r="T36">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V36">
         <v>2.84</v>
@@ -9459,7 +9459,7 @@
         <v>13.5</v>
       </c>
       <c r="Z36">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA36">
         <v>15</v>
@@ -9498,16 +9498,16 @@
         <v>65</v>
       </c>
       <c r="AM36">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN36">
         <v>60</v>
       </c>
       <c r="AO36">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AP36">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AQ36">
         <v>11</v>
@@ -9519,7 +9519,7 @@
         <v>13</v>
       </c>
       <c r="AT36">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AU36">
         <v>10.5</v>
@@ -9531,7 +9531,7 @@
         <v>12.5</v>
       </c>
       <c r="AX36">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY36">
         <v>20</v>
@@ -9540,85 +9540,85 @@
         <v>16.5</v>
       </c>
       <c r="BA36">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB36">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC36">
+        <v>10</v>
+      </c>
+      <c r="BD36">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BD36">
-        <v>9.6</v>
       </c>
       <c r="BE36">
         <v>10</v>
       </c>
       <c r="BF36">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH36">
         <v>1000</v>
       </c>
       <c r="BI36">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="BJ36">
         <v>1000</v>
       </c>
       <c r="BK36">
-        <v>6.8</v>
+        <v>1.62</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BN36">
         <v>1000</v>
       </c>
       <c r="BO36">
-        <v>7.2</v>
+        <v>1.62</v>
       </c>
       <c r="BP36">
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BT36">
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>3.6</v>
+        <v>1.23</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>6.4</v>
+        <v>1.62</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="CB36" t="s">
         <v>187</v>
@@ -9647,49 +9647,49 @@
         <v>3.4</v>
       </c>
       <c r="H37">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I37">
         <v>2.42</v>
       </c>
       <c r="J37">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K37">
         <v>3.55</v>
       </c>
       <c r="L37">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M37">
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O37">
         <v>1.33</v>
       </c>
       <c r="P37">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R37">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S37">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="T37">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U37">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W37">
         <v>1.41</v>
@@ -9716,7 +9716,7 @@
         <v>11.5</v>
       </c>
       <c r="AE37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF37">
         <v>23</v>
@@ -9728,7 +9728,7 @@
         <v>18</v>
       </c>
       <c r="AI37">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ37">
         <v>60</v>
@@ -9737,16 +9737,16 @@
         <v>40</v>
       </c>
       <c r="AL37">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM37">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN37">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO37">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP37">
         <v>12.5</v>
@@ -9761,13 +9761,13 @@
         <v>28</v>
       </c>
       <c r="AT37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU37">
         <v>7.2</v>
       </c>
       <c r="AV37">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW37">
         <v>23</v>
@@ -9800,7 +9800,7 @@
         <v>30</v>
       </c>
       <c r="BG37">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH37">
         <v>3.7</v>
@@ -9809,58 +9809,58 @@
         <v>2.82</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK37">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO37">
         <v>5</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU37">
         <v>4.1</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW37">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB37" t="s">
         <v>187</v>
@@ -9892,13 +9892,13 @@
         <v>55</v>
       </c>
       <c r="I38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J38">
         <v>25</v>
       </c>
       <c r="K38">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L38">
         <v>1.14</v>
@@ -9907,28 +9907,28 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="O38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P38">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q38">
         <v>1.21</v>
       </c>
       <c r="R38">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="S38">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="T38">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U38">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V38">
         <v>1.01</v>
@@ -9952,7 +9952,7 @@
         <v>22</v>
       </c>
       <c r="AC38">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AD38">
         <v>1000</v>
@@ -9964,7 +9964,7 @@
         <v>11.5</v>
       </c>
       <c r="AG38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH38">
         <v>1000</v>
@@ -9973,25 +9973,25 @@
         <v>1000</v>
       </c>
       <c r="AJ38">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AK38">
         <v>20</v>
       </c>
       <c r="AL38">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM38">
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AO38">
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AQ38">
         <v>55</v>
@@ -10006,7 +10006,7 @@
         <v>18</v>
       </c>
       <c r="AU38">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AV38">
         <v>46</v>
@@ -10021,16 +10021,16 @@
         <v>21</v>
       </c>
       <c r="AZ38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA38">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB38">
         <v>7</v>
       </c>
       <c r="BC38">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD38">
         <v>36</v>
@@ -10039,70 +10039,70 @@
         <v>55</v>
       </c>
       <c r="BF38">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BG38">
         <v>60</v>
       </c>
       <c r="BH38">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BI38">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="BJ38">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BK38">
-        <v>16.5</v>
+        <v>2.88</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="BN38">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BO38">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BP38">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BQ38">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BR38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BS38">
-        <v>19.5</v>
+        <v>2.92</v>
       </c>
       <c r="BT38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BU38">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="BZ38">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="CA38">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="CB38" t="s">
         <v>187</v>
@@ -10125,10 +10125,10 @@
         <v>186</v>
       </c>
       <c r="F39">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G39">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H39">
         <v>1.18</v>
@@ -10137,40 +10137,40 @@
         <v>1.2</v>
       </c>
       <c r="J39">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K39">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M39">
         <v>1.02</v>
       </c>
       <c r="N39">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="O39">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P39">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q39">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R39">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="S39">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T39">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="U39">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V39">
         <v>6</v>
@@ -10179,31 +10179,31 @@
         <v>1.04</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y39">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z39">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA39">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB39">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC39">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AD39">
+        <v>14.5</v>
+      </c>
+      <c r="AE39">
         <v>16</v>
       </c>
-      <c r="AE39">
-        <v>18.5</v>
-      </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AG39">
         <v>80</v>
@@ -10218,133 +10218,133 @@
         <v>1000</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN39">
         <v>1000</v>
       </c>
       <c r="AO39">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AP39">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AQ39">
+        <v>9.6</v>
+      </c>
+      <c r="AR39">
+        <v>7</v>
+      </c>
+      <c r="AS39">
+        <v>7</v>
+      </c>
+      <c r="AT39">
         <v>9.4</v>
       </c>
-      <c r="AR39">
-        <v>5.9</v>
-      </c>
-      <c r="AS39">
-        <v>6</v>
-      </c>
-      <c r="AT39">
-        <v>4.4</v>
-      </c>
       <c r="AU39">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV39">
+        <v>12</v>
+      </c>
+      <c r="AW39">
+        <v>13</v>
+      </c>
+      <c r="AX39">
         <v>10.5</v>
       </c>
-      <c r="AW39">
-        <v>12</v>
-      </c>
-      <c r="AX39">
-        <v>4.7</v>
-      </c>
       <c r="AY39">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ39">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA39">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB39">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BC39">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BD39">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BE39">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BF39">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BG39">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BH39">
         <v>1000</v>
       </c>
       <c r="BI39">
-        <v>3.9</v>
+        <v>2.44</v>
       </c>
       <c r="BJ39">
         <v>23</v>
       </c>
       <c r="BK39">
-        <v>11</v>
+        <v>2.22</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>21</v>
+        <v>2.44</v>
       </c>
       <c r="BN39">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BO39">
-        <v>13</v>
+        <v>2.26</v>
       </c>
       <c r="BP39">
         <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>21</v>
+        <v>2.44</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>21</v>
+        <v>2.44</v>
       </c>
       <c r="BT39">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BU39">
-        <v>3.1</v>
+        <v>1.52</v>
       </c>
       <c r="BV39">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BW39">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BX39">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>14.5</v>
+        <v>2.26</v>
       </c>
       <c r="BZ39">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA39">
-        <v>4.9</v>
+        <v>1.97</v>
       </c>
       <c r="CB39" t="s">
         <v>187</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -577,7 +577,7 @@
     <t>Benfica</t>
   </si>
   <si>
-    <t>2026-09-07 19:22:10</t>
+    <t>2026-09-07 21:33:57</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1171,7 @@
         <v>149</v>
       </c>
       <c r="F2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
         <v>2.26</v>
@@ -1180,10 +1180,10 @@
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="K2">
         <v>3.15</v>
@@ -1195,7 +1195,7 @@
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O2">
         <v>1.61</v>
@@ -1222,7 +1222,7 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X2">
         <v>7.8</v>
@@ -1255,7 +1255,7 @@
         <v>970</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -1285,10 +1285,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AS2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AT2">
         <v>5.2</v>
@@ -1297,10 +1297,10 @@
         <v>5.4</v>
       </c>
       <c r="AV2">
-        <v>2.02</v>
+        <v>17</v>
       </c>
       <c r="AW2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
@@ -1312,25 +1312,25 @@
         <v>2.02</v>
       </c>
       <c r="BA2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="BB2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="BC2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="BD2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="BE2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="BF2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="BG2">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1455,7 +1455,7 @@
         <v>2.2</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
         <v>1.01</v>
@@ -1664,10 +1664,10 @@
         <v>5.5</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
         <v>4.5</v>
@@ -1679,7 +1679,7 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>1.25</v>
@@ -1691,16 +1691,16 @@
         <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S4">
         <v>2.94</v>
       </c>
       <c r="T4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
         <v>1.2</v>
@@ -1712,10 +1712,10 @@
         <v>18.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1724,10 +1724,10 @@
         <v>9.4</v>
       </c>
       <c r="AC4">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE4">
         <v>1000</v>
@@ -1757,22 +1757,22 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
         <v>17</v>
       </c>
       <c r="AR4">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="AS4">
-        <v>3.55</v>
+        <v>17.5</v>
       </c>
       <c r="AT4">
         <v>7.8</v>
@@ -1784,7 +1784,7 @@
         <v>19</v>
       </c>
       <c r="AW4">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="AX4">
         <v>8.6</v>
@@ -1796,25 +1796,25 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>3.4</v>
+        <v>17</v>
       </c>
       <c r="BB4">
         <v>10</v>
       </c>
       <c r="BC4">
+        <v>13.5</v>
+      </c>
+      <c r="BD4">
         <v>10.5</v>
       </c>
-      <c r="BD4">
-        <v>3.25</v>
-      </c>
       <c r="BE4">
-        <v>3.55</v>
+        <v>17</v>
       </c>
       <c r="BF4">
         <v>7.6</v>
       </c>
       <c r="BG4">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1823,58 +1823,58 @@
         <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BN4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP4">
         <v>15</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BT4">
         <v>13</v>
       </c>
       <c r="BU4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BZ4">
         <v>26</v>
       </c>
       <c r="CA4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1897,19 +1897,19 @@
         <v>152</v>
       </c>
       <c r="F5">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G5">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H5">
         <v>2.78</v>
       </c>
       <c r="I5">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="J5">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
         <v>3.5</v>
@@ -1921,46 +1921,46 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="X5">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y5">
         <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB5">
         <v>10.5</v>
@@ -1969,112 +1969,112 @@
         <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG5">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
         <v>16</v>
       </c>
       <c r="AS5">
-        <v>1.96</v>
+        <v>25</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
       </c>
       <c r="AU5">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>1.96</v>
+        <v>22</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AY5">
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>1.96</v>
+        <v>29</v>
       </c>
       <c r="BB5">
-        <v>1.96</v>
+        <v>24</v>
       </c>
       <c r="BC5">
-        <v>1.96</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>1.96</v>
+        <v>28</v>
       </c>
       <c r="BE5">
-        <v>1.96</v>
+        <v>42</v>
       </c>
       <c r="BF5">
-        <v>1.96</v>
+        <v>21</v>
       </c>
       <c r="BG5">
-        <v>1.96</v>
+        <v>22</v>
       </c>
       <c r="BH5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BI5">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BN5">
         <v>1000</v>
@@ -2086,13 +2086,13 @@
         <v>34</v>
       </c>
       <c r="BQ5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BT5">
         <v>1000</v>
@@ -2104,19 +2104,19 @@
         <v>36</v>
       </c>
       <c r="BW5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BZ5">
         <v>50</v>
       </c>
       <c r="CA5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2139,7 +2139,7 @@
         <v>153</v>
       </c>
       <c r="F6">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="G6">
         <v>2.66</v>
@@ -2148,7 +2148,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
         <v>3.25</v>
@@ -2157,7 +2157,7 @@
         <v>3.5</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
         <v>1.09</v>
@@ -2166,7 +2166,7 @@
         <v>3.15</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
         <v>1.71</v>
@@ -2187,13 +2187,13 @@
         <v>1.9</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
         <v>1.6</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Y6">
         <v>12.5</v>
@@ -2202,19 +2202,19 @@
         <v>26</v>
       </c>
       <c r="AA6">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
         <v>10.5</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6">
         <v>17</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF6">
         <v>19</v>
@@ -2247,7 +2247,7 @@
         <v>55</v>
       </c>
       <c r="AP6">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6">
         <v>8.4</v>
@@ -2256,31 +2256,31 @@
         <v>15.5</v>
       </c>
       <c r="AS6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT6">
         <v>7</v>
       </c>
       <c r="AU6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV6">
         <v>11</v>
       </c>
       <c r="AW6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX6">
         <v>12</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB6">
         <v>25</v>
@@ -2289,76 +2289,76 @@
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF6">
         <v>19</v>
       </c>
       <c r="BG6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BI6">
         <v>2.52</v>
       </c>
       <c r="BJ6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BN6">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BO6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>29</v>
       </c>
       <c r="BQ6">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="BR6">
         <v>50</v>
       </c>
       <c r="BS6">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="BT6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="BV6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW6">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="BZ6">
         <v>50</v>
       </c>
       <c r="CA6">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2381,22 +2381,22 @@
         <v>154</v>
       </c>
       <c r="F7">
+        <v>3.85</v>
+      </c>
+      <c r="G7">
+        <v>4.6</v>
+      </c>
+      <c r="H7">
+        <v>1.97</v>
+      </c>
+      <c r="I7">
+        <v>2.12</v>
+      </c>
+      <c r="J7">
+        <v>3.4</v>
+      </c>
+      <c r="K7">
         <v>3.95</v>
-      </c>
-      <c r="G7">
-        <v>5.4</v>
-      </c>
-      <c r="H7">
-        <v>1.95</v>
-      </c>
-      <c r="I7">
-        <v>2.14</v>
-      </c>
-      <c r="J7">
-        <v>3.2</v>
-      </c>
-      <c r="K7">
-        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2405,10 +2405,10 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
         <v>1.73</v>
@@ -2429,13 +2429,13 @@
         <v>1.9</v>
       </c>
       <c r="V7">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y7">
         <v>9.800000000000001</v>
@@ -2447,13 +2447,13 @@
         <v>30</v>
       </c>
       <c r="AB7">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AC7">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
         <v>29</v>
@@ -2486,13 +2486,13 @@
         <v>100</v>
       </c>
       <c r="AO7">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AP7">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR7">
         <v>8.6</v>
@@ -2504,16 +2504,16 @@
         <v>11</v>
       </c>
       <c r="AU7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW7">
         <v>14</v>
       </c>
       <c r="AX7">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AY7">
         <v>13</v>
@@ -2522,22 +2522,22 @@
         <v>15</v>
       </c>
       <c r="BA7">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BC7">
-        <v>3.65</v>
+        <v>24</v>
       </c>
       <c r="BD7">
-        <v>3.65</v>
+        <v>27</v>
       </c>
       <c r="BE7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BF7">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BG7">
         <v>12.5</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BN7">
         <v>1000</v>
@@ -2570,13 +2570,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BT7">
         <v>5.4</v>
@@ -2594,13 +2594,13 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CB7" t="s">
         <v>187</v>
@@ -2626,10 +2626,10 @@
         <v>3.1</v>
       </c>
       <c r="G8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H8">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I8">
         <v>2.96</v>
@@ -2650,7 +2650,7 @@
         <v>2.18</v>
       </c>
       <c r="O8">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P8">
         <v>1.37</v>
@@ -2668,13 +2668,13 @@
         <v>2.2</v>
       </c>
       <c r="U8">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V8">
         <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X8">
         <v>970</v>
@@ -2692,7 +2692,7 @@
         <v>970</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2737,52 +2737,52 @@
         <v>5.6</v>
       </c>
       <c r="AR8">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AS8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AT8">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="AU8">
-        <v>5.4</v>
+        <v>1.58</v>
       </c>
       <c r="AV8">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AW8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AX8">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AY8">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AZ8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BA8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BB8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BC8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BD8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BE8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BF8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BG8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2865,10 +2865,10 @@
         <v>156</v>
       </c>
       <c r="F9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G9">
-        <v>2.56</v>
+        <v>110</v>
       </c>
       <c r="H9">
         <v>3</v>
@@ -2877,7 +2877,7 @@
         <v>110</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2904,7 +2904,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2913,10 +2913,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W9">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3149,10 +3149,10 @@
         <v>4.8</v>
       </c>
       <c r="T10">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V10">
         <v>1.1</v>
@@ -3218,7 +3218,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ10">
-        <v>18.5</v>
+        <v>1.63</v>
       </c>
       <c r="AR10">
         <v>1.63</v>
@@ -3251,7 +3251,7 @@
         <v>1.63</v>
       </c>
       <c r="BB10">
-        <v>10.5</v>
+        <v>1.62</v>
       </c>
       <c r="BC10">
         <v>1.63</v>
@@ -3290,7 +3290,7 @@
         <v>4.8</v>
       </c>
       <c r="BO10">
-        <v>2.7</v>
+        <v>1.26</v>
       </c>
       <c r="BP10">
         <v>15</v>
@@ -3606,7 +3606,7 @@
         <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L12">
         <v>1.37</v>
@@ -3630,10 +3630,10 @@
         <v>1.3</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U12">
         <v>2.1</v>
@@ -3717,7 +3717,7 @@
         <v>6</v>
       </c>
       <c r="AV12">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
         <v>1.61</v>
@@ -3836,7 +3836,7 @@
         <v>1.35</v>
       </c>
       <c r="G13">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="H13">
         <v>2.3</v>
@@ -3854,13 +3854,13 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
         <v>1.45</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="P13">
         <v>1.44</v>
@@ -3881,10 +3881,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4078,7 +4078,7 @@
         <v>3.05</v>
       </c>
       <c r="G14">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H14">
         <v>2.28</v>
@@ -4090,157 +4090,157 @@
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
         <v>1.34</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O14">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P14">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q14">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S14">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="T14">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="U14">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
         <v>1.68</v>
       </c>
       <c r="W14">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y14">
+        <v>12.5</v>
+      </c>
+      <c r="Z14">
+        <v>17.5</v>
+      </c>
+      <c r="AA14">
+        <v>34</v>
+      </c>
+      <c r="AB14">
+        <v>15</v>
+      </c>
+      <c r="AC14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14">
+        <v>12</v>
+      </c>
+      <c r="AE14">
+        <v>25</v>
+      </c>
+      <c r="AF14">
+        <v>25</v>
+      </c>
+      <c r="AG14">
         <v>14.5</v>
       </c>
-      <c r="Z14">
+      <c r="AH14">
+        <v>17</v>
+      </c>
+      <c r="AI14">
+        <v>38</v>
+      </c>
+      <c r="AJ14">
+        <v>55</v>
+      </c>
+      <c r="AK14">
+        <v>36</v>
+      </c>
+      <c r="AL14">
+        <v>46</v>
+      </c>
+      <c r="AM14">
+        <v>80</v>
+      </c>
+      <c r="AN14">
+        <v>30</v>
+      </c>
+      <c r="AO14">
+        <v>17</v>
+      </c>
+      <c r="AP14">
+        <v>15</v>
+      </c>
+      <c r="AQ14">
+        <v>10</v>
+      </c>
+      <c r="AR14">
+        <v>14</v>
+      </c>
+      <c r="AS14">
+        <v>8</v>
+      </c>
+      <c r="AT14">
+        <v>12</v>
+      </c>
+      <c r="AU14">
+        <v>7.6</v>
+      </c>
+      <c r="AV14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW14">
         <v>20</v>
       </c>
-      <c r="AA14">
-        <v>38</v>
-      </c>
-      <c r="AB14">
-        <v>17</v>
-      </c>
-      <c r="AC14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD14">
+      <c r="AX14">
+        <v>19.5</v>
+      </c>
+      <c r="AY14">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14">
         <v>13.5</v>
       </c>
-      <c r="AE14">
-        <v>29</v>
-      </c>
-      <c r="AF14">
-        <v>28</v>
-      </c>
-      <c r="AG14">
-        <v>16.5</v>
-      </c>
-      <c r="AH14">
-        <v>19.5</v>
-      </c>
-      <c r="AI14">
-        <v>40</v>
-      </c>
-      <c r="AJ14">
-        <v>60</v>
-      </c>
-      <c r="AK14">
-        <v>40</v>
-      </c>
-      <c r="AL14">
-        <v>55</v>
-      </c>
-      <c r="AM14">
-        <v>90</v>
-      </c>
-      <c r="AN14">
-        <v>32</v>
-      </c>
-      <c r="AO14">
-        <v>19.5</v>
-      </c>
-      <c r="AP14">
-        <v>13</v>
-      </c>
-      <c r="AQ14">
-        <v>9.6</v>
-      </c>
-      <c r="AR14">
-        <v>12.5</v>
-      </c>
-      <c r="AS14">
-        <v>21</v>
-      </c>
-      <c r="AT14">
-        <v>10.5</v>
-      </c>
-      <c r="AU14">
-        <v>6.8</v>
-      </c>
-      <c r="AV14">
+      <c r="BA14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD14">
+        <v>8.4</v>
+      </c>
+      <c r="BE14">
         <v>9.4</v>
       </c>
-      <c r="AW14">
-        <v>17.5</v>
-      </c>
-      <c r="AX14">
-        <v>17</v>
-      </c>
-      <c r="AY14">
-        <v>10</v>
-      </c>
-      <c r="AZ14">
-        <v>12</v>
-      </c>
-      <c r="BA14">
-        <v>24</v>
-      </c>
-      <c r="BB14">
-        <v>4.8</v>
-      </c>
-      <c r="BC14">
-        <v>24</v>
-      </c>
-      <c r="BD14">
-        <v>4.8</v>
-      </c>
-      <c r="BE14">
-        <v>4.9</v>
-      </c>
       <c r="BF14">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BG14">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="BJ14">
         <v>11</v>
@@ -4252,28 +4252,28 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BN14">
         <v>8</v>
       </c>
       <c r="BO14">
-        <v>5.2</v>
+        <v>2.82</v>
       </c>
       <c r="BP14">
         <v>32</v>
       </c>
       <c r="BQ14">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="BR14">
         <v>46</v>
       </c>
       <c r="BS14">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BT14">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BU14">
         <v>4.4</v>
@@ -4282,19 +4282,19 @@
         <v>23</v>
       </c>
       <c r="BW14">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="BX14">
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BZ14">
         <v>30</v>
       </c>
       <c r="CA14">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="CB14" t="s">
         <v>187</v>
@@ -4583,7 +4583,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4592,13 +4592,13 @@
         <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R16">
         <v>1.18</v>
       </c>
       <c r="S16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4607,10 +4607,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4804,19 +4804,19 @@
         <v>1.16</v>
       </c>
       <c r="G17">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="H17">
         <v>15.5</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J17">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="K17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4825,16 +4825,16 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O17">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P17">
         <v>2.66</v>
       </c>
       <c r="Q17">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R17">
         <v>1.83</v>
@@ -4849,10 +4849,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4903,64 +4903,64 @@
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AO17">
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AQ17">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AR17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AS17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AT17">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU17">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AV17">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AW17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AX17">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AY17">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AZ17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BA17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BB17">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BC17">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BD17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BF17">
         <v>2.38</v>
       </c>
       <c r="BG17">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5079,10 +5079,10 @@
         <v>1.2</v>
       </c>
       <c r="R18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S18">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T18">
         <v>1.97</v>
@@ -5097,13 +5097,13 @@
         <v>9.6</v>
       </c>
       <c r="X18">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Y18">
         <v>190</v>
       </c>
       <c r="Z18">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AA18">
         <v>1000</v>
@@ -5118,19 +5118,19 @@
         <v>140</v>
       </c>
       <c r="AE18">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AF18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH18">
         <v>55</v>
       </c>
       <c r="AI18">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AJ18">
         <v>10.5</v>
@@ -5148,7 +5148,7 @@
         <v>1.94</v>
       </c>
       <c r="AO18">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AP18">
         <v>34</v>
@@ -5157,7 +5157,7 @@
         <v>42</v>
       </c>
       <c r="AR18">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AS18">
         <v>20</v>
@@ -5172,7 +5172,7 @@
         <v>38</v>
       </c>
       <c r="AW18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX18">
         <v>12.5</v>
@@ -5187,7 +5187,7 @@
         <v>48</v>
       </c>
       <c r="BB18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC18">
         <v>13</v>
@@ -5208,25 +5208,25 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="BJ18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.7</v>
+        <v>1.18</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5235,34 +5235,34 @@
         <v>4.4</v>
       </c>
       <c r="BR18">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>2.48</v>
+        <v>1.54</v>
       </c>
       <c r="BT18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="BZ18">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>3.25</v>
+        <v>1.54</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5441,10 +5441,10 @@
         <v>34</v>
       </c>
       <c r="BF19">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BG19">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5453,10 +5453,10 @@
         <v>4.7</v>
       </c>
       <c r="BJ19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK19">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5465,25 +5465,25 @@
         <v>21</v>
       </c>
       <c r="BN19">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO19">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP19">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BS19">
         <v>12</v>
       </c>
       <c r="BT19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BU19">
         <v>11</v>
@@ -5539,7 +5539,7 @@
         <v>12.5</v>
       </c>
       <c r="J20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>7.8</v>
@@ -5560,7 +5560,7 @@
         <v>3.55</v>
       </c>
       <c r="Q20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R20">
         <v>2.1</v>
@@ -5569,10 +5569,10 @@
         <v>1.75</v>
       </c>
       <c r="T20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U20">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
         <v>1.08</v>
@@ -5599,7 +5599,7 @@
         <v>1000</v>
       </c>
       <c r="AD20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
         <v>1000</v>
@@ -5635,31 +5635,31 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AR20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AS20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AT20">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AU20">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AV20">
         <v>1.44</v>
       </c>
       <c r="AW20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AX20">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AY20">
         <v>10</v>
@@ -5668,7 +5668,7 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BB20">
         <v>10</v>
@@ -5677,16 +5677,16 @@
         <v>11</v>
       </c>
       <c r="BD20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BE20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF20">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BG20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5802,133 +5802,133 @@
         <v>1.95</v>
       </c>
       <c r="Q21">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R21">
         <v>1.36</v>
       </c>
       <c r="S21">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T21">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="U21">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V21">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W21">
         <v>1.33</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y21">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA21">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC21">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD21">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF21">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI21">
         <v>44</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP21">
-        <v>1.45</v>
+        <v>13</v>
       </c>
       <c r="AQ21">
-        <v>1.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR21">
-        <v>1.45</v>
+        <v>12</v>
       </c>
       <c r="AS21">
-        <v>1.39</v>
+        <v>19.5</v>
       </c>
       <c r="AT21">
-        <v>1.45</v>
+        <v>12.5</v>
       </c>
       <c r="AU21">
-        <v>1.29</v>
+        <v>7.2</v>
       </c>
       <c r="AV21">
-        <v>1.36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21">
-        <v>1.45</v>
+        <v>16.5</v>
       </c>
       <c r="AX21">
-        <v>1.39</v>
+        <v>19.5</v>
       </c>
       <c r="AY21">
-        <v>1.45</v>
+        <v>13</v>
       </c>
       <c r="AZ21">
-        <v>1.45</v>
+        <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>1.41</v>
+        <v>7.2</v>
       </c>
       <c r="BB21">
-        <v>1.45</v>
+        <v>7.8</v>
       </c>
       <c r="BC21">
-        <v>1.45</v>
+        <v>7.4</v>
       </c>
       <c r="BD21">
-        <v>1.45</v>
+        <v>7.6</v>
       </c>
       <c r="BE21">
-        <v>1.45</v>
+        <v>7.4</v>
       </c>
       <c r="BF21">
-        <v>1.45</v>
+        <v>7.4</v>
       </c>
       <c r="BG21">
-        <v>1.45</v>
+        <v>13.5</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6029,7 +6029,7 @@
         <v>3.15</v>
       </c>
       <c r="L22">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
         <v>1.16</v>
@@ -6089,7 +6089,7 @@
         <v>1000</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG22">
         <v>17</v>
@@ -6125,10 +6125,10 @@
         <v>5.9</v>
       </c>
       <c r="AR22">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AS22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="AT22">
         <v>6</v>
@@ -6137,40 +6137,40 @@
         <v>6</v>
       </c>
       <c r="AV22">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="AW22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="AX22">
         <v>2.32</v>
       </c>
       <c r="AY22">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="AZ22">
-        <v>2.34</v>
+        <v>19</v>
       </c>
       <c r="BA22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BB22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BC22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BD22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BE22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BF22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BG22">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6194,7 +6194,7 @@
         <v>8</v>
       </c>
       <c r="BO22">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP22">
         <v>46</v>
@@ -6212,7 +6212,7 @@
         <v>7.6</v>
       </c>
       <c r="BU22">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BV22">
         <v>40</v>
@@ -6256,19 +6256,19 @@
         <v>9.4</v>
       </c>
       <c r="G23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I23">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6283,10 +6283,10 @@
         <v>1.39</v>
       </c>
       <c r="P23">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q23">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R23">
         <v>1.3</v>
@@ -6319,7 +6319,7 @@
         <v>12.5</v>
       </c>
       <c r="AB23">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AC23">
         <v>11</v>
@@ -6328,7 +6328,7 @@
         <v>11</v>
       </c>
       <c r="AE23">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF23">
         <v>110</v>
@@ -6364,13 +6364,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR23">
         <v>6.6</v>
       </c>
       <c r="AS23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT23">
         <v>21</v>
@@ -6385,7 +6385,7 @@
         <v>16</v>
       </c>
       <c r="AX23">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY23">
         <v>24</v>
@@ -6397,19 +6397,19 @@
         <v>40</v>
       </c>
       <c r="BB23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC23">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BD23">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE23">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG23">
         <v>8.4</v>
@@ -6454,7 +6454,7 @@
         <v>4.9</v>
       </c>
       <c r="BU23">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BV23">
         <v>13.5</v>
@@ -6495,22 +6495,22 @@
         <v>171</v>
       </c>
       <c r="F24">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="G24">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H24">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="I24">
+        <v>4.1</v>
+      </c>
+      <c r="J24">
         <v>3.75</v>
       </c>
-      <c r="J24">
-        <v>3.85</v>
-      </c>
       <c r="K24">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6519,67 +6519,67 @@
         <v>1.04</v>
       </c>
       <c r="N24">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O24">
         <v>1.22</v>
       </c>
       <c r="P24">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q24">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
         <v>1.47</v>
       </c>
       <c r="S24">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T24">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U24">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="X24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y24">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Z24">
         <v>40</v>
       </c>
       <c r="AA24">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC24">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD24">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE24">
         <v>55</v>
       </c>
       <c r="AF24">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG24">
         <v>11</v>
       </c>
       <c r="AH24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI24">
         <v>55</v>
@@ -6591,70 +6591,70 @@
         <v>20</v>
       </c>
       <c r="AL24">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AM24">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN24">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO24">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AP24">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AQ24">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR24">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AS24">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AT24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU24">
         <v>8.4</v>
       </c>
       <c r="AV24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW24">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AX24">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AY24">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA24">
         <v>25</v>
       </c>
       <c r="BB24">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BC24">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BD24">
+        <v>20</v>
+      </c>
+      <c r="BE24">
+        <v>7.6</v>
+      </c>
+      <c r="BF24">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE24">
-        <v>11</v>
-      </c>
-      <c r="BF24">
-        <v>10</v>
-      </c>
       <c r="BG24">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6737,22 +6737,22 @@
         <v>172</v>
       </c>
       <c r="F25">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="G25">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="H25">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I25">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J25">
         <v>3.3</v>
       </c>
       <c r="K25">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6776,7 +6776,7 @@
         <v>1.5</v>
       </c>
       <c r="S25">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T25">
         <v>1.54</v>
@@ -6785,10 +6785,10 @@
         <v>2.34</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6806,7 +6806,7 @@
         <v>30</v>
       </c>
       <c r="AC25">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD25">
         <v>1000</v>
@@ -6818,7 +6818,7 @@
         <v>1000</v>
       </c>
       <c r="AG25">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AH25">
         <v>1000</v>
@@ -6979,22 +6979,22 @@
         <v>173</v>
       </c>
       <c r="F26">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G26">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="H26">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="I26">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J26">
         <v>3.7</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7006,58 +7006,58 @@
         <v>4.3</v>
       </c>
       <c r="O26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P26">
         <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R26">
         <v>1.48</v>
       </c>
       <c r="S26">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="T26">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U26">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="X26">
         <v>18.5</v>
       </c>
       <c r="Y26">
+        <v>15.5</v>
+      </c>
+      <c r="Z26">
+        <v>24</v>
+      </c>
+      <c r="AA26">
+        <v>55</v>
+      </c>
+      <c r="AB26">
+        <v>13</v>
+      </c>
+      <c r="AC26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26">
+        <v>14</v>
+      </c>
+      <c r="AE26">
+        <v>34</v>
+      </c>
+      <c r="AF26">
         <v>18</v>
-      </c>
-      <c r="Z26">
-        <v>30</v>
-      </c>
-      <c r="AA26">
-        <v>70</v>
-      </c>
-      <c r="AB26">
-        <v>14</v>
-      </c>
-      <c r="AC26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD26">
-        <v>17.5</v>
-      </c>
-      <c r="AE26">
-        <v>42</v>
-      </c>
-      <c r="AF26">
-        <v>16.5</v>
       </c>
       <c r="AG26">
         <v>12</v>
@@ -7066,76 +7066,76 @@
         <v>16.5</v>
       </c>
       <c r="AI26">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ26">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK26">
+        <v>25</v>
+      </c>
+      <c r="AL26">
+        <v>32</v>
+      </c>
+      <c r="AM26">
+        <v>70</v>
+      </c>
+      <c r="AN26">
+        <v>16</v>
+      </c>
+      <c r="AO26">
         <v>26</v>
-      </c>
-      <c r="AL26">
-        <v>34</v>
-      </c>
-      <c r="AM26">
-        <v>75</v>
-      </c>
-      <c r="AN26">
-        <v>15</v>
-      </c>
-      <c r="AO26">
-        <v>32</v>
       </c>
       <c r="AP26">
         <v>16</v>
       </c>
       <c r="AQ26">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR26">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="AS26">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="AT26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU26">
         <v>8</v>
       </c>
       <c r="AV26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW26">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="AX26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY26">
         <v>10</v>
       </c>
       <c r="AZ26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA26">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BB26">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="BC26">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD26">
-        <v>5.8</v>
+        <v>26</v>
       </c>
       <c r="BE26">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="BF26">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG26">
         <v>20</v>
@@ -7221,58 +7221,58 @@
         <v>174</v>
       </c>
       <c r="F27">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="G27">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="H27">
+        <v>4</v>
+      </c>
+      <c r="I27">
+        <v>5.6</v>
+      </c>
+      <c r="J27">
         <v>3.9</v>
       </c>
-      <c r="I27">
-        <v>5</v>
-      </c>
-      <c r="J27">
-        <v>3.8</v>
-      </c>
       <c r="K27">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="O27">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P27">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q27">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R27">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S27">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W27">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7290,7 +7290,7 @@
         <v>1000</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD27">
         <v>1000</v>
@@ -7323,7 +7323,7 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO27">
         <v>1000</v>
@@ -7332,7 +7332,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
         <v>1.03</v>
@@ -7341,34 +7341,34 @@
         <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
         <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
         <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
         <v>1.03</v>
@@ -7466,7 +7466,7 @@
         <v>3.8</v>
       </c>
       <c r="G28">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H28">
         <v>1.95</v>
@@ -7475,7 +7475,7 @@
         <v>2.08</v>
       </c>
       <c r="J28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K28">
         <v>4.8</v>
@@ -7499,13 +7499,13 @@
         <v>1.65</v>
       </c>
       <c r="R28">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S28">
         <v>2.64</v>
       </c>
       <c r="T28">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="U28">
         <v>2.2</v>
@@ -7565,13 +7565,13 @@
         <v>85</v>
       </c>
       <c r="AN28">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
         <v>11.5</v>
       </c>
       <c r="AP28">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28">
         <v>8</v>
@@ -7595,7 +7595,7 @@
         <v>11.5</v>
       </c>
       <c r="AX28">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AY28">
         <v>10</v>
@@ -7604,25 +7604,25 @@
         <v>10.5</v>
       </c>
       <c r="BA28">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BB28">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="BC28">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="BD28">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="BE28">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="BF28">
         <v>2.34</v>
       </c>
       <c r="BG28">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7705,43 +7705,43 @@
         <v>176</v>
       </c>
       <c r="F29">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="G29">
         <v>1.26</v>
       </c>
       <c r="H29">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="I29">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="J29">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="K29">
         <v>9</v>
       </c>
       <c r="L29">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M29">
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="O29">
         <v>1.1</v>
       </c>
       <c r="P29">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q29">
         <v>1.3</v>
       </c>
       <c r="R29">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S29">
         <v>1.74</v>
@@ -7771,7 +7771,7 @@
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
         <v>24</v>
@@ -7783,19 +7783,19 @@
         <v>210</v>
       </c>
       <c r="AF29">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG29">
         <v>15.5</v>
       </c>
       <c r="AH29">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI29">
         <v>150</v>
       </c>
       <c r="AJ29">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AK29">
         <v>14.5</v>
@@ -7807,46 +7807,46 @@
         <v>140</v>
       </c>
       <c r="AN29">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="AO29">
         <v>190</v>
       </c>
       <c r="AP29">
-        <v>8</v>
+        <v>3.65</v>
       </c>
       <c r="AQ29">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="AR29">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="AS29">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="AT29">
         <v>15</v>
       </c>
       <c r="AU29">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AV29">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="AW29">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="AX29">
         <v>10</v>
       </c>
       <c r="AY29">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="BA29">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="BB29">
         <v>9</v>
@@ -7855,16 +7855,16 @@
         <v>11.5</v>
       </c>
       <c r="BD29">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="BE29">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="BF29">
         <v>2.48</v>
       </c>
       <c r="BG29">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7953,10 +7953,10 @@
         <v>3.2</v>
       </c>
       <c r="H30">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I30">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J30">
         <v>3.5</v>
@@ -7974,31 +7974,31 @@
         <v>3.85</v>
       </c>
       <c r="O30">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P30">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q30">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R30">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S30">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T30">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U30">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V30">
         <v>1.65</v>
       </c>
       <c r="W30">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X30">
         <v>14.5</v>
@@ -8025,10 +8025,10 @@
         <v>27</v>
       </c>
       <c r="AF30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG30">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH30">
         <v>18</v>
@@ -8064,7 +8064,7 @@
         <v>14.5</v>
       </c>
       <c r="AS30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT30">
         <v>11.5</v>
@@ -8103,10 +8103,10 @@
         <v>80</v>
       </c>
       <c r="BF30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BG30">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8192,13 +8192,13 @@
         <v>2.04</v>
       </c>
       <c r="G31">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H31">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J31">
         <v>3.8</v>
@@ -8222,13 +8222,13 @@
         <v>2.14</v>
       </c>
       <c r="Q31">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="R31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S31">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T31">
         <v>1.73</v>
@@ -8240,64 +8240,64 @@
         <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X31">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y31">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z31">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AA31">
         <v>1000</v>
       </c>
       <c r="AB31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD31">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE31">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AF31">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG31">
         <v>10.5</v>
       </c>
       <c r="AH31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI31">
         <v>210</v>
       </c>
       <c r="AJ31">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AK31">
         <v>20</v>
       </c>
       <c r="AL31">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM31">
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO31">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AP31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ31">
         <v>14</v>
@@ -8306,16 +8306,16 @@
         <v>19</v>
       </c>
       <c r="AS31">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AT31">
         <v>9.800000000000001</v>
       </c>
       <c r="AU31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW31">
         <v>25</v>
@@ -8324,25 +8324,25 @@
         <v>11.5</v>
       </c>
       <c r="AY31">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA31">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BB31">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD31">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BE31">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BF31">
         <v>11</v>
@@ -8434,7 +8434,7 @@
         <v>1.36</v>
       </c>
       <c r="G32">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H32">
         <v>9.4</v>
@@ -8461,7 +8461,7 @@
         <v>1.16</v>
       </c>
       <c r="P32">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q32">
         <v>1.49</v>
@@ -8473,7 +8473,7 @@
         <v>2.2</v>
       </c>
       <c r="T32">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U32">
         <v>2.12</v>
@@ -8482,7 +8482,7 @@
         <v>1.1</v>
       </c>
       <c r="W32">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8745,7 +8745,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD33">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE33">
         <v>55</v>
@@ -8763,7 +8763,7 @@
         <v>50</v>
       </c>
       <c r="AJ33">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK33">
         <v>16.5</v>
@@ -8778,7 +8778,7 @@
         <v>7.8</v>
       </c>
       <c r="AO33">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP33">
         <v>20</v>
@@ -8832,7 +8832,7 @@
         <v>7.4</v>
       </c>
       <c r="BG33">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BH33">
         <v>4.7</v>
@@ -8844,7 +8844,7 @@
         <v>11</v>
       </c>
       <c r="BK33">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL33">
         <v>1000</v>
@@ -8915,13 +8915,13 @@
         <v>181</v>
       </c>
       <c r="F34">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G34">
         <v>5.4</v>
       </c>
       <c r="H34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="I34">
         <v>1.82</v>
@@ -8945,7 +8945,7 @@
         <v>1.34</v>
       </c>
       <c r="P34">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q34">
         <v>2.02</v>
@@ -8954,19 +8954,19 @@
         <v>1.35</v>
       </c>
       <c r="S34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T34">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U34">
         <v>2.02</v>
       </c>
       <c r="V34">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W34">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X34">
         <v>14</v>
@@ -9014,7 +9014,7 @@
         <v>75</v>
       </c>
       <c r="AM34">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN34">
         <v>90</v>
@@ -9023,7 +9023,7 @@
         <v>12.5</v>
       </c>
       <c r="AP34">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ34">
         <v>7.8</v>
@@ -9032,10 +9032,10 @@
         <v>9.4</v>
       </c>
       <c r="AS34">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU34">
         <v>8</v>
@@ -9050,7 +9050,7 @@
         <v>36</v>
       </c>
       <c r="AY34">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ34">
         <v>19.5</v>
@@ -9062,10 +9062,10 @@
         <v>42</v>
       </c>
       <c r="BC34">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BD34">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BE34">
         <v>100</v>
@@ -9074,7 +9074,7 @@
         <v>65</v>
       </c>
       <c r="BG34">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH34">
         <v>3.65</v>
@@ -9092,7 +9092,7 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BN34">
         <v>10</v>
@@ -9104,19 +9104,19 @@
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT34">
         <v>4.9</v>
       </c>
       <c r="BU34">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV34">
         <v>15.5</v>
@@ -9134,7 +9134,7 @@
         <v>32</v>
       </c>
       <c r="CA34">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="CB34" t="s">
         <v>187</v>
@@ -9157,10 +9157,10 @@
         <v>182</v>
       </c>
       <c r="F35">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H35">
         <v>4.5</v>
@@ -9199,16 +9199,16 @@
         <v>2.68</v>
       </c>
       <c r="T35">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U35">
         <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W35">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X35">
         <v>21</v>
@@ -9253,7 +9253,7 @@
         <v>17</v>
       </c>
       <c r="AL35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM35">
         <v>70</v>
@@ -9262,7 +9262,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO35">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP35">
         <v>19</v>
@@ -9316,7 +9316,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG35">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9417,7 +9417,7 @@
         <v>5.5</v>
       </c>
       <c r="L36">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M36">
         <v>1.03</v>
@@ -9426,16 +9426,16 @@
         <v>6</v>
       </c>
       <c r="O36">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P36">
         <v>2.72</v>
       </c>
       <c r="Q36">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R36">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S36">
         <v>2.24</v>
@@ -9447,7 +9447,7 @@
         <v>2.28</v>
       </c>
       <c r="V36">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="W36">
         <v>1.17</v>
@@ -9507,7 +9507,7 @@
         <v>5.5</v>
       </c>
       <c r="AP36">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ36">
         <v>11</v>
@@ -9516,10 +9516,10 @@
         <v>10</v>
       </c>
       <c r="AS36">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT36">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU36">
         <v>10.5</v>
@@ -9531,7 +9531,7 @@
         <v>12.5</v>
       </c>
       <c r="AX36">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY36">
         <v>20</v>
@@ -9540,7 +9540,7 @@
         <v>16.5</v>
       </c>
       <c r="BA36">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB36">
         <v>10.5</v>
@@ -9555,7 +9555,7 @@
         <v>10</v>
       </c>
       <c r="BF36">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG36">
         <v>4.9</v>
@@ -9665,28 +9665,28 @@
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O37">
         <v>1.33</v>
       </c>
       <c r="P37">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q37">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R37">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S37">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T37">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
         <v>1.71</v>
@@ -9710,7 +9710,7 @@
         <v>13</v>
       </c>
       <c r="AC37">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD37">
         <v>11.5</v>
@@ -9722,7 +9722,7 @@
         <v>23</v>
       </c>
       <c r="AG37">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH37">
         <v>18</v>
@@ -9749,10 +9749,10 @@
         <v>20</v>
       </c>
       <c r="AP37">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ37">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR37">
         <v>13.5</v>
@@ -9800,7 +9800,7 @@
         <v>30</v>
       </c>
       <c r="BG37">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH37">
         <v>3.7</v>
@@ -9892,13 +9892,13 @@
         <v>55</v>
       </c>
       <c r="I38">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J38">
         <v>25</v>
       </c>
       <c r="K38">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L38">
         <v>1.14</v>
@@ -9922,13 +9922,13 @@
         <v>2.72</v>
       </c>
       <c r="S38">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T38">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U38">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V38">
         <v>1.01</v>
@@ -10015,13 +10015,13 @@
         <v>60</v>
       </c>
       <c r="AX38">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY38">
         <v>21</v>
       </c>
       <c r="AZ38">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BA38">
         <v>14.5</v>
@@ -10033,13 +10033,13 @@
         <v>16.5</v>
       </c>
       <c r="BD38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE38">
         <v>55</v>
       </c>
       <c r="BF38">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BG38">
         <v>60</v>
@@ -10048,61 +10048,61 @@
         <v>1000</v>
       </c>
       <c r="BI38">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ38">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BK38">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="BN38">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP38">
         <v>5.3</v>
       </c>
       <c r="BQ38">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR38">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BS38">
-        <v>2.92</v>
+        <v>1.82</v>
       </c>
       <c r="BT38">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BU38">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="BZ38">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CA38">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="CB38" t="s">
         <v>187</v>
@@ -10125,10 +10125,10 @@
         <v>186</v>
       </c>
       <c r="F39">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G39">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H39">
         <v>1.18</v>
@@ -10137,16 +10137,16 @@
         <v>1.2</v>
       </c>
       <c r="J39">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K39">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L39">
         <v>1.25</v>
       </c>
       <c r="M39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N39">
         <v>6.4</v>
@@ -10161,13 +10161,13 @@
         <v>1.45</v>
       </c>
       <c r="R39">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S39">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="T39">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U39">
         <v>1.6</v>
@@ -10182,13 +10182,13 @@
         <v>40</v>
       </c>
       <c r="Y39">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z39">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA39">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB39">
         <v>70</v>
@@ -10203,40 +10203,40 @@
         <v>16</v>
       </c>
       <c r="AF39">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AG39">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH39">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI39">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ39">
         <v>1000</v>
       </c>
       <c r="AK39">
-        <v>470</v>
+        <v>400</v>
       </c>
       <c r="AL39">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AM39">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="AN39">
         <v>1000</v>
       </c>
       <c r="AO39">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AP39">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ39">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR39">
         <v>7</v>
@@ -10245,82 +10245,82 @@
         <v>7</v>
       </c>
       <c r="AT39">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU39">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AV39">
+        <v>11</v>
+      </c>
+      <c r="AW39">
         <v>12</v>
       </c>
-      <c r="AW39">
-        <v>13</v>
-      </c>
       <c r="AX39">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY39">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AZ39">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BA39">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BB39">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BC39">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD39">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE39">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF39">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BG39">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BH39">
         <v>1000</v>
       </c>
       <c r="BI39">
-        <v>2.44</v>
+        <v>1.52</v>
       </c>
       <c r="BJ39">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BK39">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>2.44</v>
+        <v>1.52</v>
       </c>
       <c r="BN39">
         <v>28</v>
       </c>
       <c r="BO39">
-        <v>2.26</v>
+        <v>1.44</v>
       </c>
       <c r="BP39">
         <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>2.44</v>
+        <v>1.52</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>2.44</v>
+        <v>1.52</v>
       </c>
       <c r="BT39">
         <v>1000</v>
@@ -10329,22 +10329,22 @@
         <v>1.52</v>
       </c>
       <c r="BV39">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW39">
-        <v>4.8</v>
+        <v>1.83</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>2.26</v>
+        <v>1.45</v>
       </c>
       <c r="BZ39">
         <v>9.800000000000001</v>
       </c>
       <c r="CA39">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="CB39" t="s">
         <v>187</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -577,7 +577,7 @@
     <t>Benfica</t>
   </si>
   <si>
-    <t>2026-09-07 21:33:57</t>
+    <t>2026-09-07 23:44:51</t>
   </si>
 </sst>
 </file>
@@ -1180,22 +1180,22 @@
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.6</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
         <v>1.61</v>
@@ -1413,166 +1413,166 @@
         <v>150</v>
       </c>
       <c r="F3">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
         <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
+        <v>2.6</v>
+      </c>
+      <c r="T3">
+        <v>2.06</v>
+      </c>
+      <c r="U3">
+        <v>1.77</v>
+      </c>
+      <c r="V3">
+        <v>1.06</v>
+      </c>
+      <c r="W3">
+        <v>3.4</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>60</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>10.5</v>
+      </c>
+      <c r="AC3">
+        <v>970</v>
+      </c>
+      <c r="AD3">
+        <v>65</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>970</v>
+      </c>
+      <c r="AG3">
+        <v>970</v>
+      </c>
+      <c r="AH3">
+        <v>55</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>970</v>
+      </c>
+      <c r="AK3">
+        <v>970</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>970</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>2.18</v>
+      </c>
+      <c r="AQ3">
+        <v>16.5</v>
+      </c>
+      <c r="AR3">
+        <v>2.26</v>
+      </c>
+      <c r="AS3">
+        <v>2.18</v>
+      </c>
+      <c r="AT3">
+        <v>5.7</v>
+      </c>
+      <c r="AU3">
+        <v>2.12</v>
+      </c>
+      <c r="AV3">
+        <v>20</v>
+      </c>
+      <c r="AW3">
+        <v>2.18</v>
+      </c>
+      <c r="AX3">
+        <v>1.87</v>
+      </c>
+      <c r="AY3">
+        <v>7.2</v>
+      </c>
+      <c r="AZ3">
         <v>2.2</v>
       </c>
-      <c r="T3">
-        <v>1.96</v>
-      </c>
-      <c r="U3">
-        <v>1.01</v>
-      </c>
-      <c r="V3">
-        <v>1.03</v>
-      </c>
-      <c r="W3">
-        <v>2.96</v>
-      </c>
-      <c r="X3">
-        <v>1000</v>
-      </c>
-      <c r="Y3">
-        <v>1000</v>
-      </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>1000</v>
-      </c>
-      <c r="AC3">
-        <v>1000</v>
-      </c>
-      <c r="AD3">
-        <v>1000</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>1000</v>
-      </c>
-      <c r="AG3">
-        <v>1000</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3">
-        <v>1.03</v>
-      </c>
-      <c r="AR3">
-        <v>1.02</v>
-      </c>
-      <c r="AS3">
-        <v>1.02</v>
-      </c>
-      <c r="AT3">
-        <v>1.02</v>
-      </c>
-      <c r="AU3">
-        <v>1.02</v>
-      </c>
-      <c r="AV3">
-        <v>1.03</v>
-      </c>
-      <c r="AW3">
-        <v>1.02</v>
-      </c>
-      <c r="AX3">
-        <v>1.02</v>
-      </c>
-      <c r="AY3">
-        <v>1.02</v>
-      </c>
-      <c r="AZ3">
-        <v>1.03</v>
-      </c>
       <c r="BA3">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="BB3">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="BE3">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="BF3">
-        <v>1.02</v>
+        <v>1.74</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1655,19 +1655,19 @@
         <v>151</v>
       </c>
       <c r="F4">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="G4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
         <v>4.5</v>
@@ -1688,16 +1688,16 @@
         <v>2.08</v>
       </c>
       <c r="Q4">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R4">
         <v>1.43</v>
       </c>
       <c r="S4">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U4">
         <v>2.04</v>
@@ -1706,7 +1706,7 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X4">
         <v>18.5</v>
@@ -1715,7 +1715,7 @@
         <v>60</v>
       </c>
       <c r="Z4">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1724,7 +1724,7 @@
         <v>9.4</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD4">
         <v>65</v>
@@ -1745,7 +1745,7 @@
         <v>85</v>
       </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK4">
         <v>19</v>
@@ -1763,7 +1763,7 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
         <v>17</v>
@@ -1772,7 +1772,7 @@
         <v>14</v>
       </c>
       <c r="AS4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT4">
         <v>7.8</v>
@@ -1784,7 +1784,7 @@
         <v>19</v>
       </c>
       <c r="AW4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX4">
         <v>8.6</v>
@@ -1796,16 +1796,16 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BB4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC4">
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE4">
         <v>17</v>
@@ -1814,7 +1814,7 @@
         <v>7.6</v>
       </c>
       <c r="BG4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BN4">
         <v>4.9</v>
@@ -1841,7 +1841,7 @@
         <v>3.6</v>
       </c>
       <c r="BP4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BQ4">
         <v>8.4</v>
@@ -1850,7 +1850,7 @@
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BT4">
         <v>13</v>
@@ -1862,7 +1862,7 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1874,7 +1874,7 @@
         <v>26</v>
       </c>
       <c r="CA4">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="s">
         <v>187</v>
@@ -1903,13 +1903,13 @@
         <v>2.9</v>
       </c>
       <c r="H5">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I5">
         <v>2.98</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
         <v>3.5</v>
@@ -1930,28 +1930,28 @@
         <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
         <v>1.27</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
         <v>1.53</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y5">
         <v>10.5</v>
@@ -1969,10 +1969,10 @@
         <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF5">
         <v>17.5</v>
@@ -1981,37 +1981,37 @@
         <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AJ5">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL5">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AM5">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AS5">
         <v>25</v>
@@ -2035,7 +2035,7 @@
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>29</v>
@@ -2062,19 +2062,19 @@
         <v>11</v>
       </c>
       <c r="BI5">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BJ5">
         <v>14.5</v>
       </c>
       <c r="BK5">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BN5">
         <v>1000</v>
@@ -2086,16 +2086,16 @@
         <v>34</v>
       </c>
       <c r="BQ5">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
         <v>4.5</v>
@@ -2104,19 +2104,19 @@
         <v>36</v>
       </c>
       <c r="BW5">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BZ5">
         <v>50</v>
       </c>
       <c r="CA5">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2139,7 +2139,7 @@
         <v>153</v>
       </c>
       <c r="F6">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="G6">
         <v>2.66</v>
@@ -2148,7 +2148,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J6">
         <v>3.25</v>
@@ -2187,7 +2187,7 @@
         <v>1.9</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.6</v>
@@ -2202,7 +2202,7 @@
         <v>26</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB6">
         <v>10.5</v>
@@ -2253,7 +2253,7 @@
         <v>8.4</v>
       </c>
       <c r="AR6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS6">
         <v>4.4</v>
@@ -2265,7 +2265,7 @@
         <v>5.7</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW6">
         <v>4.2</v>
@@ -2274,10 +2274,10 @@
         <v>12</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
         <v>4.3</v>
@@ -2316,25 +2316,25 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BN6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
         <v>4.4</v>
       </c>
       <c r="BP6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ6">
-        <v>1.86</v>
+        <v>4.3</v>
       </c>
       <c r="BR6">
         <v>50</v>
       </c>
       <c r="BS6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
@@ -2346,19 +2346,19 @@
         <v>40</v>
       </c>
       <c r="BW6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BZ6">
         <v>50</v>
       </c>
       <c r="CA6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CB6" t="s">
         <v>187</v>
@@ -2381,13 +2381,13 @@
         <v>154</v>
       </c>
       <c r="F7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G7">
         <v>4.6</v>
       </c>
       <c r="H7">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I7">
         <v>2.12</v>
@@ -2405,13 +2405,13 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
         <v>2.06</v>
@@ -2426,7 +2426,7 @@
         <v>1.86</v>
       </c>
       <c r="U7">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V7">
         <v>1.89</v>
@@ -2435,7 +2435,7 @@
         <v>1.27</v>
       </c>
       <c r="X7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y7">
         <v>9.800000000000001</v>
@@ -2447,10 +2447,10 @@
         <v>30</v>
       </c>
       <c r="AB7">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
         <v>11.5</v>
@@ -2486,10 +2486,10 @@
         <v>100</v>
       </c>
       <c r="AO7">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7">
         <v>6.4</v>
@@ -2504,7 +2504,7 @@
         <v>11</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
         <v>8.6</v>
@@ -2513,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="AX7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7">
         <v>13</v>
@@ -2525,19 +2525,19 @@
         <v>12.5</v>
       </c>
       <c r="BB7">
+        <v>4.2</v>
+      </c>
+      <c r="BC7">
+        <v>23</v>
+      </c>
+      <c r="BD7">
         <v>4</v>
       </c>
-      <c r="BC7">
-        <v>24</v>
-      </c>
-      <c r="BD7">
-        <v>27</v>
-      </c>
       <c r="BE7">
+        <v>4.2</v>
+      </c>
+      <c r="BF7">
         <v>4</v>
-      </c>
-      <c r="BF7">
-        <v>3.9</v>
       </c>
       <c r="BG7">
         <v>12.5</v>
@@ -2564,7 +2564,7 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>5.8</v>
+        <v>2.14</v>
       </c>
       <c r="BP7">
         <v>1000</v>
@@ -2579,7 +2579,7 @@
         <v>2.68</v>
       </c>
       <c r="BT7">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
         <v>1.78</v>
@@ -2623,10 +2623,10 @@
         <v>155</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H8">
         <v>2.66</v>
@@ -2644,10 +2644,10 @@
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
         <v>1.62</v>
@@ -2668,31 +2668,31 @@
         <v>2.2</v>
       </c>
       <c r="U8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V8">
         <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X8">
         <v>970</v>
       </c>
       <c r="Y8">
+        <v>7.8</v>
+      </c>
+      <c r="Z8">
+        <v>17.5</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>9</v>
+      </c>
+      <c r="AC8">
         <v>970</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>970</v>
-      </c>
-      <c r="AC8">
-        <v>7.4</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2704,7 +2704,7 @@
         <v>22</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH8">
         <v>1000</v>
@@ -2737,52 +2737,52 @@
         <v>5.6</v>
       </c>
       <c r="AR8">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AS8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AT8">
-        <v>1.63</v>
+        <v>7</v>
       </c>
       <c r="AU8">
-        <v>1.58</v>
+        <v>5.4</v>
       </c>
       <c r="AV8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AW8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AX8">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AY8">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AZ8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BA8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BB8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BC8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BD8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BE8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BF8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BG8">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2865,19 +2865,19 @@
         <v>156</v>
       </c>
       <c r="F9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>2.48</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I9">
         <v>110</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2889,22 +2889,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2913,10 +2913,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W9">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3107,13 +3107,13 @@
         <v>157</v>
       </c>
       <c r="F10">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G10">
         <v>1.56</v>
       </c>
       <c r="H10">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I10">
         <v>11.5</v>
@@ -3122,7 +3122,7 @@
         <v>3.65</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3131,31 +3131,31 @@
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
         <v>1.52</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
       </c>
       <c r="R10">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S10">
         <v>4.8</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U10">
         <v>1.43</v>
       </c>
       <c r="V10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W10">
         <v>2.78</v>
@@ -3185,11 +3185,11 @@
         <v>1000</v>
       </c>
       <c r="AF10">
+        <v>7.4</v>
+      </c>
+      <c r="AG10">
         <v>970</v>
       </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
       <c r="AH10">
         <v>1000</v>
       </c>
@@ -3209,124 +3209,124 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="AQ10">
-        <v>1.63</v>
+        <v>18.5</v>
       </c>
       <c r="AR10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AS10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AT10">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="AU10">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AV10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AW10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AX10">
-        <v>1.38</v>
+        <v>5.7</v>
       </c>
       <c r="AY10">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AZ10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="BA10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="BB10">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="BC10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="BD10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="BE10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="BF10">
         <v>11</v>
       </c>
       <c r="BG10">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>187</v>
@@ -3349,22 +3349,22 @@
         <v>158</v>
       </c>
       <c r="F11">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H11">
         <v>3.65</v>
       </c>
       <c r="I11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>1.29</v>
@@ -3385,10 +3385,10 @@
         <v>1.84</v>
       </c>
       <c r="R11">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S11">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3397,10 +3397,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W11">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3669,7 +3669,7 @@
         <v>36</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG12">
         <v>970</v>
@@ -3708,7 +3708,7 @@
         <v>11</v>
       </c>
       <c r="AS12">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AT12">
         <v>7.8</v>
@@ -3720,37 +3720,37 @@
         <v>10.5</v>
       </c>
       <c r="AW12">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AX12">
         <v>11</v>
       </c>
       <c r="AY12">
-        <v>8.4</v>
+        <v>1.72</v>
       </c>
       <c r="AZ12">
         <v>11</v>
       </c>
       <c r="BA12">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="BB12">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="BC12">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="BD12">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="BE12">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="BF12">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="BG12">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3881,7 +3881,7 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W13">
         <v>1.38</v>
@@ -4090,7 +4090,7 @@
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
         <v>1.34</v>
@@ -4108,7 +4108,7 @@
         <v>2.08</v>
       </c>
       <c r="Q14">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R14">
         <v>1.43</v>
@@ -4120,7 +4120,7 @@
         <v>1.65</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
         <v>1.68</v>
@@ -4192,7 +4192,7 @@
         <v>14</v>
       </c>
       <c r="AS14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT14">
         <v>12</v>
@@ -4216,22 +4216,22 @@
         <v>13.5</v>
       </c>
       <c r="BA14">
+        <v>8</v>
+      </c>
+      <c r="BB14">
+        <v>8.6</v>
+      </c>
+      <c r="BC14">
+        <v>8</v>
+      </c>
+      <c r="BD14">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD14">
-        <v>8.4</v>
-      </c>
       <c r="BE14">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG14">
         <v>14</v>
@@ -4252,7 +4252,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BN14">
         <v>8</v>
@@ -4264,16 +4264,16 @@
         <v>32</v>
       </c>
       <c r="BQ14">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BR14">
         <v>46</v>
       </c>
       <c r="BS14">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BT14">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU14">
         <v>4.4</v>
@@ -4282,19 +4282,19 @@
         <v>23</v>
       </c>
       <c r="BW14">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BX14">
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BZ14">
         <v>30</v>
       </c>
       <c r="CA14">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CB14" t="s">
         <v>187</v>
@@ -4568,7 +4568,7 @@
         <v>1.33</v>
       </c>
       <c r="I16">
-        <v>4.4</v>
+        <v>110</v>
       </c>
       <c r="J16">
         <v>3</v>
@@ -4607,10 +4607,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4984,7 +4984,7 @@
         <v>5.4</v>
       </c>
       <c r="BO17">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BP17">
         <v>8.199999999999999</v>
@@ -5049,7 +5049,7 @@
         <v>1.12</v>
       </c>
       <c r="H18">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I18">
         <v>34</v>
@@ -5067,13 +5067,13 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="O18">
         <v>1.06</v>
       </c>
       <c r="P18">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q18">
         <v>1.2</v>
@@ -5082,19 +5082,19 @@
         <v>2.9</v>
       </c>
       <c r="S18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T18">
         <v>1.97</v>
       </c>
       <c r="U18">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V18">
         <v>1.03</v>
       </c>
       <c r="W18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X18">
         <v>110</v>
@@ -5118,19 +5118,19 @@
         <v>140</v>
       </c>
       <c r="AE18">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="AF18">
         <v>14.5</v>
       </c>
       <c r="AG18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH18">
         <v>55</v>
       </c>
       <c r="AI18">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AJ18">
         <v>10.5</v>
@@ -5139,16 +5139,16 @@
         <v>15</v>
       </c>
       <c r="AL18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM18">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AO18">
-        <v>410</v>
+        <v>360</v>
       </c>
       <c r="AP18">
         <v>34</v>
@@ -5157,10 +5157,10 @@
         <v>42</v>
       </c>
       <c r="AR18">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS18">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AT18">
         <v>20</v>
@@ -5172,7 +5172,7 @@
         <v>38</v>
       </c>
       <c r="AW18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX18">
         <v>12.5</v>
@@ -5208,25 +5208,25 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BK18">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.18</v>
+        <v>3.75</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5235,34 +5235,34 @@
         <v>4.4</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS18">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BU18">
-        <v>1.54</v>
+        <v>2.54</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="CA18">
-        <v>1.54</v>
+        <v>3.3</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5315,7 +5315,7 @@
         <v>1.09</v>
       </c>
       <c r="P19">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q19">
         <v>1.28</v>
@@ -5363,7 +5363,7 @@
         <v>140</v>
       </c>
       <c r="AF19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG19">
         <v>12.5</v>
@@ -5408,7 +5408,7 @@
         <v>17.5</v>
       </c>
       <c r="AU19">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AV19">
         <v>25</v>
@@ -5420,7 +5420,7 @@
         <v>12</v>
       </c>
       <c r="AY19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
         <v>22</v>
@@ -6080,7 +6080,7 @@
         <v>8.6</v>
       </c>
       <c r="AC22">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD22">
         <v>1000</v>
@@ -6125,10 +6125,10 @@
         <v>5.9</v>
       </c>
       <c r="AR22">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AS22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AT22">
         <v>6</v>
@@ -6137,40 +6137,40 @@
         <v>6</v>
       </c>
       <c r="AV22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AW22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AX22">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="AY22">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AZ22">
         <v>19</v>
       </c>
       <c r="BA22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BB22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BC22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BD22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BE22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BF22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BG22">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6256,7 +6256,7 @@
         <v>9.4</v>
       </c>
       <c r="G23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H23">
         <v>1.44</v>
@@ -6268,7 +6268,7 @@
         <v>4.5</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6283,10 +6283,10 @@
         <v>1.39</v>
       </c>
       <c r="P23">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q23">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R23">
         <v>1.3</v>
@@ -6358,7 +6358,7 @@
         <v>490</v>
       </c>
       <c r="AO23">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AP23">
         <v>11.5</v>
@@ -6385,7 +6385,7 @@
         <v>16</v>
       </c>
       <c r="AX23">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY23">
         <v>24</v>
@@ -6397,19 +6397,19 @@
         <v>40</v>
       </c>
       <c r="BB23">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC23">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD23">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG23">
         <v>8.4</v>
@@ -6418,7 +6418,7 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BJ23">
         <v>19</v>
@@ -6430,34 +6430,34 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BN23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BO23">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BT23">
         <v>4.9</v>
       </c>
       <c r="BU23">
-        <v>2.92</v>
+        <v>1.31</v>
       </c>
       <c r="BV23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW23">
         <v>1.58</v>
@@ -6469,10 +6469,10 @@
         <v>1.73</v>
       </c>
       <c r="BZ23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA23">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CB23" t="s">
         <v>187</v>
@@ -6495,7 +6495,7 @@
         <v>171</v>
       </c>
       <c r="F24">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G24">
         <v>2.04</v>
@@ -6510,7 +6510,7 @@
         <v>3.75</v>
       </c>
       <c r="K24">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6534,7 +6534,7 @@
         <v>1.47</v>
       </c>
       <c r="S24">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T24">
         <v>1.57</v>
@@ -6597,22 +6597,22 @@
         <v>80</v>
       </c>
       <c r="AN24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO24">
         <v>40</v>
       </c>
       <c r="AP24">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ24">
         <v>16.5</v>
       </c>
       <c r="AR24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS24">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT24">
         <v>10.5</v>
@@ -6624,7 +6624,7 @@
         <v>14</v>
       </c>
       <c r="AW24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX24">
         <v>12</v>
@@ -6648,13 +6648,13 @@
         <v>20</v>
       </c>
       <c r="BE24">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF24">
         <v>9.199999999999999</v>
       </c>
       <c r="BG24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6740,7 +6740,7 @@
         <v>2.1</v>
       </c>
       <c r="G25">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H25">
         <v>3.2</v>
@@ -6767,13 +6767,13 @@
         <v>1.22</v>
       </c>
       <c r="P25">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R25">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S25">
         <v>2.66</v>
@@ -6785,10 +6785,10 @@
         <v>2.34</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6848,7 +6848,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ25">
-        <v>1.26</v>
+        <v>11</v>
       </c>
       <c r="AR25">
         <v>1.26</v>
@@ -6979,22 +6979,22 @@
         <v>173</v>
       </c>
       <c r="F26">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G26">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H26">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I26">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K26">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7006,37 +7006,37 @@
         <v>4.3</v>
       </c>
       <c r="O26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P26">
         <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R26">
         <v>1.48</v>
       </c>
       <c r="S26">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T26">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U26">
         <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W26">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X26">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y26">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z26">
         <v>24</v>
@@ -7060,7 +7060,7 @@
         <v>18</v>
       </c>
       <c r="AG26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH26">
         <v>16.5</v>
@@ -7108,7 +7108,7 @@
         <v>12</v>
       </c>
       <c r="AW26">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AX26">
         <v>14.5</v>
@@ -7144,7 +7144,7 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="BJ26">
         <v>12.5</v>
@@ -7156,16 +7156,16 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="BN26">
         <v>7</v>
       </c>
       <c r="BO26">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BP26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ26">
         <v>1.8</v>
@@ -7180,7 +7180,7 @@
         <v>9</v>
       </c>
       <c r="BU26">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BV26">
         <v>34</v>
@@ -7198,7 +7198,7 @@
         <v>30</v>
       </c>
       <c r="CA26">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CB26" t="s">
         <v>187</v>
@@ -7221,22 +7221,22 @@
         <v>174</v>
       </c>
       <c r="F27">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G27">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I27">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J27">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K27">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7254,13 +7254,13 @@
         <v>2.38</v>
       </c>
       <c r="Q27">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R27">
         <v>1.51</v>
       </c>
       <c r="S27">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="T27">
         <v>1.57</v>
@@ -7269,10 +7269,10 @@
         <v>2.26</v>
       </c>
       <c r="V27">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7514,7 +7514,7 @@
         <v>1.94</v>
       </c>
       <c r="W28">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7577,7 +7577,7 @@
         <v>8</v>
       </c>
       <c r="AR28">
-        <v>9</v>
+        <v>2.32</v>
       </c>
       <c r="AS28">
         <v>18.5</v>
@@ -7598,7 +7598,7 @@
         <v>2.2</v>
       </c>
       <c r="AY28">
-        <v>10</v>
+        <v>2.06</v>
       </c>
       <c r="AZ28">
         <v>10.5</v>
@@ -7622,7 +7622,7 @@
         <v>2.34</v>
       </c>
       <c r="BG28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7705,19 +7705,19 @@
         <v>176</v>
       </c>
       <c r="F29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G29">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H29">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="I29">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J29">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="K29">
         <v>9</v>
@@ -7729,7 +7729,7 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>1.1</v>
@@ -7738,13 +7738,13 @@
         <v>3.7</v>
       </c>
       <c r="Q29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T29">
         <v>1.86</v>
@@ -7756,7 +7756,7 @@
         <v>1.06</v>
       </c>
       <c r="W29">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>55</v>
@@ -7765,106 +7765,106 @@
         <v>75</v>
       </c>
       <c r="Z29">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA29">
         <v>1000</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC29">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD29">
         <v>60</v>
       </c>
       <c r="AE29">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AF29">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH29">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI29">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ29">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AK29">
         <v>14.5</v>
       </c>
       <c r="AL29">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM29">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN29">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="AO29">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP29">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR29">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="AS29">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AT29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU29">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AV29">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="AW29">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="AX29">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY29">
+        <v>11.5</v>
+      </c>
+      <c r="AZ29">
+        <v>7.6</v>
+      </c>
+      <c r="BA29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB29">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AZ29">
-        <v>3.5</v>
-      </c>
-      <c r="BA29">
-        <v>3.8</v>
-      </c>
-      <c r="BB29">
-        <v>9</v>
       </c>
       <c r="BC29">
         <v>11.5</v>
       </c>
       <c r="BD29">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="BE29">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BG29">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7953,10 +7953,10 @@
         <v>3.2</v>
       </c>
       <c r="H30">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I30">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J30">
         <v>3.5</v>
@@ -7974,7 +7974,7 @@
         <v>3.85</v>
       </c>
       <c r="O30">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P30">
         <v>1.96</v>
@@ -7986,16 +7986,16 @@
         <v>1.37</v>
       </c>
       <c r="S30">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T30">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U30">
         <v>2.24</v>
       </c>
       <c r="V30">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W30">
         <v>1.45</v>
@@ -8007,7 +8007,7 @@
         <v>11</v>
       </c>
       <c r="Z30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA30">
         <v>36</v>
@@ -8016,7 +8016,7 @@
         <v>12.5</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD30">
         <v>11.5</v>
@@ -8025,7 +8025,7 @@
         <v>27</v>
       </c>
       <c r="AF30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG30">
         <v>14</v>
@@ -8052,7 +8052,7 @@
         <v>34</v>
       </c>
       <c r="AO30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP30">
         <v>12.5</v>
@@ -8076,7 +8076,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX30">
         <v>18.5</v>
@@ -8088,13 +8088,13 @@
         <v>15</v>
       </c>
       <c r="BA30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB30">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="BC30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD30">
         <v>40</v>
@@ -8106,7 +8106,7 @@
         <v>20</v>
       </c>
       <c r="BG30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8213,7 +8213,7 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O31">
         <v>1.27</v>
@@ -8222,13 +8222,13 @@
         <v>2.14</v>
       </c>
       <c r="Q31">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S31">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="T31">
         <v>1.73</v>
@@ -8246,7 +8246,7 @@
         <v>18</v>
       </c>
       <c r="Y31">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z31">
         <v>30</v>
@@ -8255,13 +8255,13 @@
         <v>1000</v>
       </c>
       <c r="AB31">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC31">
         <v>9</v>
       </c>
       <c r="AD31">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE31">
         <v>50</v>
@@ -8291,13 +8291,13 @@
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO31">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ31">
         <v>14</v>
@@ -8318,7 +8318,7 @@
         <v>14</v>
       </c>
       <c r="AW31">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AX31">
         <v>11.5</v>
@@ -8434,7 +8434,7 @@
         <v>1.36</v>
       </c>
       <c r="G32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H32">
         <v>9.4</v>
@@ -8473,7 +8473,7 @@
         <v>2.2</v>
       </c>
       <c r="T32">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U32">
         <v>2.12</v>
@@ -8482,7 +8482,7 @@
         <v>1.1</v>
       </c>
       <c r="W32">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8742,7 +8742,7 @@
         <v>12</v>
       </c>
       <c r="AC33">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD33">
         <v>19</v>
@@ -8915,16 +8915,16 @@
         <v>181</v>
       </c>
       <c r="F34">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G34">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H34">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="I34">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J34">
         <v>3.85</v>
@@ -8963,10 +8963,10 @@
         <v>2.02</v>
       </c>
       <c r="V34">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W34">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
         <v>14</v>
@@ -8978,7 +8978,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB34">
         <v>17</v>
@@ -8987,10 +8987,10 @@
         <v>8.4</v>
       </c>
       <c r="AD34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE34">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF34">
         <v>42</v>
@@ -9008,13 +9008,13 @@
         <v>140</v>
       </c>
       <c r="AK34">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL34">
         <v>75</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN34">
         <v>90</v>
@@ -9032,7 +9032,7 @@
         <v>9.4</v>
       </c>
       <c r="AS34">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT34">
         <v>16</v>
@@ -9071,10 +9071,10 @@
         <v>100</v>
       </c>
       <c r="BF34">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BG34">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH34">
         <v>3.65</v>
@@ -9092,7 +9092,7 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BN34">
         <v>10</v>
@@ -9104,13 +9104,13 @@
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT34">
         <v>4.9</v>
@@ -9250,7 +9250,7 @@
         <v>21</v>
       </c>
       <c r="AK35">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL35">
         <v>27</v>
@@ -9316,7 +9316,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG35">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9352,7 +9352,7 @@
         <v>32</v>
       </c>
       <c r="BS35">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BT35">
         <v>10.5</v>
@@ -9411,10 +9411,10 @@
         <v>1.54</v>
       </c>
       <c r="J36">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L36">
         <v>1.26</v>
@@ -9435,7 +9435,7 @@
         <v>1.5</v>
       </c>
       <c r="R36">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S36">
         <v>2.24</v>
@@ -9507,7 +9507,7 @@
         <v>5.5</v>
       </c>
       <c r="AP36">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ36">
         <v>11</v>
@@ -9519,7 +9519,7 @@
         <v>12.5</v>
       </c>
       <c r="AT36">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU36">
         <v>10.5</v>
@@ -9531,7 +9531,7 @@
         <v>12.5</v>
       </c>
       <c r="AX36">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY36">
         <v>20</v>
@@ -9540,7 +9540,7 @@
         <v>16.5</v>
       </c>
       <c r="BA36">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB36">
         <v>10.5</v>
@@ -9555,7 +9555,7 @@
         <v>10</v>
       </c>
       <c r="BF36">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG36">
         <v>4.9</v>
@@ -9665,31 +9665,31 @@
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O37">
         <v>1.33</v>
       </c>
       <c r="P37">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R37">
         <v>1.35</v>
       </c>
       <c r="S37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T37">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U37">
         <v>2.18</v>
       </c>
       <c r="V37">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W37">
         <v>1.41</v>
@@ -9722,7 +9722,7 @@
         <v>23</v>
       </c>
       <c r="AG37">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH37">
         <v>18</v>
@@ -9788,7 +9788,7 @@
         <v>50</v>
       </c>
       <c r="BC37">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="BD37">
         <v>42</v>
@@ -9797,10 +9797,10 @@
         <v>36</v>
       </c>
       <c r="BF37">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BG37">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH37">
         <v>3.7</v>
@@ -9889,16 +9889,16 @@
         <v>1.06</v>
       </c>
       <c r="H38">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K38">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L38">
         <v>1.14</v>
@@ -9922,13 +9922,13 @@
         <v>2.72</v>
       </c>
       <c r="S38">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T38">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="U38">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V38">
         <v>1.01</v>
@@ -9976,7 +9976,7 @@
         <v>7.8</v>
       </c>
       <c r="AK38">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL38">
         <v>1000</v>
@@ -9985,13 +9985,13 @@
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AO38">
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ38">
         <v>55</v>
@@ -10003,7 +10003,7 @@
         <v>60</v>
       </c>
       <c r="AT38">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AU38">
         <v>32</v>
@@ -10015,22 +10015,22 @@
         <v>60</v>
       </c>
       <c r="AX38">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY38">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA38">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB38">
         <v>7</v>
       </c>
       <c r="BC38">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD38">
         <v>34</v>
@@ -10039,7 +10039,7 @@
         <v>55</v>
       </c>
       <c r="BF38">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BG38">
         <v>60</v>
@@ -10048,19 +10048,19 @@
         <v>1000</v>
       </c>
       <c r="BI38">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="BJ38">
         <v>27</v>
       </c>
       <c r="BK38">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="BN38">
         <v>1000</v>
@@ -10078,31 +10078,31 @@
         <v>32</v>
       </c>
       <c r="BS38">
-        <v>1.82</v>
+        <v>2.96</v>
       </c>
       <c r="BT38">
         <v>50</v>
       </c>
       <c r="BU38">
-        <v>1.85</v>
+        <v>3.05</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="BZ38">
         <v>5</v>
       </c>
       <c r="CA38">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="CB38" t="s">
         <v>187</v>
@@ -10125,10 +10125,10 @@
         <v>186</v>
       </c>
       <c r="F39">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="G39">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H39">
         <v>1.18</v>
@@ -10137,7 +10137,7 @@
         <v>1.2</v>
       </c>
       <c r="J39">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K39">
         <v>9.800000000000001</v>
@@ -10158,16 +10158,16 @@
         <v>2.82</v>
       </c>
       <c r="Q39">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R39">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S39">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="T39">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U39">
         <v>1.6</v>
@@ -10185,10 +10185,10 @@
         <v>12</v>
       </c>
       <c r="Z39">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA39">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB39">
         <v>70</v>
@@ -10230,10 +10230,10 @@
         <v>1000</v>
       </c>
       <c r="AO39">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AP39">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AQ39">
         <v>9.4</v>
@@ -10245,46 +10245,46 @@
         <v>7</v>
       </c>
       <c r="AT39">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU39">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AV39">
+        <v>11.5</v>
+      </c>
+      <c r="AW39">
+        <v>13</v>
+      </c>
+      <c r="AX39">
+        <v>10.5</v>
+      </c>
+      <c r="AY39">
+        <v>9.6</v>
+      </c>
+      <c r="AZ39">
+        <v>9</v>
+      </c>
+      <c r="BA39">
+        <v>9</v>
+      </c>
+      <c r="BB39">
         <v>11</v>
       </c>
-      <c r="AW39">
-        <v>12</v>
-      </c>
-      <c r="AX39">
-        <v>7.4</v>
-      </c>
-      <c r="AY39">
-        <v>7</v>
-      </c>
-      <c r="AZ39">
-        <v>6.6</v>
-      </c>
-      <c r="BA39">
-        <v>6.6</v>
-      </c>
-      <c r="BB39">
-        <v>7.6</v>
-      </c>
       <c r="BC39">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD39">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE39">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF39">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BG39">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BH39">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -796,7 +796,7 @@
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>2026-09-08 12:57:50</t>
+    <t>2026-09-08 15:11:13</t>
   </si>
 </sst>
 </file>
@@ -1390,22 +1390,22 @@
         <v>196</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
         <v>2.9</v>
       </c>
       <c r="K2">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L2">
         <v>1.69</v>
@@ -1417,7 +1417,7 @@
         <v>2.5</v>
       </c>
       <c r="O2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P2">
         <v>1.47</v>
@@ -1429,31 +1429,31 @@
         <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
         <v>28</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB2">
         <v>6.8</v>
@@ -1468,7 +1468,7 @@
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>13</v>
@@ -1495,16 +1495,16 @@
         <v>40</v>
       </c>
       <c r="AO2">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AP2">
         <v>6.6</v>
       </c>
       <c r="AQ2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS2">
         <v>17</v>
@@ -1516,7 +1516,7 @@
         <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW2">
         <v>65</v>
@@ -1531,10 +1531,10 @@
         <v>24</v>
       </c>
       <c r="BA2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB2">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="BC2">
         <v>30</v>
@@ -1543,25 +1543,25 @@
         <v>15.5</v>
       </c>
       <c r="BE2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF2">
         <v>32</v>
       </c>
       <c r="BG2">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BH2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BI2">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1570,34 +1570,34 @@
         <v>15</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS2">
         <v>12</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <v>75</v>
@@ -1635,7 +1635,7 @@
         <v>1.35</v>
       </c>
       <c r="G3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H3">
         <v>10.5</v>
@@ -1644,10 +1644,10 @@
         <v>12</v>
       </c>
       <c r="J3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L3">
         <v>1.33</v>
@@ -1656,13 +1656,13 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O3">
         <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q3">
         <v>1.74</v>
@@ -1746,10 +1746,10 @@
         <v>24</v>
       </c>
       <c r="AR3">
+        <v>9</v>
+      </c>
+      <c r="AS3">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AS3">
-        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1761,19 +1761,19 @@
         <v>29</v>
       </c>
       <c r="AW3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
         <v>22</v>
       </c>
       <c r="BA3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB3">
         <v>9.199999999999999</v>
@@ -1785,13 +1785,13 @@
         <v>29</v>
       </c>
       <c r="BE3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
@@ -1803,7 +1803,7 @@
         <v>13</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1815,13 +1815,13 @@
         <v>3.85</v>
       </c>
       <c r="BO3">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="BP3">
         <v>8</v>
       </c>
       <c r="BQ3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR3">
         <v>26</v>
@@ -1833,7 +1833,7 @@
         <v>14.5</v>
       </c>
       <c r="BU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1851,7 +1851,7 @@
         <v>13.5</v>
       </c>
       <c r="CA3">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>260</v>
@@ -2122,10 +2122,10 @@
         <v>2.9</v>
       </c>
       <c r="H5">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>3.2</v>
@@ -2137,16 +2137,16 @@
         <v>1.44</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
         <v>2.24</v>
@@ -2158,13 +2158,13 @@
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
         <v>1.53</v>
@@ -2182,7 +2182,7 @@
         <v>60</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5">
         <v>7.4</v>
@@ -2194,7 +2194,7 @@
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG5">
         <v>13</v>
@@ -2224,7 +2224,7 @@
         <v>38</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
         <v>9.199999999999999</v>
@@ -2236,16 +2236,16 @@
         <v>30</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX5">
         <v>16</v>
@@ -2257,10 +2257,10 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC5">
         <v>22</v>
@@ -2358,7 +2358,7 @@
         <v>200</v>
       </c>
       <c r="F6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G6">
         <v>2.6</v>
@@ -2370,7 +2370,7 @@
         <v>3.4</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
         <v>3.45</v>
@@ -2382,10 +2382,10 @@
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P6">
         <v>1.71</v>
@@ -2397,7 +2397,7 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
         <v>1.91</v>
@@ -2412,7 +2412,7 @@
         <v>1.63</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>11</v>
@@ -2466,7 +2466,7 @@
         <v>50</v>
       </c>
       <c r="AP6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6">
         <v>9.6</v>
@@ -2487,7 +2487,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AX6">
         <v>13.5</v>
@@ -2508,13 +2508,13 @@
         <v>27</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6">
         <v>34</v>
@@ -2615,7 +2615,7 @@
         <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2627,28 +2627,28 @@
         <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W7">
         <v>1.29</v>
@@ -2660,22 +2660,22 @@
         <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB7">
         <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>11</v>
       </c>
       <c r="AE7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7">
         <v>32</v>
@@ -2690,7 +2690,7 @@
         <v>42</v>
       </c>
       <c r="AJ7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK7">
         <v>65</v>
@@ -2711,7 +2711,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
         <v>10.5</v>
@@ -2723,40 +2723,40 @@
         <v>12</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7">
         <v>19</v>
       </c>
       <c r="AX7">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AY7">
         <v>15</v>
       </c>
       <c r="AZ7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BB7">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BC7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BD7">
+        <v>40</v>
+      </c>
+      <c r="BE7">
+        <v>70</v>
+      </c>
+      <c r="BF7">
         <v>32</v>
-      </c>
-      <c r="BE7">
-        <v>10.5</v>
-      </c>
-      <c r="BF7">
-        <v>10</v>
       </c>
       <c r="BG7">
         <v>14</v>
@@ -2842,22 +2842,22 @@
         <v>202</v>
       </c>
       <c r="F8">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="G8">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="H8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I8">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="J8">
         <v>4.1</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2866,19 +2866,19 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="Q8">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
         <v>2.5</v>
@@ -2890,10 +2890,10 @@
         <v>1.75</v>
       </c>
       <c r="V8">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3114,13 +3114,13 @@
         <v>1.52</v>
       </c>
       <c r="P9">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q9">
         <v>2.54</v>
       </c>
       <c r="R9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S9">
         <v>5.3</v>
@@ -3138,7 +3138,7 @@
         <v>2.96</v>
       </c>
       <c r="X9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y9">
         <v>28</v>
@@ -3332,7 +3332,7 @@
         <v>3.45</v>
       </c>
       <c r="H10">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I10">
         <v>2.92</v>
@@ -3341,7 +3341,7 @@
         <v>2.82</v>
       </c>
       <c r="K10">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <v>1.64</v>
@@ -3356,10 +3356,10 @@
         <v>1.67</v>
       </c>
       <c r="P10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q10">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R10">
         <v>1.15</v>
@@ -3571,13 +3571,13 @@
         <v>1.26</v>
       </c>
       <c r="G11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H11">
         <v>13</v>
       </c>
       <c r="I11">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="J11">
         <v>5.6</v>
@@ -3592,142 +3592,142 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="O11">
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="Q11">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R11">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S11">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="T11">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="U11">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V11">
         <v>1.06</v>
       </c>
       <c r="W11">
+        <v>3.95</v>
+      </c>
+      <c r="X11">
+        <v>26</v>
+      </c>
+      <c r="Y11">
+        <v>50</v>
+      </c>
+      <c r="Z11">
+        <v>170</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>10</v>
+      </c>
+      <c r="AC11">
+        <v>15.5</v>
+      </c>
+      <c r="AD11">
+        <v>65</v>
+      </c>
+      <c r="AE11">
+        <v>320</v>
+      </c>
+      <c r="AF11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG11">
+        <v>12.5</v>
+      </c>
+      <c r="AH11">
+        <v>42</v>
+      </c>
+      <c r="AI11">
+        <v>240</v>
+      </c>
+      <c r="AJ11">
+        <v>10.5</v>
+      </c>
+      <c r="AK11">
+        <v>17.5</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>250</v>
+      </c>
+      <c r="AN11">
+        <v>5.2</v>
+      </c>
+      <c r="AO11">
+        <v>490</v>
+      </c>
+      <c r="AP11">
+        <v>17</v>
+      </c>
+      <c r="AQ11">
+        <v>5.4</v>
+      </c>
+      <c r="AR11">
+        <v>5.9</v>
+      </c>
+      <c r="AS11">
+        <v>6</v>
+      </c>
+      <c r="AT11">
+        <v>7.2</v>
+      </c>
+      <c r="AU11">
+        <v>11.5</v>
+      </c>
+      <c r="AV11">
+        <v>5.6</v>
+      </c>
+      <c r="AW11">
+        <v>6</v>
+      </c>
+      <c r="AX11">
+        <v>6.4</v>
+      </c>
+      <c r="AY11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11">
+        <v>5.3</v>
+      </c>
+      <c r="BA11">
+        <v>6</v>
+      </c>
+      <c r="BB11">
+        <v>7.8</v>
+      </c>
+      <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
+        <v>5.5</v>
+      </c>
+      <c r="BE11">
+        <v>6</v>
+      </c>
+      <c r="BF11">
         <v>3.9</v>
       </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>1000</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>970</v>
-      </c>
-      <c r="AC11">
-        <v>1000</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>970</v>
-      </c>
-      <c r="AG11">
-        <v>1000</v>
-      </c>
-      <c r="AH11">
-        <v>1000</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>1000</v>
-      </c>
-      <c r="AK11">
-        <v>1000</v>
-      </c>
-      <c r="AL11">
-        <v>1000</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>970</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>1.32</v>
-      </c>
-      <c r="AQ11">
-        <v>1.32</v>
-      </c>
-      <c r="AR11">
-        <v>1.32</v>
-      </c>
-      <c r="AS11">
-        <v>1.32</v>
-      </c>
-      <c r="AT11">
-        <v>1.22</v>
-      </c>
-      <c r="AU11">
-        <v>1.32</v>
-      </c>
-      <c r="AV11">
-        <v>1.32</v>
-      </c>
-      <c r="AW11">
-        <v>1.32</v>
-      </c>
-      <c r="AX11">
-        <v>1.18</v>
-      </c>
-      <c r="AY11">
-        <v>1.32</v>
-      </c>
-      <c r="AZ11">
-        <v>1.32</v>
-      </c>
-      <c r="BA11">
-        <v>1.32</v>
-      </c>
-      <c r="BB11">
-        <v>1.32</v>
-      </c>
-      <c r="BC11">
-        <v>1.32</v>
-      </c>
-      <c r="BD11">
-        <v>1.32</v>
-      </c>
-      <c r="BE11">
-        <v>1.32</v>
-      </c>
-      <c r="BF11">
-        <v>1.17</v>
-      </c>
       <c r="BG11">
-        <v>1.32</v>
+        <v>6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3819,7 +3819,7 @@
         <v>3.75</v>
       </c>
       <c r="I12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>3.55</v>
@@ -3831,7 +3831,7 @@
         <v>1.33</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
         <v>3.95</v>
@@ -3846,16 +3846,16 @@
         <v>1.9</v>
       </c>
       <c r="R12">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T12">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
         <v>1.33</v>
@@ -3864,13 +3864,13 @@
         <v>1.86</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA12">
         <v>95</v>
@@ -3879,97 +3879,97 @@
         <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF12">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG12">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN12">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AO12">
         <v>55</v>
       </c>
       <c r="AP12">
-        <v>1.56</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12">
-        <v>1.56</v>
+        <v>13</v>
       </c>
       <c r="AR12">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="AS12">
-        <v>1.54</v>
+        <v>5.1</v>
       </c>
       <c r="AT12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU12">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV12">
-        <v>1.56</v>
+        <v>14</v>
       </c>
       <c r="AW12">
-        <v>1.56</v>
+        <v>4.9</v>
       </c>
       <c r="AX12">
-        <v>1.54</v>
+        <v>12</v>
       </c>
       <c r="AY12">
-        <v>1.73</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>1.56</v>
+        <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>1.56</v>
+        <v>5</v>
       </c>
       <c r="BB12">
-        <v>1.56</v>
+        <v>18.5</v>
       </c>
       <c r="BC12">
-        <v>1.56</v>
+        <v>16</v>
       </c>
       <c r="BD12">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="BE12">
-        <v>1.56</v>
+        <v>5.1</v>
       </c>
       <c r="BF12">
-        <v>1.49</v>
+        <v>12.5</v>
       </c>
       <c r="BG12">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="BH12">
         <v>4.1</v>
@@ -3981,13 +3981,13 @@
         <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BL12">
         <v>140</v>
       </c>
       <c r="BM12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN12">
         <v>5.7</v>
@@ -3999,7 +3999,7 @@
         <v>17.5</v>
       </c>
       <c r="BQ12">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BR12">
         <v>34</v>
@@ -4011,10 +4011,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW12">
         <v>4.3</v>
@@ -4055,19 +4055,19 @@
         <v>2.7</v>
       </c>
       <c r="G13">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H13">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I13">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J13">
         <v>3.45</v>
       </c>
       <c r="K13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L13">
         <v>1.36</v>
@@ -4082,28 +4082,28 @@
         <v>1.33</v>
       </c>
       <c r="P13">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q13">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R13">
         <v>1.34</v>
       </c>
       <c r="S13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U13">
         <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X13">
         <v>14.5</v>
@@ -4112,25 +4112,25 @@
         <v>12</v>
       </c>
       <c r="Z13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA13">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC13">
         <v>8</v>
       </c>
       <c r="AD13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG13">
         <v>13</v>
@@ -4139,22 +4139,22 @@
         <v>18</v>
       </c>
       <c r="AI13">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL13">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM13">
         <v>110</v>
       </c>
       <c r="AN13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO13">
         <v>28</v>
@@ -4166,25 +4166,25 @@
         <v>10</v>
       </c>
       <c r="AR13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS13">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AT13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
         <v>11</v>
       </c>
       <c r="AW13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY13">
         <v>11</v>
@@ -4193,10 +4193,10 @@
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="BB13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC13">
         <v>15.5</v>
@@ -4208,16 +4208,16 @@
         <v>44</v>
       </c>
       <c r="BF13">
+        <v>20</v>
+      </c>
+      <c r="BG13">
         <v>19.5</v>
-      </c>
-      <c r="BG13">
-        <v>20</v>
       </c>
       <c r="BH13">
         <v>3.75</v>
       </c>
       <c r="BI13">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
@@ -4306,34 +4306,34 @@
         <v>110</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
+        <v>1.34</v>
+      </c>
+      <c r="O14">
+        <v>1.05</v>
+      </c>
+      <c r="P14">
+        <v>1.33</v>
+      </c>
+      <c r="Q14">
         <v>1.32</v>
-      </c>
-      <c r="O14">
-        <v>1.3</v>
-      </c>
-      <c r="P14">
-        <v>1.32</v>
-      </c>
-      <c r="Q14">
-        <v>1.84</v>
       </c>
       <c r="R14">
         <v>1.18</v>
       </c>
       <c r="S14">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4342,10 +4342,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4542,13 +4542,13 @@
         <v>110</v>
       </c>
       <c r="H15">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="I15">
         <v>110</v>
       </c>
       <c r="J15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4560,22 +4560,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O15">
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R15">
         <v>1.18</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4584,10 +4584,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4778,55 +4778,55 @@
         <v>210</v>
       </c>
       <c r="F16">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H16">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="I16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J16">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K16">
         <v>3.85</v>
       </c>
       <c r="L16">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M16">
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
         <v>1.35</v>
       </c>
       <c r="P16">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q16">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S16">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T16">
         <v>1.81</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
         <v>1.84</v>
@@ -4835,7 +4835,7 @@
         <v>16</v>
       </c>
       <c r="Y16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z16">
         <v>32</v>
@@ -4850,10 +4850,10 @@
         <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF16">
         <v>13.5</v>
@@ -4862,10 +4862,10 @@
         <v>11.5</v>
       </c>
       <c r="AH16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI16">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
         <v>27</v>
@@ -4874,76 +4874,76 @@
         <v>24</v>
       </c>
       <c r="AL16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM16">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN16">
         <v>17.5</v>
       </c>
       <c r="AO16">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ16">
         <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
         <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH16">
         <v>3.4</v>
       </c>
       <c r="BI16">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16">
         <v>10.5</v>
@@ -4955,13 +4955,13 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BN16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO16">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP16">
         <v>16</v>
@@ -4973,22 +4973,22 @@
         <v>32</v>
       </c>
       <c r="BS16">
-        <v>2.36</v>
+        <v>7.8</v>
       </c>
       <c r="BT16">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU16">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW16">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="BX16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY16">
         <v>2.44</v>
@@ -4997,7 +4997,7 @@
         <v>29</v>
       </c>
       <c r="CA16">
-        <v>2.34</v>
+        <v>7.6</v>
       </c>
       <c r="CB16" t="s">
         <v>260</v>
@@ -5026,7 +5026,7 @@
         <v>1.93</v>
       </c>
       <c r="H17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I17">
         <v>5.8</v>
@@ -5041,34 +5041,34 @@
         <v>1.33</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O17">
         <v>1.31</v>
       </c>
       <c r="P17">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q17">
         <v>1.96</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V17">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W17">
         <v>2.08</v>
@@ -5128,10 +5128,10 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
         <v>1.03</v>
@@ -5140,10 +5140,10 @@
         <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
         <v>1.03</v>
@@ -5152,10 +5152,10 @@
         <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
         <v>1.03</v>
@@ -5262,25 +5262,25 @@
         <v>212</v>
       </c>
       <c r="F18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G18">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H18">
         <v>2.4</v>
       </c>
       <c r="I18">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J18">
         <v>3.55</v>
       </c>
       <c r="K18">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M18">
         <v>1.05</v>
@@ -5292,7 +5292,7 @@
         <v>1.26</v>
       </c>
       <c r="P18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q18">
         <v>1.75</v>
@@ -5310,22 +5310,22 @@
         <v>2.32</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
         <v>1.47</v>
       </c>
       <c r="X18">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA18">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB18">
         <v>15</v>
@@ -5334,10 +5334,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF18">
         <v>23</v>
@@ -5349,22 +5349,22 @@
         <v>16.5</v>
       </c>
       <c r="AI18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ18">
         <v>55</v>
       </c>
       <c r="AK18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL18">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM18">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN18">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO18">
         <v>17.5</v>
@@ -5373,13 +5373,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS18">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18">
         <v>12</v>
@@ -5388,31 +5388,31 @@
         <v>7.6</v>
       </c>
       <c r="AV18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW18">
-        <v>18.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY18">
         <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA18">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BB18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC18">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD18">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BE18">
         <v>9.4</v>
@@ -5421,7 +5421,7 @@
         <v>18.5</v>
       </c>
       <c r="BG18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH18">
         <v>3.9</v>
@@ -5433,7 +5433,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK18">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5463,7 +5463,7 @@
         <v>5.7</v>
       </c>
       <c r="BU18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV18">
         <v>18</v>
@@ -5510,22 +5510,22 @@
         <v>5.6</v>
       </c>
       <c r="H19">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I19">
         <v>2.22</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="K19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N19">
         <v>2.46</v>
@@ -5534,7 +5534,7 @@
         <v>1.5</v>
       </c>
       <c r="P19">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Q19">
         <v>2.46</v>
@@ -5546,16 +5546,16 @@
         <v>2.92</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V19">
         <v>1.82</v>
       </c>
       <c r="W19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5612,13 +5612,13 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
         <v>1.03</v>
@@ -5627,7 +5627,7 @@
         <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
         <v>1.03</v>
@@ -5755,7 +5755,7 @@
         <v>1.38</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="J20">
         <v>3</v>
@@ -5794,10 +5794,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5857,10 +5857,10 @@
         <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS20">
         <v>1.03</v>
@@ -5869,37 +5869,37 @@
         <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV20">
         <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ20">
         <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5988,226 +5988,226 @@
         <v>215</v>
       </c>
       <c r="F21">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G21">
         <v>1.19</v>
       </c>
       <c r="H21">
-        <v>1.1</v>
+        <v>21</v>
       </c>
       <c r="I21">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J21">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="L21">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O21">
         <v>1.11</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R21">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
         <v>1.8</v>
       </c>
       <c r="T21">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U21">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W21">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="X21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y21">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="Z21">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AA21">
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC21">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AD21">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AE21">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="AF21">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG21">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI21">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AJ21">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AK21">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL21">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM21">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN21">
         <v>2.76</v>
       </c>
       <c r="AO21">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="AP21">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AQ21">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AR21">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AS21">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT21">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AU21">
-        <v>5.3</v>
+        <v>19.5</v>
       </c>
       <c r="AV21">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW21">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AX21">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY21">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="AZ21">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA21">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BB21">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BC21">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="BD21">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE21">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BF21">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BG21">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BH21">
         <v>6.2</v>
       </c>
       <c r="BI21">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ21">
         <v>15</v>
       </c>
       <c r="BK21">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN21">
         <v>4.2</v>
       </c>
       <c r="BO21">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="BP21">
         <v>6</v>
       </c>
       <c r="BQ21">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR21">
+        <v>21</v>
+      </c>
+      <c r="BS21">
+        <v>6.8</v>
+      </c>
+      <c r="BT21">
         <v>22</v>
       </c>
-      <c r="BS21">
-        <v>6.6</v>
-      </c>
-      <c r="BT21">
-        <v>23</v>
-      </c>
       <c r="BU21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ21">
         <v>6.4</v>
       </c>
       <c r="CA21">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="CB21" t="s">
         <v>260</v>
@@ -6230,22 +6230,22 @@
         <v>216</v>
       </c>
       <c r="F22">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G22">
         <v>2.4</v>
       </c>
       <c r="H22">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I22">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6254,31 +6254,31 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
         <v>2.42</v>
       </c>
       <c r="Q22">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="R22">
         <v>1.59</v>
       </c>
       <c r="S22">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V22">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
         <v>1.71</v>
@@ -6287,46 +6287,46 @@
         <v>1000</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM22">
         <v>1000</v>
@@ -6338,58 +6338,58 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AQ22">
-        <v>1.02</v>
+        <v>12.5</v>
       </c>
       <c r="AR22">
-        <v>1.02</v>
+        <v>15</v>
       </c>
       <c r="AS22">
-        <v>1.02</v>
+        <v>26</v>
       </c>
       <c r="AT22">
-        <v>1.02</v>
+        <v>11</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>1.02</v>
+        <v>9.4</v>
       </c>
       <c r="AW22">
-        <v>1.02</v>
+        <v>17.5</v>
       </c>
       <c r="AX22">
-        <v>1.02</v>
+        <v>11</v>
       </c>
       <c r="AY22">
-        <v>1.02</v>
+        <v>7.8</v>
       </c>
       <c r="AZ22">
-        <v>1.02</v>
+        <v>11</v>
       </c>
       <c r="BA22">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="BB22">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="BC22">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="BD22">
-        <v>1.02</v>
+        <v>17</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6472,13 +6472,13 @@
         <v>217</v>
       </c>
       <c r="F23">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H23">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I23">
         <v>3.2</v>
@@ -6487,43 +6487,43 @@
         <v>3</v>
       </c>
       <c r="K23">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L23">
         <v>1.38</v>
       </c>
       <c r="M23">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N23">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P23">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q23">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R23">
         <v>1.23</v>
       </c>
       <c r="S23">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="T23">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U23">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V23">
         <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X23">
         <v>12.5</v>
@@ -6538,7 +6538,7 @@
         <v>60</v>
       </c>
       <c r="AB23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC23">
         <v>8.4</v>
@@ -6580,58 +6580,58 @@
         <v>46</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6714,22 +6714,22 @@
         <v>218</v>
       </c>
       <c r="F24">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="G24">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H24">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I24">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K24">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L24">
         <v>1.18</v>
@@ -6738,58 +6738,58 @@
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P24">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q24">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R24">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="T24">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U24">
         <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W24">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="X24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Y24">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z24">
+        <v>130</v>
+      </c>
+      <c r="AA24">
+        <v>360</v>
+      </c>
+      <c r="AB24">
+        <v>16.5</v>
+      </c>
+      <c r="AC24">
+        <v>17.5</v>
+      </c>
+      <c r="AD24">
+        <v>42</v>
+      </c>
+      <c r="AE24">
         <v>140</v>
-      </c>
-      <c r="AA24">
-        <v>390</v>
-      </c>
-      <c r="AB24">
-        <v>18.5</v>
-      </c>
-      <c r="AC24">
-        <v>20</v>
-      </c>
-      <c r="AD24">
-        <v>55</v>
-      </c>
-      <c r="AE24">
-        <v>150</v>
       </c>
       <c r="AF24">
         <v>12.5</v>
@@ -6798,34 +6798,34 @@
         <v>12.5</v>
       </c>
       <c r="AH24">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AI24">
         <v>110</v>
       </c>
       <c r="AJ24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AL24">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AM24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN24">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AO24">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP24">
         <v>10.5</v>
       </c>
       <c r="AQ24">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AR24">
         <v>11</v>
@@ -6834,13 +6834,13 @@
         <v>11.5</v>
       </c>
       <c r="AT24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU24">
         <v>15.5</v>
       </c>
       <c r="AV24">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="AW24">
         <v>11</v>
@@ -6852,7 +6852,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ24">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BA24">
         <v>11</v>
@@ -6864,13 +6864,13 @@
         <v>11.5</v>
       </c>
       <c r="BD24">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BE24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF24">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="BG24">
         <v>11</v>
@@ -6885,7 +6885,7 @@
         <v>11</v>
       </c>
       <c r="BK24">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
@@ -6903,37 +6903,37 @@
         <v>7.2</v>
       </c>
       <c r="BQ24">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR24">
         <v>970</v>
       </c>
       <c r="BS24">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU24">
+        <v>7</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>11.5</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>11</v>
+      </c>
+      <c r="BZ24">
         <v>7.2</v>
       </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
-        <v>12</v>
-      </c>
-      <c r="BX24">
-        <v>1000</v>
-      </c>
-      <c r="BY24">
-        <v>11.5</v>
-      </c>
-      <c r="BZ24">
-        <v>7</v>
-      </c>
       <c r="CA24">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB24" t="s">
         <v>260</v>
@@ -6980,10 +6980,10 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="O25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -6995,10 +6995,10 @@
         <v>3</v>
       </c>
       <c r="S25">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T25">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U25">
         <v>2.04</v>
@@ -7010,7 +7010,7 @@
         <v>9.6</v>
       </c>
       <c r="X25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Y25">
         <v>190</v>
@@ -7022,10 +7022,10 @@
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC25">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD25">
         <v>140</v>
@@ -7034,7 +7034,7 @@
         <v>460</v>
       </c>
       <c r="AF25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG25">
         <v>18</v>
@@ -7055,10 +7055,10 @@
         <v>36</v>
       </c>
       <c r="AM25">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN25">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AO25">
         <v>360</v>
@@ -7067,22 +7067,22 @@
         <v>36</v>
       </c>
       <c r="AQ25">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AR25">
         <v>55</v>
       </c>
       <c r="AS25">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT25">
         <v>21</v>
       </c>
       <c r="AU25">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AV25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AW25">
         <v>55</v>
@@ -7091,28 +7091,28 @@
         <v>13</v>
       </c>
       <c r="AY25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA25">
         <v>46</v>
       </c>
       <c r="BB25">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC25">
         <v>13.5</v>
       </c>
       <c r="BD25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE25">
         <v>44</v>
       </c>
       <c r="BF25">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BG25">
         <v>50</v>
@@ -7121,19 +7121,19 @@
         <v>8.6</v>
       </c>
       <c r="BI25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BJ25">
         <v>14.5</v>
       </c>
       <c r="BK25">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL25">
         <v>130</v>
       </c>
       <c r="BM25">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN25">
         <v>4.9</v>
@@ -7151,10 +7151,10 @@
         <v>17.5</v>
       </c>
       <c r="BS25">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT25">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BU25">
         <v>7.2</v>
@@ -7169,7 +7169,7 @@
         <v>110</v>
       </c>
       <c r="BY25">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ25">
         <v>4.5</v>
@@ -7207,7 +7207,7 @@
         <v>12</v>
       </c>
       <c r="I26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J26">
         <v>7.8</v>
@@ -7243,13 +7243,13 @@
         <v>1.67</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V26">
         <v>1.08</v>
       </c>
       <c r="W26">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X26">
         <v>60</v>
@@ -7267,7 +7267,7 @@
         <v>19.5</v>
       </c>
       <c r="AC26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD26">
         <v>46</v>
@@ -7279,16 +7279,16 @@
         <v>13</v>
       </c>
       <c r="AG26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH26">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI26">
         <v>95</v>
       </c>
       <c r="AJ26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK26">
         <v>13</v>
@@ -7309,7 +7309,7 @@
         <v>50</v>
       </c>
       <c r="AQ26">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AR26">
         <v>42</v>
@@ -7318,13 +7318,13 @@
         <v>55</v>
       </c>
       <c r="AT26">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU26">
         <v>18</v>
       </c>
       <c r="AV26">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AW26">
         <v>42</v>
@@ -7339,85 +7339,85 @@
         <v>22</v>
       </c>
       <c r="BA26">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB26">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC26">
         <v>11.5</v>
       </c>
       <c r="BD26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE26">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF26">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BG26">
         <v>38</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI26">
-        <v>1.57</v>
+        <v>5.9</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK26">
-        <v>1.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM26">
         <v>20</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO26">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ26">
-        <v>1.59</v>
+        <v>6</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BS26">
-        <v>1.93</v>
+        <v>8.4</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU26">
-        <v>1.93</v>
+        <v>10.5</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW26">
         <v>20</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY26">
         <v>16.5</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="CA26">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="CB26" t="s">
         <v>260</v>
@@ -7440,7 +7440,7 @@
         <v>221</v>
       </c>
       <c r="F27">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G27">
         <v>1.8</v>
@@ -7449,7 +7449,7 @@
         <v>4.6</v>
       </c>
       <c r="I27">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>4.1</v>
@@ -7458,7 +7458,7 @@
         <v>4.5</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M27">
         <v>1.04</v>
@@ -7479,13 +7479,13 @@
         <v>1.51</v>
       </c>
       <c r="S27">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="T27">
         <v>1.68</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V27">
         <v>1.25</v>
@@ -7518,7 +7518,7 @@
         <v>1000</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG27">
         <v>970</v>
@@ -7548,19 +7548,19 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AQ27">
-        <v>1.33</v>
+        <v>16</v>
       </c>
       <c r="AR27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AS27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AT27">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AU27">
         <v>8.199999999999999</v>
@@ -7569,37 +7569,37 @@
         <v>11</v>
       </c>
       <c r="AW27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AX27">
         <v>8.6</v>
       </c>
       <c r="AY27">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="AZ27">
         <v>10.5</v>
       </c>
       <c r="BA27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="BB27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="BC27">
         <v>10.5</v>
       </c>
       <c r="BD27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="BE27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="BF27">
         <v>6</v>
       </c>
       <c r="BG27">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7685,7 +7685,7 @@
         <v>2.3</v>
       </c>
       <c r="G28">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H28">
         <v>3.1</v>
@@ -7697,10 +7697,10 @@
         <v>3.8</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L28">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M28">
         <v>1.05</v>
@@ -7721,7 +7721,7 @@
         <v>1.49</v>
       </c>
       <c r="S28">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T28">
         <v>1.66</v>
@@ -7730,7 +7730,7 @@
         <v>2.44</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
         <v>1.72</v>
@@ -7784,10 +7784,10 @@
         <v>70</v>
       </c>
       <c r="AN28">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP28">
         <v>16.5</v>
@@ -7820,13 +7820,13 @@
         <v>10</v>
       </c>
       <c r="AZ28">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA28">
         <v>30</v>
       </c>
       <c r="BB28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC28">
         <v>21</v>
@@ -7859,49 +7859,49 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN28">
         <v>5.5</v>
       </c>
       <c r="BO28">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP28">
         <v>17</v>
       </c>
       <c r="BQ28">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR28">
         <v>28</v>
       </c>
       <c r="BS28">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU28">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV28">
         <v>23</v>
       </c>
       <c r="BW28">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX28">
         <v>34</v>
       </c>
       <c r="BY28">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ28">
         <v>22</v>
       </c>
       <c r="CA28">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB28" t="s">
         <v>260</v>
@@ -7927,10 +7927,10 @@
         <v>1.94</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I29">
         <v>4.1</v>
@@ -7951,13 +7951,13 @@
         <v>5</v>
       </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P29">
         <v>2.36</v>
       </c>
       <c r="Q29">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R29">
         <v>1.55</v>
@@ -7969,13 +7969,13 @@
         <v>1.64</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V29">
         <v>1.32</v>
       </c>
       <c r="W29">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X29">
         <v>22</v>
@@ -8032,10 +8032,10 @@
         <v>40</v>
       </c>
       <c r="AP29">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR29">
         <v>24</v>
@@ -8169,61 +8169,61 @@
         <v>2.96</v>
       </c>
       <c r="G30">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H30">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I30">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J30">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K30">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L30">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N30">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="O30">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P30">
+        <v>2.42</v>
+      </c>
+      <c r="Q30">
+        <v>1.58</v>
+      </c>
+      <c r="R30">
+        <v>1.58</v>
+      </c>
+      <c r="S30">
         <v>2.32</v>
       </c>
-      <c r="Q30">
-        <v>1.52</v>
-      </c>
-      <c r="R30">
-        <v>1.56</v>
-      </c>
-      <c r="S30">
-        <v>2.34</v>
-      </c>
       <c r="T30">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U30">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W30">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z30">
         <v>21</v>
@@ -8232,10 +8232,10 @@
         <v>36</v>
       </c>
       <c r="AB30">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD30">
         <v>13.5</v>
@@ -8244,88 +8244,88 @@
         <v>25</v>
       </c>
       <c r="AF30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG30">
         <v>16.5</v>
       </c>
       <c r="AH30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI30">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ30">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK30">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL30">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM30">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN30">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH30">
         <v>4.9</v>
@@ -8426,7 +8426,7 @@
         <v>4</v>
       </c>
       <c r="L31">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M31">
         <v>1.05</v>
@@ -8444,7 +8444,7 @@
         <v>1.72</v>
       </c>
       <c r="R31">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S31">
         <v>2.82</v>
@@ -8516,13 +8516,13 @@
         <v>29</v>
       </c>
       <c r="AP31">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ31">
         <v>14</v>
       </c>
       <c r="AR31">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS31">
         <v>7.8</v>
@@ -8573,19 +8573,19 @@
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BN31">
         <v>1000</v>
@@ -8597,37 +8597,37 @@
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CB31" t="s">
         <v>260</v>
@@ -8662,7 +8662,7 @@
         <v>1.5</v>
       </c>
       <c r="J32">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K32">
         <v>4.7</v>
@@ -8674,13 +8674,13 @@
         <v>1.08</v>
       </c>
       <c r="N32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O32">
         <v>1.39</v>
       </c>
       <c r="P32">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q32">
         <v>2.16</v>
@@ -8704,7 +8704,7 @@
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y32">
         <v>6.4</v>
@@ -8725,7 +8725,7 @@
         <v>11</v>
       </c>
       <c r="AE32">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AF32">
         <v>110</v>
@@ -8740,7 +8740,7 @@
         <v>65</v>
       </c>
       <c r="AJ32">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AK32">
         <v>260</v>
@@ -8752,64 +8752,64 @@
         <v>310</v>
       </c>
       <c r="AN32">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AO32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AP32">
         <v>11.5</v>
       </c>
       <c r="AQ32">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR32">
         <v>6.6</v>
       </c>
       <c r="AS32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT32">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AU32">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV32">
         <v>9.6</v>
       </c>
       <c r="AW32">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX32">
         <v>8.800000000000001</v>
       </c>
       <c r="AY32">
+        <v>8</v>
+      </c>
+      <c r="AZ32">
+        <v>7.4</v>
+      </c>
+      <c r="BA32">
+        <v>7.6</v>
+      </c>
+      <c r="BB32">
         <v>8.4</v>
       </c>
-      <c r="AZ32">
-        <v>7.8</v>
-      </c>
-      <c r="BA32">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB32">
-        <v>9.4</v>
-      </c>
       <c r="BC32">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD32">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE32">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF32">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG32">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8821,55 +8821,55 @@
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="CB32" t="s">
         <v>260</v>
@@ -8904,7 +8904,7 @@
         <v>110</v>
       </c>
       <c r="J33">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K33">
         <v>950</v>
@@ -8922,7 +8922,7 @@
         <v>1.26</v>
       </c>
       <c r="P33">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q33">
         <v>1.26</v>
@@ -8940,10 +8940,10 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9143,19 +9143,19 @@
         <v>2.84</v>
       </c>
       <c r="I34">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K34">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L34">
         <v>1.63</v>
       </c>
       <c r="M34">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N34">
         <v>2.36</v>
@@ -9167,7 +9167,7 @@
         <v>1.45</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R34">
         <v>1.15</v>
@@ -9179,10 +9179,10 @@
         <v>2.3</v>
       </c>
       <c r="U34">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V34">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>1.43</v>
@@ -9215,7 +9215,7 @@
         <v>20</v>
       </c>
       <c r="AG34">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH34">
         <v>29</v>
@@ -9251,19 +9251,19 @@
         <v>14.5</v>
       </c>
       <c r="AS34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT34">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU34">
         <v>6.2</v>
       </c>
       <c r="AV34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW34">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AX34">
         <v>16.5</v>
@@ -9272,88 +9272,88 @@
         <v>13.5</v>
       </c>
       <c r="AZ34">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA34">
+        <v>11</v>
+      </c>
+      <c r="BB34">
+        <v>11</v>
+      </c>
+      <c r="BC34">
         <v>10.5</v>
       </c>
-      <c r="BB34">
-        <v>10</v>
-      </c>
-      <c r="BC34">
-        <v>10</v>
-      </c>
       <c r="BD34">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE34">
         <v>11</v>
       </c>
       <c r="BF34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI34">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="CB34" t="s">
         <v>260</v>
@@ -9376,31 +9376,31 @@
         <v>229</v>
       </c>
       <c r="F35">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G35">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H35">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I35">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J35">
         <v>3.45</v>
       </c>
       <c r="K35">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L35">
         <v>1.39</v>
       </c>
       <c r="M35">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N35">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O35">
         <v>1.31</v>
@@ -9421,28 +9421,28 @@
         <v>1.73</v>
       </c>
       <c r="U35">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V35">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W35">
         <v>1.37</v>
       </c>
       <c r="X35">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y35">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z35">
         <v>15.5</v>
       </c>
       <c r="AA35">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AB35">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC35">
         <v>8.4</v>
@@ -9454,16 +9454,16 @@
         <v>25</v>
       </c>
       <c r="AF35">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG35">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH35">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI35">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ35">
         <v>80</v>
@@ -9481,7 +9481,7 @@
         <v>40</v>
       </c>
       <c r="AO35">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AP35">
         <v>13</v>
@@ -9493,7 +9493,7 @@
         <v>12.5</v>
       </c>
       <c r="AS35">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AT35">
         <v>12</v>
@@ -9505,10 +9505,10 @@
         <v>9.6</v>
       </c>
       <c r="AW35">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX35">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY35">
         <v>12.5</v>
@@ -9517,28 +9517,28 @@
         <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BB35">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC35">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BD35">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE35">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BF35">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BG35">
         <v>15</v>
       </c>
       <c r="BH35">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI35">
         <v>3.1</v>
@@ -9547,55 +9547,55 @@
         <v>9.6</v>
       </c>
       <c r="BK35">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BN35">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO35">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP35">
         <v>28</v>
       </c>
       <c r="BQ35">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR35">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS35">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT35">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU35">
         <v>4.5</v>
       </c>
       <c r="BV35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW35">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX35">
         <v>30</v>
       </c>
       <c r="BY35">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ35">
         <v>26</v>
       </c>
       <c r="CA35">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB35" t="s">
         <v>260</v>
@@ -9618,22 +9618,22 @@
         <v>230</v>
       </c>
       <c r="F36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G36">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H36">
         <v>2.18</v>
       </c>
       <c r="I36">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J36">
         <v>2.96</v>
       </c>
       <c r="K36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L36">
         <v>1.43</v>
@@ -9642,16 +9642,16 @@
         <v>1.06</v>
       </c>
       <c r="N36">
-        <v>2.58</v>
+        <v>1.02</v>
       </c>
       <c r="O36">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="P36">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q36">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R36">
         <v>1.18</v>
@@ -9660,16 +9660,16 @@
         <v>2.8</v>
       </c>
       <c r="T36">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V36">
         <v>1.65</v>
       </c>
       <c r="W36">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9860,58 +9860,58 @@
         <v>231</v>
       </c>
       <c r="F37">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="G37">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="H37">
         <v>11</v>
       </c>
       <c r="I37">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="J37">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="K37">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.02</v>
+      </c>
+      <c r="N37">
+        <v>3.75</v>
+      </c>
+      <c r="O37">
         <v>1.3</v>
       </c>
-      <c r="M37">
-        <v>1.01</v>
-      </c>
-      <c r="N37">
-        <v>3.7</v>
-      </c>
-      <c r="O37">
-        <v>1.29</v>
-      </c>
       <c r="P37">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="Q37">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S37">
         <v>2.5</v>
       </c>
       <c r="T37">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="U37">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="V37">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W37">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9926,7 +9926,7 @@
         <v>1000</v>
       </c>
       <c r="AB37">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC37">
         <v>1000</v>
@@ -9938,7 +9938,7 @@
         <v>1000</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG37">
         <v>1000</v>
@@ -9950,7 +9950,7 @@
         <v>1000</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK37">
         <v>1000</v>
@@ -9962,64 +9962,64 @@
         <v>1000</v>
       </c>
       <c r="AN37">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO37">
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AQ37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AS37">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AT37">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AU37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AV37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AW37">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AX37">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AZ37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="BA37">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="BB37">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BC37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="BD37">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="BE37">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -10111,10 +10111,10 @@
         <v>14</v>
       </c>
       <c r="I38">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J38">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="K38">
         <v>8.800000000000001</v>
@@ -10141,10 +10141,10 @@
         <v>2.08</v>
       </c>
       <c r="S38">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="T38">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U38">
         <v>2</v>
@@ -10204,22 +10204,22 @@
         <v>130</v>
       </c>
       <c r="AN38">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AO38">
         <v>170</v>
       </c>
       <c r="AP38">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AQ38">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AR38">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS38">
         <v>10</v>
-      </c>
-      <c r="AS38">
-        <v>10.5</v>
       </c>
       <c r="AT38">
         <v>14</v>
@@ -10228,10 +10228,10 @@
         <v>17</v>
       </c>
       <c r="AV38">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW38">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX38">
         <v>9.6</v>
@@ -10240,28 +10240,28 @@
         <v>11</v>
       </c>
       <c r="AZ38">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BA38">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB38">
         <v>9.199999999999999</v>
       </c>
       <c r="BC38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD38">
         <v>8</v>
       </c>
       <c r="BE38">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF38">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BG38">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10344,22 +10344,22 @@
         <v>233</v>
       </c>
       <c r="F39">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G39">
         <v>4.2</v>
       </c>
       <c r="H39">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="I39">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J39">
         <v>3.9</v>
       </c>
       <c r="K39">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L39">
         <v>1.3</v>
@@ -10377,22 +10377,22 @@
         <v>2.28</v>
       </c>
       <c r="Q39">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R39">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S39">
         <v>2.68</v>
       </c>
       <c r="T39">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U39">
         <v>2.34</v>
       </c>
       <c r="V39">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="W39">
         <v>1.31</v>
@@ -10446,7 +10446,7 @@
         <v>85</v>
       </c>
       <c r="AN39">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO39">
         <v>11</v>
@@ -10589,13 +10589,13 @@
         <v>3.25</v>
       </c>
       <c r="G40">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H40">
         <v>2.4</v>
       </c>
       <c r="I40">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J40">
         <v>3.5</v>
@@ -10616,10 +10616,10 @@
         <v>1.32</v>
       </c>
       <c r="P40">
+        <v>2</v>
+      </c>
+      <c r="Q40">
         <v>1.97</v>
-      </c>
-      <c r="Q40">
-        <v>1.96</v>
       </c>
       <c r="R40">
         <v>1.37</v>
@@ -10634,16 +10634,16 @@
         <v>2.22</v>
       </c>
       <c r="V40">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X40">
         <v>14</v>
       </c>
       <c r="Y40">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z40">
         <v>16</v>
@@ -10655,13 +10655,13 @@
         <v>13</v>
       </c>
       <c r="AC40">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD40">
         <v>11.5</v>
       </c>
       <c r="AE40">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF40">
         <v>22</v>
@@ -10697,10 +10697,10 @@
         <v>12.5</v>
       </c>
       <c r="AQ40">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR40">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS40">
         <v>30</v>
@@ -10709,10 +10709,10 @@
         <v>12</v>
       </c>
       <c r="AU40">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV40">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW40">
         <v>23</v>
@@ -10721,25 +10721,25 @@
         <v>18.5</v>
       </c>
       <c r="AY40">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ40">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA40">
         <v>34</v>
       </c>
       <c r="BB40">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC40">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD40">
         <v>40</v>
       </c>
       <c r="BE40">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF40">
         <v>29</v>
@@ -10766,7 +10766,7 @@
         <v>27</v>
       </c>
       <c r="BN40">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO40">
         <v>1.98</v>
@@ -10775,7 +10775,7 @@
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>2.64</v>
+        <v>10</v>
       </c>
       <c r="BR40">
         <v>1000</v>
@@ -10834,13 +10834,13 @@
         <v>2.02</v>
       </c>
       <c r="H41">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J41">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K41">
         <v>3.95</v>
@@ -10849,40 +10849,40 @@
         <v>1.33</v>
       </c>
       <c r="M41">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N41">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O41">
         <v>1.27</v>
       </c>
       <c r="P41">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q41">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R41">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S41">
         <v>3</v>
       </c>
       <c r="T41">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U41">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V41">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W41">
         <v>1.98</v>
       </c>
       <c r="X41">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y41">
         <v>17</v>
@@ -10891,13 +10891,13 @@
         <v>32</v>
       </c>
       <c r="AA41">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB41">
         <v>11</v>
       </c>
       <c r="AC41">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD41">
         <v>16.5</v>
@@ -10906,7 +10906,7 @@
         <v>46</v>
       </c>
       <c r="AF41">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG41">
         <v>11</v>
@@ -10921,13 +10921,13 @@
         <v>23</v>
       </c>
       <c r="AK41">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL41">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM41">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN41">
         <v>12</v>
@@ -10981,7 +10981,7 @@
         <v>28</v>
       </c>
       <c r="BE41">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BF41">
         <v>10.5</v>
@@ -11047,7 +11047,7 @@
         <v>1000</v>
       </c>
       <c r="CA41">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="CB41" t="s">
         <v>260</v>
@@ -11106,7 +11106,7 @@
         <v>1.47</v>
       </c>
       <c r="R42">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S42">
         <v>2.16</v>
@@ -11115,10 +11115,10 @@
         <v>1.77</v>
       </c>
       <c r="U42">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V42">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W42">
         <v>3.7</v>
@@ -11330,7 +11330,7 @@
         <v>4.3</v>
       </c>
       <c r="L43">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M43">
         <v>1.04</v>
@@ -11345,7 +11345,7 @@
         <v>2.5</v>
       </c>
       <c r="Q43">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R43">
         <v>1.6</v>
@@ -11354,10 +11354,10 @@
         <v>2.58</v>
       </c>
       <c r="T43">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U43">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V43">
         <v>1.23</v>
@@ -11366,7 +11366,7 @@
         <v>2.3</v>
       </c>
       <c r="X43">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y43">
         <v>24</v>
@@ -11381,16 +11381,16 @@
         <v>12</v>
       </c>
       <c r="AC43">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD43">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE43">
         <v>55</v>
       </c>
       <c r="AF43">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG43">
         <v>9.800000000000001</v>
@@ -11399,16 +11399,16 @@
         <v>16.5</v>
       </c>
       <c r="AI43">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ43">
         <v>18.5</v>
       </c>
       <c r="AK43">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL43">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM43">
         <v>70</v>
@@ -11417,7 +11417,7 @@
         <v>7.8</v>
       </c>
       <c r="AO43">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP43">
         <v>20</v>
@@ -11429,13 +11429,13 @@
         <v>38</v>
       </c>
       <c r="AS43">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT43">
         <v>11</v>
       </c>
       <c r="AU43">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV43">
         <v>17.5</v>
@@ -11453,7 +11453,7 @@
         <v>15.5</v>
       </c>
       <c r="BA43">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB43">
         <v>17</v>
@@ -11471,7 +11471,7 @@
         <v>7.4</v>
       </c>
       <c r="BG43">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH43">
         <v>4.2</v>
@@ -11560,10 +11560,10 @@
         <v>5.5</v>
       </c>
       <c r="H44">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I44">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J44">
         <v>3.9</v>
@@ -11617,7 +11617,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA44">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB44">
         <v>17</v>
@@ -11680,7 +11680,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV44">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW44">
         <v>17.5</v>
@@ -11692,7 +11692,7 @@
         <v>19.5</v>
       </c>
       <c r="AZ44">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA44">
         <v>34</v>
@@ -11701,7 +11701,7 @@
         <v>42</v>
       </c>
       <c r="BC44">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BD44">
         <v>65</v>
@@ -11743,13 +11743,13 @@
         <v>50</v>
       </c>
       <c r="BQ44">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BR44">
         <v>60</v>
       </c>
       <c r="BS44">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BT44">
         <v>4.3</v>
@@ -11767,13 +11767,13 @@
         <v>29</v>
       </c>
       <c r="BY44">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BZ44">
         <v>25</v>
       </c>
       <c r="CA44">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="CB44" t="s">
         <v>260</v>
@@ -11796,7 +11796,7 @@
         <v>239</v>
       </c>
       <c r="F45">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G45">
         <v>1.91</v>
@@ -11805,7 +11805,7 @@
         <v>4.3</v>
       </c>
       <c r="I45">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J45">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         <v>1.57</v>
       </c>
       <c r="S45">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T45">
         <v>1.65</v>
@@ -11880,7 +11880,7 @@
         <v>10.5</v>
       </c>
       <c r="AH45">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI45">
         <v>48</v>
@@ -11889,7 +11889,7 @@
         <v>21</v>
       </c>
       <c r="AK45">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL45">
         <v>28</v>
@@ -11943,7 +11943,7 @@
         <v>19</v>
       </c>
       <c r="BC45">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD45">
         <v>25</v>
@@ -12047,7 +12047,7 @@
         <v>1.5</v>
       </c>
       <c r="I46">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J46">
         <v>5.1</v>
@@ -12062,31 +12062,31 @@
         <v>1.03</v>
       </c>
       <c r="N46">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P46">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q46">
         <v>1.53</v>
       </c>
       <c r="R46">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S46">
         <v>2.32</v>
       </c>
       <c r="T46">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U46">
         <v>2.32</v>
       </c>
       <c r="V46">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W46">
         <v>1.16</v>
@@ -12140,7 +12140,7 @@
         <v>85</v>
       </c>
       <c r="AN46">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO46">
         <v>5.5</v>
@@ -12155,7 +12155,7 @@
         <v>10</v>
       </c>
       <c r="AS46">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT46">
         <v>26</v>
@@ -12203,7 +12203,7 @@
         <v>1000</v>
       </c>
       <c r="BI46">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="BJ46">
         <v>1000</v>
@@ -12215,7 +12215,7 @@
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="BN46">
         <v>1000</v>
@@ -12227,13 +12227,13 @@
         <v>1000</v>
       </c>
       <c r="BQ46">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="BR46">
         <v>1000</v>
       </c>
       <c r="BS46">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="BT46">
         <v>1000</v>
@@ -12245,19 +12245,19 @@
         <v>1000</v>
       </c>
       <c r="BW46">
+        <v>1.95</v>
+      </c>
+      <c r="BX46">
+        <v>1000</v>
+      </c>
+      <c r="BY46">
         <v>1.78</v>
       </c>
-      <c r="BX46">
-        <v>1000</v>
-      </c>
-      <c r="BY46">
-        <v>1.64</v>
-      </c>
       <c r="BZ46">
         <v>1000</v>
       </c>
       <c r="CA46">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="CB46" t="s">
         <v>260</v>
@@ -12283,13 +12283,13 @@
         <v>3.35</v>
       </c>
       <c r="G47">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H47">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I47">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J47">
         <v>3.45</v>
@@ -12328,10 +12328,10 @@
         <v>2.18</v>
       </c>
       <c r="V47">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W47">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X47">
         <v>14.5</v>
@@ -12358,7 +12358,7 @@
         <v>26</v>
       </c>
       <c r="AF47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG47">
         <v>14.5</v>
@@ -12382,7 +12382,7 @@
         <v>95</v>
       </c>
       <c r="AN47">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO47">
         <v>20</v>
@@ -12427,7 +12427,7 @@
         <v>50</v>
       </c>
       <c r="BC47">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BD47">
         <v>42</v>
@@ -12448,7 +12448,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ47">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK47">
         <v>8.199999999999999</v>
@@ -12457,7 +12457,7 @@
         <v>140</v>
       </c>
       <c r="BM47">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BN47">
         <v>6.6</v>
@@ -12484,7 +12484,7 @@
         <v>4.7</v>
       </c>
       <c r="BV47">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW47">
         <v>7</v>
@@ -12549,25 +12549,25 @@
         <v>14</v>
       </c>
       <c r="O48">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P48">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q48">
         <v>1.21</v>
       </c>
       <c r="R48">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="S48">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T48">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="U48">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V48">
         <v>1.01</v>
@@ -12600,10 +12600,10 @@
         <v>1000</v>
       </c>
       <c r="AF48">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG48">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH48">
         <v>1000</v>
@@ -12612,19 +12612,19 @@
         <v>1000</v>
       </c>
       <c r="AJ48">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AK48">
         <v>19</v>
       </c>
       <c r="AL48">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM48">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="AN48">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AO48">
         <v>1000</v>
@@ -12636,10 +12636,10 @@
         <v>46</v>
       </c>
       <c r="AR48">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS48">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT48">
         <v>17.5</v>
@@ -12648,10 +12648,10 @@
         <v>29</v>
       </c>
       <c r="AV48">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AW48">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX48">
         <v>10</v>
@@ -12663,13 +12663,13 @@
         <v>48</v>
       </c>
       <c r="BA48">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB48">
         <v>7.2</v>
       </c>
       <c r="BC48">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD48">
         <v>34</v>
@@ -12678,7 +12678,7 @@
         <v>55</v>
       </c>
       <c r="BF48">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BG48">
         <v>60</v>
@@ -12693,13 +12693,13 @@
         <v>20</v>
       </c>
       <c r="BK48">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN48">
         <v>4.3</v>
@@ -12717,19 +12717,19 @@
         <v>23</v>
       </c>
       <c r="BS48">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT48">
         <v>36</v>
       </c>
       <c r="BU48">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BV48">
         <v>1000</v>
       </c>
       <c r="BW48">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BX48">
         <v>190</v>
@@ -12738,7 +12738,7 @@
         <v>36</v>
       </c>
       <c r="BZ48">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CA48">
         <v>3.65</v>
@@ -12797,7 +12797,7 @@
         <v>3.55</v>
       </c>
       <c r="Q49">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="R49">
         <v>1.86</v>
@@ -12872,58 +12872,58 @@
         <v>8</v>
       </c>
       <c r="AP49">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ49">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR49">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS49">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT49">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU49">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV49">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW49">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX49">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY49">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AZ49">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA49">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB49">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC49">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD49">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE49">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF49">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG49">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -13006,22 +13006,22 @@
         <v>244</v>
       </c>
       <c r="F50">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="G50">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H50">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="I50">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="J50">
+        <v>7.8</v>
+      </c>
+      <c r="K50">
         <v>8</v>
-      </c>
-      <c r="K50">
-        <v>8.6</v>
       </c>
       <c r="L50">
         <v>1.26</v>
@@ -13030,70 +13030,70 @@
         <v>1.03</v>
       </c>
       <c r="N50">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O50">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P50">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q50">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="R50">
+        <v>1.74</v>
+      </c>
+      <c r="S50">
+        <v>2.16</v>
+      </c>
+      <c r="T50">
+        <v>2.22</v>
+      </c>
+      <c r="U50">
         <v>1.72</v>
       </c>
-      <c r="S50">
-        <v>2.28</v>
-      </c>
-      <c r="T50">
-        <v>2.32</v>
-      </c>
-      <c r="U50">
-        <v>1.71</v>
-      </c>
       <c r="V50">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
         <v>36</v>
       </c>
       <c r="Y50">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z50">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA50">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AB50">
         <v>60</v>
       </c>
       <c r="AC50">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD50">
         <v>13.5</v>
       </c>
       <c r="AE50">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF50">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AG50">
         <v>70</v>
       </c>
       <c r="AH50">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AI50">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ50">
         <v>1000</v>
@@ -13105,67 +13105,67 @@
         <v>250</v>
       </c>
       <c r="AM50">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AN50">
         <v>1000</v>
       </c>
       <c r="AO50">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AP50">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AQ50">
         <v>9.4</v>
       </c>
       <c r="AR50">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS50">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT50">
+        <v>8.4</v>
+      </c>
+      <c r="AU50">
+        <v>14.5</v>
+      </c>
+      <c r="AV50">
+        <v>10.5</v>
+      </c>
+      <c r="AW50">
+        <v>11.5</v>
+      </c>
+      <c r="AX50">
+        <v>9.4</v>
+      </c>
+      <c r="AY50">
+        <v>8.6</v>
+      </c>
+      <c r="AZ50">
+        <v>25</v>
+      </c>
+      <c r="BA50">
+        <v>34</v>
+      </c>
+      <c r="BB50">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU50">
-        <v>16</v>
-      </c>
-      <c r="AV50">
-        <v>11.5</v>
-      </c>
-      <c r="AW50">
-        <v>13</v>
-      </c>
-      <c r="AX50">
-        <v>11</v>
-      </c>
-      <c r="AY50">
-        <v>10</v>
-      </c>
-      <c r="AZ50">
+      <c r="BC50">
+        <v>9.6</v>
+      </c>
+      <c r="BD50">
         <v>9.4</v>
       </c>
-      <c r="BA50">
-        <v>9.6</v>
-      </c>
-      <c r="BB50">
-        <v>11.5</v>
-      </c>
-      <c r="BC50">
-        <v>11</v>
-      </c>
-      <c r="BD50">
-        <v>11</v>
-      </c>
       <c r="BE50">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF50">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG50">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BH50">
         <v>5.7</v>
@@ -13248,46 +13248,46 @@
         <v>245</v>
       </c>
       <c r="F51">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G51">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="I51">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J51">
         <v>2.92</v>
       </c>
       <c r="K51">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L51">
         <v>1.01</v>
       </c>
       <c r="M51">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N51">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="O51">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P51">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Q51">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="R51">
         <v>1.13</v>
       </c>
       <c r="S51">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -13296,10 +13296,10 @@
         <v>1.01</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13356,52 +13356,52 @@
         <v>1000</v>
       </c>
       <c r="AP51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF51">
         <v>1.01</v>
@@ -13505,7 +13505,7 @@
         <v>3</v>
       </c>
       <c r="K52">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13601,10 +13601,10 @@
         <v>9</v>
       </c>
       <c r="AQ52">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR52">
-        <v>5.1</v>
+        <v>17</v>
       </c>
       <c r="AS52">
         <v>6</v>
@@ -13616,19 +13616,19 @@
         <v>3.6</v>
       </c>
       <c r="AV52">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AW52">
         <v>5.9</v>
       </c>
       <c r="AX52">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="AY52">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ52">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BA52">
         <v>6</v>
@@ -13735,13 +13735,13 @@
         <v>1.27</v>
       </c>
       <c r="G53">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H53">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I53">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J53">
         <v>6</v>
@@ -13756,28 +13756,28 @@
         <v>1.06</v>
       </c>
       <c r="N53">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O53">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P53">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q53">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="R53">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S53">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="T53">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="U53">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="V53">
         <v>1.05</v>
@@ -13786,7 +13786,7 @@
         <v>4.3</v>
       </c>
       <c r="X53">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y53">
         <v>40</v>
@@ -13798,100 +13798,100 @@
         <v>1000</v>
       </c>
       <c r="AB53">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AC53">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AD53">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AE53">
         <v>1000</v>
       </c>
       <c r="AF53">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AG53">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH53">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AI53">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="AJ53">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK53">
         <v>22</v>
       </c>
       <c r="AL53">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM53">
-        <v>530</v>
+        <v>460</v>
       </c>
       <c r="AN53">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO53">
         <v>1000</v>
       </c>
       <c r="AP53">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ53">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR53">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS53">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT53">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU53">
         <v>13</v>
       </c>
       <c r="AV53">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW53">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX53">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ53">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BA53">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB53">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC53">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD53">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE53">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF53">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG53">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH53">
         <v>3.55</v>
@@ -13900,7 +13900,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ53">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BK53">
         <v>12</v>
@@ -13918,19 +13918,19 @@
         <v>3</v>
       </c>
       <c r="BP53">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ53">
         <v>6.4</v>
       </c>
       <c r="BR53">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BS53">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BT53">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BU53">
         <v>14</v>
@@ -13948,7 +13948,7 @@
         <v>21</v>
       </c>
       <c r="BZ53">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA53">
         <v>10.5</v>
@@ -13977,7 +13977,7 @@
         <v>3.05</v>
       </c>
       <c r="G54">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H54">
         <v>2.62</v>
@@ -14091,7 +14091,7 @@
         <v>14</v>
       </c>
       <c r="AS54">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT54">
         <v>8.4</v>
@@ -14103,7 +14103,7 @@
         <v>11</v>
       </c>
       <c r="AW54">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX54">
         <v>17.5</v>
@@ -14112,28 +14112,28 @@
         <v>12.5</v>
       </c>
       <c r="AZ54">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA54">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB54">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC54">
+        <v>7.8</v>
+      </c>
+      <c r="BD54">
+        <v>8</v>
+      </c>
+      <c r="BE54">
+        <v>8.6</v>
+      </c>
+      <c r="BF54">
+        <v>8</v>
+      </c>
+      <c r="BG54">
         <v>7.4</v>
-      </c>
-      <c r="BD54">
-        <v>7.6</v>
-      </c>
-      <c r="BE54">
-        <v>8</v>
-      </c>
-      <c r="BF54">
-        <v>7.4</v>
-      </c>
-      <c r="BG54">
-        <v>7</v>
       </c>
       <c r="BH54">
         <v>2.82</v>
@@ -14145,7 +14145,7 @@
         <v>11</v>
       </c>
       <c r="BK54">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL54">
         <v>1000</v>
@@ -14219,7 +14219,7 @@
         <v>1.59</v>
       </c>
       <c r="G55">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H55">
         <v>6.8</v>
@@ -14467,7 +14467,7 @@
         <v>2.62</v>
       </c>
       <c r="I56">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J56">
         <v>3.65</v>
@@ -14485,19 +14485,19 @@
         <v>4.7</v>
       </c>
       <c r="O56">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P56">
         <v>2.24</v>
       </c>
       <c r="Q56">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R56">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S56">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T56">
         <v>1.64</v>
@@ -14548,7 +14548,7 @@
         <v>40</v>
       </c>
       <c r="AJ56">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AK56">
         <v>29</v>
@@ -14700,7 +14700,7 @@
         <v>251</v>
       </c>
       <c r="F57">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G57">
         <v>2.5</v>
@@ -14844,7 +14844,7 @@
         <v>6.2</v>
       </c>
       <c r="BB57">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="BC57">
         <v>20</v>
@@ -14942,7 +14942,7 @@
         <v>252</v>
       </c>
       <c r="F58">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G58">
         <v>2.7</v>
@@ -14954,7 +14954,7 @@
         <v>3.1</v>
       </c>
       <c r="J58">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K58">
         <v>3.45</v>
@@ -14966,7 +14966,7 @@
         <v>1.08</v>
       </c>
       <c r="N58">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O58">
         <v>1.34</v>
@@ -14984,7 +14984,7 @@
         <v>3.6</v>
       </c>
       <c r="T58">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U58">
         <v>2.2</v>
@@ -14996,7 +14996,7 @@
         <v>1.58</v>
       </c>
       <c r="X58">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y58">
         <v>13.5</v>
@@ -15023,7 +15023,7 @@
         <v>21</v>
       </c>
       <c r="AG58">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH58">
         <v>16.5</v>
@@ -15056,7 +15056,7 @@
         <v>11</v>
       </c>
       <c r="AR58">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS58">
         <v>7</v>
@@ -15071,7 +15071,7 @@
         <v>12.5</v>
       </c>
       <c r="AW58">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX58">
         <v>15.5</v>
@@ -15080,13 +15080,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ58">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA58">
+        <v>7</v>
+      </c>
+      <c r="BB58">
         <v>6.8</v>
-      </c>
-      <c r="BB58">
-        <v>6.6</v>
       </c>
       <c r="BC58">
         <v>6.4</v>
@@ -15101,7 +15101,7 @@
         <v>18</v>
       </c>
       <c r="BG58">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH58">
         <v>1000</v>
@@ -15208,7 +15208,7 @@
         <v>1.01</v>
       </c>
       <c r="N59">
-        <v>4.7</v>
+        <v>2.68</v>
       </c>
       <c r="O59">
         <v>1.15</v>
@@ -15232,7 +15232,7 @@
         <v>2.56</v>
       </c>
       <c r="V59">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W59">
         <v>1.62</v>
@@ -15426,22 +15426,22 @@
         <v>254</v>
       </c>
       <c r="F60">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G60">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="H60">
         <v>5.9</v>
       </c>
       <c r="I60">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J60">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K60">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -15450,22 +15450,22 @@
         <v>1.06</v>
       </c>
       <c r="N60">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O60">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P60">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q60">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R60">
         <v>1.37</v>
       </c>
       <c r="S60">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T60">
         <v>1.84</v>
@@ -15477,10 +15477,10 @@
         <v>1.16</v>
       </c>
       <c r="W60">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="X60">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y60">
         <v>23</v>
@@ -15489,7 +15489,7 @@
         <v>60</v>
       </c>
       <c r="AA60">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB60">
         <v>9.800000000000001</v>
@@ -15537,10 +15537,10 @@
         <v>13</v>
       </c>
       <c r="AQ60">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="AR60">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS60">
         <v>5.6</v>
@@ -15552,10 +15552,10 @@
         <v>7.6</v>
       </c>
       <c r="AV60">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="AW60">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX60">
         <v>7.6</v>
@@ -15564,7 +15564,7 @@
         <v>7.8</v>
       </c>
       <c r="AZ60">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA60">
         <v>5.4</v>
@@ -15576,7 +15576,7 @@
         <v>13</v>
       </c>
       <c r="BD60">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE60">
         <v>5.5</v>
@@ -15698,10 +15698,10 @@
         <v>1.26</v>
       </c>
       <c r="P61">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q61">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="R61">
         <v>1.41</v>
@@ -15922,7 +15922,7 @@
         <v>2.44</v>
       </c>
       <c r="J62">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K62">
         <v>3.95</v>
@@ -15967,7 +15967,7 @@
         <v>20</v>
       </c>
       <c r="Y62">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z62">
         <v>17</v>
@@ -16027,10 +16027,10 @@
         <v>14.5</v>
       </c>
       <c r="AS62">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT62">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU62">
         <v>8</v>
@@ -16051,16 +16051,16 @@
         <v>14</v>
       </c>
       <c r="BA62">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BB62">
         <v>32</v>
       </c>
       <c r="BC62">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD62">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE62">
         <v>44</v>
@@ -16188,7 +16188,7 @@
         <v>1.61</v>
       </c>
       <c r="R63">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S63">
         <v>2.54</v>
@@ -16215,7 +16215,7 @@
         <v>25</v>
       </c>
       <c r="AA63">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AB63">
         <v>15</v>
@@ -16248,7 +16248,7 @@
         <v>23</v>
       </c>
       <c r="AL63">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM63">
         <v>370</v>
@@ -16266,10 +16266,10 @@
         <v>15</v>
       </c>
       <c r="AR63">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS63">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT63">
         <v>13</v>
@@ -16281,7 +16281,7 @@
         <v>12</v>
       </c>
       <c r="AW63">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX63">
         <v>16</v>
@@ -16302,10 +16302,10 @@
         <v>15.5</v>
       </c>
       <c r="BD63">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BE63">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BF63">
         <v>11</v>
@@ -16439,7 +16439,7 @@
         <v>1.48</v>
       </c>
       <c r="U64">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V64">
         <v>1.44</v>
@@ -16511,7 +16511,7 @@
         <v>21</v>
       </c>
       <c r="AS64">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AT64">
         <v>15</v>
@@ -16535,7 +16535,7 @@
         <v>12.5</v>
       </c>
       <c r="BA64">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB64">
         <v>23</v>
@@ -16544,10 +16544,10 @@
         <v>17</v>
       </c>
       <c r="BD64">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BE64">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BF64">
         <v>8.6</v>
@@ -16565,7 +16565,7 @@
         <v>8.4</v>
       </c>
       <c r="BK64">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL64">
         <v>65</v>
@@ -16669,7 +16669,7 @@
         <v>3.35</v>
       </c>
       <c r="Q65">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R65">
         <v>1.96</v>
@@ -16723,7 +16723,7 @@
         <v>15.5</v>
       </c>
       <c r="AI65">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AJ65">
         <v>22</v>
@@ -16735,7 +16735,7 @@
         <v>23</v>
       </c>
       <c r="AM65">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AN65">
         <v>5.6</v>
@@ -16747,10 +16747,10 @@
         <v>24</v>
       </c>
       <c r="AQ65">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR65">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS65">
         <v>55</v>
@@ -16777,7 +16777,7 @@
         <v>13.5</v>
       </c>
       <c r="BA65">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BB65">
         <v>18</v>
@@ -16798,64 +16798,64 @@
         <v>17</v>
       </c>
       <c r="BH65">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI65">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ65">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK65">
-        <v>1.81</v>
+        <v>7.6</v>
       </c>
       <c r="BL65">
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>2.12</v>
+        <v>12.5</v>
       </c>
       <c r="BN65">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BO65">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP65">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ65">
         <v>7.4</v>
       </c>
       <c r="BR65">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS65">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT65">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU65">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV65">
         <v>1000</v>
       </c>
       <c r="BW65">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="BX65">
         <v>1000</v>
       </c>
       <c r="BY65">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="BZ65">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA65">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="CB65" t="s">
         <v>260</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-09.xlsx
@@ -808,7 +808,7 @@
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>2026-09-08 19:36:57</t>
+    <t>2026-09-08 21:50:44</t>
   </si>
 </sst>
 </file>
@@ -1402,226 +1402,226 @@
         <v>199</v>
       </c>
       <c r="F2">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="K2">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="L2">
-        <v>1.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>1.49</v>
       </c>
       <c r="O2">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="R2">
+        <v>1.02</v>
+      </c>
+      <c r="S2">
+        <v>30</v>
+      </c>
+      <c r="T2">
+        <v>4.6</v>
+      </c>
+      <c r="U2">
+        <v>1.25</v>
+      </c>
+      <c r="V2">
+        <v>1.2</v>
+      </c>
+      <c r="W2">
+        <v>1.66</v>
+      </c>
+      <c r="X2">
+        <v>3.35</v>
+      </c>
+      <c r="Y2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z2">
+        <v>55</v>
+      </c>
+      <c r="AA2">
+        <v>490</v>
+      </c>
+      <c r="AB2">
+        <v>4.5</v>
+      </c>
+      <c r="AC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>65</v>
+      </c>
+      <c r="AE2">
+        <v>530</v>
+      </c>
+      <c r="AF2">
+        <v>12.5</v>
+      </c>
+      <c r="AG2">
+        <v>27</v>
+      </c>
+      <c r="AH2">
+        <v>150</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>55</v>
+      </c>
+      <c r="AK2">
+        <v>140</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>200</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>3.2</v>
+      </c>
+      <c r="AQ2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>42</v>
+      </c>
+      <c r="AS2">
+        <v>130</v>
+      </c>
+      <c r="AT2">
+        <v>4</v>
+      </c>
+      <c r="AU2">
+        <v>8.4</v>
+      </c>
+      <c r="AV2">
+        <v>44</v>
+      </c>
+      <c r="AW2">
+        <v>240</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>23</v>
+      </c>
+      <c r="AZ2">
+        <v>95</v>
+      </c>
+      <c r="BA2">
+        <v>420</v>
+      </c>
+      <c r="BB2">
+        <v>44</v>
+      </c>
+      <c r="BC2">
+        <v>90</v>
+      </c>
+      <c r="BD2">
+        <v>260</v>
+      </c>
+      <c r="BE2">
+        <v>19</v>
+      </c>
+      <c r="BF2">
+        <v>100</v>
+      </c>
+      <c r="BG2">
+        <v>400</v>
+      </c>
+      <c r="BH2">
         <v>1.17</v>
       </c>
-      <c r="S2">
-        <v>6.6</v>
-      </c>
-      <c r="T2">
-        <v>2.26</v>
-      </c>
-      <c r="U2">
-        <v>1.76</v>
-      </c>
-      <c r="V2">
-        <v>1.35</v>
-      </c>
-      <c r="W2">
-        <v>1.61</v>
-      </c>
-      <c r="X2">
-        <v>7.2</v>
-      </c>
-      <c r="Y2">
-        <v>9.6</v>
-      </c>
-      <c r="Z2">
-        <v>24</v>
-      </c>
-      <c r="AA2">
-        <v>85</v>
-      </c>
-      <c r="AB2">
-        <v>7.2</v>
-      </c>
-      <c r="AC2">
-        <v>6.8</v>
-      </c>
-      <c r="AD2">
-        <v>17</v>
-      </c>
-      <c r="AE2">
-        <v>65</v>
-      </c>
-      <c r="AF2">
-        <v>15</v>
-      </c>
-      <c r="AG2">
-        <v>13</v>
-      </c>
-      <c r="AH2">
-        <v>26</v>
-      </c>
-      <c r="AI2">
-        <v>100</v>
-      </c>
-      <c r="AJ2">
-        <v>44</v>
-      </c>
-      <c r="AK2">
-        <v>42</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>230</v>
-      </c>
-      <c r="AN2">
-        <v>50</v>
-      </c>
-      <c r="AO2">
-        <v>95</v>
-      </c>
-      <c r="AP2">
-        <v>6.6</v>
-      </c>
-      <c r="AQ2">
-        <v>8.6</v>
-      </c>
-      <c r="AR2">
-        <v>20</v>
-      </c>
-      <c r="AS2">
-        <v>70</v>
-      </c>
-      <c r="AT2">
-        <v>6.6</v>
-      </c>
-      <c r="AU2">
-        <v>6.2</v>
-      </c>
-      <c r="AV2">
+      <c r="BI2">
+        <v>1.14</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
         <v>15.5</v>
       </c>
-      <c r="AW2">
-        <v>55</v>
-      </c>
-      <c r="AX2">
-        <v>13</v>
-      </c>
-      <c r="AY2">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2">
-        <v>22</v>
-      </c>
-      <c r="BA2">
-        <v>85</v>
-      </c>
-      <c r="BB2">
-        <v>36</v>
-      </c>
-      <c r="BC2">
-        <v>34</v>
-      </c>
-      <c r="BD2">
-        <v>60</v>
-      </c>
-      <c r="BE2">
-        <v>18.5</v>
-      </c>
-      <c r="BF2">
-        <v>42</v>
-      </c>
-      <c r="BG2">
-        <v>75</v>
-      </c>
-      <c r="BH2">
-        <v>2.54</v>
-      </c>
-      <c r="BI2">
-        <v>2.36</v>
-      </c>
-      <c r="BJ2">
-        <v>12.5</v>
-      </c>
-      <c r="BK2">
-        <v>10.5</v>
-      </c>
       <c r="BL2">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
         <v>14</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BR2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>85</v>
       </c>
       <c r="BU2">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="s">
         <v>264</v>
@@ -1644,226 +1644,226 @@
         <v>200</v>
       </c>
       <c r="F3">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="G3">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="H3">
+        <v>9.4</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
-      <c r="I3">
+      <c r="J3">
+        <v>4.6</v>
+      </c>
+      <c r="K3">
+        <v>5.1</v>
+      </c>
+      <c r="L3">
+        <v>1.63</v>
+      </c>
+      <c r="M3">
+        <v>1.07</v>
+      </c>
+      <c r="N3">
+        <v>3.6</v>
+      </c>
+      <c r="O3">
+        <v>1.37</v>
+      </c>
+      <c r="P3">
+        <v>1.85</v>
+      </c>
+      <c r="Q3">
+        <v>2.1</v>
+      </c>
+      <c r="R3">
+        <v>1.32</v>
+      </c>
+      <c r="S3">
+        <v>3.85</v>
+      </c>
+      <c r="T3">
+        <v>2.3</v>
+      </c>
+      <c r="U3">
+        <v>1.66</v>
+      </c>
+      <c r="V3">
+        <v>1.11</v>
+      </c>
+      <c r="W3">
+        <v>3.05</v>
+      </c>
+      <c r="X3">
+        <v>15.5</v>
+      </c>
+      <c r="Y3">
+        <v>27</v>
+      </c>
+      <c r="Z3">
+        <v>100</v>
+      </c>
+      <c r="AA3">
+        <v>430</v>
+      </c>
+      <c r="AB3">
+        <v>7.2</v>
+      </c>
+      <c r="AC3">
         <v>11.5</v>
       </c>
-      <c r="J3">
-        <v>5.2</v>
-      </c>
-      <c r="K3">
-        <v>5.6</v>
-      </c>
-      <c r="L3">
-        <v>1.36</v>
-      </c>
-      <c r="M3">
-        <v>1.05</v>
-      </c>
-      <c r="N3">
-        <v>4.4</v>
-      </c>
-      <c r="O3">
-        <v>1.27</v>
-      </c>
-      <c r="P3">
-        <v>2.14</v>
-      </c>
-      <c r="Q3">
-        <v>1.81</v>
-      </c>
-      <c r="R3">
-        <v>1.45</v>
-      </c>
-      <c r="S3">
-        <v>3.05</v>
-      </c>
-      <c r="T3">
-        <v>2.08</v>
-      </c>
-      <c r="U3">
-        <v>1.76</v>
-      </c>
-      <c r="V3">
-        <v>1.09</v>
-      </c>
-      <c r="W3">
-        <v>3.5</v>
-      </c>
-      <c r="X3">
-        <v>20</v>
-      </c>
-      <c r="Y3">
-        <v>36</v>
-      </c>
-      <c r="Z3">
-        <v>150</v>
-      </c>
-      <c r="AA3">
-        <v>490</v>
-      </c>
-      <c r="AB3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC3">
-        <v>12.5</v>
-      </c>
       <c r="AD3">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AE3">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AF3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI3">
-        <v>620</v>
+        <v>180</v>
       </c>
       <c r="AJ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AN3">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AO3">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="AP3">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3">
         <v>25</v>
       </c>
       <c r="AR3">
+        <v>65</v>
+      </c>
+      <c r="AS3">
+        <v>310</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV3">
+        <v>30</v>
+      </c>
+      <c r="AW3">
+        <v>140</v>
+      </c>
+      <c r="AX3">
+        <v>7</v>
+      </c>
+      <c r="AY3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ3">
+        <v>29</v>
+      </c>
+      <c r="BA3">
+        <v>140</v>
+      </c>
+      <c r="BB3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC3">
+        <v>15.5</v>
+      </c>
+      <c r="BD3">
+        <v>46</v>
+      </c>
+      <c r="BE3">
+        <v>200</v>
+      </c>
+      <c r="BF3">
+        <v>7</v>
+      </c>
+      <c r="BG3">
+        <v>240</v>
+      </c>
+      <c r="BH3">
+        <v>2.62</v>
+      </c>
+      <c r="BI3">
+        <v>2.46</v>
+      </c>
+      <c r="BJ3">
+        <v>16.5</v>
+      </c>
+      <c r="BK3">
+        <v>15</v>
+      </c>
+      <c r="BL3">
+        <v>960</v>
+      </c>
+      <c r="BM3">
+        <v>16</v>
+      </c>
+      <c r="BN3">
+        <v>3.65</v>
+      </c>
+      <c r="BO3">
+        <v>3.25</v>
+      </c>
+      <c r="BP3">
+        <v>11.5</v>
+      </c>
+      <c r="BQ3">
+        <v>10.5</v>
+      </c>
+      <c r="BR3">
+        <v>55</v>
+      </c>
+      <c r="BS3">
+        <v>42</v>
+      </c>
+      <c r="BT3">
+        <v>12</v>
+      </c>
+      <c r="BU3">
         <v>10</v>
       </c>
-      <c r="AS3">
-        <v>10.5</v>
-      </c>
-      <c r="AT3">
-        <v>7</v>
-      </c>
-      <c r="AU3">
-        <v>10.5</v>
-      </c>
-      <c r="AV3">
-        <v>29</v>
-      </c>
-      <c r="AW3">
-        <v>10.5</v>
-      </c>
-      <c r="AX3">
-        <v>7.2</v>
-      </c>
-      <c r="AY3">
-        <v>9</v>
-      </c>
-      <c r="AZ3">
-        <v>22</v>
-      </c>
-      <c r="BA3">
-        <v>10.5</v>
-      </c>
-      <c r="BB3">
-        <v>9.6</v>
-      </c>
-      <c r="BC3">
-        <v>13</v>
-      </c>
-      <c r="BD3">
-        <v>29</v>
-      </c>
-      <c r="BE3">
-        <v>10.5</v>
-      </c>
-      <c r="BF3">
-        <v>5.6</v>
-      </c>
-      <c r="BG3">
-        <v>11</v>
-      </c>
-      <c r="BH3">
-        <v>3.95</v>
-      </c>
-      <c r="BI3">
-        <v>3.05</v>
-      </c>
-      <c r="BJ3">
-        <v>12.5</v>
-      </c>
-      <c r="BK3">
-        <v>7.8</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>11</v>
-      </c>
-      <c r="BN3">
-        <v>3.85</v>
-      </c>
-      <c r="BO3">
-        <v>3.3</v>
-      </c>
-      <c r="BP3">
-        <v>8.4</v>
-      </c>
-      <c r="BQ3">
-        <v>6</v>
-      </c>
-      <c r="BR3">
-        <v>29</v>
-      </c>
-      <c r="BS3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT3">
-        <v>13.5</v>
-      </c>
-      <c r="BU3">
-        <v>6.4</v>
-      </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>75</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>110</v>
       </c>
       <c r="BZ3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="CA3">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="CB3" t="s">
         <v>264</v>
@@ -1889,19 +1889,19 @@
         <v>2.2</v>
       </c>
       <c r="G4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J4">
         <v>3.45</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.37</v>
@@ -1916,16 +1916,16 @@
         <v>1.29</v>
       </c>
       <c r="P4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q4">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R4">
         <v>1.35</v>
       </c>
       <c r="S4">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T4">
         <v>1.64</v>
@@ -1934,13 +1934,13 @@
         <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X4">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y4">
         <v>15.5</v>
@@ -2003,7 +2003,7 @@
         <v>18.5</v>
       </c>
       <c r="AS4">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
@@ -2015,7 +2015,7 @@
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AX4">
         <v>12</v>
@@ -2024,10 +2024,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BB4">
         <v>20</v>
@@ -2036,16 +2036,16 @@
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>60</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
@@ -2078,13 +2078,13 @@
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BU4">
         <v>5.1</v>
@@ -2102,7 +2102,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -2149,7 +2149,7 @@
         <v>1.37</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
         <v>4.3</v>
@@ -2173,7 +2173,7 @@
         <v>1.9</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
         <v>1.18</v>
@@ -2191,7 +2191,7 @@
         <v>55</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB5">
         <v>9.199999999999999</v>
@@ -2203,7 +2203,7 @@
         <v>24</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF5">
         <v>9.800000000000001</v>
@@ -2215,7 +2215,7 @@
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ5">
         <v>15.5</v>
@@ -2227,13 +2227,13 @@
         <v>36</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN5">
         <v>8.4</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP5">
         <v>16</v>
@@ -2242,7 +2242,7 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS5">
         <v>44</v>
@@ -2281,7 +2281,7 @@
         <v>24</v>
       </c>
       <c r="BE5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BF5">
         <v>7.6</v>
@@ -2305,7 +2305,7 @@
         <v>160</v>
       </c>
       <c r="BM5">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.2</v>
@@ -2314,40 +2314,40 @@
         <v>3.85</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
         <v>9</v>
       </c>
       <c r="BR5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BS5">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BT5">
         <v>10.5</v>
       </c>
       <c r="BU5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
         <v>18.5</v>
       </c>
       <c r="CA5">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="s">
         <v>264</v>
@@ -2376,7 +2376,7 @@
         <v>2.88</v>
       </c>
       <c r="H6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I6">
         <v>2.98</v>
@@ -2385,7 +2385,7 @@
         <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6">
         <v>1.5</v>
@@ -2400,10 +2400,10 @@
         <v>1.42</v>
       </c>
       <c r="P6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q6">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R6">
         <v>1.28</v>
@@ -2412,7 +2412,7 @@
         <v>4.3</v>
       </c>
       <c r="T6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U6">
         <v>2.02</v>
@@ -2424,7 +2424,7 @@
         <v>1.53</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>10.5</v>
@@ -2466,10 +2466,10 @@
         <v>36</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN6">
         <v>36</v>
@@ -2487,10 +2487,10 @@
         <v>16.5</v>
       </c>
       <c r="AS6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
@@ -2508,16 +2508,16 @@
         <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB6">
         <v>32</v>
       </c>
       <c r="BC6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD6">
         <v>40</v>
@@ -2532,22 +2532,22 @@
         <v>26</v>
       </c>
       <c r="BH6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI6">
         <v>2.84</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>180</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BN6">
         <v>5.7</v>
@@ -2556,40 +2556,40 @@
         <v>5.2</v>
       </c>
       <c r="BP6">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BQ6">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR6">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BS6">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BT6">
         <v>5.8</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY6">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="CA6">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="s">
         <v>264</v>
@@ -2612,16 +2612,16 @@
         <v>204</v>
       </c>
       <c r="F7">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G7">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H7">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I7">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J7">
         <v>3.2</v>
@@ -2630,55 +2630,55 @@
         <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
         <v>2.96</v>
       </c>
       <c r="O7">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P7">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R7">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="X7">
         <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>7.4</v>
@@ -2693,46 +2693,46 @@
         <v>17</v>
       </c>
       <c r="AG7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL7">
         <v>55</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO7">
         <v>50</v>
       </c>
       <c r="AP7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7">
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU7">
         <v>6.6</v>
@@ -2762,7 +2762,7 @@
         <v>27</v>
       </c>
       <c r="BD7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE7">
         <v>34</v>
@@ -2774,43 +2774,43 @@
         <v>34</v>
       </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN7">
         <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP7">
         <v>22</v>
       </c>
       <c r="BQ7">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7">
         <v>40</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
         <v>5.6</v>
@@ -2819,19 +2819,19 @@
         <v>29</v>
       </c>
       <c r="BW7">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX7">
         <v>46</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="s">
         <v>264</v>
@@ -2854,13 +2854,13 @@
         <v>205</v>
       </c>
       <c r="F8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G8">
         <v>4.5</v>
       </c>
       <c r="H8">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I8">
         <v>2.06</v>
@@ -2869,10 +2869,10 @@
         <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
         <v>1.08</v>
@@ -2881,28 +2881,28 @@
         <v>3.5</v>
       </c>
       <c r="O8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T8">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W8">
         <v>1.28</v>
@@ -2926,7 +2926,7 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE8">
         <v>23</v>
@@ -2938,7 +2938,7 @@
         <v>18</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8">
         <v>42</v>
@@ -2953,19 +2953,19 @@
         <v>80</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN8">
         <v>75</v>
       </c>
       <c r="AO8">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP8">
         <v>11.5</v>
       </c>
       <c r="AQ8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR8">
         <v>10.5</v>
@@ -2980,13 +2980,13 @@
         <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW8">
         <v>19</v>
       </c>
       <c r="AX8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AY8">
         <v>15.5</v>
@@ -2995,13 +2995,13 @@
         <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BB8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BD8">
         <v>48</v>
@@ -3010,7 +3010,7 @@
         <v>70</v>
       </c>
       <c r="BF8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BG8">
         <v>14</v>
@@ -3022,16 +3022,16 @@
         <v>2.96</v>
       </c>
       <c r="BJ8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
@@ -3043,37 +3043,37 @@
         <v>40</v>
       </c>
       <c r="BQ8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR8">
         <v>55</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT8">
         <v>4.6</v>
       </c>
       <c r="BU8">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV8">
         <v>14.5</v>
       </c>
       <c r="BW8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX8">
         <v>32</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
         <v>264</v>
@@ -3096,31 +3096,31 @@
         <v>206</v>
       </c>
       <c r="F9">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="G9">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H9">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="I9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
         <v>1.28</v>
@@ -3132,190 +3132,190 @@
         <v>1.78</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="T9">
-        <v>1.05</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="V9">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AO9">
-        <v>340</v>
+        <v>8.4</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF9">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BG9">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB9" t="s">
         <v>264</v>
@@ -3347,7 +3347,7 @@
         <v>11</v>
       </c>
       <c r="I10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J10">
         <v>4.1</v>
@@ -3362,10 +3362,10 @@
         <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O10">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P10">
         <v>1.6</v>
@@ -3377,22 +3377,22 @@
         <v>1.2</v>
       </c>
       <c r="S10">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="T10">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="U10">
         <v>1.51</v>
       </c>
       <c r="V10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y10">
         <v>29</v>
@@ -3410,7 +3410,7 @@
         <v>11.5</v>
       </c>
       <c r="AD10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AE10">
         <v>410</v>
@@ -3464,10 +3464,10 @@
         <v>9.4</v>
       </c>
       <c r="AV10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX10">
         <v>5.9</v>
@@ -3476,10 +3476,10 @@
         <v>10</v>
       </c>
       <c r="AZ10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB10">
         <v>10.5</v>
@@ -3491,10 +3491,10 @@
         <v>6.6</v>
       </c>
       <c r="BE10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG10">
         <v>7.2</v>
@@ -3539,7 +3539,7 @@
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3595,7 +3595,7 @@
         <v>2.8</v>
       </c>
       <c r="K11">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="L11">
         <v>1.64</v>
@@ -3610,7 +3610,7 @@
         <v>1.67</v>
       </c>
       <c r="P11">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3670,16 +3670,16 @@
         <v>230</v>
       </c>
       <c r="AJ11">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK11">
         <v>65</v>
       </c>
       <c r="AL11">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AM11">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AN11">
         <v>110</v>
@@ -3688,7 +3688,7 @@
         <v>75</v>
       </c>
       <c r="AP11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11">
         <v>6.6</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BN11">
         <v>1000</v>
@@ -3799,7 +3799,7 @@
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="CB11" t="s">
         <v>264</v>
@@ -3825,19 +3825,19 @@
         <v>1.29</v>
       </c>
       <c r="G12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12">
         <v>5.3</v>
       </c>
       <c r="K12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3846,19 +3846,19 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
         <v>1.22</v>
       </c>
       <c r="P12">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q12">
         <v>1.63</v>
       </c>
       <c r="R12">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S12">
         <v>2.62</v>
@@ -3873,7 +3873,7 @@
         <v>1.07</v>
       </c>
       <c r="W12">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X12">
         <v>24</v>
@@ -3885,10 +3885,10 @@
         <v>540</v>
       </c>
       <c r="AA12">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>14</v>
@@ -3912,7 +3912,7 @@
         <v>190</v>
       </c>
       <c r="AJ12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK12">
         <v>16</v>
@@ -3927,31 +3927,31 @@
         <v>5.5</v>
       </c>
       <c r="AO12">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AP12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AR12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
         <v>11</v>
       </c>
       <c r="AV12">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AW12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12">
         <v>6.6</v>
@@ -3960,28 +3960,28 @@
         <v>9</v>
       </c>
       <c r="AZ12">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC12">
         <v>12</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BE12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4076,10 +4076,10 @@
         <v>110</v>
       </c>
       <c r="J13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4091,19 +4091,19 @@
         <v>1.37</v>
       </c>
       <c r="O13">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="P13">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="R13">
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4112,10 +4112,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4172,49 +4172,49 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
         <v>1.01</v>
@@ -4223,7 +4223,7 @@
         <v>1.55</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4312,13 +4312,13 @@
         <v>110</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I14">
         <v>970</v>
       </c>
       <c r="J14">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4354,10 +4354,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4414,49 +4414,49 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
         <v>1.01</v>
@@ -4465,7 +4465,7 @@
         <v>1.55</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4554,10 +4554,10 @@
         <v>2.16</v>
       </c>
       <c r="H15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4581,10 +4581,10 @@
         <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15">
         <v>3.3</v>
@@ -4614,7 +4614,7 @@
         <v>85</v>
       </c>
       <c r="AB15">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC15">
         <v>8.4</v>
@@ -4626,13 +4626,13 @@
         <v>55</v>
       </c>
       <c r="AF15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG15">
         <v>11</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI15">
         <v>60</v>
@@ -4641,7 +4641,7 @@
         <v>32</v>
       </c>
       <c r="AK15">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL15">
         <v>44</v>
@@ -4665,10 +4665,10 @@
         <v>25</v>
       </c>
       <c r="AS15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT15">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15">
         <v>7.4</v>
@@ -4677,7 +4677,7 @@
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX15">
         <v>12</v>
@@ -4689,7 +4689,7 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB15">
         <v>11.5</v>
@@ -4698,7 +4698,7 @@
         <v>19.5</v>
       </c>
       <c r="BD15">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BE15">
         <v>19</v>
@@ -4710,7 +4710,7 @@
         <v>8.6</v>
       </c>
       <c r="BH15">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BI15">
         <v>3.2</v>
@@ -4719,55 +4719,55 @@
         <v>11.5</v>
       </c>
       <c r="BK15">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BL15">
         <v>140</v>
       </c>
       <c r="BM15">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BN15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO15">
         <v>4.4</v>
       </c>
       <c r="BP15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ15">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BR15">
         <v>34</v>
       </c>
       <c r="BS15">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BT15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW15">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BX15">
         <v>50</v>
       </c>
       <c r="BY15">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BZ15">
         <v>29</v>
       </c>
       <c r="CA15">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="CB15" t="s">
         <v>264</v>
@@ -4793,19 +4793,19 @@
         <v>2.76</v>
       </c>
       <c r="G16">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H16">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I16">
         <v>2.8</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L16">
         <v>1.37</v>
@@ -4814,7 +4814,7 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O16">
         <v>1.33</v>
@@ -4823,34 +4823,34 @@
         <v>1.96</v>
       </c>
       <c r="Q16">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R16">
         <v>1.37</v>
       </c>
       <c r="S16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T16">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
         <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y16">
         <v>12</v>
       </c>
       <c r="Z16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA16">
         <v>44</v>
@@ -4859,7 +4859,7 @@
         <v>12</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
         <v>12.5</v>
@@ -4868,19 +4868,19 @@
         <v>32</v>
       </c>
       <c r="AF16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG16">
         <v>13</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI16">
+        <v>42</v>
+      </c>
+      <c r="AJ16">
         <v>44</v>
-      </c>
-      <c r="AJ16">
-        <v>46</v>
       </c>
       <c r="AK16">
         <v>32</v>
@@ -4889,28 +4889,28 @@
         <v>44</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AN16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO16">
         <v>27</v>
       </c>
       <c r="AP16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
         <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AT16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU16">
         <v>7.2</v>
@@ -4919,7 +4919,7 @@
         <v>11</v>
       </c>
       <c r="AW16">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AX16">
         <v>16.5</v>
@@ -4931,25 +4931,25 @@
         <v>15</v>
       </c>
       <c r="BA16">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BB16">
         <v>34</v>
       </c>
       <c r="BC16">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BD16">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BE16">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BF16">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH16">
         <v>3.75</v>
@@ -4997,7 +4997,7 @@
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BX16">
         <v>1000</v>
@@ -5038,10 +5038,10 @@
         <v>2.18</v>
       </c>
       <c r="H17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J17">
         <v>3.4</v>
@@ -5050,13 +5050,13 @@
         <v>3.85</v>
       </c>
       <c r="L17">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M17">
         <v>1.07</v>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
         <v>1.34</v>
@@ -5131,7 +5131,7 @@
         <v>40</v>
       </c>
       <c r="AM17">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN17">
         <v>17.5</v>
@@ -5140,16 +5140,16 @@
         <v>240</v>
       </c>
       <c r="AP17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17">
         <v>10.5</v>
       </c>
       <c r="AR17">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AS17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT17">
         <v>4.7</v>
@@ -5164,34 +5164,34 @@
         <v>8</v>
       </c>
       <c r="AX17">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY17">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BC17">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD17">
         <v>7.6</v>
       </c>
       <c r="BE17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17">
         <v>14</v>
       </c>
       <c r="BG17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17">
         <v>3.4</v>
@@ -5274,13 +5274,13 @@
         <v>215</v>
       </c>
       <c r="F18">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G18">
         <v>1.93</v>
       </c>
       <c r="H18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I18">
         <v>5.8</v>
@@ -5298,7 +5298,7 @@
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O18">
         <v>1.31</v>
@@ -5307,7 +5307,7 @@
         <v>1.96</v>
       </c>
       <c r="Q18">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R18">
         <v>1.31</v>
@@ -5322,7 +5322,7 @@
         <v>1.83</v>
       </c>
       <c r="V18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W18">
         <v>2.08</v>
@@ -5334,7 +5334,7 @@
         <v>1000</v>
       </c>
       <c r="Z18">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
         <v>1000</v>
@@ -5349,7 +5349,7 @@
         <v>1000</v>
       </c>
       <c r="AE18">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
         <v>1000</v>
@@ -5358,10 +5358,10 @@
         <v>1000</v>
       </c>
       <c r="AH18">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
         <v>46</v>
@@ -5373,67 +5373,67 @@
         <v>95</v>
       </c>
       <c r="AM18">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
         <v>1000</v>
       </c>
       <c r="AO18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AQ18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AR18">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AS18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AT18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AU18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AV18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AW18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AX18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AY18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AZ18">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="BA18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BB18">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BE18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BF18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BG18">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5516,19 +5516,19 @@
         <v>216</v>
       </c>
       <c r="F19">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G19">
         <v>3.15</v>
       </c>
       <c r="H19">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I19">
         <v>2.58</v>
       </c>
       <c r="J19">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K19">
         <v>3.9</v>
@@ -5558,16 +5558,16 @@
         <v>2.92</v>
       </c>
       <c r="T19">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U19">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
         <v>1.63</v>
       </c>
       <c r="W19">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X19">
         <v>18.5</v>
@@ -5612,7 +5612,7 @@
         <v>36</v>
       </c>
       <c r="AL19">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AM19">
         <v>320</v>
@@ -5764,13 +5764,13 @@
         <v>1.19</v>
       </c>
       <c r="H20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="K20">
         <v>11</v>
@@ -5782,7 +5782,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O20">
         <v>1.11</v>
@@ -5794,16 +5794,16 @@
         <v>1.33</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S20">
         <v>1.8</v>
       </c>
       <c r="T20">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U20">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V20">
         <v>1.04</v>
@@ -5818,7 +5818,7 @@
         <v>85</v>
       </c>
       <c r="Z20">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AA20">
         <v>1000</v>
@@ -5827,13 +5827,13 @@
         <v>15.5</v>
       </c>
       <c r="AC20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AD20">
         <v>510</v>
       </c>
       <c r="AE20">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AF20">
         <v>10.5</v>
@@ -5842,10 +5842,10 @@
         <v>15</v>
       </c>
       <c r="AH20">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AI20">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AJ20">
         <v>9.6</v>
@@ -5854,40 +5854,40 @@
         <v>15</v>
       </c>
       <c r="AL20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM20">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN20">
         <v>2.76</v>
       </c>
       <c r="AO20">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AP20">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AQ20">
         <v>10</v>
       </c>
       <c r="AR20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT20">
         <v>12</v>
       </c>
       <c r="AU20">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AV20">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX20">
         <v>8.6</v>
@@ -5896,28 +5896,28 @@
         <v>12</v>
       </c>
       <c r="AZ20">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BA20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC20">
         <v>12</v>
       </c>
       <c r="BD20">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BE20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF20">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BG20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH20">
         <v>6.2</v>
@@ -5926,16 +5926,16 @@
         <v>4.7</v>
       </c>
       <c r="BJ20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN20">
         <v>4.2</v>
@@ -5953,25 +5953,25 @@
         <v>21</v>
       </c>
       <c r="BS20">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BU20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ20">
         <v>6.4</v>
@@ -6000,19 +6000,19 @@
         <v>218</v>
       </c>
       <c r="F21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G21">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H21">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="I21">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J21">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
         <v>4.3</v>
@@ -6024,13 +6024,13 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O21">
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q21">
         <v>1.56</v>
@@ -6063,7 +6063,7 @@
         <v>75</v>
       </c>
       <c r="AA21">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB21">
         <v>23</v>
@@ -6123,10 +6123,10 @@
         <v>1.77</v>
       </c>
       <c r="AU21">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AV21">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21">
         <v>17.5</v>
@@ -6135,10 +6135,10 @@
         <v>1.79</v>
       </c>
       <c r="AY21">
-        <v>1.72</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>1.77</v>
+        <v>9.6</v>
       </c>
       <c r="BA21">
         <v>1.91</v>
@@ -6242,58 +6242,58 @@
         <v>219</v>
       </c>
       <c r="F22">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G22">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="I22">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J22">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N22">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P22">
         <v>1.53</v>
       </c>
       <c r="Q22">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R22">
         <v>1.18</v>
       </c>
       <c r="S22">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="T22">
         <v>1.96</v>
       </c>
       <c r="U22">
+        <v>1.74</v>
+      </c>
+      <c r="V22">
         <v>1.69</v>
       </c>
-      <c r="V22">
-        <v>1.71</v>
-      </c>
       <c r="W22">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
         <v>970</v>
@@ -6302,28 +6302,28 @@
         <v>1000</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA22">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD22">
         <v>27</v>
       </c>
       <c r="AE22">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF22">
         <v>1000</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AH22">
         <v>1000</v>
@@ -6332,13 +6332,13 @@
         <v>460</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AM22">
         <v>1000</v>
@@ -6350,61 +6350,61 @@
         <v>75</v>
       </c>
       <c r="AP22">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AR22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AS22">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AT22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AU22">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AV22">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AW22">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AX22">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AY22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AZ22">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BA22">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BB22">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BC22">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BD22">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BE22">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BF22">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="BG22">
         <v>1.55</v>
       </c>
       <c r="BH22">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
         <v>1.01</v>
@@ -6413,55 +6413,55 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>264</v>
@@ -6493,7 +6493,7 @@
         <v>1.45</v>
       </c>
       <c r="I23">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="J23">
         <v>3</v>
@@ -6517,13 +6517,13 @@
         <v>1.32</v>
       </c>
       <c r="Q23">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="R23">
         <v>1.18</v>
       </c>
       <c r="S23">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T23">
         <v>1.04</v>
@@ -6553,7 +6553,7 @@
         <v>1000</v>
       </c>
       <c r="AC23">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD23">
         <v>1000</v>
@@ -6616,7 +6616,7 @@
         <v>12</v>
       </c>
       <c r="AX23">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AY23">
         <v>2.18</v>
@@ -6625,13 +6625,13 @@
         <v>1.02</v>
       </c>
       <c r="BA23">
+        <v>2.04</v>
+      </c>
+      <c r="BB23">
+        <v>2.14</v>
+      </c>
+      <c r="BC23">
         <v>1.02</v>
-      </c>
-      <c r="BB23">
-        <v>1.02</v>
-      </c>
-      <c r="BC23">
-        <v>2.14</v>
       </c>
       <c r="BD23">
         <v>2.04</v>
@@ -6738,7 +6738,7 @@
         <v>3.1</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K24">
         <v>3.4</v>
@@ -6753,7 +6753,7 @@
         <v>3</v>
       </c>
       <c r="O24">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P24">
         <v>1.67</v>
@@ -6825,7 +6825,7 @@
         <v>65</v>
       </c>
       <c r="AM24">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AN24">
         <v>42</v>
@@ -6843,7 +6843,7 @@
         <v>14.5</v>
       </c>
       <c r="AS24">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT24">
         <v>8.199999999999999</v>
@@ -6855,10 +6855,10 @@
         <v>11</v>
       </c>
       <c r="AW24">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AX24">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY24">
         <v>11</v>
@@ -6867,25 +6867,25 @@
         <v>14.5</v>
       </c>
       <c r="BA24">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB24">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC24">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="BD24">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE24">
         <v>5.4</v>
       </c>
       <c r="BF24">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG24">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6974,7 +6974,7 @@
         <v>1.31</v>
       </c>
       <c r="H25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I25">
         <v>12.5</v>
@@ -6992,25 +6992,25 @@
         <v>1.02</v>
       </c>
       <c r="N25">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="O25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P25">
         <v>3.75</v>
       </c>
       <c r="Q25">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R25">
         <v>2.12</v>
       </c>
       <c r="S25">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="T25">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U25">
         <v>2.36</v>
@@ -7043,7 +7043,7 @@
         <v>42</v>
       </c>
       <c r="AE25">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF25">
         <v>12.5</v>
@@ -7067,7 +7067,7 @@
         <v>26</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AN25">
         <v>3.2</v>
@@ -7076,7 +7076,7 @@
         <v>90</v>
       </c>
       <c r="AP25">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AQ25">
         <v>50</v>
@@ -7085,7 +7085,7 @@
         <v>15.5</v>
       </c>
       <c r="AS25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT25">
         <v>15</v>
@@ -7097,10 +7097,10 @@
         <v>36</v>
       </c>
       <c r="AW25">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AX25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY25">
         <v>10.5</v>
@@ -7118,13 +7118,13 @@
         <v>11.5</v>
       </c>
       <c r="BD25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE25">
         <v>42</v>
       </c>
       <c r="BF25">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BG25">
         <v>15</v>
@@ -7222,10 +7222,10 @@
         <v>34</v>
       </c>
       <c r="J26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="K26">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="L26">
         <v>1.13</v>
@@ -7246,13 +7246,13 @@
         <v>1.18</v>
       </c>
       <c r="R26">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="S26">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T26">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U26">
         <v>2.04</v>
@@ -7270,7 +7270,7 @@
         <v>190</v>
       </c>
       <c r="Z26">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AA26">
         <v>1000</v>
@@ -7288,31 +7288,31 @@
         <v>540</v>
       </c>
       <c r="AF26">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG26">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH26">
         <v>55</v>
       </c>
       <c r="AI26">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AJ26">
         <v>10.5</v>
       </c>
       <c r="AK26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM26">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AN26">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AO26">
         <v>360</v>
@@ -7324,19 +7324,19 @@
         <v>90</v>
       </c>
       <c r="AR26">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS26">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="AT26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU26">
         <v>34</v>
       </c>
       <c r="AV26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AW26">
         <v>100</v>
@@ -7345,16 +7345,16 @@
         <v>12.5</v>
       </c>
       <c r="AY26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ26">
         <v>46</v>
       </c>
       <c r="BA26">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BB26">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC26">
         <v>13.5</v>
@@ -7363,73 +7363,73 @@
         <v>30</v>
       </c>
       <c r="BE26">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF26">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="BG26">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="BH26">
         <v>8.6</v>
       </c>
       <c r="BI26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BJ26">
         <v>14.5</v>
       </c>
       <c r="BK26">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL26">
         <v>120</v>
       </c>
       <c r="BM26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN26">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO26">
         <v>4.3</v>
       </c>
       <c r="BP26">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BQ26">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR26">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BS26">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BU26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BV26">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BW26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX26">
         <v>110</v>
       </c>
       <c r="BY26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ26">
         <v>4.1</v>
       </c>
       <c r="CA26">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CB26" t="s">
         <v>264</v>
@@ -7461,10 +7461,10 @@
         <v>12</v>
       </c>
       <c r="I27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J27">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="K27">
         <v>8</v>
@@ -7491,7 +7491,7 @@
         <v>2.38</v>
       </c>
       <c r="S27">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="T27">
         <v>1.66</v>
@@ -7530,7 +7530,7 @@
         <v>140</v>
       </c>
       <c r="AF27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG27">
         <v>12.5</v>
@@ -7554,7 +7554,7 @@
         <v>80</v>
       </c>
       <c r="AN27">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="AO27">
         <v>90</v>
@@ -7563,7 +7563,7 @@
         <v>50</v>
       </c>
       <c r="AQ27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AR27">
         <v>42</v>
@@ -7575,7 +7575,7 @@
         <v>18.5</v>
       </c>
       <c r="AU27">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AV27">
         <v>40</v>
@@ -7590,7 +7590,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA27">
         <v>55</v>
@@ -7605,13 +7605,13 @@
         <v>22</v>
       </c>
       <c r="BE27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF27">
         <v>2.68</v>
       </c>
       <c r="BG27">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BH27">
         <v>6.8</v>
@@ -7620,16 +7620,16 @@
         <v>6</v>
       </c>
       <c r="BJ27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK27">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL27">
         <v>75</v>
       </c>
       <c r="BM27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN27">
         <v>4.7</v>
@@ -7647,7 +7647,7 @@
         <v>16</v>
       </c>
       <c r="BS27">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BT27">
         <v>15</v>
@@ -7659,19 +7659,19 @@
         <v>65</v>
       </c>
       <c r="BW27">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX27">
         <v>48</v>
       </c>
       <c r="BY27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ27">
         <v>6.2</v>
       </c>
       <c r="CA27">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="CB27" t="s">
         <v>264</v>
@@ -7703,7 +7703,7 @@
         <v>3.85</v>
       </c>
       <c r="I28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J28">
         <v>4</v>
@@ -7736,7 +7736,7 @@
         <v>2.7</v>
       </c>
       <c r="T28">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U28">
         <v>2.48</v>
@@ -7751,13 +7751,13 @@
         <v>22</v>
       </c>
       <c r="Y28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z28">
         <v>44</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB28">
         <v>12.5</v>
@@ -7769,7 +7769,7 @@
         <v>16.5</v>
       </c>
       <c r="AE28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF28">
         <v>14.5</v>
@@ -7781,13 +7781,13 @@
         <v>16.5</v>
       </c>
       <c r="AI28">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AJ28">
         <v>32</v>
       </c>
       <c r="AK28">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL28">
         <v>46</v>
@@ -7796,7 +7796,7 @@
         <v>190</v>
       </c>
       <c r="AN28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO28">
         <v>40</v>
@@ -7832,7 +7832,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA28">
         <v>34</v>
@@ -7850,7 +7850,7 @@
         <v>48</v>
       </c>
       <c r="BF28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG28">
         <v>28</v>
@@ -7936,16 +7936,16 @@
         <v>226</v>
       </c>
       <c r="F29">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="G29">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H29">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J29">
         <v>4.1</v>
@@ -7960,88 +7960,88 @@
         <v>1.04</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O29">
         <v>1.22</v>
       </c>
       <c r="P29">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="Q29">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R29">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S29">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T29">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V29">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W29">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X29">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y29">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z29">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA29">
         <v>900</v>
       </c>
       <c r="AB29">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD29">
+        <v>19</v>
+      </c>
+      <c r="AE29">
+        <v>130</v>
+      </c>
+      <c r="AF29">
+        <v>12.5</v>
+      </c>
+      <c r="AG29">
         <v>10.5</v>
       </c>
-      <c r="AD29">
-        <v>22</v>
-      </c>
-      <c r="AE29">
-        <v>65</v>
-      </c>
-      <c r="AF29">
-        <v>13</v>
-      </c>
-      <c r="AG29">
-        <v>11</v>
-      </c>
       <c r="AH29">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI29">
-        <v>430</v>
+        <v>130</v>
       </c>
       <c r="AJ29">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM29">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN29">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO29">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AP29">
         <v>16.5</v>
@@ -8050,10 +8050,10 @@
         <v>18</v>
       </c>
       <c r="AR29">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="AS29">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="AT29">
         <v>10</v>
@@ -8065,7 +8065,7 @@
         <v>16</v>
       </c>
       <c r="AW29">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AX29">
         <v>11</v>
@@ -8077,25 +8077,25 @@
         <v>15</v>
       </c>
       <c r="BA29">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BB29">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC29">
         <v>14.5</v>
       </c>
       <c r="BD29">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BE29">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BF29">
         <v>7.6</v>
       </c>
       <c r="BG29">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8181,7 +8181,7 @@
         <v>2.3</v>
       </c>
       <c r="G30">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H30">
         <v>3.1</v>
@@ -8190,13 +8190,13 @@
         <v>3.25</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K30">
         <v>3.95</v>
       </c>
       <c r="L30">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M30">
         <v>1.05</v>
@@ -8205,7 +8205,7 @@
         <v>4.5</v>
       </c>
       <c r="O30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P30">
         <v>2.22</v>
@@ -8232,7 +8232,7 @@
         <v>1.72</v>
       </c>
       <c r="X30">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y30">
         <v>15</v>
@@ -8244,7 +8244,7 @@
         <v>55</v>
       </c>
       <c r="AB30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC30">
         <v>9</v>
@@ -8268,7 +8268,7 @@
         <v>38</v>
       </c>
       <c r="AJ30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK30">
         <v>24</v>
@@ -8316,16 +8316,16 @@
         <v>10</v>
       </c>
       <c r="AZ30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA30">
         <v>30</v>
       </c>
       <c r="BB30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD30">
         <v>28</v>
@@ -8334,7 +8334,7 @@
         <v>55</v>
       </c>
       <c r="BF30">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG30">
         <v>21</v>
@@ -8349,22 +8349,22 @@
         <v>9</v>
       </c>
       <c r="BK30">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN30">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO30">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ30">
         <v>8</v>
@@ -8373,19 +8373,19 @@
         <v>28</v>
       </c>
       <c r="BS30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT30">
         <v>6.6</v>
       </c>
       <c r="BU30">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW30">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX30">
         <v>34</v>
@@ -8397,7 +8397,7 @@
         <v>22</v>
       </c>
       <c r="CA30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB30" t="s">
         <v>264</v>
@@ -8525,22 +8525,22 @@
         <v>23</v>
       </c>
       <c r="AO31">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AP31">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ31">
         <v>7.6</v>
       </c>
       <c r="AR31">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS31">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT31">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU31">
         <v>5.1</v>
@@ -8549,10 +8549,10 @@
         <v>6.4</v>
       </c>
       <c r="AW31">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX31">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY31">
         <v>7.6</v>
@@ -8561,22 +8561,22 @@
         <v>8.4</v>
       </c>
       <c r="BA31">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB31">
+        <v>5.2</v>
+      </c>
+      <c r="BC31">
+        <v>5</v>
+      </c>
+      <c r="BD31">
         <v>4.9</v>
       </c>
-      <c r="BC31">
-        <v>4.8</v>
-      </c>
-      <c r="BD31">
+      <c r="BE31">
+        <v>5.2</v>
+      </c>
+      <c r="BF31">
         <v>4.7</v>
-      </c>
-      <c r="BE31">
-        <v>5</v>
-      </c>
-      <c r="BF31">
-        <v>4.5</v>
       </c>
       <c r="BG31">
         <v>3.95</v>
@@ -8662,19 +8662,19 @@
         <v>229</v>
       </c>
       <c r="F32">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G32">
         <v>2.24</v>
       </c>
       <c r="H32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I32">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J32">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K32">
         <v>4</v>
@@ -8689,7 +8689,7 @@
         <v>4.7</v>
       </c>
       <c r="O32">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P32">
         <v>2.26</v>
@@ -8701,19 +8701,19 @@
         <v>1.52</v>
       </c>
       <c r="S32">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="T32">
         <v>1.64</v>
       </c>
       <c r="U32">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X32">
         <v>24</v>
@@ -8725,7 +8725,7 @@
         <v>27</v>
       </c>
       <c r="AA32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB32">
         <v>13</v>
@@ -8740,7 +8740,7 @@
         <v>50</v>
       </c>
       <c r="AF32">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG32">
         <v>11.5</v>
@@ -8752,7 +8752,7 @@
         <v>50</v>
       </c>
       <c r="AJ32">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK32">
         <v>22</v>
@@ -8815,10 +8815,10 @@
         <v>14.5</v>
       </c>
       <c r="BE32">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG32">
         <v>20</v>
@@ -8904,19 +8904,19 @@
         <v>230</v>
       </c>
       <c r="F33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G33">
         <v>10.5</v>
       </c>
       <c r="H33">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I33">
         <v>1.49</v>
       </c>
       <c r="J33">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K33">
         <v>4.7</v>
@@ -8934,7 +8934,7 @@
         <v>1.39</v>
       </c>
       <c r="P33">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q33">
         <v>2.16</v>
@@ -8949,7 +8949,7 @@
         <v>2.38</v>
       </c>
       <c r="U33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V33">
         <v>3</v>
@@ -8985,7 +8985,7 @@
         <v>110</v>
       </c>
       <c r="AG33">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AH33">
         <v>36</v>
@@ -9036,7 +9036,7 @@
         <v>16.5</v>
       </c>
       <c r="AX33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY33">
         <v>32</v>
@@ -9057,7 +9057,7 @@
         <v>9</v>
       </c>
       <c r="BE33">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF33">
         <v>15</v>
@@ -9075,7 +9075,7 @@
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="BL33">
         <v>1000</v>
@@ -9087,19 +9087,19 @@
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="BT33">
         <v>1000</v>
@@ -9111,7 +9111,7 @@
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="BX33">
         <v>1000</v>
@@ -9123,7 +9123,7 @@
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="CB33" t="s">
         <v>264</v>
@@ -9146,16 +9146,16 @@
         <v>231</v>
       </c>
       <c r="F34">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G34">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="H34">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="I34">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J34">
         <v>3.35</v>
@@ -9188,7 +9188,7 @@
         <v>1.26</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U34">
         <v>1.01</v>
@@ -9200,112 +9200,112 @@
         <v>1.35</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA34">
         <v>900</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC34">
         <v>42</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH34">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ34">
         <v>900</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP34">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AQ34">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AR34">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU34">
         <v>4.9</v>
       </c>
       <c r="AV34">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AW34">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AX34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AY34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ34">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA34">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9391,19 +9391,19 @@
         <v>3.1</v>
       </c>
       <c r="G35">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H35">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I35">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J35">
         <v>2.82</v>
       </c>
       <c r="K35">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="L35">
         <v>1.63</v>
@@ -9412,7 +9412,7 @@
         <v>1.14</v>
       </c>
       <c r="N35">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O35">
         <v>1.67</v>
@@ -9433,10 +9433,10 @@
         <v>2.3</v>
       </c>
       <c r="U35">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W35">
         <v>1.43</v>
@@ -9499,7 +9499,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ35">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR35">
         <v>14.5</v>
@@ -9514,7 +9514,7 @@
         <v>6.2</v>
       </c>
       <c r="AV35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW35">
         <v>38</v>
@@ -9642,40 +9642,40 @@
         <v>2.36</v>
       </c>
       <c r="J36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K36">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L36">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M36">
         <v>1.06</v>
       </c>
       <c r="N36">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O36">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q36">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R36">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S36">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T36">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U36">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V36">
         <v>1.73</v>
@@ -9684,46 +9684,46 @@
         <v>1.37</v>
       </c>
       <c r="X36">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z36">
         <v>15.5</v>
       </c>
       <c r="AA36">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB36">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC36">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD36">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF36">
         <v>26</v>
       </c>
       <c r="AG36">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH36">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI36">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ36">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AK36">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL36">
         <v>150</v>
@@ -9732,16 +9732,16 @@
         <v>110</v>
       </c>
       <c r="AN36">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AO36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP36">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ36">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR36">
         <v>12.5</v>
@@ -9750,13 +9750,13 @@
         <v>14.5</v>
       </c>
       <c r="AT36">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU36">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV36">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW36">
         <v>20</v>
@@ -9774,22 +9774,22 @@
         <v>18</v>
       </c>
       <c r="BB36">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC36">
         <v>18</v>
       </c>
       <c r="BD36">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE36">
         <v>21</v>
       </c>
       <c r="BF36">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG36">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH36">
         <v>3.55</v>
@@ -9798,34 +9798,34 @@
         <v>3.15</v>
       </c>
       <c r="BJ36">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK36">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN36">
         <v>6.8</v>
       </c>
       <c r="BO36">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP36">
         <v>28</v>
       </c>
       <c r="BQ36">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT36">
         <v>5.2</v>
@@ -9837,19 +9837,19 @@
         <v>16.5</v>
       </c>
       <c r="BW36">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX36">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ36">
+        <v>25</v>
+      </c>
+      <c r="CA36">
         <v>9.4</v>
-      </c>
-      <c r="BZ36">
-        <v>26</v>
-      </c>
-      <c r="CA36">
-        <v>9</v>
       </c>
       <c r="CB36" t="s">
         <v>264</v>
@@ -9872,7 +9872,7 @@
         <v>234</v>
       </c>
       <c r="F37">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G37">
         <v>4.3</v>
@@ -9947,7 +9947,7 @@
         <v>1000</v>
       </c>
       <c r="AE37">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF37">
         <v>85</v>
@@ -9956,13 +9956,13 @@
         <v>1000</v>
       </c>
       <c r="AH37">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AI37">
         <v>450</v>
       </c>
       <c r="AJ37">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="AK37">
         <v>280</v>
@@ -10114,22 +10114,22 @@
         <v>235</v>
       </c>
       <c r="F38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G38">
         <v>1.28</v>
       </c>
       <c r="H38">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="I38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J38">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K38">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L38">
         <v>1.3</v>
@@ -10138,19 +10138,19 @@
         <v>1.06</v>
       </c>
       <c r="N38">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O38">
         <v>1.3</v>
       </c>
       <c r="P38">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q38">
         <v>1.86</v>
       </c>
       <c r="R38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S38">
         <v>3.2</v>
@@ -10159,13 +10159,13 @@
         <v>2.72</v>
       </c>
       <c r="U38">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V38">
         <v>1.05</v>
       </c>
       <c r="W38">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="X38">
         <v>17.5</v>
@@ -10174,7 +10174,7 @@
         <v>170</v>
       </c>
       <c r="Z38">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AA38">
         <v>1000</v>
@@ -10192,7 +10192,7 @@
         <v>1000</v>
       </c>
       <c r="AF38">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG38">
         <v>13</v>
@@ -10201,79 +10201,79 @@
         <v>330</v>
       </c>
       <c r="AI38">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="AJ38">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AK38">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL38">
         <v>430</v>
       </c>
       <c r="AM38">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="AN38">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AO38">
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ38">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR38">
+        <v>8.6</v>
+      </c>
+      <c r="AS38">
         <v>9</v>
-      </c>
-      <c r="AS38">
-        <v>9.4</v>
       </c>
       <c r="AT38">
         <v>5.8</v>
       </c>
       <c r="AU38">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV38">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AW38">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX38">
         <v>5.5</v>
       </c>
       <c r="AY38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ38">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BA38">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB38">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC38">
         <v>14.5</v>
       </c>
       <c r="BD38">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BE38">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF38">
         <v>5</v>
       </c>
       <c r="BG38">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10362,10 +10362,10 @@
         <v>1.22</v>
       </c>
       <c r="H39">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="J39">
         <v>8.199999999999999</v>
@@ -10380,13 +10380,13 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>1.1</v>
       </c>
       <c r="P39">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q39">
         <v>1.33</v>
@@ -10395,19 +10395,19 @@
         <v>2.08</v>
       </c>
       <c r="S39">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="T39">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U39">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V39">
         <v>1.05</v>
       </c>
       <c r="W39">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X39">
         <v>320</v>
@@ -10416,7 +10416,7 @@
         <v>85</v>
       </c>
       <c r="Z39">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AA39">
         <v>1000</v>
@@ -10425,7 +10425,7 @@
         <v>17</v>
       </c>
       <c r="AC39">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AD39">
         <v>510</v>
@@ -10437,10 +10437,10 @@
         <v>11</v>
       </c>
       <c r="AG39">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH39">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI39">
         <v>180</v>
@@ -10458,34 +10458,34 @@
         <v>500</v>
       </c>
       <c r="AN39">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AO39">
         <v>300</v>
       </c>
       <c r="AP39">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AQ39">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR39">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS39">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT39">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU39">
         <v>18.5</v>
       </c>
       <c r="AV39">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW39">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX39">
         <v>9.199999999999999</v>
@@ -10494,10 +10494,10 @@
         <v>11</v>
       </c>
       <c r="AZ39">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BA39">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB39">
         <v>9</v>
@@ -10509,7 +10509,7 @@
         <v>16</v>
       </c>
       <c r="BE39">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="BF39">
         <v>2.56</v>
@@ -10604,7 +10604,7 @@
         <v>4.1</v>
       </c>
       <c r="H40">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="I40">
         <v>2.02</v>
@@ -10625,19 +10625,19 @@
         <v>4.7</v>
       </c>
       <c r="O40">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P40">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q40">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="R40">
         <v>1.45</v>
       </c>
       <c r="S40">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="T40">
         <v>1.6</v>
@@ -10658,7 +10658,7 @@
         <v>12</v>
       </c>
       <c r="Z40">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA40">
         <v>24</v>
@@ -10673,7 +10673,7 @@
         <v>11</v>
       </c>
       <c r="AE40">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF40">
         <v>36</v>
@@ -10685,7 +10685,7 @@
         <v>17</v>
       </c>
       <c r="AI40">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ40">
         <v>900</v>
@@ -10724,7 +10724,7 @@
         <v>8.4</v>
       </c>
       <c r="AV40">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW40">
         <v>16.5</v>
@@ -10846,16 +10846,16 @@
         <v>3.3</v>
       </c>
       <c r="H41">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I41">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J41">
         <v>3.5</v>
       </c>
       <c r="K41">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L41">
         <v>1.37</v>
@@ -10870,13 +10870,13 @@
         <v>1.33</v>
       </c>
       <c r="P41">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q41">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R41">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S41">
         <v>3.55</v>
@@ -10885,22 +10885,22 @@
         <v>1.78</v>
       </c>
       <c r="U41">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W41">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X41">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y41">
         <v>10.5</v>
       </c>
       <c r="Z41">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA41">
         <v>34</v>
@@ -10915,13 +10915,13 @@
         <v>11</v>
       </c>
       <c r="AE41">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF41">
         <v>22</v>
       </c>
       <c r="AG41">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH41">
         <v>16.5</v>
@@ -10972,16 +10972,16 @@
         <v>23</v>
       </c>
       <c r="AX41">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY41">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ41">
         <v>16</v>
       </c>
       <c r="BA41">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB41">
         <v>50</v>
@@ -10990,7 +10990,7 @@
         <v>32</v>
       </c>
       <c r="BD41">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE41">
         <v>75</v>
@@ -11088,7 +11088,7 @@
         <v>1.96</v>
       </c>
       <c r="H42">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I42">
         <v>4.3</v>
@@ -11109,7 +11109,7 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P42">
         <v>2.22</v>
@@ -11118,16 +11118,16 @@
         <v>1.77</v>
       </c>
       <c r="R42">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S42">
         <v>2.94</v>
       </c>
       <c r="T42">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U42">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V42">
         <v>1.3</v>
@@ -11136,7 +11136,7 @@
         <v>2.04</v>
       </c>
       <c r="X42">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y42">
         <v>17.5</v>
@@ -11145,7 +11145,7 @@
         <v>32</v>
       </c>
       <c r="AA42">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AB42">
         <v>11</v>
@@ -11181,7 +11181,7 @@
         <v>32</v>
       </c>
       <c r="AM42">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AN42">
         <v>11.5</v>
@@ -11199,7 +11199,7 @@
         <v>29</v>
       </c>
       <c r="AS42">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AT42">
         <v>10</v>
@@ -11220,7 +11220,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA42">
         <v>44</v>
@@ -11229,16 +11229,16 @@
         <v>20</v>
       </c>
       <c r="BC42">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD42">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE42">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BF42">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG42">
         <v>36</v>
@@ -11354,7 +11354,7 @@
         <v>1.15</v>
       </c>
       <c r="P43">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q43">
         <v>1.46</v>
@@ -11369,7 +11369,7 @@
         <v>1.78</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V43">
         <v>1.1</v>
@@ -11378,7 +11378,7 @@
         <v>3.7</v>
       </c>
       <c r="X43">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y43">
         <v>48</v>
@@ -11405,13 +11405,13 @@
         <v>10.5</v>
       </c>
       <c r="AG43">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH43">
         <v>24</v>
       </c>
       <c r="AI43">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AJ43">
         <v>12.5</v>
@@ -11435,13 +11435,13 @@
         <v>30</v>
       </c>
       <c r="AQ43">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AR43">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="AS43">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT43">
         <v>11.5</v>
@@ -11453,7 +11453,7 @@
         <v>30</v>
       </c>
       <c r="AW43">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="AX43">
         <v>9.6</v>
@@ -11465,13 +11465,13 @@
         <v>21</v>
       </c>
       <c r="BA43">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB43">
         <v>11</v>
       </c>
       <c r="BC43">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD43">
         <v>24</v>
@@ -11480,13 +11480,13 @@
         <v>29</v>
       </c>
       <c r="BF43">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BG43">
         <v>15</v>
       </c>
       <c r="BH43">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI43">
         <v>4.5</v>
@@ -11501,7 +11501,7 @@
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN43">
         <v>4.2</v>
@@ -11519,7 +11519,7 @@
         <v>19.5</v>
       </c>
       <c r="BS43">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT43">
         <v>13.5</v>
@@ -11531,13 +11531,13 @@
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ43">
         <v>9.6</v>
@@ -11566,10 +11566,10 @@
         <v>241</v>
       </c>
       <c r="F44">
+        <v>1.75</v>
+      </c>
+      <c r="G44">
         <v>1.76</v>
-      </c>
-      <c r="G44">
-        <v>1.77</v>
       </c>
       <c r="H44">
         <v>5</v>
@@ -11599,10 +11599,10 @@
         <v>2.52</v>
       </c>
       <c r="Q44">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R44">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S44">
         <v>2.58</v>
@@ -11611,19 +11611,19 @@
         <v>1.66</v>
       </c>
       <c r="U44">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V44">
         <v>1.24</v>
       </c>
       <c r="W44">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X44">
         <v>22</v>
       </c>
       <c r="Y44">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z44">
         <v>42</v>
@@ -11638,13 +11638,13 @@
         <v>9.6</v>
       </c>
       <c r="AD44">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE44">
         <v>55</v>
       </c>
       <c r="AF44">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG44">
         <v>9.6</v>
@@ -11662,7 +11662,7 @@
         <v>16</v>
       </c>
       <c r="AL44">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM44">
         <v>65</v>
@@ -11683,7 +11683,7 @@
         <v>38</v>
       </c>
       <c r="AS44">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT44">
         <v>11</v>
@@ -11692,7 +11692,7 @@
         <v>9.4</v>
       </c>
       <c r="AV44">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW44">
         <v>48</v>
@@ -11710,7 +11710,7 @@
         <v>44</v>
       </c>
       <c r="BB44">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC44">
         <v>15</v>
@@ -11853,7 +11853,7 @@
         <v>1.97</v>
       </c>
       <c r="U45">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V45">
         <v>2.32</v>
@@ -11871,7 +11871,7 @@
         <v>9.6</v>
       </c>
       <c r="AA45">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AB45">
         <v>18</v>
@@ -11919,13 +11919,13 @@
         <v>13</v>
       </c>
       <c r="AQ45">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR45">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS45">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT45">
         <v>17</v>
@@ -11934,10 +11934,10 @@
         <v>8.4</v>
       </c>
       <c r="AV45">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW45">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX45">
         <v>40</v>
@@ -11958,7 +11958,7 @@
         <v>70</v>
       </c>
       <c r="BD45">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE45">
         <v>100</v>
@@ -12050,31 +12050,31 @@
         <v>243</v>
       </c>
       <c r="F46">
+        <v>1.83</v>
+      </c>
+      <c r="G46">
         <v>1.85</v>
       </c>
-      <c r="G46">
-        <v>1.87</v>
-      </c>
       <c r="H46">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I46">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J46">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K46">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L46">
         <v>1.32</v>
       </c>
       <c r="M46">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N46">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O46">
         <v>1.21</v>
@@ -12086,31 +12086,31 @@
         <v>1.65</v>
       </c>
       <c r="R46">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S46">
         <v>2.62</v>
       </c>
       <c r="T46">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U46">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V46">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W46">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X46">
         <v>22</v>
       </c>
       <c r="Y46">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z46">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA46">
         <v>90</v>
@@ -12119,19 +12119,19 @@
         <v>12</v>
       </c>
       <c r="AC46">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD46">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE46">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF46">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG46">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH46">
         <v>16</v>
@@ -12140,10 +12140,10 @@
         <v>46</v>
       </c>
       <c r="AJ46">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK46">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL46">
         <v>26</v>
@@ -12152,7 +12152,7 @@
         <v>65</v>
       </c>
       <c r="AN46">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO46">
         <v>38</v>
@@ -12161,10 +12161,10 @@
         <v>20</v>
       </c>
       <c r="AQ46">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR46">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS46">
         <v>75</v>
@@ -12173,13 +12173,13 @@
         <v>11</v>
       </c>
       <c r="AU46">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV46">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW46">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX46">
         <v>12</v>
@@ -12191,28 +12191,28 @@
         <v>15</v>
       </c>
       <c r="BA46">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BB46">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC46">
         <v>15.5</v>
       </c>
       <c r="BD46">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE46">
         <v>55</v>
       </c>
       <c r="BF46">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG46">
         <v>34</v>
       </c>
       <c r="BH46">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI46">
         <v>3.85</v>
@@ -12227,7 +12227,7 @@
         <v>110</v>
       </c>
       <c r="BM46">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BN46">
         <v>4.8</v>
@@ -12245,7 +12245,7 @@
         <v>27</v>
       </c>
       <c r="BS46">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT46">
         <v>8</v>
@@ -12257,19 +12257,19 @@
         <v>38</v>
       </c>
       <c r="BW46">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX46">
         <v>42</v>
       </c>
       <c r="BY46">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ46">
         <v>19</v>
       </c>
       <c r="CA46">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB46" t="s">
         <v>264</v>
@@ -12301,16 +12301,16 @@
         <v>1.49</v>
       </c>
       <c r="I47">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J47">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K47">
         <v>5.3</v>
       </c>
       <c r="L47">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M47">
         <v>1.03</v>
@@ -12319,22 +12319,22 @@
         <v>6.2</v>
       </c>
       <c r="O47">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P47">
         <v>2.78</v>
       </c>
       <c r="Q47">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R47">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S47">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T47">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U47">
         <v>2.3</v>
@@ -12346,7 +12346,7 @@
         <v>1.16</v>
       </c>
       <c r="X47">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y47">
         <v>12.5</v>
@@ -12358,7 +12358,7 @@
         <v>14</v>
       </c>
       <c r="AB47">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC47">
         <v>12.5</v>
@@ -12394,10 +12394,10 @@
         <v>85</v>
       </c>
       <c r="AN47">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO47">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AP47">
         <v>24</v>
@@ -12406,7 +12406,7 @@
         <v>11</v>
       </c>
       <c r="AR47">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS47">
         <v>12</v>
@@ -12424,7 +12424,7 @@
         <v>12.5</v>
       </c>
       <c r="AX47">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY47">
         <v>21</v>
@@ -12436,7 +12436,7 @@
         <v>23</v>
       </c>
       <c r="BB47">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC47">
         <v>28</v>
@@ -12448,7 +12448,7 @@
         <v>38</v>
       </c>
       <c r="BF47">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG47">
         <v>5</v>
@@ -12457,37 +12457,37 @@
         <v>1000</v>
       </c>
       <c r="BI47">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ47">
         <v>1000</v>
       </c>
       <c r="BK47">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BL47">
         <v>1000</v>
       </c>
       <c r="BM47">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BN47">
         <v>1000</v>
       </c>
       <c r="BO47">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BP47">
         <v>1000</v>
       </c>
       <c r="BQ47">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BR47">
         <v>1000</v>
       </c>
       <c r="BS47">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BT47">
         <v>1000</v>
@@ -12499,19 +12499,19 @@
         <v>1000</v>
       </c>
       <c r="BW47">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BX47">
         <v>1000</v>
       </c>
       <c r="BY47">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BZ47">
         <v>1000</v>
       </c>
       <c r="CA47">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CB47" t="s">
         <v>264</v>
@@ -12534,19 +12534,19 @@
         <v>245</v>
       </c>
       <c r="F48">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G48">
         <v>3.4</v>
       </c>
       <c r="H48">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I48">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J48">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K48">
         <v>3.55</v>
@@ -12555,19 +12555,19 @@
         <v>1.42</v>
       </c>
       <c r="M48">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N48">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O48">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P48">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q48">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R48">
         <v>1.35</v>
@@ -12576,16 +12576,16 @@
         <v>3.5</v>
       </c>
       <c r="T48">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U48">
         <v>2.18</v>
       </c>
       <c r="V48">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W48">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X48">
         <v>13.5</v>
@@ -12603,13 +12603,13 @@
         <v>13</v>
       </c>
       <c r="AC48">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD48">
         <v>11</v>
       </c>
       <c r="AE48">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF48">
         <v>23</v>
@@ -12633,7 +12633,7 @@
         <v>50</v>
       </c>
       <c r="AM48">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN48">
         <v>36</v>
@@ -12657,7 +12657,7 @@
         <v>12</v>
       </c>
       <c r="AU48">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV48">
         <v>10</v>
@@ -12666,10 +12666,10 @@
         <v>22</v>
       </c>
       <c r="AX48">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY48">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ48">
         <v>16</v>
@@ -12717,13 +12717,13 @@
         <v>6.6</v>
       </c>
       <c r="BO48">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP48">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ48">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR48">
         <v>44</v>
@@ -12738,7 +12738,7 @@
         <v>4.7</v>
       </c>
       <c r="BV48">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW48">
         <v>8</v>
@@ -12753,7 +12753,7 @@
         <v>32</v>
       </c>
       <c r="CA48">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB48" t="s">
         <v>264</v>
@@ -12785,13 +12785,13 @@
         <v>50</v>
       </c>
       <c r="I49">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J49">
+        <v>22</v>
+      </c>
+      <c r="K49">
         <v>23</v>
-      </c>
-      <c r="K49">
-        <v>24</v>
       </c>
       <c r="L49">
         <v>1.14</v>
@@ -12800,25 +12800,25 @@
         <v>1.01</v>
       </c>
       <c r="N49">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="O49">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P49">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q49">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R49">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="S49">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="T49">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="U49">
         <v>1.54</v>
@@ -12827,10 +12827,10 @@
         <v>1.01</v>
       </c>
       <c r="W49">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="X49">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y49">
         <v>180</v>
@@ -12842,22 +12842,22 @@
         <v>1000</v>
       </c>
       <c r="AB49">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC49">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AD49">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AE49">
         <v>1000</v>
       </c>
       <c r="AF49">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG49">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH49">
         <v>110</v>
@@ -12872,13 +12872,13 @@
         <v>18</v>
       </c>
       <c r="AL49">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AM49">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="AN49">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AO49">
         <v>1000</v>
@@ -12890,49 +12890,49 @@
         <v>48</v>
       </c>
       <c r="AR49">
+        <v>25</v>
+      </c>
+      <c r="AS49">
         <v>30</v>
       </c>
-      <c r="AS49">
-        <v>34</v>
-      </c>
       <c r="AT49">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AU49">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AV49">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AW49">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AX49">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY49">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ49">
         <v>48</v>
       </c>
       <c r="BA49">
+        <v>24</v>
+      </c>
+      <c r="BB49">
+        <v>7.8</v>
+      </c>
+      <c r="BC49">
+        <v>17</v>
+      </c>
+      <c r="BD49">
         <v>55</v>
-      </c>
-      <c r="BB49">
-        <v>7.6</v>
-      </c>
-      <c r="BC49">
-        <v>16.5</v>
-      </c>
-      <c r="BD49">
-        <v>38</v>
       </c>
       <c r="BE49">
         <v>100</v>
       </c>
       <c r="BF49">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BG49">
         <v>80</v>
@@ -12947,13 +12947,13 @@
         <v>20</v>
       </c>
       <c r="BK49">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BN49">
         <v>4.3</v>
@@ -12968,28 +12968,28 @@
         <v>4.4</v>
       </c>
       <c r="BR49">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS49">
         <v>10</v>
       </c>
       <c r="BT49">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BU49">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BV49">
         <v>1000</v>
       </c>
       <c r="BW49">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BX49">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BY49">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ49">
         <v>3.95</v>
@@ -13081,13 +13081,13 @@
         <v>1000</v>
       </c>
       <c r="AA50">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB50">
         <v>1000</v>
       </c>
       <c r="AC50">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD50">
         <v>1000</v>
@@ -13108,7 +13108,7 @@
         <v>1000</v>
       </c>
       <c r="AJ50">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK50">
         <v>1000</v>
@@ -13123,55 +13123,55 @@
         <v>970</v>
       </c>
       <c r="AO50">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AP50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AQ50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AR50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AT50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AU50">
         <v>1.2</v>
       </c>
       <c r="AV50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AW50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AX50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AY50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AZ50">
         <v>7</v>
       </c>
       <c r="BA50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BB50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BC50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BD50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BE50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BF50">
         <v>2.36</v>
@@ -13260,22 +13260,22 @@
         <v>248</v>
       </c>
       <c r="F51">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G51">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H51">
+        <v>1.2</v>
+      </c>
+      <c r="I51">
         <v>1.21</v>
       </c>
-      <c r="I51">
-        <v>1.22</v>
-      </c>
       <c r="J51">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K51">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="L51">
         <v>1.26</v>
@@ -13284,19 +13284,19 @@
         <v>1.03</v>
       </c>
       <c r="N51">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O51">
         <v>1.17</v>
       </c>
       <c r="P51">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q51">
         <v>1.51</v>
       </c>
       <c r="R51">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S51">
         <v>2.3</v>
@@ -13305,10 +13305,10 @@
         <v>2.4</v>
       </c>
       <c r="U51">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V51">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W51">
         <v>1.05</v>
@@ -13320,7 +13320,7 @@
         <v>11.5</v>
       </c>
       <c r="Z51">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AA51">
         <v>8.199999999999999</v>
@@ -13359,7 +13359,7 @@
         <v>260</v>
       </c>
       <c r="AM51">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AN51">
         <v>1000</v>
@@ -13368,10 +13368,10 @@
         <v>3.55</v>
       </c>
       <c r="AP51">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AQ51">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR51">
         <v>7</v>
@@ -13380,37 +13380,37 @@
         <v>7.2</v>
       </c>
       <c r="AT51">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU51">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV51">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW51">
         <v>13</v>
       </c>
       <c r="AX51">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY51">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ51">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA51">
         <v>34</v>
       </c>
       <c r="BB51">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC51">
         <v>10</v>
       </c>
       <c r="BD51">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE51">
         <v>10.5</v>
@@ -13419,7 +13419,7 @@
         <v>15</v>
       </c>
       <c r="BG51">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BH51">
         <v>5.7</v>
@@ -13502,40 +13502,40 @@
         <v>249</v>
       </c>
       <c r="F52">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G52">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H52">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I52">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J52">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="K52">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L52">
         <v>1.01</v>
       </c>
       <c r="M52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N52">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O52">
         <v>1.52</v>
       </c>
       <c r="P52">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q52">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R52">
         <v>1.17</v>
@@ -13544,7 +13544,7 @@
         <v>3.1</v>
       </c>
       <c r="T52">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U52">
         <v>1.72</v>
@@ -13553,52 +13553,52 @@
         <v>1.37</v>
       </c>
       <c r="W52">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X52">
         <v>970</v>
       </c>
       <c r="Y52">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z52">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA52">
         <v>900</v>
       </c>
       <c r="AB52">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC52">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD52">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AE52">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF52">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG52">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AH52">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI52">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AJ52">
         <v>900</v>
       </c>
       <c r="AK52">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL52">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM52">
         <v>1000</v>
@@ -13610,58 +13610,58 @@
         <v>1000</v>
       </c>
       <c r="AP52">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AQ52">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AR52">
-        <v>1.38</v>
+        <v>17.5</v>
       </c>
       <c r="AS52">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AT52">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AU52">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AV52">
-        <v>12</v>
+        <v>1.67</v>
       </c>
       <c r="AW52">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="AX52">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AY52">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="AZ52">
-        <v>1.38</v>
+        <v>16.5</v>
       </c>
       <c r="BA52">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="BB52">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="BC52">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="BD52">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="BE52">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="BF52">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="BG52">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13744,10 +13744,10 @@
         <v>250</v>
       </c>
       <c r="F53">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G53">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H53">
         <v>2.88</v>
@@ -13759,7 +13759,7 @@
         <v>3</v>
       </c>
       <c r="K53">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L53">
         <v>1.01</v>
@@ -13771,10 +13771,10 @@
         <v>2.92</v>
       </c>
       <c r="O53">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P53">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q53">
         <v>2.2</v>
@@ -13795,7 +13795,7 @@
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X53">
         <v>11.5</v>
@@ -13891,7 +13891,7 @@
         <v>21</v>
       </c>
       <c r="BC53">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD53">
         <v>24</v>
@@ -13986,19 +13986,19 @@
         <v>251</v>
       </c>
       <c r="F54">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G54">
         <v>1.32</v>
       </c>
       <c r="H54">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I54">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J54">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K54">
         <v>6</v>
@@ -14007,34 +14007,34 @@
         <v>1.41</v>
       </c>
       <c r="M54">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N54">
         <v>3.7</v>
       </c>
       <c r="O54">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P54">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q54">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R54">
         <v>1.36</v>
       </c>
       <c r="S54">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T54">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="U54">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V54">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W54">
         <v>4.1</v>
@@ -14046,7 +14046,7 @@
         <v>38</v>
       </c>
       <c r="Z54">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AA54">
         <v>1000</v>
@@ -14055,13 +14055,13 @@
         <v>6.6</v>
       </c>
       <c r="AC54">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AD54">
         <v>80</v>
       </c>
       <c r="AE54">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AF54">
         <v>6.6</v>
@@ -14070,13 +14070,13 @@
         <v>12</v>
       </c>
       <c r="AH54">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AI54">
         <v>470</v>
       </c>
       <c r="AJ54">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AK54">
         <v>22</v>
@@ -14088,7 +14088,7 @@
         <v>440</v>
       </c>
       <c r="AN54">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO54">
         <v>1000</v>
@@ -14097,25 +14097,25 @@
         <v>13</v>
       </c>
       <c r="AQ54">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="AR54">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AS54">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AT54">
         <v>6</v>
       </c>
       <c r="AU54">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV54">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW54">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX54">
         <v>6</v>
@@ -14124,37 +14124,37 @@
         <v>10.5</v>
       </c>
       <c r="AZ54">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BA54">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB54">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC54">
         <v>15.5</v>
       </c>
       <c r="BD54">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BE54">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF54">
         <v>5.7</v>
       </c>
       <c r="BG54">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH54">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI54">
         <v>3.2</v>
       </c>
       <c r="BJ54">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BK54">
         <v>8.4</v>
@@ -14169,13 +14169,13 @@
         <v>3.35</v>
       </c>
       <c r="BO54">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP54">
         <v>7.4</v>
       </c>
       <c r="BQ54">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR54">
         <v>34</v>
@@ -14184,7 +14184,7 @@
         <v>23</v>
       </c>
       <c r="BT54">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BU54">
         <v>13.5</v>
@@ -14202,7 +14202,7 @@
         <v>21</v>
       </c>
       <c r="BZ54">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA54">
         <v>10.5</v>
@@ -14228,22 +14228,22 @@
         <v>252</v>
       </c>
       <c r="F55">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G55">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H55">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="I55">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="J55">
         <v>3.15</v>
       </c>
       <c r="K55">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L55">
         <v>1.55</v>
@@ -14252,40 +14252,40 @@
         <v>1.11</v>
       </c>
       <c r="N55">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O55">
         <v>1.51</v>
       </c>
       <c r="P55">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q55">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R55">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S55">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T55">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U55">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V55">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W55">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X55">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y55">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z55">
         <v>19.5</v>
@@ -14300,10 +14300,10 @@
         <v>7.4</v>
       </c>
       <c r="AD55">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE55">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AF55">
         <v>25</v>
@@ -14312,7 +14312,7 @@
         <v>14.5</v>
       </c>
       <c r="AH55">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI55">
         <v>75</v>
@@ -14324,10 +14324,10 @@
         <v>60</v>
       </c>
       <c r="AL55">
-        <v>170</v>
+        <v>450</v>
       </c>
       <c r="AM55">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN55">
         <v>70</v>
@@ -14339,13 +14339,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ55">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR55">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS55">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AT55">
         <v>8.4</v>
@@ -14357,37 +14357,37 @@
         <v>11</v>
       </c>
       <c r="AW55">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX55">
         <v>17.5</v>
       </c>
       <c r="AY55">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ55">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BA55">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB55">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC55">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD55">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE55">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF55">
         <v>9.4</v>
       </c>
       <c r="BG55">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH55">
         <v>2.82</v>
@@ -14399,55 +14399,55 @@
         <v>11</v>
       </c>
       <c r="BK55">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL55">
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BN55">
         <v>6.2</v>
       </c>
       <c r="BO55">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP55">
         <v>1000</v>
       </c>
       <c r="BQ55">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR55">
         <v>1000</v>
       </c>
       <c r="BS55">
+        <v>13.5</v>
+      </c>
+      <c r="BT55">
+        <v>5.3</v>
+      </c>
+      <c r="BU55">
+        <v>4.8</v>
+      </c>
+      <c r="BV55">
+        <v>1000</v>
+      </c>
+      <c r="BW55">
+        <v>10</v>
+      </c>
+      <c r="BX55">
+        <v>1000</v>
+      </c>
+      <c r="BY55">
         <v>12.5</v>
       </c>
-      <c r="BT55">
-        <v>5.4</v>
-      </c>
-      <c r="BU55">
-        <v>4.9</v>
-      </c>
-      <c r="BV55">
-        <v>1000</v>
-      </c>
-      <c r="BW55">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX55">
-        <v>1000</v>
-      </c>
-      <c r="BY55">
-        <v>12</v>
-      </c>
       <c r="BZ55">
         <v>1000</v>
       </c>
       <c r="CA55">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB55" t="s">
         <v>264</v>
@@ -14521,7 +14521,7 @@
         <v>1.15</v>
       </c>
       <c r="W56">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X56">
         <v>12.5</v>
@@ -14536,7 +14536,7 @@
         <v>700</v>
       </c>
       <c r="AB56">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AC56">
         <v>9.4</v>
@@ -14557,7 +14557,7 @@
         <v>27</v>
       </c>
       <c r="AI56">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ56">
         <v>15.5</v>
@@ -14584,10 +14584,10 @@
         <v>16.5</v>
       </c>
       <c r="AR56">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AS56">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT56">
         <v>6.2</v>
@@ -14599,7 +14599,7 @@
         <v>20</v>
       </c>
       <c r="AW56">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AX56">
         <v>7.6</v>
@@ -14611,7 +14611,7 @@
         <v>19</v>
       </c>
       <c r="BA56">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB56">
         <v>13.5</v>
@@ -14623,73 +14623,73 @@
         <v>34</v>
       </c>
       <c r="BE56">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF56">
         <v>10</v>
       </c>
       <c r="BG56">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH56">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI56">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="BJ56">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK56">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="BL56">
         <v>1000</v>
       </c>
       <c r="BM56">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="BN56">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BO56">
-        <v>3.5</v>
+        <v>1.41</v>
       </c>
       <c r="BP56">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ56">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="BR56">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS56">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="BT56">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU56">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="BV56">
         <v>1000</v>
       </c>
       <c r="BW56">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="BX56">
         <v>1000</v>
       </c>
       <c r="BY56">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="BZ56">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA56">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="CB56" t="s">
         <v>264</v>
@@ -14715,13 +14715,13 @@
         <v>2.72</v>
       </c>
       <c r="G57">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H57">
         <v>2.62</v>
       </c>
       <c r="I57">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J57">
         <v>3.65</v>
@@ -14739,16 +14739,16 @@
         <v>4.7</v>
       </c>
       <c r="O57">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P57">
         <v>2.24</v>
       </c>
       <c r="Q57">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R57">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S57">
         <v>2.92</v>
@@ -14763,10 +14763,10 @@
         <v>1.58</v>
       </c>
       <c r="W57">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X57">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y57">
         <v>14</v>
@@ -14781,7 +14781,7 @@
         <v>14.5</v>
       </c>
       <c r="AC57">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD57">
         <v>12.5</v>
@@ -14793,7 +14793,7 @@
         <v>20</v>
       </c>
       <c r="AG57">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH57">
         <v>16</v>
@@ -14817,7 +14817,7 @@
         <v>20</v>
       </c>
       <c r="AO57">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP57">
         <v>16.5</v>
@@ -14829,7 +14829,7 @@
         <v>16.5</v>
       </c>
       <c r="AS57">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT57">
         <v>12.5</v>
@@ -14841,10 +14841,10 @@
         <v>11</v>
       </c>
       <c r="AW57">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX57">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY57">
         <v>11.5</v>
@@ -14853,19 +14853,19 @@
         <v>14</v>
       </c>
       <c r="BA57">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB57">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC57">
         <v>18</v>
       </c>
       <c r="BD57">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE57">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF57">
         <v>17.5</v>
@@ -14883,7 +14883,7 @@
         <v>1000</v>
       </c>
       <c r="BK57">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL57">
         <v>1000</v>
@@ -14895,13 +14895,13 @@
         <v>1000</v>
       </c>
       <c r="BO57">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP57">
         <v>1000</v>
       </c>
       <c r="BQ57">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR57">
         <v>1000</v>
@@ -14910,10 +14910,10 @@
         <v>1.01</v>
       </c>
       <c r="BT57">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU57">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV57">
         <v>1000</v>
@@ -14954,22 +14954,22 @@
         <v>255</v>
       </c>
       <c r="F58">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G58">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I58">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J58">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K58">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L58">
         <v>1.41</v>
@@ -14978,7 +14978,7 @@
         <v>1.07</v>
       </c>
       <c r="N58">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O58">
         <v>1.33</v>
@@ -14990,25 +14990,25 @@
         <v>1.93</v>
       </c>
       <c r="R58">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S58">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T58">
         <v>1.68</v>
       </c>
       <c r="U58">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="V58">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X58">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y58">
         <v>13</v>
@@ -15029,13 +15029,13 @@
         <v>14.5</v>
       </c>
       <c r="AE58">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF58">
         <v>18.5</v>
       </c>
       <c r="AG58">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH58">
         <v>20</v>
@@ -15044,10 +15044,10 @@
         <v>55</v>
       </c>
       <c r="AJ58">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK58">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL58">
         <v>46</v>
@@ -15071,10 +15071,10 @@
         <v>17</v>
       </c>
       <c r="AS58">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT58">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU58">
         <v>7.2</v>
@@ -15083,7 +15083,7 @@
         <v>12</v>
       </c>
       <c r="AW58">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX58">
         <v>13.5</v>
@@ -15095,85 +15095,85 @@
         <v>15</v>
       </c>
       <c r="BA58">
+        <v>6.6</v>
+      </c>
+      <c r="BB58">
         <v>6.2</v>
-      </c>
-      <c r="BB58">
-        <v>6</v>
       </c>
       <c r="BC58">
         <v>20</v>
       </c>
       <c r="BD58">
+        <v>6.4</v>
+      </c>
+      <c r="BE58">
+        <v>7</v>
+      </c>
+      <c r="BF58">
+        <v>17.5</v>
+      </c>
+      <c r="BG58">
         <v>6.2</v>
       </c>
-      <c r="BE58">
-        <v>6.6</v>
-      </c>
-      <c r="BF58">
-        <v>16.5</v>
-      </c>
-      <c r="BG58">
-        <v>6</v>
-      </c>
       <c r="BH58">
         <v>1000</v>
       </c>
       <c r="BI58">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BJ58">
         <v>1000</v>
       </c>
       <c r="BK58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BN58">
         <v>1000</v>
       </c>
       <c r="BO58">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BP58">
         <v>1000</v>
       </c>
       <c r="BQ58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BR58">
         <v>1000</v>
       </c>
       <c r="BS58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BT58">
         <v>1000</v>
       </c>
       <c r="BU58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BV58">
         <v>1000</v>
       </c>
       <c r="BW58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BX58">
         <v>1000</v>
       </c>
       <c r="BY58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BZ58">
         <v>1000</v>
       </c>
       <c r="CA58">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="CB58" t="s">
         <v>264</v>
@@ -15196,10 +15196,10 @@
         <v>256</v>
       </c>
       <c r="F59">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G59">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H59">
         <v>2.96</v>
@@ -15211,7 +15211,7 @@
         <v>3.3</v>
       </c>
       <c r="K59">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L59">
         <v>1.42</v>
@@ -15223,13 +15223,13 @@
         <v>3.7</v>
       </c>
       <c r="O59">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P59">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q59">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R59">
         <v>1.35</v>
@@ -15268,7 +15268,7 @@
         <v>7.4</v>
       </c>
       <c r="AD59">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE59">
         <v>50</v>
@@ -15313,7 +15313,7 @@
         <v>19</v>
       </c>
       <c r="AS59">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT59">
         <v>9.800000000000001</v>
@@ -15322,7 +15322,7 @@
         <v>6.4</v>
       </c>
       <c r="AV59">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW59">
         <v>30</v>
@@ -15337,25 +15337,25 @@
         <v>14</v>
       </c>
       <c r="BA59">
+        <v>8.6</v>
+      </c>
+      <c r="BB59">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB59">
-        <v>8</v>
-      </c>
       <c r="BC59">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD59">
         <v>32</v>
       </c>
       <c r="BE59">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF59">
         <v>18</v>
       </c>
       <c r="BG59">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH59">
         <v>1000</v>
@@ -15438,31 +15438,31 @@
         <v>257</v>
       </c>
       <c r="F60">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G60">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H60">
         <v>2.68</v>
       </c>
       <c r="I60">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J60">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K60">
         <v>4.6</v>
       </c>
       <c r="L60">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N60">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O60">
         <v>1.14</v>
@@ -15480,25 +15480,25 @@
         <v>2.26</v>
       </c>
       <c r="T60">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="U60">
         <v>2.62</v>
       </c>
       <c r="V60">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W60">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X60">
         <v>1000</v>
       </c>
       <c r="Y60">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z60">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA60">
         <v>1000</v>
@@ -15507,19 +15507,19 @@
         <v>1000</v>
       </c>
       <c r="AC60">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD60">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE60">
         <v>1000</v>
       </c>
       <c r="AF60">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG60">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH60">
         <v>1000</v>
@@ -15534,7 +15534,7 @@
         <v>1000</v>
       </c>
       <c r="AL60">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM60">
         <v>1000</v>
@@ -15549,10 +15549,10 @@
         <v>1.03</v>
       </c>
       <c r="AQ60">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR60">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS60">
         <v>1.03</v>
@@ -15561,25 +15561,25 @@
         <v>1.03</v>
       </c>
       <c r="AU60">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV60">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW60">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX60">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY60">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ60">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BA60">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BB60">
         <v>1.03</v>
@@ -15588,10 +15588,10 @@
         <v>1.03</v>
       </c>
       <c r="BD60">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BE60">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BF60">
         <v>1.01</v>
@@ -15692,7 +15692,7 @@
         <v>7</v>
       </c>
       <c r="J61">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K61">
         <v>4.5</v>
@@ -15713,19 +15713,19 @@
         <v>1.98</v>
       </c>
       <c r="Q61">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R61">
         <v>1.37</v>
       </c>
       <c r="S61">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T61">
         <v>1.85</v>
       </c>
       <c r="U61">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V61">
         <v>1.16</v>
@@ -15746,7 +15746,7 @@
         <v>200</v>
       </c>
       <c r="AB61">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC61">
         <v>11</v>
@@ -15788,58 +15788,58 @@
         <v>130</v>
       </c>
       <c r="AP61">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ61">
         <v>4.7</v>
       </c>
       <c r="AR61">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="AS61">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT61">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU61">
         <v>3.85</v>
       </c>
       <c r="AV61">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW61">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="AX61">
         <v>8.4</v>
       </c>
       <c r="AY61">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ61">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BA61">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB61">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="BC61">
         <v>13</v>
       </c>
       <c r="BD61">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="BE61">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF61">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG61">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH61">
         <v>4.4</v>
@@ -15925,7 +15925,7 @@
         <v>2.16</v>
       </c>
       <c r="G62">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H62">
         <v>3.1</v>
@@ -15934,7 +15934,7 @@
         <v>3.65</v>
       </c>
       <c r="J62">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K62">
         <v>4.1</v>
@@ -15955,7 +15955,7 @@
         <v>2</v>
       </c>
       <c r="Q62">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R62">
         <v>1.41</v>
@@ -15964,7 +15964,7 @@
         <v>2.96</v>
       </c>
       <c r="T62">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U62">
         <v>2.2</v>
@@ -15973,7 +15973,7 @@
         <v>1.37</v>
       </c>
       <c r="W62">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X62">
         <v>19.5</v>
@@ -15988,22 +15988,22 @@
         <v>70</v>
       </c>
       <c r="AB62">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC62">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD62">
         <v>16.5</v>
       </c>
       <c r="AE62">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF62">
         <v>17.5</v>
       </c>
       <c r="AG62">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH62">
         <v>19</v>
@@ -16018,7 +16018,7 @@
         <v>26</v>
       </c>
       <c r="AL62">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM62">
         <v>90</v>
@@ -16039,10 +16039,10 @@
         <v>18.5</v>
       </c>
       <c r="AS62">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT62">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU62">
         <v>6.6</v>
@@ -16051,37 +16051,37 @@
         <v>11</v>
       </c>
       <c r="AW62">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX62">
         <v>12</v>
       </c>
       <c r="AY62">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ62">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA62">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB62">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC62">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD62">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE62">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF62">
         <v>12.5</v>
       </c>
       <c r="BG62">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -16164,7 +16164,7 @@
         <v>260</v>
       </c>
       <c r="F63">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G63">
         <v>3.2</v>
@@ -16179,7 +16179,7 @@
         <v>3.75</v>
       </c>
       <c r="K63">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L63">
         <v>1.35</v>
@@ -16200,16 +16200,16 @@
         <v>1.74</v>
       </c>
       <c r="R63">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S63">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T63">
         <v>1.63</v>
       </c>
       <c r="U63">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V63">
         <v>1.7</v>
@@ -16227,7 +16227,7 @@
         <v>17</v>
       </c>
       <c r="AA63">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB63">
         <v>15.5</v>
@@ -16254,7 +16254,7 @@
         <v>32</v>
       </c>
       <c r="AJ63">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AK63">
         <v>32</v>
@@ -16281,7 +16281,7 @@
         <v>14.5</v>
       </c>
       <c r="AS63">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT63">
         <v>13.5</v>
@@ -16305,19 +16305,19 @@
         <v>14</v>
       </c>
       <c r="BA63">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB63">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC63">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BD63">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE63">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF63">
         <v>20</v>
@@ -16365,7 +16365,7 @@
         <v>1000</v>
       </c>
       <c r="BU63">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BV63">
         <v>1000</v>
@@ -16406,22 +16406,22 @@
         <v>261</v>
       </c>
       <c r="F64">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G64">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H64">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I64">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J64">
         <v>3.9</v>
       </c>
       <c r="K64">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L64">
         <v>1.3</v>
@@ -16430,13 +16430,13 @@
         <v>1.04</v>
       </c>
       <c r="N64">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O64">
         <v>1.2</v>
       </c>
       <c r="P64">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q64">
         <v>1.61</v>
@@ -16445,7 +16445,7 @@
         <v>1.61</v>
       </c>
       <c r="S64">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T64">
         <v>1.55</v>
@@ -16454,19 +16454,19 @@
         <v>2.68</v>
       </c>
       <c r="V64">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="X64">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y64">
         <v>17.5</v>
       </c>
       <c r="Z64">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA64">
         <v>75</v>
@@ -16478,55 +16478,55 @@
         <v>9.6</v>
       </c>
       <c r="AD64">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE64">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AF64">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG64">
         <v>12</v>
       </c>
       <c r="AH64">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI64">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AJ64">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AK64">
         <v>23</v>
       </c>
       <c r="AL64">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM64">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AN64">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO64">
+        <v>17.5</v>
+      </c>
+      <c r="AP64">
         <v>18.5</v>
-      </c>
-      <c r="AP64">
-        <v>21</v>
       </c>
       <c r="AQ64">
         <v>15</v>
       </c>
       <c r="AR64">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS64">
         <v>30</v>
       </c>
       <c r="AT64">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU64">
         <v>8.6</v>
@@ -16535,7 +16535,7 @@
         <v>12</v>
       </c>
       <c r="AW64">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX64">
         <v>16</v>
@@ -16550,7 +16550,7 @@
         <v>21</v>
       </c>
       <c r="BB64">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC64">
         <v>19.5</v>
@@ -16562,16 +16562,16 @@
         <v>36</v>
       </c>
       <c r="BF64">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG64">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH64">
         <v>4.9</v>
       </c>
       <c r="BI64">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ64">
         <v>9.800000000000001</v>
@@ -16583,49 +16583,49 @@
         <v>85</v>
       </c>
       <c r="BM64">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BN64">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO64">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP64">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ64">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BR64">
         <v>27</v>
       </c>
       <c r="BS64">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BT64">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU64">
         <v>5.8</v>
       </c>
       <c r="BV64">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW64">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BX64">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BY64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BZ64">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA64">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="CB64" t="s">
         <v>264</v>
@@ -16648,7 +16648,7 @@
         <v>262</v>
       </c>
       <c r="F65">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G65">
         <v>2.26</v>
@@ -16663,7 +16663,7 @@
         <v>4.1</v>
       </c>
       <c r="K65">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L65">
         <v>1.26</v>
@@ -16684,7 +16684,7 @@
         <v>1.49</v>
       </c>
       <c r="R65">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S65">
         <v>2.22</v>
@@ -16741,13 +16741,13 @@
         <v>29</v>
       </c>
       <c r="AK65">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL65">
         <v>25</v>
       </c>
       <c r="AM65">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AN65">
         <v>9.6</v>
@@ -16789,13 +16789,13 @@
         <v>12.5</v>
       </c>
       <c r="BA65">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB65">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC65">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD65">
         <v>18.5</v>
@@ -16813,7 +16813,7 @@
         <v>4.9</v>
       </c>
       <c r="BI65">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ65">
         <v>8.4</v>
@@ -16831,7 +16831,7 @@
         <v>5.8</v>
       </c>
       <c r="BO65">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP65">
         <v>14.5</v>
@@ -16899,7 +16899,7 @@
         <v>4.4</v>
       </c>
       <c r="I66">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J66">
         <v>4.6</v>
@@ -16923,7 +16923,7 @@
         <v>3.35</v>
       </c>
       <c r="Q66">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R66">
         <v>1.96</v>
@@ -16935,7 +16935,7 @@
         <v>1.47</v>
       </c>
       <c r="U66">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V66">
         <v>1.27</v>
@@ -16944,7 +16944,7 @@
         <v>2.28</v>
       </c>
       <c r="X66">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y66">
         <v>34</v>
@@ -16965,7 +16965,7 @@
         <v>20</v>
       </c>
       <c r="AE66">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AF66">
         <v>17</v>
@@ -16974,10 +16974,10 @@
         <v>11.5</v>
       </c>
       <c r="AH66">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI66">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ66">
         <v>21</v>
@@ -16989,7 +16989,7 @@
         <v>23</v>
       </c>
       <c r="AM66">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AN66">
         <v>5.6</v>
@@ -16998,13 +16998,13 @@
         <v>27</v>
       </c>
       <c r="AP66">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ66">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR66">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS66">
         <v>55</v>
@@ -17013,7 +17013,7 @@
         <v>15.5</v>
       </c>
       <c r="AU66">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV66">
         <v>16.5</v>
@@ -17031,7 +17031,7 @@
         <v>13.5</v>
       </c>
       <c r="BA66">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BB66">
         <v>18.5</v>
@@ -17052,7 +17052,7 @@
         <v>17.5</v>
       </c>
       <c r="BH66">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI66">
         <v>4.8</v>
@@ -17067,7 +17067,7 @@
         <v>1000</v>
       </c>
       <c r="BM66">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN66">
         <v>5.3</v>
@@ -17079,37 +17079,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ66">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR66">
         <v>17.5</v>
       </c>
       <c r="BS66">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT66">
         <v>8.800000000000001</v>
       </c>
       <c r="BU66">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV66">
         <v>29</v>
       </c>
       <c r="BW66">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX66">
         <v>29</v>
       </c>
       <c r="BY66">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ66">
         <v>10.5</v>
       </c>
       <c r="CA66">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB66" t="s">
         <v>264</v>
